--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AC914C-E66D-1048-BC6D-87AF01B02D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6763BE09-8245-9046-A2DC-9ED198AEE670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38980" yWindow="1380" windowWidth="40000" windowHeight="21680" activeTab="1" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="38980" yWindow="1380" windowWidth="40000" windowHeight="21680" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="22">
   <si>
     <t>Branch</t>
   </si>
@@ -103,13 +103,16 @@
   </si>
   <si>
     <t>Run</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -119,6 +122,12 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -145,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -156,6 +165,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71848BA-D8C3-7041-A0EE-B663A4811CD2}">
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
@@ -674,6 +684,48 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
+      <c r="C4" s="6">
+        <v>4.7361520297999897</v>
+      </c>
+      <c r="E4" s="6">
+        <v>21.1806411148</v>
+      </c>
+      <c r="G4" s="6">
+        <v>9.4521483475999908</v>
+      </c>
+      <c r="I4" s="6">
+        <v>6.2249833689000003</v>
+      </c>
+      <c r="K4" s="6">
+        <v>4.7699677447999997</v>
+      </c>
+      <c r="M4" s="6">
+        <v>4.7879055426999999</v>
+      </c>
+      <c r="O4" s="6">
+        <v>4.8561072632000002</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>4.9457645918999997</v>
+      </c>
+      <c r="S4" s="6">
+        <v>4.8490968258999896</v>
+      </c>
+      <c r="U4" s="6">
+        <v>10.3908139883</v>
+      </c>
+      <c r="W4" s="6">
+        <v>4.7319136024999997</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>0.56397134309999997</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>80.952135558099997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="N14" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -698,7 +750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D90E2C0-8C68-E84F-BBAA-6A32D2F1D90D}">
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
@@ -722,21 +774,6 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -754,102 +791,553 @@
       <c r="AB2" s="2"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>4.7340293059999903</v>
+      </c>
+      <c r="D5">
+        <v>21.176729871999999</v>
+      </c>
+      <c r="E5">
+        <v>9.4457361899999892</v>
+      </c>
+      <c r="F5">
+        <v>6.2217804140000004</v>
+      </c>
+      <c r="G5">
+        <v>4.7682641119999998</v>
+      </c>
+      <c r="H5">
+        <v>4.78634752199999</v>
+      </c>
+      <c r="I5">
+        <v>4.8526370550000104</v>
+      </c>
+      <c r="J5">
+        <v>4.9441060699999904</v>
+      </c>
+      <c r="K5">
+        <v>4.8479211129999804</v>
+      </c>
+      <c r="L5">
+        <v>10.389432319999999</v>
+      </c>
+      <c r="M5">
+        <v>4.73018520599999</v>
+      </c>
+      <c r="N5">
+        <v>0.57304119499999995</v>
+      </c>
+      <c r="O5">
+        <v>80.923910221</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4.7393095049999996</v>
+      </c>
+      <c r="D6">
+        <v>21.173363765999898</v>
+      </c>
+      <c r="E6">
+        <v>9.4572644579999796</v>
+      </c>
+      <c r="F6">
+        <v>6.2261814449999999</v>
+      </c>
+      <c r="G6">
+        <v>4.7731040329999903</v>
+      </c>
+      <c r="H6">
+        <v>4.7896122209999898</v>
+      </c>
+      <c r="I6">
+        <v>4.8602087559999996</v>
+      </c>
+      <c r="J6">
+        <v>4.9492782460000004</v>
+      </c>
+      <c r="K6">
+        <v>4.8529851260000001</v>
+      </c>
+      <c r="L6">
+        <v>10.393453508</v>
+      </c>
+      <c r="M6">
+        <v>4.7350227470000004</v>
+      </c>
+      <c r="N6">
+        <v>0.57079999699999995</v>
+      </c>
+      <c r="O6">
+        <v>80.976149698</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4.7078935550000001</v>
+      </c>
+      <c r="D7">
+        <v>21.146499433999999</v>
+      </c>
+      <c r="E7">
+        <v>9.3944941359999898</v>
+      </c>
+      <c r="F7">
+        <v>6.1949537149999996</v>
+      </c>
+      <c r="G7">
+        <v>4.7398854799999999</v>
+      </c>
+      <c r="H7">
+        <v>4.7574510490000002</v>
+      </c>
+      <c r="I7">
+        <v>4.8284425640000102</v>
+      </c>
+      <c r="J7">
+        <v>4.9171688830000102</v>
+      </c>
+      <c r="K7">
+        <v>4.8211042189999898</v>
+      </c>
+      <c r="L7">
+        <v>10.363234916</v>
+      </c>
+      <c r="M7">
+        <v>4.7036561429999999</v>
+      </c>
+      <c r="N7">
+        <v>0.57259144100000003</v>
+      </c>
+      <c r="O7">
+        <v>80.601453527000004</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>4.8357023659999996</v>
+      </c>
+      <c r="D8">
+        <v>21.283297358999999</v>
+      </c>
+      <c r="E8">
+        <v>9.6534851180000008</v>
+      </c>
+      <c r="F8">
+        <v>6.3259116600000098</v>
+      </c>
+      <c r="G8">
+        <v>4.8699703429999897</v>
+      </c>
+      <c r="H8">
+        <v>4.8880030239999899</v>
+      </c>
+      <c r="I8">
+        <v>4.9540698719999998</v>
+      </c>
+      <c r="J8">
+        <v>5.0477363430000004</v>
+      </c>
+      <c r="K8">
+        <v>4.9493739049999999</v>
+      </c>
+      <c r="L8">
+        <v>10.490154618999901</v>
+      </c>
+      <c r="M8">
+        <v>4.8317443500000001</v>
+      </c>
+      <c r="N8">
+        <v>0.56438216600000002</v>
+      </c>
+      <c r="O8">
+        <v>82.156601383999998</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>4.7201029639999899</v>
+      </c>
+      <c r="D9">
+        <v>21.162477132999999</v>
+      </c>
+      <c r="E9">
+        <v>9.4234756789999992</v>
+      </c>
+      <c r="F9">
+        <v>6.2093324299999804</v>
+      </c>
+      <c r="G9">
+        <v>4.7542486399999904</v>
+      </c>
+      <c r="H9">
+        <v>4.7723286930000004</v>
+      </c>
+      <c r="I9">
+        <v>4.8406304889999996</v>
+      </c>
+      <c r="J9">
+        <v>4.92910223999999</v>
+      </c>
+      <c r="K9">
+        <v>4.8331939989999997</v>
+      </c>
+      <c r="L9">
+        <v>10.376906498999899</v>
+      </c>
+      <c r="M9">
+        <v>4.7158174270000002</v>
+      </c>
+      <c r="N9">
+        <v>0.57460502199999997</v>
+      </c>
+      <c r="O9">
+        <v>80.764317835</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>4.7483563999999898</v>
+      </c>
+      <c r="D10">
+        <v>21.204867498999899</v>
+      </c>
+      <c r="E10">
+        <v>9.4793780250000097</v>
+      </c>
+      <c r="F10">
+        <v>6.2381119399999996</v>
+      </c>
+      <c r="G10">
+        <v>4.7830271779999904</v>
+      </c>
+      <c r="H10">
+        <v>4.8021576899999898</v>
+      </c>
+      <c r="I10">
+        <v>4.8694124350000001</v>
+      </c>
+      <c r="J10">
+        <v>4.9590571159999897</v>
+      </c>
+      <c r="K10">
+        <v>4.8623519149999801</v>
+      </c>
+      <c r="L10">
+        <v>10.401261198</v>
+      </c>
+      <c r="M10">
+        <v>4.74394939799999</v>
+      </c>
+      <c r="N10">
+        <v>0.55289784900000005</v>
+      </c>
+      <c r="O10">
+        <v>81.118364749999998</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>4.7037826629999904</v>
+      </c>
+      <c r="D11">
+        <v>21.152131596</v>
+      </c>
+      <c r="E11">
+        <v>9.3876109779999997</v>
+      </c>
+      <c r="F11">
+        <v>6.1921738199999998</v>
+      </c>
+      <c r="G11">
+        <v>4.73704256899999</v>
+      </c>
+      <c r="H11">
+        <v>4.7546049190000099</v>
+      </c>
+      <c r="I11">
+        <v>4.8231421749999903</v>
+      </c>
+      <c r="J11">
+        <v>4.9121940719999904</v>
+      </c>
+      <c r="K11">
+        <v>4.8161531389999999</v>
+      </c>
+      <c r="L11">
+        <v>10.356330882</v>
+      </c>
+      <c r="M11">
+        <v>4.6991199909999901</v>
+      </c>
+      <c r="N11">
+        <v>0.55554261299999996</v>
+      </c>
+      <c r="O11">
+        <v>80.560378224999994</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B12">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>4.6960157959999904</v>
+      </c>
+      <c r="D12">
+        <v>21.135143617000001</v>
+      </c>
+      <c r="E12">
+        <v>9.3704731389999907</v>
+      </c>
+      <c r="F12">
+        <v>6.1849777839999902</v>
+      </c>
+      <c r="G12">
+        <v>4.7298488310000097</v>
+      </c>
+      <c r="H12">
+        <v>4.74821225899999</v>
+      </c>
+      <c r="I12">
+        <v>4.8161023499999898</v>
+      </c>
+      <c r="J12">
+        <v>4.9041083179999996</v>
+      </c>
+      <c r="K12">
+        <v>4.8065764169999996</v>
+      </c>
+      <c r="L12">
+        <v>10.353393854</v>
+      </c>
+      <c r="M12">
+        <v>4.6916778209999901</v>
+      </c>
+      <c r="N12">
+        <v>0.55554574300000004</v>
+      </c>
+      <c r="O12">
+        <v>80.462678502000003</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>4.7152222879999997</v>
+      </c>
+      <c r="D13">
+        <v>21.163150134999899</v>
+      </c>
+      <c r="E13">
+        <v>9.4112512409999898</v>
+      </c>
+      <c r="F13">
+        <v>6.2047871109999999</v>
+      </c>
+      <c r="G13">
+        <v>4.7493141909999999</v>
+      </c>
+      <c r="H13">
+        <v>4.7671523330000003</v>
+      </c>
+      <c r="I13">
+        <v>4.8345936519999997</v>
+      </c>
+      <c r="J13">
+        <v>4.9243923099999902</v>
+      </c>
+      <c r="K13">
+        <v>4.8269851900000003</v>
+      </c>
+      <c r="L13">
+        <v>10.369362314</v>
+      </c>
+      <c r="M13">
+        <v>4.7109683779999898</v>
+      </c>
+      <c r="N13">
+        <v>0.56577272000000001</v>
+      </c>
+      <c r="O13">
+        <v>80.705057595</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B14">
         <v>9</v>
+      </c>
+      <c r="C14">
+        <v>4.7611054549999903</v>
+      </c>
+      <c r="D14">
+        <v>21.208750736999999</v>
+      </c>
+      <c r="E14">
+        <v>9.4983145119999808</v>
+      </c>
+      <c r="F14">
+        <v>6.2516233699999999</v>
+      </c>
+      <c r="G14">
+        <v>4.7949720709999903</v>
+      </c>
+      <c r="H14">
+        <v>4.8131857169999996</v>
+      </c>
+      <c r="I14">
+        <v>4.8818332839999803</v>
+      </c>
+      <c r="J14">
+        <v>4.9705023209999997</v>
+      </c>
+      <c r="K14">
+        <v>4.8743232359999897</v>
+      </c>
+      <c r="L14">
+        <v>10.414609773</v>
+      </c>
+      <c r="M14">
+        <v>4.7569945640000002</v>
+      </c>
+      <c r="N14">
+        <v>0.55453468500000003</v>
+      </c>
+      <c r="O14">
+        <v>81.252443843999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4.7361520297999897</v>
+      </c>
+      <c r="D15" s="3">
+        <v>21.1806411148</v>
+      </c>
+      <c r="E15" s="3">
+        <v>9.4521483475999908</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6.2249833689000003</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4.7699677447999997</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4.7879055426999999</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4.8561072632000002</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4.9457645918999997</v>
+      </c>
+      <c r="K15" s="3">
+        <v>4.8490968258999896</v>
+      </c>
+      <c r="L15" s="3">
+        <v>10.3908139883</v>
+      </c>
+      <c r="M15" s="3">
+        <v>4.7319136024999997</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.56397134309999997</v>
+      </c>
+      <c r="O15" s="3">
+        <v>80.952135558099997</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:O1"/>
+    <mergeCell ref="C3:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6763BE09-8245-9046-A2DC-9ED198AEE670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F6BD87-1522-1041-BDA5-C1C1F92C82C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38980" yWindow="1380" windowWidth="40000" windowHeight="21680" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="38240" yWindow="1520" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
     <sheet name="Trackslot_Xorwow" sheetId="2" r:id="rId2"/>
+    <sheet name="Trackslot_Ranluxpp" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="24">
   <si>
     <t>Branch</t>
   </si>
@@ -106,6 +107,12 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average </t>
+  </si>
+  <si>
+    <t>Rel Diff (%)</t>
   </si>
 </sst>
 </file>
@@ -154,24 +161,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF3500"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -500,14 +512,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71848BA-D8C3-7041-A0EE-B663A4811CD2}">
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AO14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
@@ -536,68 +549,94 @@
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1" t="s">
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1" t="s">
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1" t="s">
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1" t="s">
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1" t="s">
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="1"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
         <v>18</v>
       </c>
@@ -605,16 +644,16 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
@@ -623,16 +662,16 @@
         <v>19</v>
       </c>
       <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>19</v>
       </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O3" t="s">
         <v>18</v>
@@ -641,16 +680,16 @@
         <v>19</v>
       </c>
       <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
         <v>18</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>19</v>
       </c>
-      <c r="S3" t="s">
-        <v>18</v>
-      </c>
       <c r="T3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="U3" t="s">
         <v>18</v>
@@ -659,16 +698,16 @@
         <v>19</v>
       </c>
       <c r="W3" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" t="s">
         <v>18</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" t="s">
-        <v>18</v>
-      </c>
       <c r="Z3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="s">
         <v>18</v>
@@ -676,81 +715,341 @@
       <c r="AB3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="2">
         <v>4.7361520297999897</v>
       </c>
-      <c r="E4" s="6">
+      <c r="D4" s="2">
+        <v>2.1667207299999901E-2</v>
+      </c>
+      <c r="E4">
+        <f>((C4-D4)/C4)*100</f>
+        <v>99.542514531550736</v>
+      </c>
+      <c r="F4" s="2">
         <v>21.1806411148</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="2">
+        <v>7.7907680781999904</v>
+      </c>
+      <c r="H4">
+        <f>((F4-G4)/F4)*100</f>
+        <v>63.217505853700615</v>
+      </c>
+      <c r="I4" s="2">
         <v>9.4521483475999908</v>
       </c>
-      <c r="I4" s="6">
+      <c r="J4" s="2">
+        <v>9.8861430799999997E-2</v>
+      </c>
+      <c r="K4">
+        <f>((I4-J4)/I4)*100</f>
+        <v>98.954085069717493</v>
+      </c>
+      <c r="L4" s="2">
         <v>6.2249833689000003</v>
       </c>
-      <c r="K4" s="6">
+      <c r="M4" s="2">
+        <v>1.51414486739999</v>
+      </c>
+      <c r="N4">
+        <f>((L4-M4)/L4)*100</f>
+        <v>75.67632268762911</v>
+      </c>
+      <c r="O4" s="2">
         <v>4.7699677447999997</v>
       </c>
-      <c r="M4" s="6">
+      <c r="P4" s="2">
+        <v>5.6586210900000003E-2</v>
+      </c>
+      <c r="Q4">
+        <f>((O4-P4)/O4)*100</f>
+        <v>98.813698248553408</v>
+      </c>
+      <c r="R4" s="2">
         <v>4.7879055426999999</v>
       </c>
-      <c r="O4" s="6">
+      <c r="S4" s="2">
+        <v>0.45787295140000001</v>
+      </c>
+      <c r="T4">
+        <f>((R4-S4)/R4)*100</f>
+        <v>90.436884200898504</v>
+      </c>
+      <c r="U4" s="2">
         <v>4.8561072632000002</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="V4" s="2">
+        <v>6.06435311949999</v>
+      </c>
+      <c r="W4">
+        <f>((U4-V4)/U4)*100</f>
+        <v>-24.880954863912937</v>
+      </c>
+      <c r="X4" s="2">
         <v>4.9457645918999997</v>
       </c>
-      <c r="S4" s="6">
+      <c r="Y4" s="2">
+        <v>0.27247939299999901</v>
+      </c>
+      <c r="Z4">
+        <f>((X4-Y4)/X4)*100</f>
+        <v>94.490651790296354</v>
+      </c>
+      <c r="AA4" s="2">
         <v>4.8490968258999896</v>
       </c>
-      <c r="U4" s="6">
+      <c r="AB4" s="2">
+        <v>0.49238697640000001</v>
+      </c>
+      <c r="AC4">
+        <f>((AA4-AB4)/AA4)*100</f>
+        <v>89.845800278310321</v>
+      </c>
+      <c r="AD4" s="2">
         <v>10.3908139883</v>
       </c>
-      <c r="W4" s="6">
+      <c r="AE4" s="2">
+        <v>3.9042500502999902</v>
+      </c>
+      <c r="AF4">
+        <f>((AD4-AE4)/AD4)*100</f>
+        <v>62.425946083760579</v>
+      </c>
+      <c r="AG4" s="2">
         <v>4.7319136024999997</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="AH4" s="2">
+        <v>2.0140641300000001E-2</v>
+      </c>
+      <c r="AI4">
+        <f>((AG4-AH4)/AG4)*100</f>
+        <v>99.574365827614457</v>
+      </c>
+      <c r="AJ4" s="2">
         <v>0.56397134309999997</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AK4" s="2">
+        <v>0.56001018679999903</v>
+      </c>
+      <c r="AL4">
+        <f>((AJ4-AK4)/AJ4)*100</f>
+        <v>0.70236836471646147</v>
+      </c>
+      <c r="AM4" s="2">
         <v>80.952135558099997</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="N14" s="6"/>
+      <c r="AN4" s="2">
+        <v>20.710805148799999</v>
+      </c>
+      <c r="AO4">
+        <f>((AM4-AN4)/AM4)*100</f>
+        <v>74.415986674081395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="T14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="C1:AB1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="C1:AO1"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
   </mergeCells>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W4">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC4">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI4">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL4">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D90E2C0-8C68-E84F-BBAA-6A32D2F1D90D}">
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
@@ -767,30 +1066,23 @@
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AB2" s="2"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
@@ -807,51 +1099,51 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>0</v>
       </c>
@@ -895,7 +1187,7 @@
         <v>80.923910221</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1</v>
       </c>
@@ -939,7 +1231,7 @@
         <v>80.976149698</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2</v>
       </c>
@@ -983,7 +1275,7 @@
         <v>80.601453527000004</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1027,7 +1319,7 @@
         <v>82.156601383999998</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1071,7 +1363,7 @@
         <v>80.764317835</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>5</v>
       </c>
@@ -1115,7 +1407,7 @@
         <v>81.118364749999998</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>6</v>
       </c>
@@ -1159,7 +1451,7 @@
         <v>80.560378224999994</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>7</v>
       </c>
@@ -1203,7 +1495,7 @@
         <v>80.462678502000003</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>8</v>
       </c>
@@ -1247,7 +1539,7 @@
         <v>80.705057595</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>9</v>
       </c>
@@ -1291,48 +1583,622 @@
         <v>81.252443843999998</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>4.7361520297999897</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="1">
         <v>21.1806411148</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
         <v>9.4521483475999908</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="1">
         <v>6.2249833689000003</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="1">
         <v>4.7699677447999997</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="1">
         <v>4.7879055426999999</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="1">
         <v>4.8561072632000002</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="1">
         <v>4.9457645918999997</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="1">
         <v>4.8490968258999896</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="1">
         <v>10.3908139883</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="1">
         <v>4.7319136024999997</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="1">
         <v>0.56397134309999997</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="1">
         <v>80.952135558099997</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B17374F-425A-0C4A-B316-973C7C980C22}">
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>2.1720421999999899E-2</v>
+      </c>
+      <c r="D5">
+        <v>7.7920159560000002</v>
+      </c>
+      <c r="E5">
+        <v>9.8926041000000201E-2</v>
+      </c>
+      <c r="F5">
+        <v>1.514987834</v>
+      </c>
+      <c r="G5">
+        <v>5.6670711999999998E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.45792223899999901</v>
+      </c>
+      <c r="I5">
+        <v>6.0629683709999904</v>
+      </c>
+      <c r="J5">
+        <v>0.27254366399999902</v>
+      </c>
+      <c r="K5">
+        <v>0.492584572</v>
+      </c>
+      <c r="L5">
+        <v>3.9054659680000001</v>
+      </c>
+      <c r="M5">
+        <v>2.0203208E-2</v>
+      </c>
+      <c r="N5">
+        <v>0.64593537300000003</v>
+      </c>
+      <c r="O5">
+        <v>20.713234384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2.1932872999999901E-2</v>
+      </c>
+      <c r="D6">
+        <v>7.7932568639999804</v>
+      </c>
+      <c r="E6">
+        <v>0.100150211999999</v>
+      </c>
+      <c r="F6">
+        <v>1.5148518119999901</v>
+      </c>
+      <c r="G6">
+        <v>5.6832657999999897E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.45801357599999998</v>
+      </c>
+      <c r="I6">
+        <v>6.0620578969999999</v>
+      </c>
+      <c r="J6">
+        <v>0.27391537499999902</v>
+      </c>
+      <c r="K6">
+        <v>0.49292541600000001</v>
+      </c>
+      <c r="L6">
+        <v>3.8996984129999999</v>
+      </c>
+      <c r="M6">
+        <v>2.0393437E-2</v>
+      </c>
+      <c r="N6">
+        <v>0.550244972</v>
+      </c>
+      <c r="O6">
+        <v>20.712029911999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2.1673924000000001E-2</v>
+      </c>
+      <c r="D7">
+        <v>7.78517397500001</v>
+      </c>
+      <c r="E7">
+        <v>9.8263606000000295E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.5145982249999901</v>
+      </c>
+      <c r="G7">
+        <v>5.6453717E-2</v>
+      </c>
+      <c r="H7">
+        <v>0.45786797299999998</v>
+      </c>
+      <c r="I7">
+        <v>6.06432882399998</v>
+      </c>
+      <c r="J7">
+        <v>0.272134289999999</v>
+      </c>
+      <c r="K7">
+        <v>0.49234655300000002</v>
+      </c>
+      <c r="L7">
+        <v>3.9066906959999899</v>
+      </c>
+      <c r="M7">
+        <v>2.0032529E-2</v>
+      </c>
+      <c r="N7">
+        <v>0.57788008999999996</v>
+      </c>
+      <c r="O7">
+        <v>20.706679097999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>2.1524842999999998E-2</v>
+      </c>
+      <c r="D8">
+        <v>7.7903554359999898</v>
+      </c>
+      <c r="E8">
+        <v>9.8635195999999897E-2</v>
+      </c>
+      <c r="F8">
+        <v>1.51497759599999</v>
+      </c>
+      <c r="G8">
+        <v>5.6425546999999902E-2</v>
+      </c>
+      <c r="H8">
+        <v>0.45780708199999898</v>
+      </c>
+      <c r="I8">
+        <v>6.06703356199999</v>
+      </c>
+      <c r="J8">
+        <v>0.27221806099999901</v>
+      </c>
+      <c r="K8">
+        <v>0.49258481599999798</v>
+      </c>
+      <c r="L8">
+        <v>3.90604397499999</v>
+      </c>
+      <c r="M8">
+        <v>2.0019353999999899E-2</v>
+      </c>
+      <c r="N8">
+        <v>0.54926370899999999</v>
+      </c>
+      <c r="O8">
+        <v>20.714700707999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2.1505045999999899E-2</v>
+      </c>
+      <c r="D9">
+        <v>7.79237521900001</v>
+      </c>
+      <c r="E9">
+        <v>9.8110879999999998E-2</v>
+      </c>
+      <c r="F9">
+        <v>1.514759403</v>
+      </c>
+      <c r="G9">
+        <v>5.6454982000000001E-2</v>
+      </c>
+      <c r="H9">
+        <v>0.45782401499999897</v>
+      </c>
+      <c r="I9">
+        <v>6.0658227059999996</v>
+      </c>
+      <c r="J9">
+        <v>0.27235633199999898</v>
+      </c>
+      <c r="K9">
+        <v>0.492267179</v>
+      </c>
+      <c r="L9">
+        <v>3.9025007180000002</v>
+      </c>
+      <c r="M9">
+        <v>2.0040321E-2</v>
+      </c>
+      <c r="N9">
+        <v>0.54740489599999997</v>
+      </c>
+      <c r="O9">
+        <v>20.711233804999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>2.1446732999999999E-2</v>
+      </c>
+      <c r="D10">
+        <v>7.79217742799998</v>
+      </c>
+      <c r="E10">
+        <v>9.8305396999999906E-2</v>
+      </c>
+      <c r="F10">
+        <v>1.51437720799999</v>
+      </c>
+      <c r="G10">
+        <v>5.6399120000000101E-2</v>
+      </c>
+      <c r="H10">
+        <v>0.45764157999999899</v>
+      </c>
+      <c r="I10">
+        <v>6.0663063140000002</v>
+      </c>
+      <c r="J10">
+        <v>0.27173915100000001</v>
+      </c>
+      <c r="K10">
+        <v>0.49202296899999898</v>
+      </c>
+      <c r="L10">
+        <v>3.9073114050000002</v>
+      </c>
+      <c r="M10">
+        <v>1.9971797999999999E-2</v>
+      </c>
+      <c r="N10">
+        <v>0.54614090900000001</v>
+      </c>
+      <c r="O10">
+        <v>20.714789747000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>2.1616896999999899E-2</v>
+      </c>
+      <c r="D11">
+        <v>7.7921428089999898</v>
+      </c>
+      <c r="E11">
+        <v>9.9132750000000006E-2</v>
+      </c>
+      <c r="F11">
+        <v>1.5150120439999899</v>
+      </c>
+      <c r="G11">
+        <v>5.6688913E-2</v>
+      </c>
+      <c r="H11">
+        <v>0.45803382599999998</v>
+      </c>
+      <c r="I11">
+        <v>6.0665790959999804</v>
+      </c>
+      <c r="J11">
+        <v>0.27280712099999999</v>
+      </c>
+      <c r="K11">
+        <v>0.49276028799999899</v>
+      </c>
+      <c r="L11">
+        <v>3.9066536109999901</v>
+      </c>
+      <c r="M11">
+        <v>2.0168087000000001E-2</v>
+      </c>
+      <c r="N11">
+        <v>0.54705949499999995</v>
+      </c>
+      <c r="O11">
+        <v>20.718696206000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>2.1699502999999998E-2</v>
+      </c>
+      <c r="D12">
+        <v>7.7960570239999702</v>
+      </c>
+      <c r="E12">
+        <v>9.8950826000000006E-2</v>
+      </c>
+      <c r="F12">
+        <v>1.5138778100000001</v>
+      </c>
+      <c r="G12">
+        <v>5.6606003000000002E-2</v>
+      </c>
+      <c r="H12">
+        <v>0.45791276199999997</v>
+      </c>
+      <c r="I12">
+        <v>6.0653505989999896</v>
+      </c>
+      <c r="J12">
+        <v>0.27221119799999999</v>
+      </c>
+      <c r="K12">
+        <v>0.49230500999999999</v>
+      </c>
+      <c r="L12">
+        <v>3.9038788939999902</v>
+      </c>
+      <c r="M12">
+        <v>2.0186594999999901E-2</v>
+      </c>
+      <c r="N12">
+        <v>0.54342701900000001</v>
+      </c>
+      <c r="O12">
+        <v>20.716681764</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>2.17129459999999E-2</v>
+      </c>
+      <c r="D13">
+        <v>7.78897069599999</v>
+      </c>
+      <c r="E13">
+        <v>9.8518339000000094E-2</v>
+      </c>
+      <c r="F13">
+        <v>1.51190811199999</v>
+      </c>
+      <c r="G13">
+        <v>5.6603623999999998E-2</v>
+      </c>
+      <c r="H13">
+        <v>0.45760492600000002</v>
+      </c>
+      <c r="I13">
+        <v>6.0605655199999902</v>
+      </c>
+      <c r="J13">
+        <v>0.27217079099999902</v>
+      </c>
+      <c r="K13">
+        <v>0.49201673399999901</v>
+      </c>
+      <c r="L13">
+        <v>3.8966925989999899</v>
+      </c>
+      <c r="M13">
+        <v>2.0140801E-2</v>
+      </c>
+      <c r="N13">
+        <v>0.54602609599999996</v>
+      </c>
+      <c r="O13">
+        <v>20.694066958000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>2.1838885999999901E-2</v>
+      </c>
+      <c r="D14">
+        <v>7.7851553749999898</v>
+      </c>
+      <c r="E14">
+        <v>9.9621060999999997E-2</v>
+      </c>
+      <c r="F14">
+        <v>1.5120986300000001</v>
+      </c>
+      <c r="G14">
+        <v>5.6726833000000101E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.458101534999999</v>
+      </c>
+      <c r="I14">
+        <v>6.0625183060000003</v>
+      </c>
+      <c r="J14">
+        <v>0.272697946999999</v>
+      </c>
+      <c r="K14">
+        <v>0.49205622700000001</v>
+      </c>
+      <c r="L14">
+        <v>3.9075642240000001</v>
+      </c>
+      <c r="M14">
+        <v>2.0250283000000001E-2</v>
+      </c>
+      <c r="N14">
+        <v>0.54671930899999999</v>
+      </c>
+      <c r="O14">
+        <v>20.705938906</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.1667207299999901E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7.7907680781999904</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9.8861430799999997E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.51414486739999</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5.6586210900000003E-2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.45787295140000001</v>
+      </c>
+      <c r="I15" s="1">
+        <v>6.06435311949999</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.27247939299999901</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.49238697640000001</v>
+      </c>
+      <c r="L15" s="1">
+        <v>3.9042500502999902</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2.0140641300000001E-2</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0.56001018679999903</v>
+      </c>
+      <c r="O15" s="1">
+        <v>20.710805148799999</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F6BD87-1522-1041-BDA5-C1C1F92C82C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA1CDE0-9160-0642-80B2-BA4607FE6B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38240" yWindow="1520" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="43100" yWindow="1360" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
     <sheet name="Trackslot_Xorwow" sheetId="2" r:id="rId2"/>
     <sheet name="Trackslot_Ranluxpp" sheetId="3" r:id="rId3"/>
+    <sheet name="Track_Xorwow" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="26">
   <si>
     <t>Branch</t>
   </si>
@@ -113,6 +114,12 @@
   </si>
   <si>
     <t>Rel Diff (%)</t>
+  </si>
+  <si>
+    <t>Trackslot reseeding</t>
+  </si>
+  <si>
+    <t>Track reseeding</t>
   </si>
 </sst>
 </file>
@@ -521,6 +528,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
@@ -564,11 +577,11 @@
       <c r="AO1" s="4"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -756,11 +769,8 @@
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2">
         <v>4.7361520297999897</v>
@@ -893,7 +903,54 @@
         <v>74.415986674081395</v>
       </c>
     </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.0490970599999998E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>7.7896655604999996</v>
+      </c>
+      <c r="I5" s="1">
+        <v>9.1392076700000005E-2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1.50496271489999</v>
+      </c>
+      <c r="O5" s="1">
+        <v>5.7508319799999902E-2</v>
+      </c>
+      <c r="R5" s="1">
+        <v>8.0266894699999994E-2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.14648018700000001</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.22424833150000001</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.1457526992</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>1.5127066299</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>1.93910095E-2</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.57490099240000003</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>11.6087681536</v>
+      </c>
+    </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="T14" s="2"/>
     </row>
   </sheetData>
@@ -2207,4 +2264,578 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE3BDD0-3A87-544A-A16E-D142A4C1F8FB}">
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>2.0424912999999999E-2</v>
+      </c>
+      <c r="D5">
+        <v>7.7867697349999903</v>
+      </c>
+      <c r="E5">
+        <v>9.1322597999999894E-2</v>
+      </c>
+      <c r="F5">
+        <v>1.5043494099999899</v>
+      </c>
+      <c r="G5">
+        <v>5.7297887999999901E-2</v>
+      </c>
+      <c r="H5">
+        <v>8.0126062999999803E-2</v>
+      </c>
+      <c r="I5">
+        <v>0.14635807000000001</v>
+      </c>
+      <c r="J5">
+        <v>0.22410363699999999</v>
+      </c>
+      <c r="K5">
+        <v>0.145887511</v>
+      </c>
+      <c r="L5">
+        <v>1.5135437140000001</v>
+      </c>
+      <c r="M5">
+        <v>1.9270493999999899E-2</v>
+      </c>
+      <c r="N5">
+        <v>0.63718657899999998</v>
+      </c>
+      <c r="O5">
+        <v>11.605081670000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2.1145951E-2</v>
+      </c>
+      <c r="D6">
+        <v>7.7860681689999902</v>
+      </c>
+      <c r="E6">
+        <v>9.1019702999999993E-2</v>
+      </c>
+      <c r="F6">
+        <v>1.504760248</v>
+      </c>
+      <c r="G6">
+        <v>5.8056615999999998E-2</v>
+      </c>
+      <c r="H6">
+        <v>7.9142330999999899E-2</v>
+      </c>
+      <c r="I6">
+        <v>0.14721379100000001</v>
+      </c>
+      <c r="J6">
+        <v>0.22464350599999999</v>
+      </c>
+      <c r="K6">
+        <v>0.14654013999999899</v>
+      </c>
+      <c r="L6">
+        <v>1.5158264749999999</v>
+      </c>
+      <c r="M6">
+        <v>2.0120513999999999E-2</v>
+      </c>
+      <c r="N6">
+        <v>0.58061084600000001</v>
+      </c>
+      <c r="O6">
+        <v>11.611603560000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2.0321663E-2</v>
+      </c>
+      <c r="D7">
+        <v>7.7858370370000003</v>
+      </c>
+      <c r="E7">
+        <v>9.1435814000000198E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.50463510299999</v>
+      </c>
+      <c r="G7">
+        <v>5.7139267999999903E-2</v>
+      </c>
+      <c r="H7">
+        <v>8.0468895999999998E-2</v>
+      </c>
+      <c r="I7">
+        <v>0.146477828</v>
+      </c>
+      <c r="J7">
+        <v>0.22378975800000001</v>
+      </c>
+      <c r="K7">
+        <v>0.14580547599999999</v>
+      </c>
+      <c r="L7">
+        <v>1.5118537869999999</v>
+      </c>
+      <c r="M7">
+        <v>1.9273346999999899E-2</v>
+      </c>
+      <c r="N7">
+        <v>0.56270112800000005</v>
+      </c>
+      <c r="O7">
+        <v>11.603158564999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>2.0864639000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>7.791942186</v>
+      </c>
+      <c r="E8">
+        <v>9.3432404999999899E-2</v>
+      </c>
+      <c r="F8">
+        <v>1.5056955270000001</v>
+      </c>
+      <c r="G8">
+        <v>5.7837718999999899E-2</v>
+      </c>
+      <c r="H8">
+        <v>8.0883411999999794E-2</v>
+      </c>
+      <c r="I8">
+        <v>0.14729577499999999</v>
+      </c>
+      <c r="J8">
+        <v>0.22659679099999999</v>
+      </c>
+      <c r="K8">
+        <v>0.14671094299999901</v>
+      </c>
+      <c r="L8">
+        <v>1.5164940629999999</v>
+      </c>
+      <c r="M8">
+        <v>1.9708712999999999E-2</v>
+      </c>
+      <c r="N8">
+        <v>0.56443909199999998</v>
+      </c>
+      <c r="O8">
+        <v>11.62344429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2.0280942999999899E-2</v>
+      </c>
+      <c r="D9">
+        <v>7.7999430569999904</v>
+      </c>
+      <c r="E9">
+        <v>9.0877374999999802E-2</v>
+      </c>
+      <c r="F9">
+        <v>1.50655010599999</v>
+      </c>
+      <c r="G9">
+        <v>5.7248313999999897E-2</v>
+      </c>
+      <c r="H9">
+        <v>8.0485838000000101E-2</v>
+      </c>
+      <c r="I9">
+        <v>0.14656117699999999</v>
+      </c>
+      <c r="J9">
+        <v>0.22409077799999999</v>
+      </c>
+      <c r="K9">
+        <v>0.14573356700000001</v>
+      </c>
+      <c r="L9">
+        <v>1.51249728199999</v>
+      </c>
+      <c r="M9">
+        <v>1.9202230000000001E-2</v>
+      </c>
+      <c r="N9">
+        <v>0.562185775</v>
+      </c>
+      <c r="O9">
+        <v>11.619479439999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>2.043876E-2</v>
+      </c>
+      <c r="D10">
+        <v>7.7974293039999996</v>
+      </c>
+      <c r="E10">
+        <v>9.1080436999999903E-2</v>
+      </c>
+      <c r="F10">
+        <v>1.5064454389999899</v>
+      </c>
+      <c r="G10">
+        <v>5.7185278999999797E-2</v>
+      </c>
+      <c r="H10">
+        <v>8.0402278999999993E-2</v>
+      </c>
+      <c r="I10">
+        <v>0.14645081199999899</v>
+      </c>
+      <c r="J10">
+        <v>0.22453524499999999</v>
+      </c>
+      <c r="K10">
+        <v>0.145886615999999</v>
+      </c>
+      <c r="L10">
+        <v>1.511602659</v>
+      </c>
+      <c r="M10">
+        <v>1.9318756999999999E-2</v>
+      </c>
+      <c r="N10">
+        <v>0.57984765400000005</v>
+      </c>
+      <c r="O10">
+        <v>11.616513956</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>2.0353184E-2</v>
+      </c>
+      <c r="D11">
+        <v>7.7924300309999897</v>
+      </c>
+      <c r="E11">
+        <v>9.0809097000000102E-2</v>
+      </c>
+      <c r="F11">
+        <v>1.5053146959999999</v>
+      </c>
+      <c r="G11">
+        <v>5.7189707999999902E-2</v>
+      </c>
+      <c r="H11">
+        <v>8.0279349E-2</v>
+      </c>
+      <c r="I11">
+        <v>0.146382653999999</v>
+      </c>
+      <c r="J11">
+        <v>0.22355650699999999</v>
+      </c>
+      <c r="K11">
+        <v>0.14538958199999999</v>
+      </c>
+      <c r="L11">
+        <v>1.513626312</v>
+      </c>
+      <c r="M11">
+        <v>1.9171847999999901E-2</v>
+      </c>
+      <c r="N11">
+        <v>0.560336846</v>
+      </c>
+      <c r="O11">
+        <v>11.610014887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>2.0289628999999899E-2</v>
+      </c>
+      <c r="D12">
+        <v>7.7860702429999904</v>
+      </c>
+      <c r="E12">
+        <v>9.1088189E-2</v>
+      </c>
+      <c r="F12">
+        <v>1.5032416559999899</v>
+      </c>
+      <c r="G12">
+        <v>5.7050234999999901E-2</v>
+      </c>
+      <c r="H12">
+        <v>8.02704679999999E-2</v>
+      </c>
+      <c r="I12">
+        <v>0.14590045199999899</v>
+      </c>
+      <c r="J12">
+        <v>0.223113902999999</v>
+      </c>
+      <c r="K12">
+        <v>0.14498377500000001</v>
+      </c>
+      <c r="L12">
+        <v>1.51002137499999</v>
+      </c>
+      <c r="M12">
+        <v>1.9153499000000001E-2</v>
+      </c>
+      <c r="N12">
+        <v>0.56179270699999995</v>
+      </c>
+      <c r="O12">
+        <v>11.596820626</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>2.03218539999999E-2</v>
+      </c>
+      <c r="D13">
+        <v>7.7836237120000096</v>
+      </c>
+      <c r="E13">
+        <v>9.1111495999999903E-2</v>
+      </c>
+      <c r="F13">
+        <v>1.5051262249999999</v>
+      </c>
+      <c r="G13">
+        <v>5.7253967999999898E-2</v>
+      </c>
+      <c r="H13">
+        <v>8.0286094000000099E-2</v>
+      </c>
+      <c r="I13">
+        <v>0.145972402</v>
+      </c>
+      <c r="J13">
+        <v>0.22355931900000001</v>
+      </c>
+      <c r="K13">
+        <v>0.145110973999999</v>
+      </c>
+      <c r="L13">
+        <v>1.511406241</v>
+      </c>
+      <c r="M13">
+        <v>1.9221361999999999E-2</v>
+      </c>
+      <c r="N13">
+        <v>0.58119497399999998</v>
+      </c>
+      <c r="O13">
+        <v>11.598596659</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>2.04681699999999E-2</v>
+      </c>
+      <c r="D14">
+        <v>7.786542131</v>
+      </c>
+      <c r="E14">
+        <v>9.1743652999999897E-2</v>
+      </c>
+      <c r="F14">
+        <v>1.5035087389999899</v>
+      </c>
+      <c r="G14">
+        <v>5.8824202999999797E-2</v>
+      </c>
+      <c r="H14">
+        <v>8.0324217000000003E-2</v>
+      </c>
+      <c r="I14">
+        <v>0.14618890900000001</v>
+      </c>
+      <c r="J14">
+        <v>0.22449387100000001</v>
+      </c>
+      <c r="K14">
+        <v>0.145478408</v>
+      </c>
+      <c r="L14">
+        <v>1.510194391</v>
+      </c>
+      <c r="M14">
+        <v>1.9469330999999999E-2</v>
+      </c>
+      <c r="N14">
+        <v>0.55871432300000001</v>
+      </c>
+      <c r="O14">
+        <v>11.602967883</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0490970599999998E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7.7896655604999996</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9.1392076700000005E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.50496271489999</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5.7508319799999902E-2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8.0266894699999994E-2</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.14648018700000001</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.22424833150000001</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.1457526992</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1.5127066299</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1.93910095E-2</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0.57490099240000003</v>
+      </c>
+      <c r="O15" s="1">
+        <v>11.6087681536</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA1CDE0-9160-0642-80B2-BA4607FE6B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05EABA7-3707-E845-95BC-AFF0085B4065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43100" yWindow="1360" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="33400" yWindow="660" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
     <sheet name="Trackslot_Xorwow" sheetId="2" r:id="rId2"/>
     <sheet name="Trackslot_Ranluxpp" sheetId="3" r:id="rId3"/>
     <sheet name="Track_Xorwow" sheetId="4" r:id="rId4"/>
+    <sheet name="Track_Ranluxpp" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="26">
   <si>
     <t>Branch</t>
   </si>
@@ -907,50 +908,253 @@
       <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>2.0490970599999998E-2</v>
       </c>
-      <c r="F5" s="1">
+      <c r="D5" s="2">
+        <v>2.16922599E-2</v>
+      </c>
+      <c r="E5">
+        <f>((C5-D5)/C5)*100</f>
+        <v>-5.8625300062653052</v>
+      </c>
+      <c r="F5" s="2">
         <v>7.7896655604999996</v>
       </c>
-      <c r="I5" s="1">
+      <c r="G5" s="2">
+        <v>7.7896106538999899</v>
+      </c>
+      <c r="H5" s="2">
+        <f>((F5-G5)/F5)*100</f>
+        <v>7.0486466438496851E-4</v>
+      </c>
+      <c r="I5" s="2">
         <v>9.1392076700000005E-2</v>
       </c>
-      <c r="L5" s="1">
+      <c r="J5" s="2">
+        <v>9.8359574300000002E-2</v>
+      </c>
+      <c r="K5">
+        <f>((I5-J5)/I5)*100</f>
+        <v>-7.6237436018345743</v>
+      </c>
+      <c r="L5" s="2">
         <v>1.50496271489999</v>
       </c>
-      <c r="O5" s="1">
+      <c r="M5" s="2">
+        <v>1.51386815239999</v>
+      </c>
+      <c r="N5">
+        <f>((L5-M5)/L5)*100</f>
+        <v>-0.59173808173657938</v>
+      </c>
+      <c r="O5" s="2">
         <v>5.7508319799999902E-2</v>
       </c>
-      <c r="R5" s="1">
+      <c r="P5" s="2">
+        <v>5.6594890299999999E-2</v>
+      </c>
+      <c r="Q5">
+        <f>((O5-P5)/O5)*100</f>
+        <v>1.5883432226442902</v>
+      </c>
+      <c r="R5" s="2">
         <v>8.0266894699999994E-2</v>
       </c>
-      <c r="U5" s="1">
+      <c r="S5" s="2">
+        <v>0.45789087749999902</v>
+      </c>
+      <c r="T5">
+        <f>((R5-S5)/R5)*100</f>
+        <v>-470.46043603827002</v>
+      </c>
+      <c r="U5" s="2">
         <v>0.14648018700000001</v>
       </c>
-      <c r="X5" s="1">
+      <c r="V5" s="2">
+        <v>6.0640335470000002</v>
+      </c>
+      <c r="W5">
+        <f>((U5-V5)/U5)*100</f>
+        <v>-4039.83192621129</v>
+      </c>
+      <c r="X5" s="2">
         <v>0.22424833150000001</v>
       </c>
-      <c r="AA5" s="1">
+      <c r="Y5" s="2">
+        <v>0.27265967940000002</v>
+      </c>
+      <c r="Z5">
+        <f>((X5-Y5)/X5)*100</f>
+        <v>-21.588275630046329</v>
+      </c>
+      <c r="AA5" s="2">
         <v>0.1457526992</v>
       </c>
-      <c r="AD5" s="1">
+      <c r="AB5" s="2">
+        <v>0.49234086289999901</v>
+      </c>
+      <c r="AC5">
+        <f>((AA5-AB5)/AA5)*100</f>
+        <v>-237.79193497090242</v>
+      </c>
+      <c r="AD5" s="2">
         <v>1.5127066299</v>
       </c>
-      <c r="AG5" s="1">
+      <c r="AE5" s="2">
+        <v>3.9051250898999901</v>
+      </c>
+      <c r="AF5">
+        <f>((AD5-AE5)/AD5)*100</f>
+        <v>-158.154820816654</v>
+      </c>
+      <c r="AG5" s="2">
         <v>1.93910095E-2</v>
       </c>
-      <c r="AJ5" s="1">
+      <c r="AH5" s="2">
+        <v>2.0148734299999999E-2</v>
+      </c>
+      <c r="AI5">
+        <f>((AG5-AH5)/AG5)*100</f>
+        <v>-3.9076088328459537</v>
+      </c>
+      <c r="AJ5" s="2">
         <v>0.57490099240000003</v>
       </c>
-      <c r="AM5" s="1">
+      <c r="AK5" s="2">
+        <v>0.55649489640000005</v>
+      </c>
+      <c r="AL5">
+        <f>((AJ5-AK5)/AJ5)*100</f>
+        <v>3.2016114502014177</v>
+      </c>
+      <c r="AM5" s="2">
         <v>11.6087681536</v>
       </c>
+      <c r="AN5" s="2">
+        <v>20.709697601799999</v>
+      </c>
+      <c r="AO5">
+        <f>((AM5-AN5)/AM5)*100</f>
+        <v>-78.397029967195152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <f>((C4-C5)/C4)*100</f>
+        <v>99.567349813285759</v>
+      </c>
+      <c r="D6">
+        <f>((D4-D5)/D4)*100</f>
+        <v>-0.1156244995177548</v>
+      </c>
+      <c r="F6">
+        <f>((F4-F5)/F4)*100</f>
+        <v>63.222711162142488</v>
+      </c>
+      <c r="G6">
+        <f>((G4-G5)/G4)*100</f>
+        <v>1.4856356759473173E-2</v>
+      </c>
+      <c r="I6">
+        <f>((I4-I5)/I4)*100</f>
+        <v>99.033107888925528</v>
+      </c>
+      <c r="J6">
+        <f>((J4-J5)/J4)*100</f>
+        <v>0.50763629045109337</v>
+      </c>
+      <c r="L6">
+        <f>((L4-L5)/L4)*100</f>
+        <v>75.823827539543657</v>
+      </c>
+      <c r="M6">
+        <f>((M4-M5)/M4)*100</f>
+        <v>1.8275331902369348E-2</v>
+      </c>
+      <c r="O6">
+        <f>((O4-O5)/O4)*100</f>
+        <v>98.794366694351481</v>
+      </c>
+      <c r="P6">
+        <f>((P4-P5)/P4)*100</f>
+        <v>-1.53383657642925E-2</v>
+      </c>
+      <c r="R6">
+        <f>((R4-R5)/R4)*100</f>
+        <v>98.323548909138765</v>
+      </c>
+      <c r="S6">
+        <f>((S4-S5)/S4)*100</f>
+        <v>-3.9150816714984731E-3</v>
+      </c>
+      <c r="U6">
+        <f>((U4-U5)/U4)*100</f>
+        <v>96.983588313420526</v>
+      </c>
+      <c r="V6">
+        <f>((V4-V5)/V4)*100</f>
+        <v>5.2696881875534066E-3</v>
+      </c>
+      <c r="X6">
+        <f>((X4-X5)/X4)*100</f>
+        <v>95.465851086659754</v>
+      </c>
+      <c r="Y6">
+        <f>((Y4-Y5)/Y4)*100</f>
+        <v>-6.6165150331572747E-2</v>
+      </c>
+      <c r="AA6">
+        <f>((AA4-AA5)/AA4)*100</f>
+        <v>96.994229968320994</v>
+      </c>
+      <c r="AB6">
+        <f>((AB4-AB5)/AB4)*100</f>
+        <v>9.3652964459275539E-3</v>
+      </c>
+      <c r="AD6">
+        <f>((AD4-AD5)/AD4)*100</f>
+        <v>85.441885192023463</v>
+      </c>
+      <c r="AE6">
+        <f>((AE4-AE5)/AE4)*100</f>
+        <v>-2.2412488665593273E-2</v>
+      </c>
+      <c r="AG6">
+        <f>((AG4-AG5)/AG4)*100</f>
+        <v>99.590207870875858</v>
+      </c>
+      <c r="AH6">
+        <f>((AH4-AH5)/AH4)*100</f>
+        <v>-4.0182434508662906E-2</v>
+      </c>
+      <c r="AJ6">
+        <f>((AJ4-AJ5)/AJ4)*100</f>
+        <v>-1.9379795505074249</v>
+      </c>
+      <c r="AK6">
+        <f>((AK4-AK5)/AK4)*100</f>
+        <v>0.62771900991408691</v>
+      </c>
+      <c r="AM6">
+        <f>((AM4-AM5)/AM4)*100</f>
+        <v>85.659713516429363</v>
+      </c>
+      <c r="AN6">
+        <f>((AN4-AN5)/AN4)*100</f>
+        <v>5.3476771764439362E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B14" s="1"/>
       <c r="T14" s="2"/>
     </row>
   </sheetData>
@@ -970,8 +1174,8 @@
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="E4:E5">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -980,8 +1184,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="H4:H5">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -990,8 +1194,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="K4:K5">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1000,8 +1204,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="N4:N5">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1010,8 +1214,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="Q4:Q5">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1020,8 +1224,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T4">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="T4:T5">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1030,8 +1234,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W4">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="W4:W5">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1040,8 +1244,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z4">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="Z4:Z5">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1050,8 +1254,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="AC4:AC5">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1060,8 +1264,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF4">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="AF4:AF5">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1070,8 +1274,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI4">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="AI4:AI5">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1080,8 +1284,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL4">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="AL4:AL5">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1090,12 +1294,142 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO4">
+  <conditionalFormatting sqref="AO4:AO5">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:G6">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:J6">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:M6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O6:P6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6:S6">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6:V6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X6:Y6">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AB6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6:AE6">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG6:AH6">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6:AK6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM6:AN6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
+        <color rgb="FFFF0000"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
@@ -2838,4 +3172,578 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF611A7-FF5C-9946-82AC-26D645B98B8C}">
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>2.1670388999999901E-2</v>
+      </c>
+      <c r="D5">
+        <v>7.788605767</v>
+      </c>
+      <c r="E5">
+        <v>9.9566999999999795E-2</v>
+      </c>
+      <c r="F5">
+        <v>1.51476287599999</v>
+      </c>
+      <c r="G5">
+        <v>5.6594470000000001E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.45763494700000001</v>
+      </c>
+      <c r="I5">
+        <v>6.0642653989999999</v>
+      </c>
+      <c r="J5">
+        <v>0.27255439599999898</v>
+      </c>
+      <c r="K5">
+        <v>0.49231615699999998</v>
+      </c>
+      <c r="L5">
+        <v>3.9079429750000001</v>
+      </c>
+      <c r="M5">
+        <v>2.0160246999999999E-2</v>
+      </c>
+      <c r="N5">
+        <v>0.62630026999999999</v>
+      </c>
+      <c r="O5">
+        <v>20.713497519000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2.19130099999999E-2</v>
+      </c>
+      <c r="D6">
+        <v>7.79280851900001</v>
+      </c>
+      <c r="E6">
+        <v>9.9675741000000095E-2</v>
+      </c>
+      <c r="F6">
+        <v>1.514690286</v>
+      </c>
+      <c r="G6">
+        <v>5.6976826000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.45819648799999901</v>
+      </c>
+      <c r="I6">
+        <v>6.0626823300000003</v>
+      </c>
+      <c r="J6">
+        <v>0.274515538</v>
+      </c>
+      <c r="K6">
+        <v>0.49315212899999999</v>
+      </c>
+      <c r="L6">
+        <v>3.900064135</v>
+      </c>
+      <c r="M6">
+        <v>2.0464525000000001E-2</v>
+      </c>
+      <c r="N6">
+        <v>0.54645062600000005</v>
+      </c>
+      <c r="O6">
+        <v>20.712612427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2.1715781E-2</v>
+      </c>
+      <c r="D7">
+        <v>7.78769075099998</v>
+      </c>
+      <c r="E7">
+        <v>9.8289989999999897E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.51437557399999</v>
+      </c>
+      <c r="G7">
+        <v>5.6514841000000003E-2</v>
+      </c>
+      <c r="H7">
+        <v>0.45803918399999999</v>
+      </c>
+      <c r="I7">
+        <v>6.0630073089999899</v>
+      </c>
+      <c r="J7">
+        <v>0.27229793999999902</v>
+      </c>
+      <c r="K7">
+        <v>0.49229077099999902</v>
+      </c>
+      <c r="L7">
+        <v>3.9083897669999899</v>
+      </c>
+      <c r="M7">
+        <v>2.0096164E-2</v>
+      </c>
+      <c r="N7">
+        <v>0.54734508500000001</v>
+      </c>
+      <c r="O7">
+        <v>20.709862891</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>2.1558777000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>7.7885421700000004</v>
+      </c>
+      <c r="E8">
+        <v>9.7385553000000097E-2</v>
+      </c>
+      <c r="F8">
+        <v>1.5140554819999901</v>
+      </c>
+      <c r="G8">
+        <v>5.6435298999999897E-2</v>
+      </c>
+      <c r="H8">
+        <v>0.45793884199999901</v>
+      </c>
+      <c r="I8">
+        <v>6.064377371</v>
+      </c>
+      <c r="J8">
+        <v>0.27229752899999998</v>
+      </c>
+      <c r="K8">
+        <v>0.492120908999999</v>
+      </c>
+      <c r="L8">
+        <v>3.9084012960000001</v>
+      </c>
+      <c r="M8">
+        <v>1.9987675999999999E-2</v>
+      </c>
+      <c r="N8">
+        <v>0.55720628400000005</v>
+      </c>
+      <c r="O8">
+        <v>20.710153963</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2.1566398000000001E-2</v>
+      </c>
+      <c r="D9">
+        <v>7.7886827629999997</v>
+      </c>
+      <c r="E9">
+        <v>9.7693707000000005E-2</v>
+      </c>
+      <c r="F9">
+        <v>1.5148509079999899</v>
+      </c>
+      <c r="G9">
+        <v>5.6489028999999899E-2</v>
+      </c>
+      <c r="H9">
+        <v>0.45799976599999997</v>
+      </c>
+      <c r="I9">
+        <v>6.0669434850000004</v>
+      </c>
+      <c r="J9">
+        <v>0.27245112300000002</v>
+      </c>
+      <c r="K9">
+        <v>0.49225550400000001</v>
+      </c>
+      <c r="L9">
+        <v>3.9067603819999901</v>
+      </c>
+      <c r="M9">
+        <v>2.00978629999999E-2</v>
+      </c>
+      <c r="N9">
+        <v>0.54859861300000001</v>
+      </c>
+      <c r="O9">
+        <v>20.713437281000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>2.1632118999999901E-2</v>
+      </c>
+      <c r="D10">
+        <v>7.7915927429999901</v>
+      </c>
+      <c r="E10">
+        <v>9.7113913000000093E-2</v>
+      </c>
+      <c r="F10">
+        <v>1.51434344799999</v>
+      </c>
+      <c r="G10">
+        <v>5.64154830000001E-2</v>
+      </c>
+      <c r="H10">
+        <v>0.45765355000000002</v>
+      </c>
+      <c r="I10">
+        <v>6.0666592069999998</v>
+      </c>
+      <c r="J10">
+        <v>0.271916721999999</v>
+      </c>
+      <c r="K10">
+        <v>0.493578724999999</v>
+      </c>
+      <c r="L10">
+        <v>3.90671174799999</v>
+      </c>
+      <c r="M10">
+        <v>2.0044738999999999E-2</v>
+      </c>
+      <c r="N10">
+        <v>0.54808315500000004</v>
+      </c>
+      <c r="O10">
+        <v>20.715232767</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>2.1658759999999899E-2</v>
+      </c>
+      <c r="D11">
+        <v>7.7947981879999997</v>
+      </c>
+      <c r="E11">
+        <v>9.8980616000000105E-2</v>
+      </c>
+      <c r="F11">
+        <v>1.5148128999999999</v>
+      </c>
+      <c r="G11">
+        <v>5.6672052000000001E-2</v>
+      </c>
+      <c r="H11">
+        <v>0.457924215999999</v>
+      </c>
+      <c r="I11">
+        <v>6.0668586840000103</v>
+      </c>
+      <c r="J11">
+        <v>0.272893575</v>
+      </c>
+      <c r="K11">
+        <v>0.492327072999999</v>
+      </c>
+      <c r="L11">
+        <v>3.9048722989999902</v>
+      </c>
+      <c r="M11">
+        <v>2.0216452999999999E-2</v>
+      </c>
+      <c r="N11">
+        <v>0.54761473100000002</v>
+      </c>
+      <c r="O11">
+        <v>20.719440948999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>2.1639038999999999E-2</v>
+      </c>
+      <c r="D12">
+        <v>7.7899716459999997</v>
+      </c>
+      <c r="E12">
+        <v>9.8083506999999903E-2</v>
+      </c>
+      <c r="F12">
+        <v>1.5127594169999901</v>
+      </c>
+      <c r="G12">
+        <v>5.6608270000000002E-2</v>
+      </c>
+      <c r="H12">
+        <v>0.45777858199999899</v>
+      </c>
+      <c r="I12">
+        <v>6.0622548540000096</v>
+      </c>
+      <c r="J12">
+        <v>0.27232184799999998</v>
+      </c>
+      <c r="K12">
+        <v>0.49182620599999899</v>
+      </c>
+      <c r="L12">
+        <v>3.9037054969999998</v>
+      </c>
+      <c r="M12">
+        <v>2.0026265000000001E-2</v>
+      </c>
+      <c r="N12">
+        <v>0.54539367400000005</v>
+      </c>
+      <c r="O12">
+        <v>20.704204261000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>2.1713296999999999E-2</v>
+      </c>
+      <c r="D13">
+        <v>7.787347113</v>
+      </c>
+      <c r="E13">
+        <v>9.7883269000000106E-2</v>
+      </c>
+      <c r="F13">
+        <v>1.51182173999999</v>
+      </c>
+      <c r="G13">
+        <v>5.6496790999999998E-2</v>
+      </c>
+      <c r="H13">
+        <v>0.45767707799999902</v>
+      </c>
+      <c r="I13">
+        <v>6.0607472580000001</v>
+      </c>
+      <c r="J13">
+        <v>0.27223769999999903</v>
+      </c>
+      <c r="K13">
+        <v>0.49176235600000001</v>
+      </c>
+      <c r="L13">
+        <v>3.89744741999999</v>
+      </c>
+      <c r="M13">
+        <v>2.0108869000000001E-2</v>
+      </c>
+      <c r="N13">
+        <v>0.55015700700000003</v>
+      </c>
+      <c r="O13">
+        <v>20.692585380000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>2.1855028999999901E-2</v>
+      </c>
+      <c r="D14">
+        <v>7.7860668789999696</v>
+      </c>
+      <c r="E14">
+        <v>9.8922446999999997E-2</v>
+      </c>
+      <c r="F14">
+        <v>1.51220889299999</v>
+      </c>
+      <c r="G14">
+        <v>5.6745841999999901E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.45806612199999902</v>
+      </c>
+      <c r="I14">
+        <v>6.0625395729999996</v>
+      </c>
+      <c r="J14">
+        <v>0.27311042299999999</v>
+      </c>
+      <c r="K14">
+        <v>0.49177879899999999</v>
+      </c>
+      <c r="L14">
+        <v>3.9069553799999999</v>
+      </c>
+      <c r="M14">
+        <v>2.0284541999999999E-2</v>
+      </c>
+      <c r="N14">
+        <v>0.54779951900000001</v>
+      </c>
+      <c r="O14">
+        <v>20.705948580000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.16922599E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7.7896106538999899</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9.8359574300000002E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.51386815239999</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5.6594890299999999E-2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.45789087749999902</v>
+      </c>
+      <c r="I15" s="1">
+        <v>6.0640335470000002</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.27265967940000002</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.49234086289999901</v>
+      </c>
+      <c r="L15" s="1">
+        <v>3.9051250898999901</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2.0148734299999999E-2</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0.55649489640000005</v>
+      </c>
+      <c r="O15" s="1">
+        <v>20.709697601799999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05EABA7-3707-E845-95BC-AFF0085B4065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29E3D8-7825-7447-8785-B14548994AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33400" yWindow="660" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="56320" yWindow="0" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="26">
   <si>
     <t>Branch</t>
   </si>
@@ -520,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71848BA-D8C3-7041-A0EE-B663A4811CD2}">
-  <dimension ref="A1:AO14"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
@@ -774,134 +774,134 @@
         <v>24</v>
       </c>
       <c r="C4" s="2">
-        <v>4.7361520297999897</v>
+        <v>2.10134848999999E-2</v>
       </c>
       <c r="D4" s="2">
-        <v>2.1667207299999901E-2</v>
+        <v>2.1044281399999899E-2</v>
       </c>
       <c r="E4">
         <f>((C4-D4)/C4)*100</f>
-        <v>99.542514531550736</v>
+        <v>-0.14655589087938234</v>
       </c>
       <c r="F4" s="2">
-        <v>21.1806411148</v>
+        <v>7.7868371409000003</v>
       </c>
       <c r="G4" s="2">
-        <v>7.7907680781999904</v>
+        <v>7.7882990942999903</v>
       </c>
       <c r="H4">
         <f>((F4-G4)/F4)*100</f>
-        <v>63.217505853700615</v>
+        <v>-1.8774675436720758E-2</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4521483475999908</v>
+        <v>0.10106857869999999</v>
       </c>
       <c r="J4" s="2">
-        <v>9.8861430799999997E-2</v>
+        <v>0.1008018878</v>
       </c>
       <c r="K4">
         <f>((I4-J4)/I4)*100</f>
-        <v>98.954085069717493</v>
+        <v>0.26387122825938303</v>
       </c>
       <c r="L4" s="2">
-        <v>6.2249833689000003</v>
+        <v>1.5133286373999999</v>
       </c>
       <c r="M4" s="2">
-        <v>1.51414486739999</v>
+        <v>1.5134209893999899</v>
       </c>
       <c r="N4">
         <f>((L4-M4)/L4)*100</f>
-        <v>75.67632268762911</v>
+        <v>-6.102574001949284E-3</v>
       </c>
       <c r="O4" s="2">
-        <v>4.7699677447999997</v>
+        <v>5.5878251300000001E-2</v>
       </c>
       <c r="P4" s="2">
-        <v>5.6586210900000003E-2</v>
+        <v>5.5854686299999998E-2</v>
       </c>
       <c r="Q4">
         <f>((O4-P4)/O4)*100</f>
-        <v>98.813698248553408</v>
+        <v>4.2172042703138721E-2</v>
       </c>
       <c r="R4" s="2">
-        <v>4.7879055426999999</v>
+        <v>0.45890807779999998</v>
       </c>
       <c r="S4" s="2">
-        <v>0.45787295140000001</v>
+        <v>0.45886056159999999</v>
       </c>
       <c r="T4">
         <f>((R4-S4)/R4)*100</f>
-        <v>90.436884200898504</v>
+        <v>1.0354186883738974E-2</v>
       </c>
       <c r="U4" s="2">
-        <v>4.8561072632000002</v>
+        <v>6.0628989352999998</v>
       </c>
       <c r="V4" s="2">
-        <v>6.06435311949999</v>
+        <v>6.0622900875000001</v>
       </c>
       <c r="W4">
         <f>((U4-V4)/U4)*100</f>
-        <v>-24.880954863912937</v>
+        <v>1.0042189495437705E-2</v>
       </c>
       <c r="X4" s="2">
-        <v>4.9457645918999997</v>
+        <v>0.27203544940000002</v>
       </c>
       <c r="Y4" s="2">
-        <v>0.27247939299999901</v>
+        <v>0.27205333569999901</v>
       </c>
       <c r="Z4">
         <f>((X4-Y4)/X4)*100</f>
-        <v>94.490651790296354</v>
+        <v>-6.5749886782926767E-3</v>
       </c>
       <c r="AA4" s="2">
-        <v>4.8490968258999896</v>
+        <v>0.49175476299999998</v>
       </c>
       <c r="AB4" s="2">
-        <v>0.49238697640000001</v>
+        <v>0.49182936509999903</v>
       </c>
       <c r="AC4">
         <f>((AA4-AB4)/AA4)*100</f>
-        <v>89.845800278310321</v>
+        <v>-1.5170590223453264E-2</v>
       </c>
       <c r="AD4" s="2">
-        <v>10.3908139883</v>
+        <v>3.9014598262999902</v>
       </c>
       <c r="AE4" s="2">
-        <v>3.9042500502999902</v>
+        <v>3.9008079268000002</v>
       </c>
       <c r="AF4">
         <f>((AD4-AE4)/AD4)*100</f>
-        <v>62.425946083760579</v>
+        <v>1.6709117330787542E-2</v>
       </c>
       <c r="AG4" s="2">
-        <v>4.7319136024999997</v>
+        <v>1.93700037999999E-2</v>
       </c>
       <c r="AH4" s="2">
-        <v>2.0140641300000001E-2</v>
+        <v>1.93747672E-2</v>
       </c>
       <c r="AI4">
         <f>((AG4-AH4)/AG4)*100</f>
-        <v>99.574365827614457</v>
+        <v>-2.459163172750858E-2</v>
       </c>
       <c r="AJ4" s="2">
-        <v>0.56397134309999997</v>
+        <v>0.54875180800000001</v>
       </c>
       <c r="AK4" s="2">
-        <v>0.56001018679999903</v>
+        <v>0.54884408070000001</v>
       </c>
       <c r="AL4">
         <f>((AJ4-AK4)/AJ4)*100</f>
-        <v>0.70236836471646147</v>
+        <v>-1.6815015213582085E-2</v>
       </c>
       <c r="AM4" s="2">
-        <v>80.952135558099997</v>
+        <v>20.700766578500001</v>
       </c>
       <c r="AN4" s="2">
-        <v>20.710805148799999</v>
+        <v>20.7009069424</v>
       </c>
       <c r="AO4">
         <f>((AM4-AN4)/AM4)*100</f>
-        <v>74.415986674081395</v>
+        <v>-6.7806136292530817E-4</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.2">
@@ -909,134 +909,134 @@
         <v>25</v>
       </c>
       <c r="C5" s="2">
-        <v>2.0490970599999998E-2</v>
+        <v>2.1148022799999899E-2</v>
       </c>
       <c r="D5" s="2">
-        <v>2.16922599E-2</v>
+        <v>2.1138030700000001E-2</v>
       </c>
       <c r="E5">
         <f>((C5-D5)/C5)*100</f>
-        <v>-5.8625300062653052</v>
+        <v>4.7248388629019415E-2</v>
       </c>
       <c r="F5" s="2">
-        <v>7.7896655604999996</v>
+        <v>7.7888443829999998</v>
       </c>
       <c r="G5" s="2">
-        <v>7.7896106538999899</v>
-      </c>
-      <c r="H5" s="2">
+        <v>7.7902623423999904</v>
+      </c>
+      <c r="H5">
         <f>((F5-G5)/F5)*100</f>
-        <v>7.0486466438496851E-4</v>
+        <v>-1.8205003595724873E-2</v>
       </c>
       <c r="I5" s="2">
-        <v>9.1392076700000005E-2</v>
+        <v>0.1013372595</v>
       </c>
       <c r="J5" s="2">
-        <v>9.8359574300000002E-2</v>
+        <v>0.1010922164</v>
       </c>
       <c r="K5">
         <f>((I5-J5)/I5)*100</f>
-        <v>-7.6237436018345743</v>
+        <v>0.2418094797600035</v>
       </c>
       <c r="L5" s="2">
-        <v>1.50496271489999</v>
+        <v>1.5131773657000001</v>
       </c>
       <c r="M5" s="2">
-        <v>1.51386815239999</v>
+        <v>1.5147833314000001</v>
       </c>
       <c r="N5">
         <f>((L5-M5)/L5)*100</f>
-        <v>-0.59173808173657938</v>
+        <v>-0.10613201970921107</v>
       </c>
       <c r="O5" s="2">
-        <v>5.7508319799999902E-2</v>
+        <v>5.5961258899999998E-2</v>
       </c>
       <c r="P5" s="2">
-        <v>5.6594890299999999E-2</v>
+        <v>5.59714298E-2</v>
       </c>
       <c r="Q5">
         <f>((O5-P5)/O5)*100</f>
-        <v>1.5883432226442902</v>
+        <v>-1.8174894918244817E-2</v>
       </c>
       <c r="R5" s="2">
-        <v>8.0266894699999994E-2</v>
+        <v>0.45887892660000001</v>
       </c>
       <c r="S5" s="2">
-        <v>0.45789087749999902</v>
+        <v>0.45877713409999998</v>
       </c>
       <c r="T5">
         <f>((R5-S5)/R5)*100</f>
-        <v>-470.46043603827002</v>
+        <v>2.2182866568802424E-2</v>
       </c>
       <c r="U5" s="2">
-        <v>0.14648018700000001</v>
+        <v>6.0627548560999998</v>
       </c>
       <c r="V5" s="2">
-        <v>6.0640335470000002</v>
+        <v>6.0636236880999999</v>
       </c>
       <c r="W5">
         <f>((U5-V5)/U5)*100</f>
-        <v>-4039.83192621129</v>
+        <v>-1.4330647051083181E-2</v>
       </c>
       <c r="X5" s="2">
-        <v>0.22424833150000001</v>
+        <v>0.27224948490000001</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.27265967940000002</v>
+        <v>0.27250950699999998</v>
       </c>
       <c r="Z5">
         <f>((X5-Y5)/X5)*100</f>
-        <v>-21.588275630046329</v>
+        <v>-9.5508757379463141E-2</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.1457526992</v>
+        <v>0.49188873370000002</v>
       </c>
       <c r="AB5" s="2">
-        <v>0.49234086289999901</v>
+        <v>0.49214803059999901</v>
       </c>
       <c r="AC5">
         <f>((AA5-AB5)/AA5)*100</f>
-        <v>-237.79193497090242</v>
+        <v>-5.2714543398574322E-2</v>
       </c>
       <c r="AD5" s="2">
-        <v>1.5127066299</v>
+        <v>3.8996550481000001</v>
       </c>
       <c r="AE5" s="2">
-        <v>3.9051250898999901</v>
+        <v>3.8996497178</v>
       </c>
       <c r="AF5">
         <f>((AD5-AE5)/AD5)*100</f>
-        <v>-158.154820816654</v>
+        <v>1.3668644878339834E-4</v>
       </c>
       <c r="AG5" s="2">
-        <v>1.93910095E-2</v>
+        <v>1.9472640100000001E-2</v>
       </c>
       <c r="AH5" s="2">
-        <v>2.0148734299999999E-2</v>
+        <v>1.9451079699999999E-2</v>
       </c>
       <c r="AI5">
         <f>((AG5-AH5)/AG5)*100</f>
-        <v>-3.9076088328459537</v>
+        <v>0.11072150406560535</v>
       </c>
       <c r="AJ5" s="2">
-        <v>0.57490099240000003</v>
+        <v>0.55042533940000005</v>
       </c>
       <c r="AK5" s="2">
-        <v>0.55649489640000005</v>
+        <v>0.55477528669999998</v>
       </c>
       <c r="AL5">
         <f>((AJ5-AK5)/AJ5)*100</f>
-        <v>3.2016114502014177</v>
+        <v>-0.7902883440543752</v>
       </c>
       <c r="AM5" s="2">
-        <v>11.6087681536</v>
+        <v>20.701861121499999</v>
       </c>
       <c r="AN5" s="2">
-        <v>20.709697601799999</v>
+        <v>20.705847007199999</v>
       </c>
       <c r="AO5">
         <f>((AM5-AN5)/AM5)*100</f>
-        <v>-78.397029967195152</v>
+        <v>-1.9253755382703359E-2</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.2">
@@ -1045,117 +1045,127 @@
       </c>
       <c r="C6">
         <f>((C4-C5)/C4)*100</f>
-        <v>99.567349813285759</v>
+        <v>-0.64024554061472838</v>
       </c>
       <c r="D6">
         <f>((D4-D5)/D4)*100</f>
-        <v>-0.1156244995177548</v>
+        <v>-0.44548586962015346</v>
       </c>
       <c r="F6">
         <f>((F4-F5)/F4)*100</f>
-        <v>63.222711162142488</v>
+        <v>-2.5777373581585869E-2</v>
       </c>
       <c r="G6">
         <f>((G4-G5)/G4)*100</f>
-        <v>1.4856356759473173E-2</v>
+        <v>-2.5207661855678808E-2</v>
       </c>
       <c r="I6">
         <f>((I4-I5)/I4)*100</f>
-        <v>99.033107888925528</v>
+        <v>-0.26584008942831217</v>
       </c>
       <c r="J6">
         <f>((J4-J5)/J4)*100</f>
-        <v>0.50763629045109337</v>
+        <v>-0.28801901069158398</v>
       </c>
       <c r="L6">
         <f>((L4-L5)/L4)*100</f>
-        <v>75.823827539543657</v>
+        <v>9.9959583306200531E-3</v>
       </c>
       <c r="M6">
         <f>((M4-M5)/M4)*100</f>
-        <v>1.8275331902369348E-2</v>
+        <v>-9.001738508663662E-2</v>
       </c>
       <c r="O6">
         <f>((O4-O5)/O4)*100</f>
-        <v>98.794366694351481</v>
+        <v>-0.14855081909121434</v>
       </c>
       <c r="P6">
         <f>((P4-P5)/P4)*100</f>
-        <v>-1.53383657642925E-2</v>
+        <v>-0.20901290067759673</v>
       </c>
       <c r="R6">
         <f>((R4-R5)/R4)*100</f>
-        <v>98.323548909138765</v>
+        <v>6.352296115535074E-3</v>
       </c>
       <c r="S6">
         <f>((S4-S5)/S4)*100</f>
-        <v>-3.9150816714984731E-3</v>
+        <v>1.8181449220457616E-2</v>
       </c>
       <c r="U6">
         <f>((U4-U5)/U4)*100</f>
-        <v>96.983588313420526</v>
+        <v>2.3764077471449142E-3</v>
       </c>
       <c r="V6">
         <f>((V4-V5)/V4)*100</f>
-        <v>5.2696881875534066E-3</v>
+        <v>-2.1998297355475444E-2</v>
       </c>
       <c r="X6">
         <f>((X4-X5)/X4)*100</f>
-        <v>95.465851086659754</v>
+        <v>-7.8679267893968508E-2</v>
       </c>
       <c r="Y6">
         <f>((Y4-Y5)/Y4)*100</f>
-        <v>-6.6165150331572747E-2</v>
+        <v>-0.16767715743210254</v>
       </c>
       <c r="AA6">
         <f>((AA4-AA5)/AA4)*100</f>
-        <v>96.994229968320994</v>
+        <v>-2.7243396522026404E-2</v>
       </c>
       <c r="AB6">
         <f>((AB4-AB5)/AB4)*100</f>
-        <v>9.3652964459275539E-3</v>
+        <v>-6.4791881618371933E-2</v>
       </c>
       <c r="AD6">
         <f>((AD4-AD5)/AD4)*100</f>
-        <v>85.441885192023463</v>
+        <v>4.6259048672602429E-2</v>
       </c>
       <c r="AE6">
         <f>((AE4-AE5)/AE4)*100</f>
-        <v>-2.2412488665593273E-2</v>
+        <v>2.9691515750951521E-2</v>
       </c>
       <c r="AG6">
         <f>((AG4-AG5)/AG4)*100</f>
-        <v>99.590207870875858</v>
+        <v>-0.52987237927181707</v>
       </c>
       <c r="AH6">
         <f>((AH4-AH5)/AH4)*100</f>
-        <v>-4.0182434508662906E-2</v>
+        <v>-0.39387570034905117</v>
       </c>
       <c r="AJ6">
         <f>((AJ4-AJ5)/AJ4)*100</f>
-        <v>-1.9379795505074249</v>
+        <v>-0.30497054872574358</v>
       </c>
       <c r="AK6">
         <f>((AK4-AK5)/AK4)*100</f>
-        <v>0.62771900991408691</v>
+        <v>-1.0806723090527386</v>
       </c>
       <c r="AM6">
         <f>((AM4-AM5)/AM4)*100</f>
-        <v>85.659713516429363</v>
+        <v>-5.2874515339635716E-3</v>
       </c>
       <c r="AN6">
         <f>((AN4-AN5)/AN4)*100</f>
-        <v>5.3476771764439362E-3</v>
-      </c>
+        <v>-2.3864001774150271E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="T14" s="2"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1174,8 +1184,18 @@
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
   </mergeCells>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E4:E5">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1185,7 +1205,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="colorScale" priority="25">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1195,7 +1215,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K5">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1205,7 +1225,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N5">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1215,7 +1235,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q5">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1225,7 +1245,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T5">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1235,7 +1255,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W4:W5">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1245,7 +1265,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1255,7 +1275,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1265,7 +1285,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF4:AF5">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1275,7 +1295,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI4:AI5">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1285,7 +1305,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AL5">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1295,7 +1315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO4:AO5">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1304,132 +1324,252 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="C6">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:G6">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="F6">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J6">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:M6">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="I6">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O6:P6">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="J6">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R6:S6">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="L6">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U6:V6">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="M6">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X6:Y6">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="O6">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AB6">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="P6">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD6:AE6">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="R6">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG6:AH6">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="S6">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AK6">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="U6">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM6:AN6">
+  <conditionalFormatting sqref="V6">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X6">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y6">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG6">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
@@ -1443,7 +1583,7 @@
   <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" customWidth="1"/>
     <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -1539,43 +1679,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>4.7340293059999903</v>
+        <v>2.0945292000000001E-2</v>
       </c>
       <c r="D5">
-        <v>21.176729871999999</v>
+        <v>7.7977030729999903</v>
       </c>
       <c r="E5">
-        <v>9.4457361899999892</v>
+        <v>0.100677564</v>
       </c>
       <c r="F5">
-        <v>6.2217804140000004</v>
+        <v>1.51638297</v>
       </c>
       <c r="G5">
-        <v>4.7682641119999998</v>
+        <v>5.5917888000000103E-2</v>
       </c>
       <c r="H5">
-        <v>4.78634752199999</v>
+        <v>0.45915287100000002</v>
       </c>
       <c r="I5">
-        <v>4.8526370550000104</v>
+        <v>6.0677486629999997</v>
       </c>
       <c r="J5">
-        <v>4.9441060699999904</v>
+        <v>0.27247442699999902</v>
       </c>
       <c r="K5">
-        <v>4.8479211129999804</v>
+        <v>0.492297602</v>
       </c>
       <c r="L5">
-        <v>10.389432319999999</v>
+        <v>3.9035411389999899</v>
       </c>
       <c r="M5">
-        <v>4.73018520599999</v>
+        <v>1.9352582E-2</v>
       </c>
       <c r="N5">
-        <v>0.57304119499999995</v>
+        <v>0.61789860100000005</v>
       </c>
       <c r="O5">
-        <v>80.923910221</v>
+        <v>20.722267380000002</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -1583,43 +1723,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4.7393095049999996</v>
+        <v>2.1359196999999899E-2</v>
       </c>
       <c r="D6">
-        <v>21.173363765999898</v>
+        <v>7.795109515</v>
       </c>
       <c r="E6">
-        <v>9.4572644579999796</v>
+        <v>0.10401200099999899</v>
       </c>
       <c r="F6">
-        <v>6.2261814449999999</v>
+        <v>1.5165825909999899</v>
       </c>
       <c r="G6">
-        <v>4.7731040329999903</v>
+        <v>5.6184010999999902E-2</v>
       </c>
       <c r="H6">
-        <v>4.7896122209999898</v>
+        <v>0.459507095999999</v>
       </c>
       <c r="I6">
-        <v>4.8602087559999996</v>
+        <v>6.063977951</v>
       </c>
       <c r="J6">
-        <v>4.9492782460000004</v>
+        <v>0.27396532500000098</v>
       </c>
       <c r="K6">
-        <v>4.8529851260000001</v>
+        <v>0.49250761799999898</v>
       </c>
       <c r="L6">
-        <v>10.393453508</v>
+        <v>3.9045517169999799</v>
       </c>
       <c r="M6">
-        <v>4.7350227470000004</v>
+        <v>1.967207E-2</v>
       </c>
       <c r="N6">
-        <v>0.57079999699999995</v>
+        <v>0.54323971000000004</v>
       </c>
       <c r="O6">
-        <v>80.976149698</v>
+        <v>20.724220821999999</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -1627,43 +1767,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>4.7078935550000001</v>
+        <v>2.0935884999999901E-2</v>
       </c>
       <c r="D7">
-        <v>21.146499433999999</v>
+        <v>7.7921811439999997</v>
       </c>
       <c r="E7">
-        <v>9.3944941359999898</v>
+        <v>0.101148921999999</v>
       </c>
       <c r="F7">
-        <v>6.1949537149999996</v>
+        <v>1.514309538</v>
       </c>
       <c r="G7">
-        <v>4.7398854799999999</v>
+        <v>5.585818E-2</v>
       </c>
       <c r="H7">
-        <v>4.7574510490000002</v>
+        <v>0.458939813999999</v>
       </c>
       <c r="I7">
-        <v>4.8284425640000102</v>
+        <v>6.0662435300000004</v>
       </c>
       <c r="J7">
-        <v>4.9171688830000102</v>
+        <v>0.27186163400000002</v>
       </c>
       <c r="K7">
-        <v>4.8211042189999898</v>
+        <v>0.491587261</v>
       </c>
       <c r="L7">
-        <v>10.363234916</v>
+        <v>3.90386092699999</v>
       </c>
       <c r="M7">
-        <v>4.7036561429999999</v>
+        <v>1.93052139999999E-2</v>
       </c>
       <c r="N7">
-        <v>0.57259144100000003</v>
+        <v>0.54461698599999997</v>
       </c>
       <c r="O7">
-        <v>80.601453527000004</v>
+        <v>20.712324318</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -1671,43 +1811,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>4.8357023659999996</v>
+        <v>2.08336719999999E-2</v>
       </c>
       <c r="D8">
-        <v>21.283297358999999</v>
+        <v>7.7812151570000001</v>
       </c>
       <c r="E8">
-        <v>9.6534851180000008</v>
+        <v>0.10033523599999999</v>
       </c>
       <c r="F8">
-        <v>6.3259116600000098</v>
+        <v>1.512441935</v>
       </c>
       <c r="G8">
-        <v>4.8699703429999897</v>
+        <v>5.5827926999999999E-2</v>
       </c>
       <c r="H8">
-        <v>4.8880030239999899</v>
+        <v>0.45860525600000002</v>
       </c>
       <c r="I8">
-        <v>4.9540698719999998</v>
+        <v>6.0625658989999902</v>
       </c>
       <c r="J8">
-        <v>5.0477363430000004</v>
+        <v>0.27135582499999999</v>
       </c>
       <c r="K8">
-        <v>4.9493739049999999</v>
+        <v>0.49157306899999997</v>
       </c>
       <c r="L8">
-        <v>10.490154618999901</v>
+        <v>3.9030260699999899</v>
       </c>
       <c r="M8">
-        <v>4.8317443500000001</v>
+        <v>1.9307754E-2</v>
       </c>
       <c r="N8">
-        <v>0.56438216600000002</v>
+        <v>0.54530207200000003</v>
       </c>
       <c r="O8">
-        <v>82.156601383999998</v>
+        <v>20.693376035</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -1715,43 +1855,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>4.7201029639999899</v>
+        <v>2.0906497E-2</v>
       </c>
       <c r="D9">
-        <v>21.162477132999999</v>
+        <v>7.7805381919999999</v>
       </c>
       <c r="E9">
-        <v>9.4234756789999992</v>
+        <v>0.100159464999999</v>
       </c>
       <c r="F9">
-        <v>6.2093324299999804</v>
+        <v>1.5116671129999899</v>
       </c>
       <c r="G9">
-        <v>4.7542486399999904</v>
+        <v>5.5745634000000002E-2</v>
       </c>
       <c r="H9">
-        <v>4.7723286930000004</v>
+        <v>0.45859409299999998</v>
       </c>
       <c r="I9">
-        <v>4.8406304889999996</v>
+        <v>6.0593861860000002</v>
       </c>
       <c r="J9">
-        <v>4.92910223999999</v>
+        <v>0.27132947599999901</v>
       </c>
       <c r="K9">
-        <v>4.8331939989999997</v>
+        <v>0.49138484900000001</v>
       </c>
       <c r="L9">
-        <v>10.376906498999899</v>
+        <v>3.9032113759999998</v>
       </c>
       <c r="M9">
-        <v>4.7158174270000002</v>
+        <v>1.9323584000000001E-2</v>
       </c>
       <c r="N9">
-        <v>0.57460502199999997</v>
+        <v>0.53678791199999998</v>
       </c>
       <c r="O9">
-        <v>80.764317835</v>
+        <v>20.688285358000002</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -1759,43 +1899,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>4.7483563999999898</v>
+        <v>2.08305289999999E-2</v>
       </c>
       <c r="D10">
-        <v>21.204867498999899</v>
+        <v>7.7814282109999997</v>
       </c>
       <c r="E10">
-        <v>9.4793780250000097</v>
+        <v>0.10019067299999999</v>
       </c>
       <c r="F10">
-        <v>6.2381119399999996</v>
+        <v>1.5114285030000001</v>
       </c>
       <c r="G10">
-        <v>4.7830271779999904</v>
+        <v>5.5645885000000103E-2</v>
       </c>
       <c r="H10">
-        <v>4.8021576899999898</v>
+        <v>0.45858836200000003</v>
       </c>
       <c r="I10">
-        <v>4.8694124350000001</v>
+        <v>6.0617983099999897</v>
       </c>
       <c r="J10">
-        <v>4.9590571159999897</v>
+        <v>0.27090224999999901</v>
       </c>
       <c r="K10">
-        <v>4.8623519149999801</v>
+        <v>0.49130033099999898</v>
       </c>
       <c r="L10">
-        <v>10.401261198</v>
+        <v>3.9017135810000001</v>
       </c>
       <c r="M10">
-        <v>4.74394939799999</v>
+        <v>1.9188847999999901E-2</v>
       </c>
       <c r="N10">
-        <v>0.55289784900000005</v>
+        <v>0.54013573299999995</v>
       </c>
       <c r="O10">
-        <v>81.118364749999998</v>
+        <v>20.689045309000001</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -1803,43 +1943,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>4.7037826629999904</v>
+        <v>2.1090906E-2</v>
       </c>
       <c r="D11">
-        <v>21.152131596</v>
+        <v>7.7843653549999896</v>
       </c>
       <c r="E11">
-        <v>9.3876109779999997</v>
+        <v>0.101818195</v>
       </c>
       <c r="F11">
-        <v>6.1921738199999998</v>
+        <v>1.512677534</v>
       </c>
       <c r="G11">
-        <v>4.73704256899999</v>
+        <v>5.5970686000000103E-2</v>
       </c>
       <c r="H11">
-        <v>4.7546049190000099</v>
+        <v>0.45885493099999902</v>
       </c>
       <c r="I11">
-        <v>4.8231421749999903</v>
+        <v>6.061748981</v>
       </c>
       <c r="J11">
-        <v>4.9121940719999904</v>
+        <v>0.272130135</v>
       </c>
       <c r="K11">
-        <v>4.8161531389999999</v>
+        <v>0.49171955099999898</v>
       </c>
       <c r="L11">
-        <v>10.356330882</v>
+        <v>3.8977867249999898</v>
       </c>
       <c r="M11">
-        <v>4.6991199909999901</v>
+        <v>1.9382218999999899E-2</v>
       </c>
       <c r="N11">
-        <v>0.55554261299999996</v>
+        <v>0.53911805499999998</v>
       </c>
       <c r="O11">
-        <v>80.560378224999994</v>
+        <v>20.693866938999999</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -1847,43 +1987,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>4.6960157959999904</v>
+        <v>2.1049211999999901E-2</v>
       </c>
       <c r="D12">
-        <v>21.135143617000001</v>
+        <v>7.7794660599999803</v>
       </c>
       <c r="E12">
-        <v>9.3704731389999907</v>
+        <v>0.10056599300000001</v>
       </c>
       <c r="F12">
-        <v>6.1849777839999902</v>
+        <v>1.511711612</v>
       </c>
       <c r="G12">
-        <v>4.7298488310000097</v>
+        <v>5.5815807000000099E-2</v>
       </c>
       <c r="H12">
-        <v>4.74821225899999</v>
+        <v>0.45880408700000003</v>
       </c>
       <c r="I12">
-        <v>4.8161023499999898</v>
+        <v>6.0617813089999997</v>
       </c>
       <c r="J12">
-        <v>4.9041083179999996</v>
+        <v>0.27180590999999898</v>
       </c>
       <c r="K12">
-        <v>4.8065764169999996</v>
+        <v>0.49144501099999999</v>
       </c>
       <c r="L12">
-        <v>10.353393854</v>
+        <v>3.9043868549999901</v>
       </c>
       <c r="M12">
-        <v>4.6916778209999901</v>
+        <v>1.93601149999999E-2</v>
       </c>
       <c r="N12">
-        <v>0.55554574300000004</v>
+        <v>0.53863703100000004</v>
       </c>
       <c r="O12">
-        <v>80.462678502000003</v>
+        <v>20.692317829</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -1891,43 +2031,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>4.7152222879999997</v>
+        <v>2.1036944999999901E-2</v>
       </c>
       <c r="D13">
-        <v>21.163150134999899</v>
+        <v>7.7869990860000096</v>
       </c>
       <c r="E13">
-        <v>9.4112512409999898</v>
+        <v>0.100745107999999</v>
       </c>
       <c r="F13">
-        <v>6.2047871109999999</v>
+        <v>1.513208957</v>
       </c>
       <c r="G13">
-        <v>4.7493141909999999</v>
+        <v>5.5890241000000097E-2</v>
       </c>
       <c r="H13">
-        <v>4.7671523330000003</v>
+        <v>0.45893628199999997</v>
       </c>
       <c r="I13">
-        <v>4.8345936519999997</v>
+        <v>6.0607884379999897</v>
       </c>
       <c r="J13">
-        <v>4.9243923099999902</v>
+        <v>0.27208739399999998</v>
       </c>
       <c r="K13">
-        <v>4.8269851900000003</v>
+        <v>0.491826123</v>
       </c>
       <c r="L13">
-        <v>10.369362314</v>
+        <v>3.8965046640000001</v>
       </c>
       <c r="M13">
-        <v>4.7109683779999898</v>
+        <v>1.9376067999999899E-2</v>
       </c>
       <c r="N13">
-        <v>0.56577272000000001</v>
+        <v>0.54174849199999997</v>
       </c>
       <c r="O13">
-        <v>80.705057595</v>
+        <v>20.693725327999999</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -1935,43 +2075,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>4.7611054549999903</v>
+        <v>2.1146714E-2</v>
       </c>
       <c r="D14">
-        <v>21.208750736999999</v>
+        <v>7.7893656160000004</v>
       </c>
       <c r="E14">
-        <v>9.4983145119999808</v>
+        <v>0.10103263</v>
       </c>
       <c r="F14">
-        <v>6.2516233699999999</v>
+        <v>1.5128756209999901</v>
       </c>
       <c r="G14">
-        <v>4.7949720709999903</v>
+        <v>5.5926254000000002E-2</v>
       </c>
       <c r="H14">
-        <v>4.8131857169999996</v>
+        <v>0.45909798600000001</v>
       </c>
       <c r="I14">
-        <v>4.8818332839999803</v>
+        <v>6.0629500860000096</v>
       </c>
       <c r="J14">
-        <v>4.9705023209999997</v>
+        <v>0.27244211800000001</v>
       </c>
       <c r="K14">
-        <v>4.8743232359999897</v>
+        <v>0.49190621499999898</v>
       </c>
       <c r="L14">
-        <v>10.414609773</v>
+        <v>3.89601520899999</v>
       </c>
       <c r="M14">
-        <v>4.7569945640000002</v>
+        <v>1.9431583999999901E-2</v>
       </c>
       <c r="N14">
-        <v>0.55453468500000003</v>
+        <v>0.54003348799999995</v>
       </c>
       <c r="O14">
-        <v>81.252443843999998</v>
+        <v>20.698236467000001</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -1979,43 +2119,43 @@
         <v>21</v>
       </c>
       <c r="C15" s="1">
-        <v>4.7361520297999897</v>
+        <v>2.10134848999999E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>21.1806411148</v>
+        <v>7.7868371409000003</v>
       </c>
       <c r="E15" s="1">
-        <v>9.4521483475999908</v>
+        <v>0.10106857869999999</v>
       </c>
       <c r="F15" s="1">
-        <v>6.2249833689000003</v>
+        <v>1.5133286373999999</v>
       </c>
       <c r="G15" s="1">
-        <v>4.7699677447999997</v>
+        <v>5.5878251300000001E-2</v>
       </c>
       <c r="H15" s="1">
-        <v>4.7879055426999999</v>
+        <v>0.45890807779999998</v>
       </c>
       <c r="I15" s="1">
-        <v>4.8561072632000002</v>
+        <v>6.0628989352999998</v>
       </c>
       <c r="J15" s="1">
-        <v>4.9457645918999997</v>
+        <v>0.27203544940000002</v>
       </c>
       <c r="K15" s="1">
-        <v>4.8490968258999896</v>
+        <v>0.49175476299999998</v>
       </c>
       <c r="L15" s="1">
-        <v>10.3908139883</v>
+        <v>3.9014598262999902</v>
       </c>
       <c r="M15" s="1">
-        <v>4.7319136024999997</v>
+        <v>1.93700037999999E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.56397134309999997</v>
+        <v>0.54875180800000001</v>
       </c>
       <c r="O15" s="1">
-        <v>80.952135558099997</v>
+        <v>20.700766578500001</v>
       </c>
     </row>
   </sheetData>
@@ -2113,43 +2253,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.1720421999999899E-2</v>
+        <v>2.1101384000000001E-2</v>
       </c>
       <c r="D5">
-        <v>7.7920159560000002</v>
+        <v>7.79302745099998</v>
       </c>
       <c r="E5">
-        <v>9.8926041000000201E-2</v>
+        <v>0.100698307</v>
       </c>
       <c r="F5">
-        <v>1.514987834</v>
+        <v>1.5172041649999899</v>
       </c>
       <c r="G5">
-        <v>5.6670711999999998E-2</v>
+        <v>5.5791908000000001E-2</v>
       </c>
       <c r="H5">
-        <v>0.45792223899999901</v>
+        <v>0.45921943500000001</v>
       </c>
       <c r="I5">
-        <v>6.0629683709999904</v>
+        <v>6.0636783699999901</v>
       </c>
       <c r="J5">
-        <v>0.27254366399999902</v>
+        <v>0.27255087899999902</v>
       </c>
       <c r="K5">
-        <v>0.492584572</v>
+        <v>0.49235883599999802</v>
       </c>
       <c r="L5">
-        <v>3.9054659680000001</v>
+        <v>3.9059577489999899</v>
       </c>
       <c r="M5">
-        <v>2.0203208E-2</v>
+        <v>1.94064139999999E-2</v>
       </c>
       <c r="N5">
-        <v>0.64593537300000003</v>
+        <v>0.61528601199999999</v>
       </c>
       <c r="O5">
-        <v>20.713234384</v>
+        <v>20.717549983000001</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2157,43 +2297,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.1932872999999901E-2</v>
+        <v>2.1279628999999901E-2</v>
       </c>
       <c r="D6">
-        <v>7.7932568639999804</v>
+        <v>7.79709311199999</v>
       </c>
       <c r="E6">
-        <v>0.100150211999999</v>
+        <v>0.101755966</v>
       </c>
       <c r="F6">
-        <v>1.5148518119999901</v>
+        <v>1.5162854719999901</v>
       </c>
       <c r="G6">
-        <v>5.6832657999999897E-2</v>
+        <v>5.60827320000001E-2</v>
       </c>
       <c r="H6">
-        <v>0.45801357599999998</v>
+        <v>0.45925363499999999</v>
       </c>
       <c r="I6">
-        <v>6.0620578969999999</v>
+        <v>6.0638862659999901</v>
       </c>
       <c r="J6">
-        <v>0.27391537499999902</v>
+        <v>0.27413057499999899</v>
       </c>
       <c r="K6">
-        <v>0.49292541600000001</v>
+        <v>0.492675635</v>
       </c>
       <c r="L6">
-        <v>3.8996984129999999</v>
+        <v>3.9011064999999898</v>
       </c>
       <c r="M6">
-        <v>2.0393437E-2</v>
+        <v>1.9632154999999998E-2</v>
       </c>
       <c r="N6">
-        <v>0.550244972</v>
+        <v>0.54432430300000001</v>
       </c>
       <c r="O6">
-        <v>20.712029911999998</v>
+        <v>20.719638375999999</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2201,43 +2341,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.1673924000000001E-2</v>
+        <v>2.0974719999999902E-2</v>
       </c>
       <c r="D7">
-        <v>7.78517397500001</v>
+        <v>7.7970552969999902</v>
       </c>
       <c r="E7">
-        <v>9.8263606000000295E-2</v>
+        <v>0.101015059</v>
       </c>
       <c r="F7">
-        <v>1.5145982249999901</v>
+        <v>1.51517175599999</v>
       </c>
       <c r="G7">
-        <v>5.6453717E-2</v>
+        <v>5.5776628000000002E-2</v>
       </c>
       <c r="H7">
-        <v>0.45786797299999998</v>
+        <v>0.45908050299999897</v>
       </c>
       <c r="I7">
-        <v>6.06432882399998</v>
+        <v>6.0662717739999996</v>
       </c>
       <c r="J7">
-        <v>0.272134289999999</v>
+        <v>0.27210804100000002</v>
       </c>
       <c r="K7">
-        <v>0.49234655300000002</v>
+        <v>0.49236375399999999</v>
       </c>
       <c r="L7">
-        <v>3.9066906959999899</v>
+        <v>3.9055599729999999</v>
       </c>
       <c r="M7">
-        <v>2.0032529E-2</v>
+        <v>1.93282919999999E-2</v>
       </c>
       <c r="N7">
-        <v>0.57788008999999996</v>
+        <v>0.54036128100000003</v>
       </c>
       <c r="O7">
-        <v>20.706679097999999</v>
+        <v>20.720896796000002</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2245,43 +2385,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.1524842999999998E-2</v>
+        <v>2.0956139999999901E-2</v>
       </c>
       <c r="D8">
-        <v>7.7903554359999898</v>
+        <v>7.7877697669999897</v>
       </c>
       <c r="E8">
-        <v>9.8635195999999897E-2</v>
+        <v>9.9885357999999896E-2</v>
       </c>
       <c r="F8">
-        <v>1.51497759599999</v>
+        <v>1.51211037499999</v>
       </c>
       <c r="G8">
-        <v>5.6425546999999902E-2</v>
+        <v>5.5762935999999999E-2</v>
       </c>
       <c r="H8">
-        <v>0.45780708199999898</v>
+        <v>0.45854220199999901</v>
       </c>
       <c r="I8">
-        <v>6.06703356199999</v>
+        <v>6.0622401990000103</v>
       </c>
       <c r="J8">
-        <v>0.27221806099999901</v>
+        <v>0.27117142399999999</v>
       </c>
       <c r="K8">
-        <v>0.49258481599999798</v>
+        <v>0.491552883</v>
       </c>
       <c r="L8">
-        <v>3.90604397499999</v>
+        <v>3.8963203659999901</v>
       </c>
       <c r="M8">
-        <v>2.0019353999999899E-2</v>
+        <v>1.9265055E-2</v>
       </c>
       <c r="N8">
-        <v>0.54926370899999999</v>
+        <v>0.550553124</v>
       </c>
       <c r="O8">
-        <v>20.714700707999999</v>
+        <v>20.691628844</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2289,43 +2429,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.1505045999999899E-2</v>
+        <v>2.0884650000000001E-2</v>
       </c>
       <c r="D9">
-        <v>7.79237521900001</v>
+        <v>7.7794520330000099</v>
       </c>
       <c r="E9">
-        <v>9.8110879999999998E-2</v>
+        <v>0.10029113200000001</v>
       </c>
       <c r="F9">
-        <v>1.514759403</v>
+        <v>1.5121290780000001</v>
       </c>
       <c r="G9">
-        <v>5.6454982000000001E-2</v>
+        <v>5.5753456999999999E-2</v>
       </c>
       <c r="H9">
-        <v>0.45782401499999897</v>
+        <v>0.45871501999999897</v>
       </c>
       <c r="I9">
-        <v>6.0658227059999996</v>
+        <v>6.0606006370000101</v>
       </c>
       <c r="J9">
-        <v>0.27235633199999898</v>
+        <v>0.27122294399999902</v>
       </c>
       <c r="K9">
-        <v>0.492267179</v>
+        <v>0.49128346099999998</v>
       </c>
       <c r="L9">
-        <v>3.9025007180000002</v>
+        <v>3.9011952289999901</v>
       </c>
       <c r="M9">
-        <v>2.0040321E-2</v>
+        <v>1.9221643999999899E-2</v>
       </c>
       <c r="N9">
-        <v>0.54740489599999997</v>
+        <v>0.54035476100000002</v>
       </c>
       <c r="O9">
-        <v>20.711233804999999</v>
+        <v>20.686977975000001</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2333,43 +2473,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.1446732999999999E-2</v>
+        <v>2.0807343999999901E-2</v>
       </c>
       <c r="D10">
-        <v>7.79217742799998</v>
+        <v>7.7878391180000097</v>
       </c>
       <c r="E10">
-        <v>9.8305396999999906E-2</v>
+        <v>9.9926715000000096E-2</v>
       </c>
       <c r="F10">
-        <v>1.51437720799999</v>
+        <v>1.5117757669999901</v>
       </c>
       <c r="G10">
-        <v>5.6399120000000101E-2</v>
+        <v>5.5649369999999997E-2</v>
       </c>
       <c r="H10">
-        <v>0.45764157999999899</v>
+        <v>0.45859571700000001</v>
       </c>
       <c r="I10">
-        <v>6.0663063140000002</v>
+        <v>6.0603357109999996</v>
       </c>
       <c r="J10">
-        <v>0.27173915100000001</v>
+        <v>0.27112144100000002</v>
       </c>
       <c r="K10">
-        <v>0.49202296899999898</v>
+        <v>0.49142884599999898</v>
       </c>
       <c r="L10">
-        <v>3.9073114050000002</v>
+        <v>3.9000256759999998</v>
       </c>
       <c r="M10">
-        <v>1.9971797999999999E-2</v>
+        <v>1.9312329999999999E-2</v>
       </c>
       <c r="N10">
-        <v>0.54614090900000001</v>
+        <v>0.53915951100000004</v>
       </c>
       <c r="O10">
-        <v>20.714789747000001</v>
+        <v>20.692864118999999</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2377,43 +2517,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.1616896999999899E-2</v>
+        <v>2.1106718999999899E-2</v>
       </c>
       <c r="D11">
-        <v>7.7921428089999898</v>
+        <v>7.7843844669999802</v>
       </c>
       <c r="E11">
-        <v>9.9132750000000006E-2</v>
+        <v>0.100622691</v>
       </c>
       <c r="F11">
-        <v>1.5150120439999899</v>
+        <v>1.51220974199999</v>
       </c>
       <c r="G11">
-        <v>5.6688913E-2</v>
+        <v>5.5990173999999997E-2</v>
       </c>
       <c r="H11">
-        <v>0.45803382599999998</v>
+        <v>0.458783633999999</v>
       </c>
       <c r="I11">
-        <v>6.0665790959999804</v>
+        <v>6.0625688519999903</v>
       </c>
       <c r="J11">
-        <v>0.27280712099999999</v>
+        <v>0.271670675999999</v>
       </c>
       <c r="K11">
-        <v>0.49276028799999899</v>
+        <v>0.49157911700000001</v>
       </c>
       <c r="L11">
-        <v>3.9066536109999901</v>
+        <v>3.89965502799999</v>
       </c>
       <c r="M11">
-        <v>2.0168087000000001E-2</v>
+        <v>1.9355522999999899E-2</v>
       </c>
       <c r="N11">
-        <v>0.54705949499999995</v>
+        <v>0.53928374499999998</v>
       </c>
       <c r="O11">
-        <v>20.718696206000001</v>
+        <v>20.694036471</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2421,43 +2561,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.1699502999999998E-2</v>
+        <v>2.1055265999999899E-2</v>
       </c>
       <c r="D12">
-        <v>7.7960570239999702</v>
+        <v>7.7870121919999997</v>
       </c>
       <c r="E12">
-        <v>9.8950826000000006E-2</v>
+        <v>0.10130739499999999</v>
       </c>
       <c r="F12">
-        <v>1.5138778100000001</v>
+        <v>1.51215378999999</v>
       </c>
       <c r="G12">
-        <v>5.6606003000000002E-2</v>
+        <v>5.5870721999999901E-2</v>
       </c>
       <c r="H12">
-        <v>0.45791276199999997</v>
+        <v>0.45870782199999999</v>
       </c>
       <c r="I12">
-        <v>6.0653505989999896</v>
+        <v>6.0600565519999998</v>
       </c>
       <c r="J12">
-        <v>0.27221119799999999</v>
+        <v>0.272015848</v>
       </c>
       <c r="K12">
-        <v>0.49230500999999999</v>
+        <v>0.491494870999999</v>
       </c>
       <c r="L12">
-        <v>3.9038788939999902</v>
+        <v>3.902312512</v>
       </c>
       <c r="M12">
-        <v>2.0186594999999901E-2</v>
+        <v>1.9278192999999999E-2</v>
       </c>
       <c r="N12">
-        <v>0.54342701900000001</v>
+        <v>0.53867469499999998</v>
       </c>
       <c r="O12">
-        <v>20.716681764</v>
+        <v>20.697453193000001</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2465,43 +2605,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.17129459999999E-2</v>
+        <v>2.1009811999999999E-2</v>
       </c>
       <c r="D13">
-        <v>7.78897069599999</v>
+        <v>7.78079164399999</v>
       </c>
       <c r="E13">
-        <v>9.8518339000000094E-2</v>
+        <v>0.101113538999999</v>
       </c>
       <c r="F13">
-        <v>1.51190811199999</v>
+        <v>1.5124974799999999</v>
       </c>
       <c r="G13">
-        <v>5.6603623999999998E-2</v>
+        <v>5.5813125999999998E-2</v>
       </c>
       <c r="H13">
-        <v>0.45760492600000002</v>
+        <v>0.45869143800000001</v>
       </c>
       <c r="I13">
-        <v>6.0605655199999902</v>
+        <v>6.0603539730000104</v>
       </c>
       <c r="J13">
-        <v>0.27217079099999902</v>
+        <v>0.27183335199999897</v>
       </c>
       <c r="K13">
-        <v>0.49201673399999901</v>
+        <v>0.491635667</v>
       </c>
       <c r="L13">
-        <v>3.8966925989999899</v>
+        <v>3.900215749</v>
       </c>
       <c r="M13">
-        <v>2.0140801E-2</v>
+        <v>1.9421697000000002E-2</v>
       </c>
       <c r="N13">
-        <v>0.54602609599999996</v>
+        <v>0.53861486400000003</v>
       </c>
       <c r="O13">
-        <v>20.694066958000001</v>
+        <v>20.689566696</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2509,43 +2649,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.1838885999999901E-2</v>
+        <v>2.1267149999999999E-2</v>
       </c>
       <c r="D14">
-        <v>7.7851553749999898</v>
+        <v>7.78856586200002</v>
       </c>
       <c r="E14">
-        <v>9.9621060999999997E-2</v>
+        <v>0.101402716</v>
       </c>
       <c r="F14">
-        <v>1.5120986300000001</v>
+        <v>1.5126722690000001</v>
       </c>
       <c r="G14">
-        <v>5.6726833000000101E-2</v>
+        <v>5.60558099999999E-2</v>
       </c>
       <c r="H14">
-        <v>0.458101534999999</v>
+        <v>0.45901620999999998</v>
       </c>
       <c r="I14">
-        <v>6.0625183060000003</v>
+        <v>6.0629085410000103</v>
       </c>
       <c r="J14">
-        <v>0.272697946999999</v>
+        <v>0.272708176999999</v>
       </c>
       <c r="K14">
-        <v>0.49205622700000001</v>
+        <v>0.49192058099999902</v>
       </c>
       <c r="L14">
-        <v>3.9075642240000001</v>
+        <v>3.8957304859999899</v>
       </c>
       <c r="M14">
-        <v>2.0250283000000001E-2</v>
+        <v>1.9526368999999998E-2</v>
       </c>
       <c r="N14">
-        <v>0.54671930899999999</v>
+        <v>0.54182851099999996</v>
       </c>
       <c r="O14">
-        <v>20.705938906</v>
+        <v>20.698456970999999</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2553,43 +2693,43 @@
         <v>22</v>
       </c>
       <c r="C15" s="1">
-        <v>2.1667207299999901E-2</v>
+        <v>2.1044281399999899E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>7.7907680781999904</v>
+        <v>7.7882990942999903</v>
       </c>
       <c r="E15" s="1">
-        <v>9.8861430799999997E-2</v>
+        <v>0.1008018878</v>
       </c>
       <c r="F15" s="1">
-        <v>1.51414486739999</v>
+        <v>1.5134209893999899</v>
       </c>
       <c r="G15" s="1">
-        <v>5.6586210900000003E-2</v>
+        <v>5.5854686299999998E-2</v>
       </c>
       <c r="H15" s="1">
-        <v>0.45787295140000001</v>
+        <v>0.45886056159999999</v>
       </c>
       <c r="I15" s="1">
-        <v>6.06435311949999</v>
+        <v>6.0622900875000001</v>
       </c>
       <c r="J15" s="1">
-        <v>0.27247939299999901</v>
+        <v>0.27205333569999901</v>
       </c>
       <c r="K15" s="1">
-        <v>0.49238697640000001</v>
+        <v>0.49182936509999903</v>
       </c>
       <c r="L15" s="1">
-        <v>3.9042500502999902</v>
+        <v>3.9008079268000002</v>
       </c>
       <c r="M15" s="1">
-        <v>2.0140641300000001E-2</v>
+        <v>1.93747672E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.56001018679999903</v>
+        <v>0.54884408070000001</v>
       </c>
       <c r="O15" s="1">
-        <v>20.710805148799999</v>
+        <v>20.7009069424</v>
       </c>
     </row>
   </sheetData>
@@ -2687,43 +2827,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.0424912999999999E-2</v>
+        <v>2.1066069999999999E-2</v>
       </c>
       <c r="D5">
-        <v>7.7867697349999903</v>
+        <v>7.7994737460000003</v>
       </c>
       <c r="E5">
-        <v>9.1322597999999894E-2</v>
+        <v>0.101644125</v>
       </c>
       <c r="F5">
-        <v>1.5043494099999899</v>
+        <v>1.5162155929999901</v>
       </c>
       <c r="G5">
-        <v>5.7297887999999901E-2</v>
+        <v>5.5874482000000003E-2</v>
       </c>
       <c r="H5">
-        <v>8.0126062999999803E-2</v>
+        <v>0.45912639099999902</v>
       </c>
       <c r="I5">
-        <v>0.14635807000000001</v>
+        <v>6.0657522789999998</v>
       </c>
       <c r="J5">
-        <v>0.22410363699999999</v>
+        <v>0.27239945999999998</v>
       </c>
       <c r="K5">
-        <v>0.145887511</v>
+        <v>0.49202833999999901</v>
       </c>
       <c r="L5">
-        <v>1.5135437140000001</v>
+        <v>3.9017833849999999</v>
       </c>
       <c r="M5">
-        <v>1.9270493999999899E-2</v>
+        <v>1.9374984000000001E-2</v>
       </c>
       <c r="N5">
-        <v>0.63718657899999998</v>
+        <v>0.616310998</v>
       </c>
       <c r="O5">
-        <v>11.605081670000001</v>
+        <v>20.72091713</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2731,43 +2871,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.1145951E-2</v>
+        <v>2.2013108999999999E-2</v>
       </c>
       <c r="D6">
-        <v>7.7860681689999902</v>
+        <v>7.8010432889999999</v>
       </c>
       <c r="E6">
-        <v>9.1019702999999993E-2</v>
+        <v>0.101714957999999</v>
       </c>
       <c r="F6">
-        <v>1.504760248</v>
+        <v>1.51559118599999</v>
       </c>
       <c r="G6">
-        <v>5.8056615999999998E-2</v>
+        <v>5.6949554999999999E-2</v>
       </c>
       <c r="H6">
-        <v>7.9142330999999899E-2</v>
+        <v>0.45848459899999999</v>
       </c>
       <c r="I6">
-        <v>0.14721379100000001</v>
+        <v>6.0653772449999996</v>
       </c>
       <c r="J6">
-        <v>0.22464350599999999</v>
+        <v>0.27441423099999901</v>
       </c>
       <c r="K6">
-        <v>0.14654013999999899</v>
+        <v>0.493028518999999</v>
       </c>
       <c r="L6">
-        <v>1.5158264749999999</v>
+        <v>3.8995791579999901</v>
       </c>
       <c r="M6">
-        <v>2.0120513999999999E-2</v>
+        <v>2.0546848E-2</v>
       </c>
       <c r="N6">
-        <v>0.58061084600000001</v>
+        <v>0.55257705899999998</v>
       </c>
       <c r="O6">
-        <v>11.611603560000001</v>
+        <v>20.726886456999999</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2775,43 +2915,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.0321663E-2</v>
+        <v>2.1102395999999898E-2</v>
       </c>
       <c r="D7">
-        <v>7.7858370370000003</v>
+        <v>7.7918346869999997</v>
       </c>
       <c r="E7">
-        <v>9.1435814000000198E-2</v>
+        <v>0.101059461</v>
       </c>
       <c r="F7">
-        <v>1.50463510299999</v>
+        <v>1.513774784</v>
       </c>
       <c r="G7">
-        <v>5.7139267999999903E-2</v>
+        <v>5.5743058999999998E-2</v>
       </c>
       <c r="H7">
-        <v>8.0468895999999998E-2</v>
+        <v>0.45918726999999998</v>
       </c>
       <c r="I7">
-        <v>0.146477828</v>
+        <v>6.0655896979999904</v>
       </c>
       <c r="J7">
-        <v>0.22378975800000001</v>
+        <v>0.27184363299999997</v>
       </c>
       <c r="K7">
-        <v>0.14580547599999999</v>
+        <v>0.49198598100000002</v>
       </c>
       <c r="L7">
-        <v>1.5118537869999999</v>
+        <v>3.9020698170000001</v>
       </c>
       <c r="M7">
-        <v>1.9273346999999899E-2</v>
+        <v>1.9253632999999899E-2</v>
       </c>
       <c r="N7">
-        <v>0.56270112800000005</v>
+        <v>0.54308842300000004</v>
       </c>
       <c r="O7">
-        <v>11.603158564999999</v>
+        <v>20.709690736999999</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2819,43 +2959,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.0864639000000001E-2</v>
+        <v>2.0968386999999901E-2</v>
       </c>
       <c r="D8">
-        <v>7.791942186</v>
+        <v>7.7860453190000101</v>
       </c>
       <c r="E8">
-        <v>9.3432404999999899E-2</v>
+        <v>0.100349826</v>
       </c>
       <c r="F8">
-        <v>1.5056955270000001</v>
+        <v>1.512698646</v>
       </c>
       <c r="G8">
-        <v>5.7837718999999899E-2</v>
+        <v>5.5743950000000098E-2</v>
       </c>
       <c r="H8">
-        <v>8.0883411999999794E-2</v>
+        <v>0.45916385300000001</v>
       </c>
       <c r="I8">
-        <v>0.14729577499999999</v>
+        <v>6.0618285339999902</v>
       </c>
       <c r="J8">
-        <v>0.22659679099999999</v>
+        <v>0.27276218800000002</v>
       </c>
       <c r="K8">
-        <v>0.14671094299999901</v>
+        <v>0.49155756699999997</v>
       </c>
       <c r="L8">
-        <v>1.5164940629999999</v>
+        <v>3.8938646370000001</v>
       </c>
       <c r="M8">
-        <v>1.9708712999999999E-2</v>
+        <v>1.9304002000000001E-2</v>
       </c>
       <c r="N8">
-        <v>0.56443909199999998</v>
+        <v>0.54494798700000002</v>
       </c>
       <c r="O8">
-        <v>11.62344429</v>
+        <v>20.690456955999998</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2863,43 +3003,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.0280942999999899E-2</v>
+        <v>2.0973215999999899E-2</v>
       </c>
       <c r="D9">
-        <v>7.7999430569999904</v>
+        <v>7.7813027589999901</v>
       </c>
       <c r="E9">
-        <v>9.0877374999999802E-2</v>
+        <v>0.101126643</v>
       </c>
       <c r="F9">
-        <v>1.50655010599999</v>
+        <v>1.5121788599999899</v>
       </c>
       <c r="G9">
-        <v>5.7248313999999897E-2</v>
+        <v>5.5740315999999998E-2</v>
       </c>
       <c r="H9">
-        <v>8.0485838000000101E-2</v>
+        <v>0.45859746899999898</v>
       </c>
       <c r="I9">
-        <v>0.14656117699999999</v>
+        <v>6.0613853170000001</v>
       </c>
       <c r="J9">
-        <v>0.22409077799999999</v>
+        <v>0.27138312999999897</v>
       </c>
       <c r="K9">
-        <v>0.14573356700000001</v>
+        <v>0.49132802600000097</v>
       </c>
       <c r="L9">
-        <v>1.51249728199999</v>
+        <v>3.9025352089999998</v>
       </c>
       <c r="M9">
-        <v>1.9202230000000001E-2</v>
+        <v>1.9322946999999899E-2</v>
       </c>
       <c r="N9">
-        <v>0.562185775</v>
+        <v>0.53796646000000004</v>
       </c>
       <c r="O9">
-        <v>11.619479439999999</v>
+        <v>20.692053219000002</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2907,43 +3047,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.043876E-2</v>
+        <v>2.095733E-2</v>
       </c>
       <c r="D10">
-        <v>7.7974293039999996</v>
+        <v>7.7859232969999903</v>
       </c>
       <c r="E10">
-        <v>9.1080436999999903E-2</v>
+        <v>0.101294805</v>
       </c>
       <c r="F10">
-        <v>1.5064454389999899</v>
+        <v>1.51144327999999</v>
       </c>
       <c r="G10">
-        <v>5.7185278999999797E-2</v>
+        <v>5.5792281000000103E-2</v>
       </c>
       <c r="H10">
-        <v>8.0402278999999993E-2</v>
+        <v>0.45866275299999898</v>
       </c>
       <c r="I10">
-        <v>0.14645081199999899</v>
+        <v>6.0614671599999896</v>
       </c>
       <c r="J10">
-        <v>0.22453524499999999</v>
+        <v>0.27114375799999901</v>
       </c>
       <c r="K10">
-        <v>0.145886615999999</v>
+        <v>0.491510909</v>
       </c>
       <c r="L10">
-        <v>1.511602659</v>
+        <v>3.9005954509999898</v>
       </c>
       <c r="M10">
-        <v>1.9318756999999999E-2</v>
+        <v>1.9233350999999999E-2</v>
       </c>
       <c r="N10">
-        <v>0.57984765400000005</v>
+        <v>0.54721948499999995</v>
       </c>
       <c r="O10">
-        <v>11.616513956</v>
+        <v>20.694206857000001</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2951,43 +3091,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.0353184E-2</v>
+        <v>2.10826109999999E-2</v>
       </c>
       <c r="D11">
-        <v>7.7924300309999897</v>
+        <v>7.7838895780000099</v>
       </c>
       <c r="E11">
-        <v>9.0809097000000102E-2</v>
+        <v>0.10192346100000001</v>
       </c>
       <c r="F11">
-        <v>1.5053146959999999</v>
+        <v>1.512189867</v>
       </c>
       <c r="G11">
-        <v>5.7189707999999902E-2</v>
+        <v>5.5874761000000002E-2</v>
       </c>
       <c r="H11">
-        <v>8.0279349E-2</v>
+        <v>0.45884820900000001</v>
       </c>
       <c r="I11">
-        <v>0.146382653999999</v>
+        <v>6.0617735640000001</v>
       </c>
       <c r="J11">
-        <v>0.22355650699999999</v>
+        <v>0.271952155999999</v>
       </c>
       <c r="K11">
-        <v>0.14538958199999999</v>
+        <v>0.49183482699999898</v>
       </c>
       <c r="L11">
-        <v>1.513626312</v>
+        <v>3.8974218359999999</v>
       </c>
       <c r="M11">
-        <v>1.9171847999999901E-2</v>
+        <v>1.9351515E-2</v>
       </c>
       <c r="N11">
-        <v>0.560336846</v>
+        <v>0.53907629400000001</v>
       </c>
       <c r="O11">
-        <v>11.610014887</v>
+        <v>20.692990059</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2995,43 +3135,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.0289628999999899E-2</v>
+        <v>2.1112009000000001E-2</v>
       </c>
       <c r="D12">
-        <v>7.7860702429999904</v>
+        <v>7.7827500570000003</v>
       </c>
       <c r="E12">
-        <v>9.1088189E-2</v>
+        <v>0.101276436</v>
       </c>
       <c r="F12">
-        <v>1.5032416559999899</v>
+        <v>1.511931492</v>
       </c>
       <c r="G12">
-        <v>5.7050234999999901E-2</v>
+        <v>5.5863916999999999E-2</v>
       </c>
       <c r="H12">
-        <v>8.02704679999999E-2</v>
+        <v>0.45887003999999998</v>
       </c>
       <c r="I12">
-        <v>0.14590045199999899</v>
+        <v>6.0604057690000097</v>
       </c>
       <c r="J12">
-        <v>0.223113902999999</v>
+        <v>0.27196870099999998</v>
       </c>
       <c r="K12">
-        <v>0.14498377500000001</v>
+        <v>0.491854862</v>
       </c>
       <c r="L12">
-        <v>1.51002137499999</v>
+        <v>3.9037895489999901</v>
       </c>
       <c r="M12">
-        <v>1.9153499000000001E-2</v>
+        <v>1.9461340000000001E-2</v>
       </c>
       <c r="N12">
-        <v>0.56179270699999995</v>
+        <v>0.54147638300000001</v>
       </c>
       <c r="O12">
-        <v>11.596820626</v>
+        <v>20.695688261000001</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -3039,43 +3179,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.03218539999999E-2</v>
+        <v>2.1062636999999901E-2</v>
       </c>
       <c r="D13">
-        <v>7.7836237120000096</v>
+        <v>7.7881428579999898</v>
       </c>
       <c r="E13">
-        <v>9.1111495999999903E-2</v>
+        <v>0.10146572199999999</v>
       </c>
       <c r="F13">
-        <v>1.5051262249999999</v>
+        <v>1.5128203149999899</v>
       </c>
       <c r="G13">
-        <v>5.7253967999999898E-2</v>
+        <v>5.5973003999999903E-2</v>
       </c>
       <c r="H13">
-        <v>8.0286094000000099E-2</v>
+        <v>0.45890385499999897</v>
       </c>
       <c r="I13">
-        <v>0.145972402</v>
+        <v>6.0601249340000001</v>
       </c>
       <c r="J13">
-        <v>0.22355931900000001</v>
+        <v>0.27200566399999998</v>
       </c>
       <c r="K13">
-        <v>0.145110973999999</v>
+        <v>0.49187511699999997</v>
       </c>
       <c r="L13">
-        <v>1.511406241</v>
+        <v>3.89971205599999</v>
       </c>
       <c r="M13">
-        <v>1.9221361999999999E-2</v>
+        <v>1.9399731E-2</v>
       </c>
       <c r="N13">
-        <v>0.58119497399999998</v>
+        <v>0.53865003</v>
       </c>
       <c r="O13">
-        <v>11.598596659</v>
+        <v>20.697728300000001</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -3083,43 +3223,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.04681699999999E-2</v>
+        <v>2.1142463E-2</v>
       </c>
       <c r="D14">
-        <v>7.786542131</v>
+        <v>7.7880382399999997</v>
       </c>
       <c r="E14">
-        <v>9.1743652999999897E-2</v>
+        <v>0.101517158</v>
       </c>
       <c r="F14">
-        <v>1.5035087389999899</v>
+        <v>1.512929634</v>
       </c>
       <c r="G14">
-        <v>5.8824202999999797E-2</v>
+        <v>5.6057263999999898E-2</v>
       </c>
       <c r="H14">
-        <v>8.0324217000000003E-2</v>
+        <v>0.458944827000001</v>
       </c>
       <c r="I14">
-        <v>0.14618890900000001</v>
+        <v>6.0638440610000002</v>
       </c>
       <c r="J14">
-        <v>0.22449387100000001</v>
+        <v>0.27262192800000001</v>
       </c>
       <c r="K14">
-        <v>0.145478408</v>
+        <v>0.491883189</v>
       </c>
       <c r="L14">
-        <v>1.510194391</v>
+        <v>3.895199383</v>
       </c>
       <c r="M14">
-        <v>1.9469330999999999E-2</v>
+        <v>1.947805E-2</v>
       </c>
       <c r="N14">
-        <v>0.55871432300000001</v>
+        <v>0.54294027499999997</v>
       </c>
       <c r="O14">
-        <v>11.602967883</v>
+        <v>20.697993238999999</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -3127,43 +3267,43 @@
         <v>21</v>
       </c>
       <c r="C15" s="1">
-        <v>2.0490970599999998E-2</v>
+        <v>2.1148022799999899E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>7.7896655604999996</v>
+        <v>7.7888443829999998</v>
       </c>
       <c r="E15" s="1">
-        <v>9.1392076700000005E-2</v>
+        <v>0.1013372595</v>
       </c>
       <c r="F15" s="1">
-        <v>1.50496271489999</v>
+        <v>1.5131773657000001</v>
       </c>
       <c r="G15" s="1">
-        <v>5.7508319799999902E-2</v>
+        <v>5.5961258899999998E-2</v>
       </c>
       <c r="H15" s="1">
-        <v>8.0266894699999994E-2</v>
+        <v>0.45887892660000001</v>
       </c>
       <c r="I15" s="1">
-        <v>0.14648018700000001</v>
+        <v>6.0627548560999998</v>
       </c>
       <c r="J15" s="1">
-        <v>0.22424833150000001</v>
+        <v>0.27224948490000001</v>
       </c>
       <c r="K15" s="1">
-        <v>0.1457526992</v>
+        <v>0.49188873370000002</v>
       </c>
       <c r="L15" s="1">
-        <v>1.5127066299</v>
+        <v>3.8996550481000001</v>
       </c>
       <c r="M15" s="1">
-        <v>1.93910095E-2</v>
+        <v>1.9472640100000001E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.57490099240000003</v>
+        <v>0.55042533940000005</v>
       </c>
       <c r="O15" s="1">
-        <v>11.6087681536</v>
+        <v>20.701861121499999</v>
       </c>
     </row>
   </sheetData>
@@ -3261,43 +3401,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.1670388999999901E-2</v>
+        <v>2.1042589E-2</v>
       </c>
       <c r="D5">
-        <v>7.788605767</v>
+        <v>7.7889424449999902</v>
       </c>
       <c r="E5">
-        <v>9.9566999999999795E-2</v>
+        <v>0.100951946999999</v>
       </c>
       <c r="F5">
-        <v>1.51476287599999</v>
+        <v>1.5158345339999999</v>
       </c>
       <c r="G5">
-        <v>5.6594470000000001E-2</v>
+        <v>5.5972837000000199E-2</v>
       </c>
       <c r="H5">
-        <v>0.45763494700000001</v>
+        <v>0.45902342800000101</v>
       </c>
       <c r="I5">
-        <v>6.0642653989999999</v>
+        <v>6.0615342429999997</v>
       </c>
       <c r="J5">
-        <v>0.27255439599999898</v>
+        <v>0.27380757500000003</v>
       </c>
       <c r="K5">
-        <v>0.49231615699999998</v>
+        <v>0.49236302999999798</v>
       </c>
       <c r="L5">
-        <v>3.9079429750000001</v>
+        <v>3.9015166990000001</v>
       </c>
       <c r="M5">
-        <v>2.0160246999999999E-2</v>
+        <v>1.9348687999999899E-2</v>
       </c>
       <c r="N5">
-        <v>0.62630026999999999</v>
+        <v>0.61524506599999995</v>
       </c>
       <c r="O5">
-        <v>20.713497519000001</v>
+        <v>20.706959798</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -3305,43 +3445,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.19130099999999E-2</v>
+        <v>2.1353419999999901E-2</v>
       </c>
       <c r="D6">
-        <v>7.79280851900001</v>
+        <v>7.79279711299999</v>
       </c>
       <c r="E6">
-        <v>9.9675741000000095E-2</v>
+        <v>0.101451716999999</v>
       </c>
       <c r="F6">
-        <v>1.514690286</v>
+        <v>1.5155008459999999</v>
       </c>
       <c r="G6">
-        <v>5.6976826000000001E-2</v>
+        <v>5.6154192000000103E-2</v>
       </c>
       <c r="H6">
-        <v>0.45819648799999901</v>
+        <v>0.45903085100000002</v>
       </c>
       <c r="I6">
-        <v>6.0626823300000003</v>
+        <v>6.0616481880000004</v>
       </c>
       <c r="J6">
-        <v>0.274515538</v>
+        <v>0.27378674200000003</v>
       </c>
       <c r="K6">
-        <v>0.49315212899999999</v>
+        <v>0.492847905999999</v>
       </c>
       <c r="L6">
-        <v>3.900064135</v>
+        <v>3.8941756330000001</v>
       </c>
       <c r="M6">
-        <v>2.0464525000000001E-2</v>
+        <v>1.9657917999999899E-2</v>
       </c>
       <c r="N6">
-        <v>0.54645062600000005</v>
+        <v>0.54726605800000006</v>
       </c>
       <c r="O6">
-        <v>20.712612427</v>
+        <v>20.704733495999999</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -3349,43 +3489,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.1715781E-2</v>
+        <v>2.0981407000000001E-2</v>
       </c>
       <c r="D7">
-        <v>7.78769075099998</v>
+        <v>7.7878332510000199</v>
       </c>
       <c r="E7">
-        <v>9.8289989999999897E-2</v>
+        <v>0.10093611299999999</v>
       </c>
       <c r="F7">
-        <v>1.51437557399999</v>
+        <v>1.515356916</v>
       </c>
       <c r="G7">
-        <v>5.6514841000000003E-2</v>
+        <v>5.5867665999999899E-2</v>
       </c>
       <c r="H7">
-        <v>0.45803918399999999</v>
+        <v>0.45886558199999899</v>
       </c>
       <c r="I7">
-        <v>6.0630073089999899</v>
+        <v>6.0629193100000096</v>
       </c>
       <c r="J7">
-        <v>0.27229793999999902</v>
+        <v>0.272240977</v>
       </c>
       <c r="K7">
-        <v>0.49229077099999902</v>
+        <v>0.49222443199999999</v>
       </c>
       <c r="L7">
-        <v>3.9083897669999899</v>
+        <v>3.8956862029999999</v>
       </c>
       <c r="M7">
-        <v>2.0096164E-2</v>
+        <v>1.9402821000000001E-2</v>
       </c>
       <c r="N7">
-        <v>0.54734508500000001</v>
+        <v>0.55455117300000001</v>
       </c>
       <c r="O7">
-        <v>20.709862891</v>
+        <v>20.698519548</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -3393,43 +3533,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.1558777000000001E-2</v>
+        <v>2.0956864999999901E-2</v>
       </c>
       <c r="D8">
-        <v>7.7885421700000004</v>
+        <v>7.7949866609999896</v>
       </c>
       <c r="E8">
-        <v>9.7385553000000097E-2</v>
+        <v>0.101300022</v>
       </c>
       <c r="F8">
-        <v>1.5140554819999901</v>
+        <v>1.51590531099999</v>
       </c>
       <c r="G8">
-        <v>5.6435298999999897E-2</v>
+        <v>5.5848188000000097E-2</v>
       </c>
       <c r="H8">
-        <v>0.45793884199999901</v>
+        <v>0.458857927</v>
       </c>
       <c r="I8">
-        <v>6.064377371</v>
+        <v>6.0650248729999898</v>
       </c>
       <c r="J8">
-        <v>0.27229752899999998</v>
+        <v>0.271976990999999</v>
       </c>
       <c r="K8">
-        <v>0.492120908999999</v>
+        <v>0.49213513599999997</v>
       </c>
       <c r="L8">
-        <v>3.9084012960000001</v>
+        <v>3.8964746520000002</v>
       </c>
       <c r="M8">
-        <v>1.9987675999999999E-2</v>
+        <v>1.9164344999999899E-2</v>
       </c>
       <c r="N8">
-        <v>0.55720628400000005</v>
+        <v>0.548205426</v>
       </c>
       <c r="O8">
-        <v>20.710153963</v>
+        <v>20.708969687</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -3437,43 +3577,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.1566398000000001E-2</v>
+        <v>2.0996747E-2</v>
       </c>
       <c r="D9">
-        <v>7.7886827629999997</v>
+        <v>7.7998079390000097</v>
       </c>
       <c r="E9">
-        <v>9.7693707000000005E-2</v>
+        <v>0.10090756400000001</v>
       </c>
       <c r="F9">
-        <v>1.5148509079999899</v>
+        <v>1.5161694799999901</v>
       </c>
       <c r="G9">
-        <v>5.6489028999999899E-2</v>
+        <v>5.5789725999999998E-2</v>
       </c>
       <c r="H9">
-        <v>0.45799976599999997</v>
+        <v>0.45893492999999902</v>
       </c>
       <c r="I9">
-        <v>6.0669434850000004</v>
+        <v>6.0662951339999998</v>
       </c>
       <c r="J9">
-        <v>0.27245112300000002</v>
+        <v>0.27210715099999999</v>
       </c>
       <c r="K9">
-        <v>0.49225550400000001</v>
+        <v>0.49207820800000002</v>
       </c>
       <c r="L9">
-        <v>3.9067603819999901</v>
+        <v>3.8898433239999899</v>
       </c>
       <c r="M9">
-        <v>2.00978629999999E-2</v>
+        <v>1.9294316999999998E-2</v>
       </c>
       <c r="N9">
-        <v>0.54859861300000001</v>
+        <v>0.55612084299999998</v>
       </c>
       <c r="O9">
-        <v>20.713437281000001</v>
+        <v>20.708475618000001</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -3481,43 +3621,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.1632118999999901E-2</v>
+        <v>2.0857225999999899E-2</v>
       </c>
       <c r="D10">
-        <v>7.7915927429999901</v>
+        <v>7.7925777399999898</v>
       </c>
       <c r="E10">
-        <v>9.7113913000000093E-2</v>
+        <v>0.100856243</v>
       </c>
       <c r="F10">
-        <v>1.51434344799999</v>
+        <v>1.5150176310000001</v>
       </c>
       <c r="G10">
-        <v>5.64154830000001E-2</v>
+        <v>5.5715932000000003E-2</v>
       </c>
       <c r="H10">
-        <v>0.45765355000000002</v>
+        <v>0.45881665199999999</v>
       </c>
       <c r="I10">
-        <v>6.0666592069999998</v>
+        <v>6.0656675150000003</v>
       </c>
       <c r="J10">
-        <v>0.271916721999999</v>
+        <v>0.271613084</v>
       </c>
       <c r="K10">
-        <v>0.493578724999999</v>
+        <v>0.492251412</v>
       </c>
       <c r="L10">
-        <v>3.90671174799999</v>
+        <v>3.9026557720000001</v>
       </c>
       <c r="M10">
-        <v>2.0044738999999999E-2</v>
+        <v>1.91470919999999E-2</v>
       </c>
       <c r="N10">
-        <v>0.54808315500000004</v>
+        <v>0.54054987300000001</v>
       </c>
       <c r="O10">
-        <v>20.715232767</v>
+        <v>20.71121874</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -3525,43 +3665,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.1658759999999899E-2</v>
+        <v>2.1145300999999901E-2</v>
       </c>
       <c r="D11">
-        <v>7.7947981879999997</v>
+        <v>7.7946861409999801</v>
       </c>
       <c r="E11">
-        <v>9.8980616000000105E-2</v>
+        <v>0.10150352999999999</v>
       </c>
       <c r="F11">
-        <v>1.5148128999999999</v>
+        <v>1.5156918319999999</v>
       </c>
       <c r="G11">
-        <v>5.6672052000000001E-2</v>
+        <v>5.5788429E-2</v>
       </c>
       <c r="H11">
-        <v>0.457924215999999</v>
+        <v>0.45897850600000001</v>
       </c>
       <c r="I11">
-        <v>6.0668586840000103</v>
+        <v>6.0672738399999897</v>
       </c>
       <c r="J11">
-        <v>0.272893575</v>
+        <v>0.27248283299999998</v>
       </c>
       <c r="K11">
-        <v>0.492327072999999</v>
+        <v>0.49234507700000002</v>
       </c>
       <c r="L11">
-        <v>3.9048722989999902</v>
+        <v>3.90366275199999</v>
       </c>
       <c r="M11">
-        <v>2.0216452999999999E-2</v>
+        <v>1.94385929999999E-2</v>
       </c>
       <c r="N11">
-        <v>0.54761473100000002</v>
+        <v>0.54143225800000006</v>
       </c>
       <c r="O11">
-        <v>20.719440948999999</v>
+        <v>20.719628178000001</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -3569,43 +3709,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.1639038999999999E-2</v>
+        <v>2.1019667999999998E-2</v>
       </c>
       <c r="D12">
-        <v>7.7899716459999997</v>
+        <v>7.7841760030000096</v>
       </c>
       <c r="E12">
-        <v>9.8083506999999903E-2</v>
+        <v>0.101018384</v>
       </c>
       <c r="F12">
-        <v>1.5127594169999901</v>
+        <v>1.5131399320000001</v>
       </c>
       <c r="G12">
-        <v>5.6608270000000002E-2</v>
+        <v>5.5908588000000099E-2</v>
       </c>
       <c r="H12">
-        <v>0.45777858199999899</v>
+        <v>0.45871410000000001</v>
       </c>
       <c r="I12">
-        <v>6.0622548540000096</v>
+        <v>6.0621998450000003</v>
       </c>
       <c r="J12">
-        <v>0.27232184799999998</v>
+        <v>0.27208021499999901</v>
       </c>
       <c r="K12">
-        <v>0.49182620599999899</v>
+        <v>0.491994816</v>
       </c>
       <c r="L12">
-        <v>3.9037054969999998</v>
+        <v>3.9061300939999999</v>
       </c>
       <c r="M12">
-        <v>2.0026265000000001E-2</v>
+        <v>1.9380764000000002E-2</v>
       </c>
       <c r="N12">
-        <v>0.54539367400000005</v>
+        <v>0.53954938200000002</v>
       </c>
       <c r="O12">
-        <v>20.704204261000001</v>
+        <v>20.702092305000001</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -3613,43 +3753,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.1713296999999999E-2</v>
+        <v>2.1795710999999902E-2</v>
       </c>
       <c r="D13">
-        <v>7.787347113</v>
+        <v>7.7842876979999804</v>
       </c>
       <c r="E13">
-        <v>9.7883269000000106E-2</v>
+        <v>0.100048781999999</v>
       </c>
       <c r="F13">
-        <v>1.51182173999999</v>
+        <v>1.5122951069999999</v>
       </c>
       <c r="G13">
-        <v>5.6496790999999998E-2</v>
+        <v>5.6704179000000098E-2</v>
       </c>
       <c r="H13">
-        <v>0.45767707799999902</v>
+        <v>0.45760545999999902</v>
       </c>
       <c r="I13">
-        <v>6.0607472580000001</v>
+        <v>6.060382626</v>
       </c>
       <c r="J13">
-        <v>0.27223769999999903</v>
+        <v>0.27251588799999898</v>
       </c>
       <c r="K13">
-        <v>0.49176235600000001</v>
+        <v>0.49164730800000001</v>
       </c>
       <c r="L13">
-        <v>3.89744741999999</v>
+        <v>3.9049001079999899</v>
       </c>
       <c r="M13">
-        <v>2.0108869000000001E-2</v>
+        <v>2.0220420999999999E-2</v>
       </c>
       <c r="N13">
-        <v>0.55015700700000003</v>
+        <v>0.56252935400000004</v>
       </c>
       <c r="O13">
-        <v>20.692585380000001</v>
+        <v>20.699717342</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -3657,43 +3797,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.1855028999999901E-2</v>
+        <v>2.1231373000000001E-2</v>
       </c>
       <c r="D14">
-        <v>7.7860668789999696</v>
+        <v>7.7825284329999702</v>
       </c>
       <c r="E14">
-        <v>9.8922446999999997E-2</v>
+        <v>0.101947862</v>
       </c>
       <c r="F14">
-        <v>1.51220889299999</v>
+        <v>1.512921725</v>
       </c>
       <c r="G14">
-        <v>5.6745841999999901E-2</v>
+        <v>5.5964560999999899E-2</v>
       </c>
       <c r="H14">
-        <v>0.45806612199999902</v>
+        <v>0.45894390499999899</v>
       </c>
       <c r="I14">
-        <v>6.0625395729999996</v>
+        <v>6.0632913069999903</v>
       </c>
       <c r="J14">
-        <v>0.27311042299999999</v>
+        <v>0.27248361399999999</v>
       </c>
       <c r="K14">
-        <v>0.49177879899999999</v>
+        <v>0.49159298099999899</v>
       </c>
       <c r="L14">
-        <v>3.9069553799999999</v>
+        <v>3.9014519409999999</v>
       </c>
       <c r="M14">
-        <v>2.0284541999999999E-2</v>
+        <v>1.9455838E-2</v>
       </c>
       <c r="N14">
-        <v>0.54779951900000001</v>
+        <v>0.54230343400000003</v>
       </c>
       <c r="O14">
-        <v>20.705948580000001</v>
+        <v>20.698155360000001</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -3701,43 +3841,43 @@
         <v>21</v>
       </c>
       <c r="C15" s="1">
-        <v>2.16922599E-2</v>
+        <v>2.1138030700000001E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>7.7896106538999899</v>
+        <v>7.7902623423999904</v>
       </c>
       <c r="E15" s="1">
-        <v>9.8359574300000002E-2</v>
+        <v>0.1010922164</v>
       </c>
       <c r="F15" s="1">
-        <v>1.51386815239999</v>
+        <v>1.5147833314000001</v>
       </c>
       <c r="G15" s="1">
-        <v>5.6594890299999999E-2</v>
+        <v>5.59714298E-2</v>
       </c>
       <c r="H15" s="1">
-        <v>0.45789087749999902</v>
+        <v>0.45877713409999998</v>
       </c>
       <c r="I15" s="1">
-        <v>6.0640335470000002</v>
+        <v>6.0636236880999999</v>
       </c>
       <c r="J15" s="1">
-        <v>0.27265967940000002</v>
+        <v>0.27250950699999998</v>
       </c>
       <c r="K15" s="1">
-        <v>0.49234086289999901</v>
+        <v>0.49214803059999901</v>
       </c>
       <c r="L15" s="1">
-        <v>3.9051250898999901</v>
+        <v>3.8996497178</v>
       </c>
       <c r="M15" s="1">
-        <v>2.0148734299999999E-2</v>
+        <v>1.9451079699999999E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.55649489640000005</v>
+        <v>0.55477528669999998</v>
       </c>
       <c r="O15" s="1">
-        <v>20.709697601799999</v>
+        <v>20.705847007199999</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29E3D8-7825-7447-8785-B14548994AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914623F3-FD16-FA48-9026-C65353E34719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56320" yWindow="0" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="1940" yWindow="1040" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="61">
   <si>
     <t>Branch</t>
   </si>
@@ -121,6 +121,111 @@
   </si>
   <si>
     <t>Track reseeding</t>
+  </si>
+  <si>
+    <t>Atlas</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>along-step-neutral</t>
+  </si>
+  <si>
+    <t>along-step-uniform-msc</t>
+  </si>
+  <si>
+    <t>initialize-tracks</t>
+  </si>
+  <si>
+    <t>4.739928893000003</t>
+  </si>
+  <si>
+    <t>14.157920361000004</t>
+  </si>
+  <si>
+    <t>1.0943939320000016</t>
+  </si>
+  <si>
+    <t>4.8677925869999825</t>
+  </si>
+  <si>
+    <t>18.495831963000015</t>
+  </si>
+  <si>
+    <t>1.1414978990000058</t>
+  </si>
+  <si>
+    <t>4.539082406000011</t>
+  </si>
+  <si>
+    <t>14.07058440100002</t>
+  </si>
+  <si>
+    <t>1.0826401049999994</t>
+  </si>
+  <si>
+    <t>4.668021015000011</t>
+  </si>
+  <si>
+    <t>14.893830847000004</t>
+  </si>
+  <si>
+    <t>1.108715906000003</t>
+  </si>
+  <si>
+    <t>4.716793254999993</t>
+  </si>
+  <si>
+    <t>14.763301993999992</t>
+  </si>
+  <si>
+    <t>1.1058321380000014</t>
+  </si>
+  <si>
+    <t>4.854639256000009</t>
+  </si>
+  <si>
+    <t>14.163557716000016</t>
+  </si>
+  <si>
+    <t>1.0933890839999998</t>
+  </si>
+  <si>
+    <t>4.778291417000004</t>
+  </si>
+  <si>
+    <t>15.691015406000004</t>
+  </si>
+  <si>
+    <t>1.0883493359999996</t>
+  </si>
+  <si>
+    <t>4.617111119999994</t>
+  </si>
+  <si>
+    <t>15.159481652999983</t>
+  </si>
+  <si>
+    <t>1.088345942000003</t>
+  </si>
+  <si>
+    <t>4.672728067000012</t>
+  </si>
+  <si>
+    <t>15.186083537000004</t>
+  </si>
+  <si>
+    <t>1.122389057000007</t>
+  </si>
+  <si>
+    <t>4.704523719000007</t>
+  </si>
+  <si>
+    <t>13.082084631999992</t>
+  </si>
+  <si>
+    <t>1.1098299730000005</t>
   </si>
 </sst>
 </file>
@@ -169,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -179,6 +284,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71848BA-D8C3-7041-A0EE-B663A4811CD2}">
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AO22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
@@ -1148,27 +1255,298 @@
         <v>-2.3864001774150271E-2</v>
       </c>
     </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="C10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="5"/>
+    </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="D13" s="1"/>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4.7158911735000002</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4.6291748970000004</v>
+      </c>
+      <c r="E13">
+        <f>((C13-D13)/C13)*100</f>
+        <v>1.8388099578566284</v>
+      </c>
+      <c r="F13" s="1">
+        <v>14.966369251</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15.464017373900001</v>
+      </c>
+      <c r="H13">
+        <f>((F13-G13)/F13)*100</f>
+        <v>-3.3251092135572562</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.1035383372000001</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1.1174958406</v>
+      </c>
+      <c r="K13">
+        <f>((I13-J13)/I13)*100</f>
+        <v>-1.264795515433943</v>
+      </c>
+      <c r="L13" s="1">
+        <v>45.087971282799998</v>
+      </c>
+      <c r="M13" s="1">
+        <v>44.8257993271</v>
+      </c>
+      <c r="N13">
+        <f>((L13-M13)/L13)*100</f>
+        <v>0.5814676248252717</v>
+      </c>
+      <c r="O13" s="1">
+        <v>21.769039145499999</v>
+      </c>
+      <c r="P13" s="1">
+        <v>22.5076772191</v>
+      </c>
+      <c r="Q13">
+        <f>((O13-P13)/O13)*100</f>
+        <v>-3.3930669546923422</v>
+      </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B14" s="1"/>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4.6941893570999902</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4.6335907109000001</v>
+      </c>
+      <c r="E14">
+        <f>((C14-D14)/C14)*100</f>
+        <v>1.2909288822858049</v>
+      </c>
+      <c r="F14" s="1">
+        <v>14.3304367599</v>
+      </c>
+      <c r="G14" s="1">
+        <v>15.5303682837</v>
+      </c>
+      <c r="H14">
+        <f>((F14-G14)/F14)*100</f>
+        <v>-8.3733074148702595</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.1054981386</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1.1140971225</v>
+      </c>
+      <c r="K14">
+        <f>((I14-J14)/I14)*100</f>
+        <v>-0.77783793565584414</v>
+      </c>
+      <c r="L14" s="1">
+        <v>44.914485792800001</v>
+      </c>
+      <c r="M14" s="1">
+        <v>44.739087787199999</v>
+      </c>
+      <c r="N14">
+        <f>((L14-M14)/L14)*100</f>
+        <v>0.39051544842158442</v>
+      </c>
+      <c r="O14" s="1">
+        <v>21.1182229148</v>
+      </c>
+      <c r="P14" s="1">
+        <v>22.523737777600001</v>
+      </c>
+      <c r="Q14">
+        <f>((O14-P14)/O14)*100</f>
+        <v>-6.6554599242107271</v>
+      </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <f>((C13-C14)/C13)*100</f>
+        <v>0.46018484315242458</v>
+      </c>
+      <c r="D15">
+        <f>((D13-D14)/D13)*100</f>
+        <v>-9.5390949753516641E-2</v>
+      </c>
+      <c r="F15">
+        <f>((F13-F14)/F13)*100</f>
+        <v>4.2490765825352694</v>
+      </c>
+      <c r="G15">
+        <f>((G13-G14)/G13)*100</f>
+        <v>-0.42906644629089163</v>
+      </c>
+      <c r="I15">
+        <f>((I13-I14)/I13)*100</f>
+        <v>-0.17759250711421146</v>
+      </c>
+      <c r="J15">
+        <f>((J13-J14)/J13)*100</f>
+        <v>0.30413697989024269</v>
+      </c>
+      <c r="L15">
+        <f>((L13-L14)/L13)*100</f>
+        <v>0.38477111536437214</v>
+      </c>
+      <c r="M15">
+        <f>((M13-M14)/M13)*100</f>
+        <v>0.19344114595091852</v>
+      </c>
+      <c r="O15">
+        <f>((O13-O14)/O13)*100</f>
+        <v>2.9896415103582208</v>
+      </c>
+      <c r="P15">
+        <f>((P13-P14)/P13)*100</f>
+        <v>-7.1355912667755608E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="D22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="20">
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="C10:Q10"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="C1:AO1"/>
     <mergeCell ref="U2:W2"/>
@@ -1184,8 +1562,18 @@
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
   </mergeCells>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="colorScale" priority="60">
+    <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1195,7 +1583,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E5">
-    <cfRule type="colorScale" priority="74">
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1205,7 +1613,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H5">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
     <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1215,7 +1643,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K5">
-    <cfRule type="colorScale" priority="36">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M6">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1225,7 +1673,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N5">
-    <cfRule type="colorScale" priority="35">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O6">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1235,7 +1703,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q5">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S6">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1245,7 +1733,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T5">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V6">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1255,7 +1763,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W4:W5">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X6">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y6">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1265,7 +1793,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB6">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1275,7 +1823,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1285,7 +1853,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF4:AF5">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG6">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH6">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1295,7 +1883,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI4:AI5">
-    <cfRule type="colorScale" priority="28">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1305,7 +1913,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AL5">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM6">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN6">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1315,7 +1943,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO4:AO5">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1324,8 +1952,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="colorScale" priority="25">
+  <conditionalFormatting sqref="C15">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1334,8 +1962,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="colorScale" priority="24">
+  <conditionalFormatting sqref="D15">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1344,8 +1982,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="23">
+  <conditionalFormatting sqref="G15">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1354,8 +2002,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="colorScale" priority="22">
+  <conditionalFormatting sqref="J15">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L15">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1364,8 +2022,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="colorScale" priority="21">
+  <conditionalFormatting sqref="M15">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O15">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1374,8 +2042,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6">
-    <cfRule type="colorScale" priority="20">
+  <conditionalFormatting sqref="P15">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E14">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1384,8 +2062,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="H13:H14">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1394,8 +2072,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O6">
-    <cfRule type="colorScale" priority="18">
+  <conditionalFormatting sqref="K13:K14">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1404,8 +2082,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P6">
-    <cfRule type="colorScale" priority="17">
+  <conditionalFormatting sqref="N13:N14">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1414,157 +2092,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S6">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V6">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X6">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y6">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB6">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE6">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG6">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH6">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK6">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM6">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN6">
+  <conditionalFormatting sqref="Q13:Q14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1580,13 +2108,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D90E2C0-8C68-E84F-BBAA-6A32D2F1D90D}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.1640625" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -2158,9 +2686,281 @@
         <v>20.700766578500001</v>
       </c>
     </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20">
+        <v>45.178059114</v>
+      </c>
+      <c r="G20">
+        <v>20.935805562999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21">
+        <v>44.446670339999997</v>
+      </c>
+      <c r="G21">
+        <v>25.681944958999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22">
+        <v>44.993960194000003</v>
+      </c>
+      <c r="G22">
+        <v>20.587326808</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23">
+        <v>44.808145336999999</v>
+      </c>
+      <c r="G23">
+        <v>21.655821433</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>44.748611527000001</v>
+      </c>
+      <c r="G24">
+        <v>21.545505545000001</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25">
+        <v>44.639488767000003</v>
+      </c>
+      <c r="G25">
+        <v>21.058005052999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26">
+        <v>44.722949407000002</v>
+      </c>
+      <c r="G26">
+        <v>22.522632615999999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27">
+        <v>44.645210781000003</v>
+      </c>
+      <c r="G27">
+        <v>21.857823479</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28">
+        <v>47.971052186999998</v>
+      </c>
+      <c r="G28">
+        <v>22.030840081000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <v>44.725565174000003</v>
+      </c>
+      <c r="G29">
+        <v>19.814685917999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.7158911735000002</v>
+      </c>
+      <c r="D30" s="1">
+        <v>14.966369251</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.1035383372000001</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45.087971282799998</v>
+      </c>
+      <c r="G30" s="1">
+        <v>21.769039145499999</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C3:O3"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2168,8 +2968,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B17374F-425A-0C4A-B316-973C7C980C22}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -2732,9 +3539,260 @@
         <v>20.7009069424</v>
       </c>
     </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>4.8237869980000001</v>
+      </c>
+      <c r="D20">
+        <v>16.405531232999898</v>
+      </c>
+      <c r="E20">
+        <v>1.153891198</v>
+      </c>
+      <c r="F20">
+        <v>44.99530566</v>
+      </c>
+      <c r="G20">
+        <v>23.770921220999998</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>4.6673217520000003</v>
+      </c>
+      <c r="D21">
+        <v>14.449837002999899</v>
+      </c>
+      <c r="E21">
+        <v>1.1181004369999901</v>
+      </c>
+      <c r="F21">
+        <v>45.118839434999998</v>
+      </c>
+      <c r="G21">
+        <v>21.509625474</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>4.7014450299999897</v>
+      </c>
+      <c r="D22">
+        <v>15.184039253</v>
+      </c>
+      <c r="E22">
+        <v>1.1095911629999999</v>
+      </c>
+      <c r="F22">
+        <v>44.721127103000001</v>
+      </c>
+      <c r="G22">
+        <v>22.276340040000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>4.4885547370000003</v>
+      </c>
+      <c r="D23">
+        <v>15.4021777489999</v>
+      </c>
+      <c r="E23">
+        <v>1.10351937899999</v>
+      </c>
+      <c r="F23">
+        <v>44.616166184999997</v>
+      </c>
+      <c r="G23">
+        <v>22.257800827000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>4.7220404680000003</v>
+      </c>
+      <c r="D24">
+        <v>16.394596872000001</v>
+      </c>
+      <c r="E24">
+        <v>1.12422092099999</v>
+      </c>
+      <c r="F24">
+        <v>44.595392926000002</v>
+      </c>
+      <c r="G24">
+        <v>23.554986079999999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>4.8406276199999896</v>
+      </c>
+      <c r="D25">
+        <v>15.607468506999901</v>
+      </c>
+      <c r="E25">
+        <v>1.1448489749999899</v>
+      </c>
+      <c r="F25">
+        <v>44.5322107</v>
+      </c>
+      <c r="G25">
+        <v>22.953275693999998</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>4.4273572260000096</v>
+      </c>
+      <c r="D26">
+        <v>14.531455789000001</v>
+      </c>
+      <c r="E26">
+        <v>1.09781243699999</v>
+      </c>
+      <c r="F26">
+        <v>44.845106297000001</v>
+      </c>
+      <c r="G26">
+        <v>21.291217564</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>4.4705501949999897</v>
+      </c>
+      <c r="D27">
+        <v>15.201100657</v>
+      </c>
+      <c r="E27">
+        <v>1.0945569470000001</v>
+      </c>
+      <c r="F27">
+        <v>44.662393252999998</v>
+      </c>
+      <c r="G27">
+        <v>21.995210685</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>4.59382215000001</v>
+      </c>
+      <c r="D28">
+        <v>15.862654592999901</v>
+      </c>
+      <c r="E28">
+        <v>1.1204468359999999</v>
+      </c>
+      <c r="F28">
+        <v>45.072985840999998</v>
+      </c>
+      <c r="G28">
+        <v>22.860605258</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>4.5562427940000001</v>
+      </c>
+      <c r="D29">
+        <v>15.6013120829999</v>
+      </c>
+      <c r="E29">
+        <v>1.1079701129999999</v>
+      </c>
+      <c r="F29">
+        <v>45.098465871000002</v>
+      </c>
+      <c r="G29">
+        <v>22.606789348</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.6291748970000004</v>
+      </c>
+      <c r="D30" s="1">
+        <v>15.464017373900001</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.1174958406</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44.8257993271</v>
+      </c>
+      <c r="G30" s="1">
+        <v>22.5076772191</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C3:O3"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2742,7 +3800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE3BDD0-3A87-544A-A16E-D142A4C1F8FB}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -3306,9 +4364,267 @@
         <v>20.701861121499999</v>
       </c>
     </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>4.6006060579999897</v>
+      </c>
+      <c r="D20">
+        <v>15.542913898</v>
+      </c>
+      <c r="E20">
+        <v>1.0821381290000001</v>
+      </c>
+      <c r="F20">
+        <v>44.868074825000001</v>
+      </c>
+      <c r="G20">
+        <v>22.239466582999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>4.6237777609999897</v>
+      </c>
+      <c r="D21">
+        <v>14.005688256999999</v>
+      </c>
+      <c r="E21">
+        <v>1.0931326799999901</v>
+      </c>
+      <c r="F21">
+        <v>45.367524641000003</v>
+      </c>
+      <c r="G21">
+        <v>20.678480005000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>4.5162472820000001</v>
+      </c>
+      <c r="D22">
+        <v>14.3467801379999</v>
+      </c>
+      <c r="E22">
+        <v>1.1148718719999899</v>
+      </c>
+      <c r="F22">
+        <v>44.413765368</v>
+      </c>
+      <c r="G22">
+        <v>20.931622545</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>4.8416728419999897</v>
+      </c>
+      <c r="D23">
+        <v>14.1692157299999</v>
+      </c>
+      <c r="E23">
+        <v>1.12419611599999</v>
+      </c>
+      <c r="F23">
+        <v>45.201858715999997</v>
+      </c>
+      <c r="G23">
+        <v>21.150967145999999</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>4.8448703529999904</v>
+      </c>
+      <c r="D24">
+        <v>13.885040346</v>
+      </c>
+      <c r="E24">
+        <v>1.1458932610000001</v>
+      </c>
+      <c r="F24">
+        <v>44.601139498000002</v>
+      </c>
+      <c r="G24">
+        <v>20.890493974999998</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>4.7523815999999899</v>
+      </c>
+      <c r="D25">
+        <v>14.416007534999901</v>
+      </c>
+      <c r="E25">
+        <v>1.104802775</v>
+      </c>
+      <c r="F25">
+        <v>44.893572736000003</v>
+      </c>
+      <c r="G25">
+        <v>21.308788703000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>4.7771238329999903</v>
+      </c>
+      <c r="D26">
+        <v>14.535514169000001</v>
+      </c>
+      <c r="E26">
+        <v>1.13063033</v>
+      </c>
+      <c r="F26">
+        <v>45.022300168999998</v>
+      </c>
+      <c r="G26">
+        <v>21.462349112999998</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>4.6711723949999797</v>
+      </c>
+      <c r="D27">
+        <v>14.424652171999901</v>
+      </c>
+      <c r="E27">
+        <v>1.07934710399999</v>
+      </c>
+      <c r="F27">
+        <v>45.100189931999999</v>
+      </c>
+      <c r="G27">
+        <v>21.122489199</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>4.5969812780000003</v>
+      </c>
+      <c r="D28">
+        <v>14.396043703999901</v>
+      </c>
+      <c r="E28">
+        <v>1.09079157099999</v>
+      </c>
+      <c r="F28">
+        <v>44.191400801</v>
+      </c>
+      <c r="G28">
+        <v>21.039077846000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>4.7170601689999998</v>
+      </c>
+      <c r="D29">
+        <v>13.582511649999899</v>
+      </c>
+      <c r="E29">
+        <v>1.0891775480000001</v>
+      </c>
+      <c r="F29">
+        <v>45.485031241999998</v>
+      </c>
+      <c r="G29">
+        <v>20.358494032999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.6941893570999902</v>
+      </c>
+      <c r="D30" s="1">
+        <v>14.3304367599</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.1054981386</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44.914485792800001</v>
+      </c>
+      <c r="G30" s="1">
+        <v>21.1182229148</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C3:O3"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3316,7 +4632,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF611A7-FF5C-9946-82AC-26D645B98B8C}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -3880,9 +5196,260 @@
         <v>20.705847007199999</v>
       </c>
     </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>4.6821826419999999</v>
+      </c>
+      <c r="D20">
+        <v>15.9062169909999</v>
+      </c>
+      <c r="E20">
+        <v>1.121482047</v>
+      </c>
+      <c r="F20">
+        <v>44.397116122</v>
+      </c>
+      <c r="G20">
+        <v>22.945172749000001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>4.9315779149999903</v>
+      </c>
+      <c r="D21">
+        <v>16.390990083999998</v>
+      </c>
+      <c r="E21">
+        <v>1.192110045</v>
+      </c>
+      <c r="F21">
+        <v>45.113467712999999</v>
+      </c>
+      <c r="G21">
+        <v>23.885588552000002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>4.4953373430000001</v>
+      </c>
+      <c r="D22">
+        <v>15.650422679999901</v>
+      </c>
+      <c r="E22">
+        <v>1.1235293309999901</v>
+      </c>
+      <c r="F22">
+        <v>44.746627072000003</v>
+      </c>
+      <c r="G22">
+        <v>22.479247667999999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>4.5581672070000003</v>
+      </c>
+      <c r="D23">
+        <v>14.377298114</v>
+      </c>
+      <c r="E23">
+        <v>1.10439433899999</v>
+      </c>
+      <c r="F23">
+        <v>45.184373686000001</v>
+      </c>
+      <c r="G23">
+        <v>21.237795102</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>4.5335301469999996</v>
+      </c>
+      <c r="D24">
+        <v>15.151445159</v>
+      </c>
+      <c r="E24">
+        <v>1.0928487359999901</v>
+      </c>
+      <c r="F24">
+        <v>44.322336700000001</v>
+      </c>
+      <c r="G24">
+        <v>21.952346764000001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>4.7823800330000097</v>
+      </c>
+      <c r="D25">
+        <v>15.646650354999901</v>
+      </c>
+      <c r="E25">
+        <v>1.1116416419999999</v>
+      </c>
+      <c r="F25">
+        <v>44.701800239000001</v>
+      </c>
+      <c r="G25">
+        <v>22.869030379000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>4.4649637659999897</v>
+      </c>
+      <c r="D26">
+        <v>15.741240229999899</v>
+      </c>
+      <c r="E26">
+        <v>1.0914018059999899</v>
+      </c>
+      <c r="F26">
+        <v>44.399810017</v>
+      </c>
+      <c r="G26">
+        <v>22.544032024</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>4.7631122550000002</v>
+      </c>
+      <c r="D27">
+        <v>15.3062458429999</v>
+      </c>
+      <c r="E27">
+        <v>1.126965164</v>
+      </c>
+      <c r="F27">
+        <v>44.695782704000003</v>
+      </c>
+      <c r="G27">
+        <v>22.480037155000002</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>4.5826042339999997</v>
+      </c>
+      <c r="D28">
+        <v>15.840817636999899</v>
+      </c>
+      <c r="E28">
+        <v>1.099819111</v>
+      </c>
+      <c r="F28">
+        <v>45.131765295999998</v>
+      </c>
+      <c r="G28">
+        <v>22.729038668000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>4.5420515669999997</v>
+      </c>
+      <c r="D29">
+        <v>15.2923557439999</v>
+      </c>
+      <c r="E29">
+        <v>1.076779004</v>
+      </c>
+      <c r="F29">
+        <v>44.697798323000001</v>
+      </c>
+      <c r="G29">
+        <v>22.115088714999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.6335907109000001</v>
+      </c>
+      <c r="D30" s="1">
+        <v>15.5303682837</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.1140971225</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44.739087787199999</v>
+      </c>
+      <c r="G30" s="1">
+        <v>22.523737777600001</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C3:O3"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914623F3-FD16-FA48-9026-C65353E34719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754DAB99-1EEA-314D-B189-92C1CD16F1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="1040" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="55460" yWindow="1100" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="37">
   <si>
     <t>Branch</t>
   </si>
@@ -138,94 +138,22 @@
     <t>initialize-tracks</t>
   </si>
   <si>
-    <t>4.739928893000003</t>
+    <t>6a97cc5300474f5feb5c4258abe22a77519818dc</t>
   </si>
   <si>
-    <t>14.157920361000004</t>
+    <t>boundary-init</t>
   </si>
   <si>
-    <t>1.0943939320000016</t>
+    <t>boundary-post</t>
   </si>
   <si>
-    <t>4.8677925869999825</t>
+    <t>discrete-select</t>
   </si>
   <si>
-    <t>18.495831963000015</t>
+    <t>rayleigh</t>
   </si>
   <si>
-    <t>1.1414978990000058</t>
-  </si>
-  <si>
-    <t>4.539082406000011</t>
-  </si>
-  <si>
-    <t>14.07058440100002</t>
-  </si>
-  <si>
-    <t>1.0826401049999994</t>
-  </si>
-  <si>
-    <t>4.668021015000011</t>
-  </si>
-  <si>
-    <t>14.893830847000004</t>
-  </si>
-  <si>
-    <t>1.108715906000003</t>
-  </si>
-  <si>
-    <t>4.716793254999993</t>
-  </si>
-  <si>
-    <t>14.763301993999992</t>
-  </si>
-  <si>
-    <t>1.1058321380000014</t>
-  </si>
-  <si>
-    <t>4.854639256000009</t>
-  </si>
-  <si>
-    <t>14.163557716000016</t>
-  </si>
-  <si>
-    <t>1.0933890839999998</t>
-  </si>
-  <si>
-    <t>4.778291417000004</t>
-  </si>
-  <si>
-    <t>15.691015406000004</t>
-  </si>
-  <si>
-    <t>1.0883493359999996</t>
-  </si>
-  <si>
-    <t>4.617111119999994</t>
-  </si>
-  <si>
-    <t>15.159481652999983</t>
-  </si>
-  <si>
-    <t>1.088345942000003</t>
-  </si>
-  <si>
-    <t>4.672728067000012</t>
-  </si>
-  <si>
-    <t>15.186083537000004</t>
-  </si>
-  <si>
-    <t>1.122389057000007</t>
-  </si>
-  <si>
-    <t>4.704523719000007</t>
-  </si>
-  <si>
-    <t>13.082084631999992</t>
-  </si>
-  <si>
-    <t>1.1098299730000005</t>
+    <t>surface-physics</t>
   </si>
 </sst>
 </file>
@@ -254,12 +182,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -274,18 +208,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,10 +558,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71848BA-D8C3-7041-A0EE-B663A4811CD2}">
-  <dimension ref="A1:AO22"/>
+  <dimension ref="A1:AO27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
     <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.83203125" customWidth="1"/>
   </cols>
@@ -689,73 +620,73 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3" t="s">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3" t="s">
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3" t="s">
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3" t="s">
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3" t="s">
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
@@ -877,273 +808,273 @@
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2">
-        <v>2.10134848999999E-2</v>
+      <c r="C4">
+        <v>2.5502058000000001E-2</v>
       </c>
       <c r="D4" s="2">
-        <v>2.1044281399999899E-2</v>
+        <v>2.5704619599999898E-2</v>
       </c>
       <c r="E4">
-        <f>((C4-D4)/C4)*100</f>
-        <v>-0.14655589087938234</v>
-      </c>
-      <c r="F4" s="2">
-        <v>7.7868371409000003</v>
+        <f>(ABS(D4-C4)/C4)*100</f>
+        <v>0.79429511139805808</v>
+      </c>
+      <c r="F4">
+        <v>10.099553321999901</v>
       </c>
       <c r="G4" s="2">
-        <v>7.7882990942999903</v>
+        <v>10.0925216713</v>
       </c>
       <c r="H4">
-        <f>((F4-G4)/F4)*100</f>
-        <v>-1.8774675436720758E-2</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.10106857869999999</v>
+        <f>(ABS(G4-F4)/F4)*100</f>
+        <v>6.9623383091443877E-2</v>
+      </c>
+      <c r="I4">
+        <v>2.330985192</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1008018878</v>
+        <v>2.3349653803999901</v>
       </c>
       <c r="K4">
-        <f>((I4-J4)/I4)*100</f>
-        <v>0.26387122825938303</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1.5133286373999999</v>
+        <f>(ABS(J4-I4)/I4)*100</f>
+        <v>0.17075133783132793</v>
+      </c>
+      <c r="L4">
+        <v>7.1190351000000096E-2</v>
       </c>
       <c r="M4" s="2">
-        <v>1.5134209893999899</v>
+        <v>6.9502298399999898E-2</v>
       </c>
       <c r="N4">
-        <f>((L4-M4)/L4)*100</f>
-        <v>-6.102574001949284E-3</v>
-      </c>
-      <c r="O4" s="2">
-        <v>5.5878251300000001E-2</v>
+        <f>(ABS(M4-L4)/L4)*100</f>
+        <v>2.3711817350081552</v>
+      </c>
+      <c r="O4">
+        <v>0.105847889</v>
       </c>
       <c r="P4" s="2">
-        <v>5.5854686299999998E-2</v>
+        <v>0.58595583539999996</v>
       </c>
       <c r="Q4">
-        <f>((O4-P4)/O4)*100</f>
-        <v>4.2172042703138721E-2</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0.45890807779999998</v>
+        <f>(ABS(P4-O4)/O4)*100</f>
+        <v>453.58292067591447</v>
+      </c>
+      <c r="R4">
+        <v>0.116869266999999</v>
       </c>
       <c r="S4" s="2">
-        <v>0.45886056159999999</v>
+        <v>0.1196328408</v>
       </c>
       <c r="T4">
-        <f>((R4-S4)/R4)*100</f>
-        <v>1.0354186883738974E-2</v>
-      </c>
-      <c r="U4" s="2">
-        <v>6.0628989352999998</v>
+        <f>(ABS(S4-R4)/R4)*100</f>
+        <v>2.3646711158041445</v>
+      </c>
+      <c r="U4">
+        <v>0.195518261</v>
       </c>
       <c r="V4" s="2">
-        <v>6.0622900875000001</v>
+        <v>0.67183863479999895</v>
       </c>
       <c r="W4">
-        <f>((U4-V4)/U4)*100</f>
-        <v>1.0042189495437705E-2</v>
-      </c>
-      <c r="X4" s="2">
-        <v>0.27203544940000002</v>
+        <f>(ABS(V4-U4)/U4)*100</f>
+        <v>243.61937926606197</v>
+      </c>
+      <c r="X4">
+        <v>1.9271281440000001</v>
       </c>
       <c r="Y4" s="2">
-        <v>0.27205333569999901</v>
+        <v>5.028672587</v>
       </c>
       <c r="Z4">
-        <f>((X4-Y4)/X4)*100</f>
-        <v>-6.5749886782926767E-3</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>0.49175476299999998</v>
+        <f>(ABS(Y4-X4)/X4)*100</f>
+        <v>160.94126655025386</v>
+      </c>
+      <c r="AA4">
+        <v>0.209259116999999</v>
       </c>
       <c r="AB4" s="2">
-        <v>0.49182936509999903</v>
+        <v>9.9499744934999903</v>
       </c>
       <c r="AC4">
-        <f>((AA4-AB4)/AA4)*100</f>
-        <v>-1.5170590223453264E-2</v>
-      </c>
-      <c r="AD4" s="2">
-        <v>3.9014598262999902</v>
+        <f>(ABS(AB4-AA4)/AA4)*100</f>
+        <v>4654.8583001523602</v>
+      </c>
+      <c r="AD4">
+        <v>0.29808918699999898</v>
       </c>
       <c r="AE4" s="2">
-        <v>3.9008079268000002</v>
+        <v>0.37503557399999898</v>
       </c>
       <c r="AF4">
-        <f>((AD4-AE4)/AD4)*100</f>
-        <v>1.6709117330787542E-2</v>
-      </c>
-      <c r="AG4" s="2">
-        <v>1.93700037999999E-2</v>
+        <f>(ABS(AE4-AD4)/AD4)*100</f>
+        <v>25.813209722364157</v>
+      </c>
+      <c r="AG4">
+        <v>2.4367838999999999E-2</v>
       </c>
       <c r="AH4" s="2">
-        <v>1.93747672E-2</v>
+        <v>2.3758901599999899E-2</v>
       </c>
       <c r="AI4">
-        <f>((AG4-AH4)/AG4)*100</f>
-        <v>-2.459163172750858E-2</v>
-      </c>
-      <c r="AJ4" s="2">
-        <v>0.54875180800000001</v>
+        <f>(ABS(AH4-AG4)/AG4)*100</f>
+        <v>2.4989388677432558</v>
+      </c>
+      <c r="AJ4">
+        <v>0.61301483700000003</v>
       </c>
       <c r="AK4" s="2">
-        <v>0.54884408070000001</v>
+        <v>0.58678082080000005</v>
       </c>
       <c r="AL4">
-        <f>((AJ4-AK4)/AJ4)*100</f>
-        <v>-1.6815015213582085E-2</v>
-      </c>
-      <c r="AM4" s="2">
-        <v>20.700766578500001</v>
+        <f>(ABS(AK4-AJ4)/AJ4)*100</f>
+        <v>4.2795075447741544</v>
+      </c>
+      <c r="AM4">
+        <v>15.422933222999999</v>
       </c>
       <c r="AN4" s="2">
-        <v>20.7009069424</v>
+        <v>29.295764520799999</v>
       </c>
       <c r="AO4">
-        <f>((AM4-AN4)/AM4)*100</f>
-        <v>-6.7806136292530817E-4</v>
+        <f>(ABS(AN4-AM4)/AM4)*100</f>
+        <v>89.949370182784989</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="2">
-        <v>2.1148022799999899E-2</v>
+        <v>2.5521457199999899E-2</v>
       </c>
       <c r="D5" s="2">
-        <v>2.1138030700000001E-2</v>
+        <v>2.5699852099999899E-2</v>
       </c>
       <c r="E5">
-        <f>((C5-D5)/C5)*100</f>
-        <v>4.7248388629019415E-2</v>
+        <f>(ABS(D5-C5)/C5)*100</f>
+        <v>0.69899966370259103</v>
       </c>
       <c r="F5" s="2">
-        <v>7.7888443829999998</v>
+        <v>10.0991415404999</v>
       </c>
       <c r="G5" s="2">
-        <v>7.7902623423999904</v>
+        <v>10.0941187058999</v>
       </c>
       <c r="H5">
-        <f>((F5-G5)/F5)*100</f>
-        <v>-1.8205003595724873E-2</v>
+        <f>(ABS(G5-F5)/F5)*100</f>
+        <v>4.97352629414822E-2</v>
       </c>
       <c r="I5" s="2">
-        <v>0.1013372595</v>
+        <v>2.3305051410000002</v>
       </c>
       <c r="J5" s="2">
-        <v>0.1010922164</v>
+        <v>2.3350911164999899</v>
       </c>
       <c r="K5">
-        <f>((I5-J5)/I5)*100</f>
-        <v>0.2418094797600035</v>
+        <f>(ABS(J5-I5)/I5)*100</f>
+        <v>0.19678032111192567</v>
       </c>
       <c r="L5" s="2">
-        <v>1.5131773657000001</v>
+        <v>7.1178903799999901E-2</v>
       </c>
       <c r="M5" s="2">
-        <v>1.5147833314000001</v>
+        <v>6.9504739900000001E-2</v>
       </c>
       <c r="N5">
-        <f>((L5-M5)/L5)*100</f>
-        <v>-0.10613201970921107</v>
+        <f>(ABS(M5-L5)/L5)*100</f>
+        <v>2.352050692862599</v>
       </c>
       <c r="O5" s="2">
-        <v>5.5961258899999998E-2</v>
+        <v>0.10564063680000001</v>
       </c>
       <c r="P5" s="2">
-        <v>5.59714298E-2</v>
+        <v>0.58601875989999996</v>
       </c>
       <c r="Q5">
-        <f>((O5-P5)/O5)*100</f>
-        <v>-1.8174894918244817E-2</v>
+        <f>(ABS(P5-O5)/O5)*100</f>
+        <v>454.72853785372098</v>
       </c>
       <c r="R5" s="2">
-        <v>0.45887892660000001</v>
+        <v>0.1165891476</v>
       </c>
       <c r="S5" s="2">
-        <v>0.45877713409999998</v>
+        <v>0.11909431970000001</v>
       </c>
       <c r="T5">
-        <f>((R5-S5)/R5)*100</f>
-        <v>2.2182866568802424E-2</v>
+        <f>(ABS(S5-R5)/R5)*100</f>
+        <v>2.1487180853186101</v>
       </c>
       <c r="U5" s="2">
-        <v>6.0627548560999998</v>
+        <v>0.1954054365</v>
       </c>
       <c r="V5" s="2">
-        <v>6.0636236880999999</v>
+        <v>0.6719217072</v>
       </c>
       <c r="W5">
-        <f>((U5-V5)/U5)*100</f>
-        <v>-1.4330647051083181E-2</v>
+        <f>(ABS(V5-U5)/U5)*100</f>
+        <v>243.86029336496992</v>
       </c>
       <c r="X5" s="2">
-        <v>0.27224948490000001</v>
+        <v>1.9289283071999901</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.27250950699999998</v>
+        <v>5.0273797492999899</v>
       </c>
       <c r="Z5">
-        <f>((X5-Y5)/X5)*100</f>
-        <v>-9.5508757379463141E-2</v>
+        <f>(ABS(Y5-X5)/X5)*100</f>
+        <v>160.6307207237617</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.49188873370000002</v>
+        <v>0.2089056393</v>
       </c>
       <c r="AB5" s="2">
-        <v>0.49214803059999901</v>
+        <v>9.9510771030999994</v>
       </c>
       <c r="AC5">
-        <f>((AA5-AB5)/AA5)*100</f>
-        <v>-5.2714543398574322E-2</v>
+        <f>(ABS(AB5-AA5)/AA5)*100</f>
+        <v>4663.4315360964029</v>
       </c>
       <c r="AD5" s="2">
-        <v>3.8996550481000001</v>
+        <v>0.29732985619999902</v>
       </c>
       <c r="AE5" s="2">
-        <v>3.8996497178</v>
+        <v>0.37508046959999902</v>
       </c>
       <c r="AF5">
-        <f>((AD5-AE5)/AD5)*100</f>
-        <v>1.3668644878339834E-4</v>
+        <f>(ABS(AE5-AD5)/AD5)*100</f>
+        <v>26.149615243381756</v>
       </c>
       <c r="AG5" s="2">
-        <v>1.9472640100000001E-2</v>
+        <v>2.4375689799999999E-2</v>
       </c>
       <c r="AH5" s="2">
-        <v>1.9451079699999999E-2</v>
+        <v>2.3737580799999901E-2</v>
       </c>
       <c r="AI5">
-        <f>((AG5-AH5)/AG5)*100</f>
-        <v>0.11072150406560535</v>
+        <f>(ABS(AH5-AG5)/AG5)*100</f>
+        <v>2.6178089942714093</v>
       </c>
       <c r="AJ5" s="2">
-        <v>0.55042533940000005</v>
+        <v>0.61320205890000001</v>
       </c>
       <c r="AK5" s="2">
-        <v>0.55477528669999998</v>
+        <v>0.60076852670000003</v>
       </c>
       <c r="AL5">
-        <f>((AJ5-AK5)/AJ5)*100</f>
-        <v>-0.7902883440543752</v>
+        <f>(ABS(AK5-AJ5)/AJ5)*100</f>
+        <v>2.0276403217406069</v>
       </c>
       <c r="AM5" s="2">
-        <v>20.701861121499999</v>
+        <v>15.422410439199901</v>
       </c>
       <c r="AN5" s="2">
-        <v>20.705847007199999</v>
+        <v>29.296997711900001</v>
       </c>
       <c r="AO5">
-        <f>((AM5-AN5)/AM5)*100</f>
-        <v>-1.9253755382703359E-2</v>
+        <f>(ABS(AN5-AM5)/AM5)*100</f>
+        <v>89.963805122410562</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.2">
@@ -1151,402 +1082,417 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <f>((C4-C5)/C4)*100</f>
-        <v>-0.64024554061472838</v>
+        <f>(ABS(C4-C5)/C4)*100</f>
+        <v>7.6069154888983442E-2</v>
       </c>
       <c r="D6">
-        <f>((D4-D5)/D4)*100</f>
-        <v>-0.44548586962015346</v>
-      </c>
+        <f>(ABS(D4-D5)/D4)*100</f>
+        <v>1.8547249771395283E-2</v>
+      </c>
+      <c r="E6" s="5"/>
       <c r="F6">
-        <f>((F4-F5)/F4)*100</f>
-        <v>-2.5777373581585869E-2</v>
+        <f t="shared" ref="F6:G6" si="0">(ABS(F4-F5)/F4)*100</f>
+        <v>4.0772248719499748E-3</v>
       </c>
       <c r="G6">
-        <f>((G4-G5)/G4)*100</f>
-        <v>-2.5207661855678808E-2</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>1.5823940259069226E-2</v>
+      </c>
+      <c r="H6" s="5"/>
       <c r="I6">
-        <f>((I4-I5)/I4)*100</f>
-        <v>-0.26584008942831217</v>
+        <f t="shared" ref="I6:J6" si="1">(ABS(I4-I5)/I4)*100</f>
+        <v>2.0594339322590378E-2</v>
       </c>
       <c r="J6">
-        <f>((J4-J5)/J4)*100</f>
-        <v>-0.28801901069158398</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>5.3849235220024749E-3</v>
+      </c>
+      <c r="K6" s="5"/>
       <c r="L6">
-        <f>((L4-L5)/L4)*100</f>
-        <v>9.9959583306200531E-3</v>
+        <f t="shared" ref="L6:M6" si="2">(ABS(L4-L5)/L4)*100</f>
+        <v>1.6079707206661627E-2</v>
       </c>
       <c r="M6">
-        <f>((M4-M5)/M4)*100</f>
-        <v>-9.001738508663662E-2</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>3.5128334692636357E-3</v>
+      </c>
+      <c r="N6" s="5"/>
       <c r="O6">
-        <f>((O4-O5)/O4)*100</f>
-        <v>-0.14855081909121434</v>
+        <f t="shared" ref="O6:P6" si="3">(ABS(O4-O5)/O4)*100</f>
+        <v>0.19580192100004357</v>
       </c>
       <c r="P6">
-        <f>((P4-P5)/P4)*100</f>
-        <v>-0.20901290067759673</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>1.0738778624339577E-2</v>
+      </c>
+      <c r="Q6" s="5"/>
       <c r="R6">
-        <f>((R4-R5)/R4)*100</f>
-        <v>6.352296115535074E-3</v>
+        <f t="shared" ref="R6:S6" si="4">(ABS(R4-R5)/R4)*100</f>
+        <v>0.23968611012081037</v>
       </c>
       <c r="S6">
-        <f>((S4-S5)/S4)*100</f>
-        <v>1.8181449220457616E-2</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>0.45014487359727939</v>
+      </c>
+      <c r="T6" s="5"/>
       <c r="U6">
-        <f>((U4-U5)/U4)*100</f>
-        <v>2.3764077471449142E-3</v>
+        <f t="shared" ref="U6:V6" si="5">(ABS(U4-U5)/U4)*100</f>
+        <v>5.770535162441795E-2</v>
       </c>
       <c r="V6">
-        <f>((V4-V5)/V4)*100</f>
-        <v>-2.1998297355475444E-2</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>1.2364933437592445E-2</v>
+      </c>
+      <c r="W6" s="5"/>
       <c r="X6">
-        <f>((X4-X5)/X4)*100</f>
-        <v>-7.8679267893968508E-2</v>
+        <f t="shared" ref="X6:Y6" si="6">(ABS(X4-X5)/X4)*100</f>
+        <v>9.3411702049741335E-2</v>
       </c>
       <c r="Y6">
-        <f>((Y4-Y5)/Y4)*100</f>
-        <v>-0.16767715743210254</v>
-      </c>
+        <f t="shared" si="6"/>
+        <v>2.5709323437606749E-2</v>
+      </c>
+      <c r="Z6" s="5"/>
       <c r="AA6">
-        <f>((AA4-AA5)/AA4)*100</f>
-        <v>-2.7243396522026404E-2</v>
+        <f t="shared" ref="AA6:AB6" si="7">(ABS(AA4-AA5)/AA4)*100</f>
+        <v>0.16891866173696787</v>
       </c>
       <c r="AB6">
-        <f>((AB4-AB5)/AB4)*100</f>
-        <v>-6.4791881618371933E-2</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>1.1081531924824282E-2</v>
+      </c>
+      <c r="AC6" s="5"/>
       <c r="AD6">
-        <f>((AD4-AD5)/AD4)*100</f>
-        <v>4.6259048672602429E-2</v>
+        <f t="shared" ref="AD6:AE6" si="8">(ABS(AD4-AD5)/AD4)*100</f>
+        <v>0.25473275553600011</v>
       </c>
       <c r="AE6">
-        <f>((AE4-AE5)/AE4)*100</f>
-        <v>2.9691515750951521E-2</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>1.1971024380753549E-2</v>
+      </c>
+      <c r="AF6" s="5"/>
       <c r="AG6">
-        <f>((AG4-AG5)/AG4)*100</f>
-        <v>-0.52987237927181707</v>
+        <f t="shared" ref="AG6:AH6" si="9">(ABS(AG4-AG5)/AG4)*100</f>
+        <v>3.2217875372537105E-2</v>
       </c>
       <c r="AH6">
-        <f>((AH4-AH5)/AH4)*100</f>
-        <v>-0.39387570034905117</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>8.9738155235251485E-2</v>
+      </c>
+      <c r="AI6" s="5"/>
       <c r="AJ6">
-        <f>((AJ4-AJ5)/AJ4)*100</f>
-        <v>-0.30497054872574358</v>
+        <f t="shared" ref="AJ6:AK6" si="10">(ABS(AJ4-AJ5)/AJ4)*100</f>
+        <v>3.0541169430125657E-2</v>
       </c>
       <c r="AK6">
-        <f>((AK4-AK5)/AK4)*100</f>
-        <v>-1.0806723090527386</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>2.3838042083464051</v>
+      </c>
+      <c r="AL6" s="5"/>
       <c r="AM6">
-        <f>((AM4-AM5)/AM4)*100</f>
-        <v>-5.2874515339635716E-3</v>
+        <f t="shared" ref="AM6:AN6" si="11">(ABS(AM4-AM5)/AM4)*100</f>
+        <v>3.3896522311275797E-3</v>
       </c>
       <c r="AN6">
-        <f>((AN4-AN5)/AN4)*100</f>
-        <v>-2.3864001774150271E-2</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>4.2094518445728313E-3</v>
+      </c>
+      <c r="AO6" s="5"/>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="C10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
-      <c r="AI10" s="5"/>
-      <c r="AJ10" s="5"/>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="5"/>
-      <c r="AM10" s="5"/>
-      <c r="AN10" s="5"/>
-      <c r="AO10" s="5"/>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="1"/>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B12" s="1"/>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>19</v>
-      </c>
-      <c r="N12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" t="s">
-        <v>18</v>
-      </c>
-      <c r="P12" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4.7158911735000002</v>
-      </c>
-      <c r="D13" s="1">
-        <v>4.6291748970000004</v>
-      </c>
-      <c r="E13">
-        <f>((C13-D13)/C13)*100</f>
-        <v>1.8388099578566284</v>
-      </c>
-      <c r="F13" s="1">
-        <v>14.966369251</v>
-      </c>
-      <c r="G13" s="1">
-        <v>15.464017373900001</v>
-      </c>
-      <c r="H13">
-        <f>((F13-G13)/F13)*100</f>
-        <v>-3.3251092135572562</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.1035383372000001</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1.1174958406</v>
-      </c>
-      <c r="K13">
-        <f>((I13-J13)/I13)*100</f>
-        <v>-1.264795515433943</v>
-      </c>
-      <c r="L13" s="1">
-        <v>45.087971282799998</v>
-      </c>
-      <c r="M13" s="1">
-        <v>44.8257993271</v>
-      </c>
-      <c r="N13">
-        <f>((L13-M13)/L13)*100</f>
-        <v>0.5814676248252717</v>
-      </c>
-      <c r="O13" s="1">
-        <v>21.769039145499999</v>
-      </c>
-      <c r="P13" s="1">
-        <v>22.5076772191</v>
-      </c>
-      <c r="Q13">
-        <f>((O13-P13)/O13)*100</f>
-        <v>-3.3930669546923422</v>
-      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4.6941893570999902</v>
-      </c>
-      <c r="D14" s="1">
-        <v>4.6335907109000001</v>
-      </c>
-      <c r="E14">
-        <f>((C14-D14)/C14)*100</f>
-        <v>1.2909288822858049</v>
-      </c>
-      <c r="F14" s="1">
-        <v>14.3304367599</v>
-      </c>
-      <c r="G14" s="1">
-        <v>15.5303682837</v>
-      </c>
-      <c r="H14">
-        <f>((F14-G14)/F14)*100</f>
-        <v>-8.3733074148702595</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1.1054981386</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1.1140971225</v>
-      </c>
-      <c r="K14">
-        <f>((I14-J14)/I14)*100</f>
-        <v>-0.77783793565584414</v>
-      </c>
-      <c r="L14" s="1">
-        <v>44.914485792800001</v>
-      </c>
-      <c r="M14" s="1">
-        <v>44.739087787199999</v>
-      </c>
-      <c r="N14">
-        <f>((L14-M14)/L14)*100</f>
-        <v>0.39051544842158442</v>
-      </c>
-      <c r="O14" s="1">
-        <v>21.1182229148</v>
-      </c>
-      <c r="P14" s="1">
-        <v>22.523737777600001</v>
-      </c>
-      <c r="Q14">
-        <f>((O14-P14)/O14)*100</f>
-        <v>-6.6554599242107271</v>
-      </c>
       <c r="T14" s="2"/>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15">
-        <f>((C13-C14)/C13)*100</f>
-        <v>0.46018484315242458</v>
-      </c>
-      <c r="D15">
-        <f>((D13-D14)/D13)*100</f>
-        <v>-9.5390949753516641E-2</v>
-      </c>
-      <c r="F15">
-        <f>((F13-F14)/F13)*100</f>
-        <v>4.2490765825352694</v>
-      </c>
-      <c r="G15">
-        <f>((G13-G14)/G13)*100</f>
-        <v>-0.42906644629089163</v>
-      </c>
-      <c r="I15">
-        <f>((I13-I14)/I13)*100</f>
-        <v>-0.17759250711421146</v>
-      </c>
-      <c r="J15">
-        <f>((J13-J14)/J13)*100</f>
-        <v>0.30413697989024269</v>
-      </c>
-      <c r="L15">
-        <f>((L13-L14)/L13)*100</f>
-        <v>0.38477111536437214</v>
-      </c>
-      <c r="M15">
-        <f>((M13-M14)/M13)*100</f>
-        <v>0.19344114595091852</v>
-      </c>
-      <c r="O15">
-        <f>((O13-O14)/O13)*100</f>
-        <v>2.9896415103582208</v>
-      </c>
-      <c r="P15">
-        <f>((P13-P14)/P13)*100</f>
-        <v>-7.1355912667755608E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="D22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" t="s">
+        <v>19</v>
+      </c>
+      <c r="N24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" t="s">
+        <v>18</v>
+      </c>
+      <c r="P24" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4.7158911735000002</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4.6291748970000004</v>
+      </c>
+      <c r="E25">
+        <f>((C25-D25)/C25)*100</f>
+        <v>1.8388099578566284</v>
+      </c>
+      <c r="F25" s="1">
+        <v>14.966369251</v>
+      </c>
+      <c r="G25" s="1">
+        <v>15.464017373900001</v>
+      </c>
+      <c r="H25">
+        <f>((F25-G25)/F25)*100</f>
+        <v>-3.3251092135572562</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1.1035383372000001</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1.1174958406</v>
+      </c>
+      <c r="K25">
+        <f>((I25-J25)/I25)*100</f>
+        <v>-1.264795515433943</v>
+      </c>
+      <c r="L25" s="1">
+        <v>45.087971282799998</v>
+      </c>
+      <c r="M25" s="1">
+        <v>44.8257993271</v>
+      </c>
+      <c r="N25">
+        <f>((L25-M25)/L25)*100</f>
+        <v>0.5814676248252717</v>
+      </c>
+      <c r="O25" s="1">
+        <v>21.769039145499999</v>
+      </c>
+      <c r="P25" s="1">
+        <v>22.5076772191</v>
+      </c>
+      <c r="Q25">
+        <f>((O25-P25)/O25)*100</f>
+        <v>-3.3930669546923422</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4.6941893570999902</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4.6335907109000001</v>
+      </c>
+      <c r="E26">
+        <f>((C26-D26)/C26)*100</f>
+        <v>1.2909288822858049</v>
+      </c>
+      <c r="F26" s="1">
+        <v>14.3304367599</v>
+      </c>
+      <c r="G26" s="1">
+        <v>15.5303682837</v>
+      </c>
+      <c r="H26">
+        <f>((F26-G26)/F26)*100</f>
+        <v>-8.3733074148702595</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1.1054981386</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1.1140971225</v>
+      </c>
+      <c r="K26">
+        <f>((I26-J26)/I26)*100</f>
+        <v>-0.77783793565584414</v>
+      </c>
+      <c r="L26" s="1">
+        <v>44.914485792800001</v>
+      </c>
+      <c r="M26" s="1">
+        <v>44.739087787199999</v>
+      </c>
+      <c r="N26">
+        <f>((L26-M26)/L26)*100</f>
+        <v>0.39051544842158442</v>
+      </c>
+      <c r="O26" s="1">
+        <v>21.1182229148</v>
+      </c>
+      <c r="P26" s="1">
+        <v>22.523737777600001</v>
+      </c>
+      <c r="Q26">
+        <f>((O26-P26)/O26)*100</f>
+        <v>-6.6554599242107271</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <f>((C25-C26)/C25)*100</f>
+        <v>0.46018484315242458</v>
+      </c>
+      <c r="D27">
+        <f>((D25-D26)/D25)*100</f>
+        <v>-9.5390949753516641E-2</v>
+      </c>
+      <c r="F27">
+        <f>((F25-F26)/F25)*100</f>
+        <v>4.2490765825352694</v>
+      </c>
+      <c r="G27">
+        <f>((G25-G26)/G25)*100</f>
+        <v>-0.42906644629089163</v>
+      </c>
+      <c r="I27">
+        <f>((I25-I26)/I25)*100</f>
+        <v>-0.17759250711421146</v>
+      </c>
+      <c r="J27">
+        <f>((J25-J26)/J25)*100</f>
+        <v>0.30413697989024269</v>
+      </c>
+      <c r="L27">
+        <f>((L25-L26)/L25)*100</f>
+        <v>0.38477111536437214</v>
+      </c>
+      <c r="M27">
+        <f>((M25-M26)/M25)*100</f>
+        <v>0.19344114595091852</v>
+      </c>
+      <c r="O27">
+        <f>((O25-O26)/O25)*100</f>
+        <v>2.9896415103582208</v>
+      </c>
+      <c r="P27">
+        <f>((P25-P26)/P25)*100</f>
+        <v>-7.1355912667755608E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="C10:Q10"/>
+    <mergeCell ref="C22:Q22"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="C1:AO1"/>
     <mergeCell ref="U2:W2"/>
@@ -1561,9 +1507,24 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27">
+    <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1572,8 +1533,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="colorScale" priority="75">
+  <conditionalFormatting sqref="D27">
+    <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1583,7 +1544,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E5">
-    <cfRule type="colorScale" priority="89">
+    <cfRule type="colorScale" priority="150">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:E26">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1592,8 +1563,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="colorScale" priority="39">
+  <conditionalFormatting sqref="F27">
+    <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1602,8 +1573,108 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="G27">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I27">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25:K26">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L27">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M27">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25:N26">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O27">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF3500"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P27">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q25:Q26">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1613,492 +1684,242 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="colorScale" priority="52">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K5">
-    <cfRule type="colorScale" priority="51">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L6">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M6">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N5">
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O6">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P6">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q5">
-    <cfRule type="colorScale" priority="49">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S6">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T5">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V6">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W4:W5">
-    <cfRule type="colorScale" priority="47">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X6">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y6">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB6">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE6">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF4:AF5">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG6">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH6">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI4:AI5">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK6">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AL5">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM6">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN6">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO4:AO5">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="F6:G6">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="colorScale" priority="15">
+  <conditionalFormatting sqref="I6:J6">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="L6:M6">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="O6:P6">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="R6:S6">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="U6:V6">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="X6:Y6">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M15">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="AA6:AB6">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O15">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="AD6:AE6">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P15">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="AG6:AH6">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E14">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="AJ6:AK6">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:H14">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K14">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:N14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q13:Q14">
+  <conditionalFormatting sqref="AM6:AN6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2112,17 +1933,17 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.1640625" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -2160,7 +1981,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -2169,28 +1990,28 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>15</v>
@@ -2207,43 +2028,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.0945292000000001E-2</v>
+        <v>2.5442388999999899E-2</v>
       </c>
       <c r="D5">
-        <v>7.7977030729999903</v>
+        <v>10.0966351579999</v>
       </c>
       <c r="E5">
-        <v>0.100677564</v>
+        <v>2.3308504699999899</v>
       </c>
       <c r="F5">
-        <v>1.51638297</v>
+        <v>7.1160886000000104E-2</v>
       </c>
       <c r="G5">
-        <v>5.5917888000000103E-2</v>
+        <v>0.10534255199999901</v>
       </c>
       <c r="H5">
-        <v>0.45915287100000002</v>
+        <v>0.11671878500000001</v>
       </c>
       <c r="I5">
-        <v>6.0677486629999997</v>
+        <v>0.19536178500000001</v>
       </c>
       <c r="J5">
-        <v>0.27247442699999902</v>
+        <v>1.9308818759999899</v>
       </c>
       <c r="K5">
-        <v>0.492297602</v>
+        <v>0.20881275799999899</v>
       </c>
       <c r="L5">
-        <v>3.9035411389999899</v>
+        <v>0.29738986399999801</v>
       </c>
       <c r="M5">
-        <v>1.9352582E-2</v>
+        <v>2.4405590000000001E-2</v>
       </c>
       <c r="N5">
-        <v>0.61789860100000005</v>
+        <v>0.61840965299999995</v>
       </c>
       <c r="O5">
-        <v>20.722267380000002</v>
+        <v>15.421738940999999</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2251,43 +2072,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.1359196999999899E-2</v>
+        <v>2.5527887999999901E-2</v>
       </c>
       <c r="D6">
-        <v>7.795109515</v>
+        <v>10.099466587</v>
       </c>
       <c r="E6">
-        <v>0.10401200099999899</v>
+        <v>2.3298336310000001</v>
       </c>
       <c r="F6">
-        <v>1.5165825909999899</v>
+        <v>7.1114231000000194E-2</v>
       </c>
       <c r="G6">
-        <v>5.6184010999999902E-2</v>
+        <v>0.105502281</v>
       </c>
       <c r="H6">
-        <v>0.459507095999999</v>
+        <v>0.11693131</v>
       </c>
       <c r="I6">
-        <v>6.063977951</v>
+        <v>0.19548254899999901</v>
       </c>
       <c r="J6">
-        <v>0.27396532500000098</v>
+        <v>1.9275563</v>
       </c>
       <c r="K6">
-        <v>0.49250761799999898</v>
+        <v>0.208805876</v>
       </c>
       <c r="L6">
-        <v>3.9045517169999799</v>
+        <v>0.29737015900000002</v>
       </c>
       <c r="M6">
-        <v>1.967207E-2</v>
+        <v>2.43905029999999E-2</v>
       </c>
       <c r="N6">
-        <v>0.54323971000000004</v>
+        <v>0.60543443500000005</v>
       </c>
       <c r="O6">
-        <v>20.724220821999999</v>
+        <v>15.420494411</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2295,43 +2116,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.0935884999999901E-2</v>
+        <v>2.5385048999999899E-2</v>
       </c>
       <c r="D7">
-        <v>7.7921811439999997</v>
+        <v>10.0960650269999</v>
       </c>
       <c r="E7">
-        <v>0.101148921999999</v>
+        <v>2.3300957509999898</v>
       </c>
       <c r="F7">
-        <v>1.514309538</v>
+        <v>7.1090112999999802E-2</v>
       </c>
       <c r="G7">
-        <v>5.585818E-2</v>
+        <v>0.105297339</v>
       </c>
       <c r="H7">
-        <v>0.458939813999999</v>
+        <v>0.115763148</v>
       </c>
       <c r="I7">
-        <v>6.0662435300000004</v>
+        <v>0.194802856</v>
       </c>
       <c r="J7">
-        <v>0.27186163400000002</v>
+        <v>1.930564739</v>
       </c>
       <c r="K7">
-        <v>0.491587261</v>
+        <v>0.20860229199999999</v>
       </c>
       <c r="L7">
-        <v>3.90386092699999</v>
+        <v>0.29655467600000002</v>
       </c>
       <c r="M7">
-        <v>1.93052139999999E-2</v>
+        <v>2.4209992999999999E-2</v>
       </c>
       <c r="N7">
-        <v>0.54461698599999997</v>
+        <v>0.61446489999999998</v>
       </c>
       <c r="O7">
-        <v>20.712324318</v>
+        <v>15.417055752</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2339,43 +2160,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.08336719999999E-2</v>
+        <v>2.6101022000000001E-2</v>
       </c>
       <c r="D8">
-        <v>7.7812151570000001</v>
+        <v>10.098430702</v>
       </c>
       <c r="E8">
-        <v>0.10033523599999999</v>
+        <v>2.3316661330000001</v>
       </c>
       <c r="F8">
-        <v>1.512441935</v>
+        <v>7.1733575000000105E-2</v>
       </c>
       <c r="G8">
-        <v>5.5827926999999999E-2</v>
+        <v>0.105952269</v>
       </c>
       <c r="H8">
-        <v>0.45860525600000002</v>
+        <v>0.11880186199999999</v>
       </c>
       <c r="I8">
-        <v>6.0625658989999902</v>
+        <v>0.19629432499999899</v>
       </c>
       <c r="J8">
-        <v>0.27135582499999999</v>
+        <v>1.9334173370000001</v>
       </c>
       <c r="K8">
-        <v>0.49157306899999997</v>
+        <v>0.20952352299999899</v>
       </c>
       <c r="L8">
-        <v>3.9030260699999899</v>
+        <v>0.30171195399999901</v>
       </c>
       <c r="M8">
-        <v>1.9307754E-2</v>
+        <v>2.4924894999999999E-2</v>
       </c>
       <c r="N8">
-        <v>0.54530207200000003</v>
+        <v>0.60585072799999995</v>
       </c>
       <c r="O8">
-        <v>20.693376035</v>
+        <v>15.437552728</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2383,43 +2204,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.0906497E-2</v>
+        <v>2.5467621999999902E-2</v>
       </c>
       <c r="D9">
-        <v>7.7805381919999999</v>
+        <v>10.097089739999999</v>
       </c>
       <c r="E9">
-        <v>0.100159464999999</v>
+        <v>2.33055346</v>
       </c>
       <c r="F9">
-        <v>1.5116671129999899</v>
+        <v>7.1005021000000099E-2</v>
       </c>
       <c r="G9">
-        <v>5.5745634000000002E-2</v>
+        <v>0.105564771</v>
       </c>
       <c r="H9">
-        <v>0.45859409299999998</v>
+        <v>0.116066537</v>
       </c>
       <c r="I9">
-        <v>6.0593861860000002</v>
+        <v>0.19509827699999899</v>
       </c>
       <c r="J9">
-        <v>0.27132947599999901</v>
+        <v>1.9262916639999901</v>
       </c>
       <c r="K9">
-        <v>0.49138484900000001</v>
+        <v>0.20904875099999901</v>
       </c>
       <c r="L9">
-        <v>3.9032113759999998</v>
+        <v>0.29693615399999901</v>
       </c>
       <c r="M9">
-        <v>1.9323584000000001E-2</v>
+        <v>2.4270594E-2</v>
       </c>
       <c r="N9">
-        <v>0.53678791199999998</v>
+        <v>0.61751658399999998</v>
       </c>
       <c r="O9">
-        <v>20.688285358000002</v>
+        <v>15.415884576</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2427,43 +2248,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.08305289999999E-2</v>
+        <v>2.5504596000000001E-2</v>
       </c>
       <c r="D10">
-        <v>7.7814282109999997</v>
+        <v>10.100004812</v>
       </c>
       <c r="E10">
-        <v>0.10019067299999999</v>
+        <v>2.3292280779999999</v>
       </c>
       <c r="F10">
-        <v>1.5114285030000001</v>
+        <v>7.1259157000000004E-2</v>
       </c>
       <c r="G10">
-        <v>5.5645885000000103E-2</v>
+        <v>0.10528825</v>
       </c>
       <c r="H10">
-        <v>0.45858836200000003</v>
+        <v>0.11755757999999999</v>
       </c>
       <c r="I10">
-        <v>6.0617983099999897</v>
+        <v>0.19545280199999901</v>
       </c>
       <c r="J10">
-        <v>0.27090224999999901</v>
+        <v>1.9316526859999901</v>
       </c>
       <c r="K10">
-        <v>0.49130033099999898</v>
+        <v>0.208745985999999</v>
       </c>
       <c r="L10">
-        <v>3.9017135810000001</v>
+        <v>0.297633022999999</v>
       </c>
       <c r="M10">
-        <v>1.9188847999999901E-2</v>
+        <v>2.4402429E-2</v>
       </c>
       <c r="N10">
-        <v>0.54013573299999995</v>
+        <v>0.62008680500000002</v>
       </c>
       <c r="O10">
-        <v>20.689045309000001</v>
+        <v>15.425324863</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2471,43 +2292,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.1090906E-2</v>
+        <v>2.53951529999999E-2</v>
       </c>
       <c r="D11">
-        <v>7.7843653549999896</v>
+        <v>10.099723987000001</v>
       </c>
       <c r="E11">
-        <v>0.101818195</v>
+        <v>2.32941839999999</v>
       </c>
       <c r="F11">
-        <v>1.512677534</v>
+        <v>7.0885852999999999E-2</v>
       </c>
       <c r="G11">
-        <v>5.5970686000000103E-2</v>
+        <v>0.105280375999999</v>
       </c>
       <c r="H11">
-        <v>0.45885493099999902</v>
+        <v>0.116655853</v>
       </c>
       <c r="I11">
-        <v>6.061748981</v>
+        <v>0.195017264</v>
       </c>
       <c r="J11">
-        <v>0.272130135</v>
+        <v>1.9323679599999899</v>
       </c>
       <c r="K11">
-        <v>0.49171955099999898</v>
+        <v>0.208760261999999</v>
       </c>
       <c r="L11">
-        <v>3.8977867249999898</v>
+        <v>0.29636837399999899</v>
       </c>
       <c r="M11">
-        <v>1.9382218999999899E-2</v>
+        <v>2.4179472E-2</v>
       </c>
       <c r="N11">
-        <v>0.53911805499999998</v>
+        <v>0.611222712</v>
       </c>
       <c r="O11">
-        <v>20.693866938999999</v>
+        <v>15.422380399</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2515,43 +2336,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.1049211999999901E-2</v>
+        <v>2.5459150999999999E-2</v>
       </c>
       <c r="D12">
-        <v>7.7794660599999803</v>
+        <v>10.1016256789999</v>
       </c>
       <c r="E12">
-        <v>0.10056599300000001</v>
+        <v>2.3297095759999902</v>
       </c>
       <c r="F12">
-        <v>1.511711612</v>
+        <v>7.0876266000000104E-2</v>
       </c>
       <c r="G12">
-        <v>5.5815807000000099E-2</v>
+        <v>0.105656811</v>
       </c>
       <c r="H12">
-        <v>0.45880408700000003</v>
+        <v>0.11626690299999901</v>
       </c>
       <c r="I12">
-        <v>6.0617813089999997</v>
+        <v>0.194941688999999</v>
       </c>
       <c r="J12">
-        <v>0.27180590999999898</v>
+        <v>1.9301710480000001</v>
       </c>
       <c r="K12">
-        <v>0.49144501099999999</v>
+        <v>0.20866443800000001</v>
       </c>
       <c r="L12">
-        <v>3.9043868549999901</v>
+        <v>0.29608520999999899</v>
       </c>
       <c r="M12">
-        <v>1.93601149999999E-2</v>
+        <v>2.41489599999999E-2</v>
       </c>
       <c r="N12">
-        <v>0.53863703100000004</v>
+        <v>0.62176095799999997</v>
       </c>
       <c r="O12">
-        <v>20.692317829</v>
+        <v>15.422180737</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2559,43 +2380,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.1036944999999901E-2</v>
+        <v>2.5351556000000001E-2</v>
       </c>
       <c r="D13">
-        <v>7.7869990860000096</v>
+        <v>10.0917733379999</v>
       </c>
       <c r="E13">
-        <v>0.100745107999999</v>
+        <v>2.3303256639999899</v>
       </c>
       <c r="F13">
-        <v>1.513208957</v>
+        <v>7.1009946999999796E-2</v>
       </c>
       <c r="G13">
-        <v>5.5890241000000097E-2</v>
+        <v>0.105642655</v>
       </c>
       <c r="H13">
-        <v>0.45893628199999997</v>
+        <v>0.115968692999999</v>
       </c>
       <c r="I13">
-        <v>6.0607884379999897</v>
+        <v>0.19533699800000001</v>
       </c>
       <c r="J13">
-        <v>0.27208739399999998</v>
+        <v>1.9303339069999901</v>
       </c>
       <c r="K13">
-        <v>0.491826123</v>
+        <v>0.20884250299999901</v>
       </c>
       <c r="L13">
-        <v>3.8965046640000001</v>
+        <v>0.29673680200000002</v>
       </c>
       <c r="M13">
-        <v>1.9376067999999899E-2</v>
+        <v>2.4217947999999899E-2</v>
       </c>
       <c r="N13">
-        <v>0.54174849199999997</v>
+        <v>0.61045812600000005</v>
       </c>
       <c r="O13">
-        <v>20.693725327999999</v>
+        <v>15.414110351</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2603,87 +2424,87 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.1146714E-2</v>
+        <v>2.5502058000000001E-2</v>
       </c>
       <c r="D14">
-        <v>7.7893656160000004</v>
+        <v>10.099553321999901</v>
       </c>
       <c r="E14">
-        <v>0.10103263</v>
+        <v>2.330985192</v>
       </c>
       <c r="F14">
-        <v>1.5128756209999901</v>
+        <v>7.1190351000000096E-2</v>
       </c>
       <c r="G14">
-        <v>5.5926254000000002E-2</v>
+        <v>0.105847889</v>
       </c>
       <c r="H14">
-        <v>0.45909798600000001</v>
+        <v>0.116869266999999</v>
       </c>
       <c r="I14">
-        <v>6.0629500860000096</v>
+        <v>0.195518261</v>
       </c>
       <c r="J14">
-        <v>0.27244211800000001</v>
+        <v>1.9271281440000001</v>
       </c>
       <c r="K14">
-        <v>0.49190621499999898</v>
+        <v>0.209259116999999</v>
       </c>
       <c r="L14">
-        <v>3.89601520899999</v>
+        <v>0.29808918699999898</v>
       </c>
       <c r="M14">
-        <v>1.9431583999999901E-2</v>
+        <v>2.4367838999999999E-2</v>
       </c>
       <c r="N14">
-        <v>0.54003348799999995</v>
+        <v>0.61301483700000003</v>
       </c>
       <c r="O14">
-        <v>20.698236467000001</v>
+        <v>15.422933222999999</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="1">
-        <v>2.10134848999999E-2</v>
-      </c>
-      <c r="D15" s="1">
-        <v>7.7868371409000003</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.10106857869999999</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1.5133286373999999</v>
-      </c>
-      <c r="G15" s="1">
-        <v>5.5878251300000001E-2</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.45890807779999998</v>
-      </c>
-      <c r="I15" s="1">
-        <v>6.0628989352999998</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0.27203544940000002</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0.49175476299999998</v>
-      </c>
-      <c r="L15" s="1">
-        <v>3.9014598262999902</v>
-      </c>
-      <c r="M15" s="1">
-        <v>1.93700037999999E-2</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0.54875180800000001</v>
-      </c>
-      <c r="O15" s="1">
-        <v>20.700766578500001</v>
+      <c r="C15">
+        <v>2.5502058000000001E-2</v>
+      </c>
+      <c r="D15">
+        <v>10.099553321999901</v>
+      </c>
+      <c r="E15">
+        <v>2.330985192</v>
+      </c>
+      <c r="F15">
+        <v>7.1190351000000096E-2</v>
+      </c>
+      <c r="G15">
+        <v>0.105847889</v>
+      </c>
+      <c r="H15">
+        <v>0.116869266999999</v>
+      </c>
+      <c r="I15">
+        <v>0.195518261</v>
+      </c>
+      <c r="J15">
+        <v>1.9271281440000001</v>
+      </c>
+      <c r="K15">
+        <v>0.209259116999999</v>
+      </c>
+      <c r="L15">
+        <v>0.29808918699999898</v>
+      </c>
+      <c r="M15">
+        <v>2.4367838999999999E-2</v>
+      </c>
+      <c r="N15">
+        <v>0.61301483700000003</v>
+      </c>
+      <c r="O15">
+        <v>15.422933222999999</v>
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
@@ -2695,14 +2516,14 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -2725,237 +2546,77 @@
       </c>
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20">
-        <v>45.178059114</v>
-      </c>
-      <c r="G20">
-        <v>20.935805562999999</v>
-      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21">
-        <v>44.446670339999997</v>
-      </c>
-      <c r="G21">
-        <v>25.681944958999999</v>
-      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22">
-        <v>44.993960194000003</v>
-      </c>
-      <c r="G22">
-        <v>20.587326808</v>
-      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23">
-        <v>44.808145336999999</v>
-      </c>
-      <c r="G23">
-        <v>21.655821433</v>
-      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <v>44.748611527000001</v>
-      </c>
-      <c r="G24">
-        <v>21.545505545000001</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
     </row>
     <row r="25" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25">
-        <v>44.639488767000003</v>
-      </c>
-      <c r="G25">
-        <v>21.058005052999999</v>
-      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26">
-        <v>44.722949407000002</v>
-      </c>
-      <c r="G26">
-        <v>22.522632615999999</v>
-      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>7</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27">
-        <v>44.645210781000003</v>
-      </c>
-      <c r="G27">
-        <v>21.857823479</v>
-      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28">
-        <v>47.971052186999998</v>
-      </c>
-      <c r="G28">
-        <v>22.030840081000001</v>
-      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>9</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29">
-        <v>44.725565174000003</v>
-      </c>
-      <c r="G29">
-        <v>19.814685917999999</v>
-      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1">
-        <v>4.7158911735000002</v>
-      </c>
-      <c r="D30" s="1">
-        <v>14.966369251</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1.1035383372000001</v>
-      </c>
-      <c r="F30" s="1">
-        <v>45.087971282799998</v>
-      </c>
-      <c r="G30" s="1">
-        <v>21.769039145499999</v>
-      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2976,6 +2637,11 @@
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -3013,7 +2679,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -3022,28 +2688,28 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>15</v>
@@ -3060,43 +2726,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.1101384000000001E-2</v>
+        <v>2.5658337E-2</v>
       </c>
       <c r="D5">
-        <v>7.79302745099998</v>
+        <v>10.093682463</v>
       </c>
       <c r="E5">
-        <v>0.100698307</v>
+        <v>2.3356965279999899</v>
       </c>
       <c r="F5">
-        <v>1.5172041649999899</v>
+        <v>6.9424951999999804E-2</v>
       </c>
       <c r="G5">
-        <v>5.5791908000000001E-2</v>
+        <v>0.58602730300000105</v>
       </c>
       <c r="H5">
-        <v>0.45921943500000001</v>
+        <v>0.119650152</v>
       </c>
       <c r="I5">
-        <v>6.0636783699999901</v>
+        <v>0.67160559399999997</v>
       </c>
       <c r="J5">
-        <v>0.27255087899999902</v>
+        <v>5.0263704220000003</v>
       </c>
       <c r="K5">
-        <v>0.49235883599999802</v>
+        <v>9.9511652299999902</v>
       </c>
       <c r="L5">
-        <v>3.9059577489999899</v>
+        <v>0.375086950999999</v>
       </c>
       <c r="M5">
-        <v>1.94064139999999E-2</v>
+        <v>2.38158279999999E-2</v>
       </c>
       <c r="N5">
-        <v>0.61528601199999999</v>
+        <v>0.58706498600000001</v>
       </c>
       <c r="O5">
-        <v>20.717549983000001</v>
+        <v>29.296331703</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -3104,43 +2770,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.1279628999999901E-2</v>
+        <v>2.6117731000000002E-2</v>
       </c>
       <c r="D6">
-        <v>7.79709311199999</v>
+        <v>10.093207673</v>
       </c>
       <c r="E6">
-        <v>0.101755966</v>
+        <v>2.3354211849999902</v>
       </c>
       <c r="F6">
-        <v>1.5162854719999901</v>
+        <v>6.9868729999999907E-2</v>
       </c>
       <c r="G6">
-        <v>5.60827320000001E-2</v>
+        <v>0.58612498400000002</v>
       </c>
       <c r="H6">
-        <v>0.45925363499999999</v>
+        <v>0.120571596999999</v>
       </c>
       <c r="I6">
-        <v>6.0638862659999901</v>
+        <v>0.67255381299999795</v>
       </c>
       <c r="J6">
-        <v>0.27413057499999899</v>
+        <v>5.02376399799999</v>
       </c>
       <c r="K6">
-        <v>0.492675635</v>
+        <v>9.9486751629999901</v>
       </c>
       <c r="L6">
-        <v>3.9011064999999898</v>
+        <v>0.37712743699999901</v>
       </c>
       <c r="M6">
-        <v>1.9632154999999998E-2</v>
+        <v>2.40840149999999E-2</v>
       </c>
       <c r="N6">
-        <v>0.54432430300000001</v>
+        <v>0.58786943700000005</v>
       </c>
       <c r="O6">
-        <v>20.719638375999999</v>
+        <v>29.295960938</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -3148,43 +2814,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.0974719999999902E-2</v>
+        <v>2.5716586999999898E-2</v>
       </c>
       <c r="D7">
-        <v>7.7970552969999902</v>
+        <v>10.0858451799999</v>
       </c>
       <c r="E7">
-        <v>0.101015059</v>
+        <v>2.334463183</v>
       </c>
       <c r="F7">
-        <v>1.51517175599999</v>
+        <v>6.9381901999999898E-2</v>
       </c>
       <c r="G7">
-        <v>5.5776628000000002E-2</v>
+        <v>0.58605405499999996</v>
       </c>
       <c r="H7">
-        <v>0.45908050299999897</v>
+        <v>0.119483336999999</v>
       </c>
       <c r="I7">
-        <v>6.0662717739999996</v>
+        <v>0.67152304200000001</v>
       </c>
       <c r="J7">
-        <v>0.27210804100000002</v>
+        <v>5.0294800439999898</v>
       </c>
       <c r="K7">
-        <v>0.49236375399999999</v>
+        <v>9.9507343529999801</v>
       </c>
       <c r="L7">
-        <v>3.9055599729999999</v>
+        <v>0.37440991299999998</v>
       </c>
       <c r="M7">
-        <v>1.93282919999999E-2</v>
+        <v>2.3655680999999901E-2</v>
       </c>
       <c r="N7">
-        <v>0.54036128100000003</v>
+        <v>0.59000862700000001</v>
       </c>
       <c r="O7">
-        <v>20.720896796000002</v>
+        <v>29.289230675999999</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -3192,43 +2858,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.0956139999999901E-2</v>
+        <v>2.5602241000000001E-2</v>
       </c>
       <c r="D8">
-        <v>7.7877697669999897</v>
+        <v>10.0942111739999</v>
       </c>
       <c r="E8">
-        <v>9.9885357999999896E-2</v>
+        <v>2.3348518619999998</v>
       </c>
       <c r="F8">
-        <v>1.51211037499999</v>
+        <v>6.9413334000000104E-2</v>
       </c>
       <c r="G8">
-        <v>5.5762935999999999E-2</v>
+        <v>0.58577078400000004</v>
       </c>
       <c r="H8">
-        <v>0.45854220199999901</v>
+        <v>0.11941281499999901</v>
       </c>
       <c r="I8">
-        <v>6.0622401990000103</v>
+        <v>0.67177803199999897</v>
       </c>
       <c r="J8">
-        <v>0.27117142399999999</v>
+        <v>5.0270572470000001</v>
       </c>
       <c r="K8">
-        <v>0.491552883</v>
+        <v>9.9493412180000007</v>
       </c>
       <c r="L8">
-        <v>3.8963203659999901</v>
+        <v>0.37423348699999898</v>
       </c>
       <c r="M8">
-        <v>1.9265055E-2</v>
+        <v>2.36104579999999E-2</v>
       </c>
       <c r="N8">
-        <v>0.550553124</v>
+        <v>0.57972277400000005</v>
       </c>
       <c r="O8">
-        <v>20.691628844</v>
+        <v>29.293794720000001</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -3236,43 +2902,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.0884650000000001E-2</v>
+        <v>2.5563717999999999E-2</v>
       </c>
       <c r="D9">
-        <v>7.7794520330000099</v>
+        <v>10.089171578</v>
       </c>
       <c r="E9">
-        <v>0.10029113200000001</v>
+        <v>2.3348916059999998</v>
       </c>
       <c r="F9">
-        <v>1.5121290780000001</v>
+        <v>6.9234457999999999E-2</v>
       </c>
       <c r="G9">
-        <v>5.5753456999999999E-2</v>
+        <v>0.58554126699999998</v>
       </c>
       <c r="H9">
-        <v>0.45871501999999897</v>
+        <v>0.11848811300000001</v>
       </c>
       <c r="I9">
-        <v>6.0606006370000101</v>
+        <v>0.67167505500000002</v>
       </c>
       <c r="J9">
-        <v>0.27122294399999902</v>
+        <v>5.0229294330000096</v>
       </c>
       <c r="K9">
-        <v>0.49128346099999998</v>
+        <v>9.9507623999999897</v>
       </c>
       <c r="L9">
-        <v>3.9011952289999901</v>
+        <v>0.374504591</v>
       </c>
       <c r="M9">
-        <v>1.9221643999999899E-2</v>
+        <v>2.3632976999999999E-2</v>
       </c>
       <c r="N9">
-        <v>0.54035476100000002</v>
+        <v>0.58698483199999996</v>
       </c>
       <c r="O9">
-        <v>20.686977975000001</v>
+        <v>29.284437164</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -3280,43 +2946,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.0807343999999901E-2</v>
+        <v>2.5582337999999899E-2</v>
       </c>
       <c r="D10">
-        <v>7.7878391180000097</v>
+        <v>10.091677192000001</v>
       </c>
       <c r="E10">
-        <v>9.9926715000000096E-2</v>
+        <v>2.3338897409999899</v>
       </c>
       <c r="F10">
-        <v>1.5117757669999901</v>
+        <v>6.9303388999999896E-2</v>
       </c>
       <c r="G10">
-        <v>5.5649369999999997E-2</v>
+        <v>0.58556129800000001</v>
       </c>
       <c r="H10">
-        <v>0.45859571700000001</v>
+        <v>0.119283062</v>
       </c>
       <c r="I10">
-        <v>6.0603357109999996</v>
+        <v>0.67143237300000103</v>
       </c>
       <c r="J10">
-        <v>0.27112144100000002</v>
+        <v>5.0257071829999997</v>
       </c>
       <c r="K10">
-        <v>0.49142884599999898</v>
+        <v>9.9482321210000002</v>
       </c>
       <c r="L10">
-        <v>3.9000256759999998</v>
+        <v>0.373783804</v>
       </c>
       <c r="M10">
-        <v>1.9312329999999999E-2</v>
+        <v>2.3626337000000001E-2</v>
       </c>
       <c r="N10">
-        <v>0.53915951100000004</v>
+        <v>0.585429219</v>
       </c>
       <c r="O10">
-        <v>20.692864118999999</v>
+        <v>29.285996446999999</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -3324,43 +2990,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.1106718999999899E-2</v>
+        <v>2.5649974999999901E-2</v>
       </c>
       <c r="D11">
-        <v>7.7843844669999802</v>
+        <v>10.092924089</v>
       </c>
       <c r="E11">
-        <v>0.100622691</v>
+        <v>2.3345521119999999</v>
       </c>
       <c r="F11">
-        <v>1.51220974199999</v>
+        <v>6.9512702999999898E-2</v>
       </c>
       <c r="G11">
-        <v>5.5990173999999997E-2</v>
+        <v>0.58594524999999897</v>
       </c>
       <c r="H11">
-        <v>0.458783633999999</v>
+        <v>0.11947503900000001</v>
       </c>
       <c r="I11">
-        <v>6.0625688519999903</v>
+        <v>0.67165192299999898</v>
       </c>
       <c r="J11">
-        <v>0.271670675999999</v>
+        <v>5.0327991549999904</v>
       </c>
       <c r="K11">
-        <v>0.49157911700000001</v>
+        <v>9.9519940199999901</v>
       </c>
       <c r="L11">
-        <v>3.89965502799999</v>
+        <v>0.37499023199999898</v>
       </c>
       <c r="M11">
-        <v>1.9355522999999899E-2</v>
+        <v>2.3805277E-2</v>
       </c>
       <c r="N11">
-        <v>0.53928374499999998</v>
+        <v>0.590182557</v>
       </c>
       <c r="O11">
-        <v>20.694036471</v>
+        <v>29.301290112</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -3368,43 +3034,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.1055265999999899E-2</v>
+        <v>2.5590978999999899E-2</v>
       </c>
       <c r="D12">
-        <v>7.7870121919999997</v>
+        <v>10.090467065</v>
       </c>
       <c r="E12">
-        <v>0.10130739499999999</v>
+        <v>2.3349920929999901</v>
       </c>
       <c r="F12">
-        <v>1.51215378999999</v>
+        <v>6.9451468999999905E-2</v>
       </c>
       <c r="G12">
-        <v>5.5870721999999901E-2</v>
+        <v>0.58626539</v>
       </c>
       <c r="H12">
-        <v>0.45870782199999999</v>
+        <v>0.119900559999999</v>
       </c>
       <c r="I12">
-        <v>6.0600565519999998</v>
+        <v>0.67195465299999901</v>
       </c>
       <c r="J12">
-        <v>0.272015848</v>
+        <v>5.0288948449999902</v>
       </c>
       <c r="K12">
-        <v>0.491494870999999</v>
+        <v>9.9484108240000104</v>
       </c>
       <c r="L12">
-        <v>3.902312512</v>
+        <v>0.37497456699999798</v>
       </c>
       <c r="M12">
-        <v>1.9278192999999999E-2</v>
+        <v>2.3692873999999999E-2</v>
       </c>
       <c r="N12">
-        <v>0.53867469499999998</v>
+        <v>0.58494116900000004</v>
       </c>
       <c r="O12">
-        <v>20.697453193000001</v>
+        <v>29.292886993</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -3412,43 +3078,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.1009811999999999E-2</v>
+        <v>2.5695407999999999E-2</v>
       </c>
       <c r="D13">
-        <v>7.78079164399999</v>
+        <v>10.096569122</v>
       </c>
       <c r="E13">
-        <v>0.101113538999999</v>
+        <v>2.3356758239999902</v>
       </c>
       <c r="F13">
-        <v>1.5124974799999999</v>
+        <v>6.9783545000000002E-2</v>
       </c>
       <c r="G13">
-        <v>5.5813125999999998E-2</v>
+        <v>0.58585584799999901</v>
       </c>
       <c r="H13">
-        <v>0.45869143800000001</v>
+        <v>0.11943102799999999</v>
       </c>
       <c r="I13">
-        <v>6.0603539730000104</v>
+        <v>0.67184591299999996</v>
       </c>
       <c r="J13">
-        <v>0.27183335199999897</v>
+        <v>5.0319200479999999</v>
       </c>
       <c r="K13">
-        <v>0.491635667</v>
+        <v>9.9486950479999905</v>
       </c>
       <c r="L13">
-        <v>3.900215749</v>
+        <v>0.37527459000000002</v>
       </c>
       <c r="M13">
-        <v>1.9421697000000002E-2</v>
+        <v>2.3776411000000001E-2</v>
       </c>
       <c r="N13">
-        <v>0.53861486400000003</v>
+        <v>0.58932202600000005</v>
       </c>
       <c r="O13">
-        <v>20.689566696</v>
+        <v>29.302501491000001</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -3456,43 +3122,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.1267149999999999E-2</v>
+        <v>2.5868881999999899E-2</v>
       </c>
       <c r="D14">
-        <v>7.78856586200002</v>
+        <v>10.0974611769999</v>
       </c>
       <c r="E14">
-        <v>0.101402716</v>
+        <v>2.3352196699999999</v>
       </c>
       <c r="F14">
-        <v>1.5126722690000001</v>
+        <v>6.9648502000000001E-2</v>
       </c>
       <c r="G14">
-        <v>5.60558099999999E-2</v>
+        <v>0.58641217499999898</v>
       </c>
       <c r="H14">
-        <v>0.45901620999999998</v>
+        <v>0.12063270499999899</v>
       </c>
       <c r="I14">
-        <v>6.0629085410000103</v>
+        <v>0.67236594999999999</v>
       </c>
       <c r="J14">
-        <v>0.272708176999999</v>
+        <v>5.0378034949999799</v>
       </c>
       <c r="K14">
-        <v>0.49192058099999902</v>
+        <v>9.9517345579999894</v>
       </c>
       <c r="L14">
-        <v>3.8957304859999899</v>
+        <v>0.375970167999998</v>
       </c>
       <c r="M14">
-        <v>1.9526368999999998E-2</v>
+        <v>2.38891579999999E-2</v>
       </c>
       <c r="N14">
-        <v>0.54182851099999996</v>
+        <v>0.58628258099999997</v>
       </c>
       <c r="O14">
-        <v>20.698456970999999</v>
+        <v>29.315214963999999</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -3500,43 +3166,43 @@
         <v>22</v>
       </c>
       <c r="C15" s="1">
-        <v>2.1044281399999899E-2</v>
+        <v>2.5704619599999898E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>7.7882990942999903</v>
+        <v>10.0925216713</v>
       </c>
       <c r="E15" s="1">
-        <v>0.1008018878</v>
+        <v>2.3349653803999901</v>
       </c>
       <c r="F15" s="1">
-        <v>1.5134209893999899</v>
+        <v>6.9502298399999898E-2</v>
       </c>
       <c r="G15" s="1">
-        <v>5.5854686299999998E-2</v>
+        <v>0.58595583539999996</v>
       </c>
       <c r="H15" s="1">
-        <v>0.45886056159999999</v>
+        <v>0.1196328408</v>
       </c>
       <c r="I15" s="1">
-        <v>6.0622900875000001</v>
+        <v>0.67183863479999895</v>
       </c>
       <c r="J15" s="1">
-        <v>0.27205333569999901</v>
+        <v>5.028672587</v>
       </c>
       <c r="K15" s="1">
-        <v>0.49182936509999903</v>
+        <v>9.9499744934999903</v>
       </c>
       <c r="L15" s="1">
-        <v>3.9008079268000002</v>
+        <v>0.37503557399999898</v>
       </c>
       <c r="M15" s="1">
-        <v>1.93747672E-2</v>
+        <v>2.3758901599999899E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.54884408070000001</v>
+        <v>0.58678082080000005</v>
       </c>
       <c r="O15" s="1">
-        <v>20.7009069424</v>
+        <v>29.295764520799999</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
@@ -3569,225 +3235,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>4.8237869980000001</v>
-      </c>
-      <c r="D20">
-        <v>16.405531232999898</v>
-      </c>
-      <c r="E20">
-        <v>1.153891198</v>
-      </c>
-      <c r="F20">
-        <v>44.99530566</v>
-      </c>
-      <c r="G20">
-        <v>23.770921220999998</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>4.6673217520000003</v>
-      </c>
-      <c r="D21">
-        <v>14.449837002999899</v>
-      </c>
-      <c r="E21">
-        <v>1.1181004369999901</v>
-      </c>
-      <c r="F21">
-        <v>45.118839434999998</v>
-      </c>
-      <c r="G21">
-        <v>21.509625474</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>4.7014450299999897</v>
-      </c>
-      <c r="D22">
-        <v>15.184039253</v>
-      </c>
-      <c r="E22">
-        <v>1.1095911629999999</v>
-      </c>
-      <c r="F22">
-        <v>44.721127103000001</v>
-      </c>
-      <c r="G22">
-        <v>22.276340040000001</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>4.4885547370000003</v>
-      </c>
-      <c r="D23">
-        <v>15.4021777489999</v>
-      </c>
-      <c r="E23">
-        <v>1.10351937899999</v>
-      </c>
-      <c r="F23">
-        <v>44.616166184999997</v>
-      </c>
-      <c r="G23">
-        <v>22.257800827000001</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24">
-        <v>4.7220404680000003</v>
-      </c>
-      <c r="D24">
-        <v>16.394596872000001</v>
-      </c>
-      <c r="E24">
-        <v>1.12422092099999</v>
-      </c>
-      <c r="F24">
-        <v>44.595392926000002</v>
-      </c>
-      <c r="G24">
-        <v>23.554986079999999</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>4.8406276199999896</v>
-      </c>
-      <c r="D25">
-        <v>15.607468506999901</v>
-      </c>
-      <c r="E25">
-        <v>1.1448489749999899</v>
-      </c>
-      <c r="F25">
-        <v>44.5322107</v>
-      </c>
-      <c r="G25">
-        <v>22.953275693999998</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>4.4273572260000096</v>
-      </c>
-      <c r="D26">
-        <v>14.531455789000001</v>
-      </c>
-      <c r="E26">
-        <v>1.09781243699999</v>
-      </c>
-      <c r="F26">
-        <v>44.845106297000001</v>
-      </c>
-      <c r="G26">
-        <v>21.291217564</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>7</v>
-      </c>
-      <c r="C27">
-        <v>4.4705501949999897</v>
-      </c>
-      <c r="D27">
-        <v>15.201100657</v>
-      </c>
-      <c r="E27">
-        <v>1.0945569470000001</v>
-      </c>
-      <c r="F27">
-        <v>44.662393252999998</v>
-      </c>
-      <c r="G27">
-        <v>21.995210685</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>4.59382215000001</v>
-      </c>
-      <c r="D28">
-        <v>15.862654592999901</v>
-      </c>
-      <c r="E28">
-        <v>1.1204468359999999</v>
-      </c>
-      <c r="F28">
-        <v>45.072985840999998</v>
-      </c>
-      <c r="G28">
-        <v>22.860605258</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>9</v>
-      </c>
-      <c r="C29">
-        <v>4.5562427940000001</v>
-      </c>
-      <c r="D29">
-        <v>15.6013120829999</v>
-      </c>
-      <c r="E29">
-        <v>1.1079701129999999</v>
-      </c>
-      <c r="F29">
-        <v>45.098465871000002</v>
-      </c>
-      <c r="G29">
-        <v>22.606789348</v>
-      </c>
-    </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="1">
-        <v>4.6291748970000004</v>
-      </c>
-      <c r="D30" s="1">
-        <v>15.464017373900001</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1.1174958406</v>
-      </c>
-      <c r="F30" s="1">
-        <v>44.8257993271</v>
-      </c>
-      <c r="G30" s="1">
-        <v>22.5076772191</v>
-      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3802,6 +3258,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE3BDD0-3A87-544A-A16E-D142A4C1F8FB}">
   <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -3838,7 +3307,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -3847,28 +3316,28 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>15</v>
@@ -3885,43 +3354,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.1066069999999999E-2</v>
+        <v>2.5381299999999999E-2</v>
       </c>
       <c r="D5">
-        <v>7.7994737460000003</v>
+        <v>10.094796578999899</v>
       </c>
       <c r="E5">
-        <v>0.101644125</v>
+        <v>2.3297894640000001</v>
       </c>
       <c r="F5">
-        <v>1.5162155929999901</v>
+        <v>7.1154372999999896E-2</v>
       </c>
       <c r="G5">
-        <v>5.5874482000000003E-2</v>
+        <v>0.10554603999999999</v>
       </c>
       <c r="H5">
-        <v>0.45912639099999902</v>
+        <v>0.116100254</v>
       </c>
       <c r="I5">
-        <v>6.0657522789999998</v>
+        <v>0.19477443699999999</v>
       </c>
       <c r="J5">
-        <v>0.27239945999999998</v>
+        <v>1.9261226809999901</v>
       </c>
       <c r="K5">
-        <v>0.49202833999999901</v>
+        <v>0.20856348599999999</v>
       </c>
       <c r="L5">
-        <v>3.9017833849999999</v>
+        <v>0.29711332899999998</v>
       </c>
       <c r="M5">
-        <v>1.9374984000000001E-2</v>
+        <v>2.4299680999999899E-2</v>
       </c>
       <c r="N5">
-        <v>0.616310998</v>
+        <v>0.61107526700000003</v>
       </c>
       <c r="O5">
-        <v>20.72091713</v>
+        <v>15.41287142</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -3929,43 +3398,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.2013108999999999E-2</v>
+        <v>2.5593776999999901E-2</v>
       </c>
       <c r="D6">
-        <v>7.8010432889999999</v>
+        <v>10.100115025999999</v>
       </c>
       <c r="E6">
-        <v>0.101714957999999</v>
+        <v>2.330984489</v>
       </c>
       <c r="F6">
-        <v>1.51559118599999</v>
+        <v>7.1201850999999997E-2</v>
       </c>
       <c r="G6">
-        <v>5.6949554999999999E-2</v>
+        <v>0.105698706</v>
       </c>
       <c r="H6">
-        <v>0.45848459899999999</v>
+        <v>0.116485776</v>
       </c>
       <c r="I6">
-        <v>6.0653772449999996</v>
+        <v>0.19517368800000001</v>
       </c>
       <c r="J6">
-        <v>0.27441423099999901</v>
+        <v>1.926507255</v>
       </c>
       <c r="K6">
-        <v>0.493028518999999</v>
+        <v>0.208958596999999</v>
       </c>
       <c r="L6">
-        <v>3.8995791579999901</v>
+        <v>0.297431798999999</v>
       </c>
       <c r="M6">
-        <v>2.0546848E-2</v>
+        <v>2.4301185999999898E-2</v>
       </c>
       <c r="N6">
-        <v>0.55257705899999998</v>
+        <v>0.61642061800000003</v>
       </c>
       <c r="O6">
-        <v>20.726886456999999</v>
+        <v>15.421131693</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -3973,43 +3442,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.1102395999999898E-2</v>
+        <v>2.5385094E-2</v>
       </c>
       <c r="D7">
-        <v>7.7918346869999997</v>
+        <v>10.099606200999901</v>
       </c>
       <c r="E7">
-        <v>0.101059461</v>
+        <v>2.33054201499999</v>
       </c>
       <c r="F7">
-        <v>1.513774784</v>
+        <v>7.0956227999999996E-2</v>
       </c>
       <c r="G7">
-        <v>5.5743058999999998E-2</v>
+        <v>0.105521774999999</v>
       </c>
       <c r="H7">
-        <v>0.45918726999999998</v>
+        <v>0.116174641999999</v>
       </c>
       <c r="I7">
-        <v>6.0655896979999904</v>
+        <v>0.195038249</v>
       </c>
       <c r="J7">
-        <v>0.27184363299999997</v>
+        <v>1.9270152439999899</v>
       </c>
       <c r="K7">
-        <v>0.49198598100000002</v>
+        <v>0.20866674900000001</v>
       </c>
       <c r="L7">
-        <v>3.9020698170000001</v>
+        <v>0.29660057899999898</v>
       </c>
       <c r="M7">
-        <v>1.9253632999999899E-2</v>
+        <v>2.4239949E-2</v>
       </c>
       <c r="N7">
-        <v>0.54308842300000004</v>
+        <v>0.627401451</v>
       </c>
       <c r="O7">
-        <v>20.709690736999999</v>
+        <v>15.418322413</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -4017,43 +3486,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.0968386999999901E-2</v>
+        <v>2.6014560999999901E-2</v>
       </c>
       <c r="D8">
-        <v>7.7860453190000101</v>
+        <v>10.102088583</v>
       </c>
       <c r="E8">
-        <v>0.100349826</v>
+        <v>2.3322300930000002</v>
       </c>
       <c r="F8">
-        <v>1.512698646</v>
+        <v>7.1691403999999903E-2</v>
       </c>
       <c r="G8">
-        <v>5.5743950000000098E-2</v>
+        <v>0.10630519099999999</v>
       </c>
       <c r="H8">
-        <v>0.45916385300000001</v>
+        <v>0.118632460999999</v>
       </c>
       <c r="I8">
-        <v>6.0618285339999902</v>
+        <v>0.19646021399999999</v>
       </c>
       <c r="J8">
-        <v>0.27276218800000002</v>
+        <v>1.93047126799999</v>
       </c>
       <c r="K8">
-        <v>0.49155756699999997</v>
+        <v>0.20953254999999901</v>
       </c>
       <c r="L8">
-        <v>3.8938646370000001</v>
+        <v>0.30036306699999898</v>
       </c>
       <c r="M8">
-        <v>1.9304002000000001E-2</v>
+        <v>2.4989052000000001E-2</v>
       </c>
       <c r="N8">
-        <v>0.54494798700000002</v>
+        <v>0.606074903</v>
       </c>
       <c r="O8">
-        <v>20.690456955999998</v>
+        <v>15.438222739</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -4061,43 +3530,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.0973215999999899E-2</v>
+        <v>2.5452000999999901E-2</v>
       </c>
       <c r="D9">
-        <v>7.7813027589999901</v>
+        <v>10.099061013999901</v>
       </c>
       <c r="E9">
-        <v>0.101126643</v>
+        <v>2.33031469499999</v>
       </c>
       <c r="F9">
-        <v>1.5121788599999899</v>
+        <v>7.1123694999999806E-2</v>
       </c>
       <c r="G9">
-        <v>5.5740315999999998E-2</v>
+        <v>0.105617700999999</v>
       </c>
       <c r="H9">
-        <v>0.45859746899999898</v>
+        <v>0.117144761</v>
       </c>
       <c r="I9">
-        <v>6.0613853170000001</v>
+        <v>0.19552296</v>
       </c>
       <c r="J9">
-        <v>0.27138312999999897</v>
+        <v>1.9273427089999999</v>
       </c>
       <c r="K9">
-        <v>0.49132802600000097</v>
+        <v>0.208768761999999</v>
       </c>
       <c r="L9">
-        <v>3.9025352089999998</v>
+        <v>0.29684469199999902</v>
       </c>
       <c r="M9">
-        <v>1.9322946999999899E-2</v>
+        <v>2.4375148999999999E-2</v>
       </c>
       <c r="N9">
-        <v>0.53796646000000004</v>
+        <v>0.61160619699999996</v>
       </c>
       <c r="O9">
-        <v>20.692053219000002</v>
+        <v>15.420349859</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -4105,43 +3574,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.095733E-2</v>
+        <v>2.56382449999999E-2</v>
       </c>
       <c r="D10">
-        <v>7.7859232969999903</v>
+        <v>10.1002633769999</v>
       </c>
       <c r="E10">
-        <v>0.101294805</v>
+        <v>2.3293710559999998</v>
       </c>
       <c r="F10">
-        <v>1.51144327999999</v>
+        <v>7.1283706000000002E-2</v>
       </c>
       <c r="G10">
-        <v>5.5792281000000103E-2</v>
+        <v>0.105543874</v>
       </c>
       <c r="H10">
-        <v>0.45866275299999898</v>
+        <v>0.116905810999999</v>
       </c>
       <c r="I10">
-        <v>6.0614671599999896</v>
+        <v>0.19579743999999999</v>
       </c>
       <c r="J10">
-        <v>0.27114375799999901</v>
+        <v>1.9320005089999901</v>
       </c>
       <c r="K10">
-        <v>0.491510909</v>
+        <v>0.20879339699999999</v>
       </c>
       <c r="L10">
-        <v>3.9005954509999898</v>
+        <v>0.29746052699999898</v>
       </c>
       <c r="M10">
-        <v>1.9233350999999999E-2</v>
+        <v>2.4490805000000001E-2</v>
       </c>
       <c r="N10">
-        <v>0.54721948499999995</v>
+        <v>0.61472893100000003</v>
       </c>
       <c r="O10">
-        <v>20.694206857000001</v>
+        <v>15.426239952</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -4149,43 +3618,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.10826109999999E-2</v>
+        <v>2.53563159999999E-2</v>
       </c>
       <c r="D11">
-        <v>7.7838895780000099</v>
+        <v>10.097232775</v>
       </c>
       <c r="E11">
-        <v>0.10192346100000001</v>
+        <v>2.330120403</v>
       </c>
       <c r="F11">
-        <v>1.512189867</v>
+        <v>7.0971029000000005E-2</v>
       </c>
       <c r="G11">
-        <v>5.5874761000000002E-2</v>
+        <v>0.105499201</v>
       </c>
       <c r="H11">
-        <v>0.45884820900000001</v>
+        <v>0.116216875</v>
       </c>
       <c r="I11">
-        <v>6.0617735640000001</v>
+        <v>0.19511076799999999</v>
       </c>
       <c r="J11">
-        <v>0.271952155999999</v>
+        <v>1.92850694699999</v>
       </c>
       <c r="K11">
-        <v>0.49183482699999898</v>
+        <v>0.208701631</v>
       </c>
       <c r="L11">
-        <v>3.8974218359999999</v>
+        <v>0.296478294999999</v>
       </c>
       <c r="M11">
-        <v>1.9351515E-2</v>
+        <v>2.4226696999999998E-2</v>
       </c>
       <c r="N11">
-        <v>0.53907629400000001</v>
+        <v>0.60892937800000002</v>
       </c>
       <c r="O11">
-        <v>20.692990059</v>
+        <v>15.41752153</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -4193,43 +3662,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.1112009000000001E-2</v>
+        <v>2.5323974999999999E-2</v>
       </c>
       <c r="D12">
-        <v>7.7827500570000003</v>
+        <v>10.097166528000001</v>
       </c>
       <c r="E12">
-        <v>0.101276436</v>
+        <v>2.329730944</v>
       </c>
       <c r="F12">
-        <v>1.511931492</v>
+        <v>7.0901585999999697E-2</v>
       </c>
       <c r="G12">
-        <v>5.5863916999999999E-2</v>
+        <v>0.10541447499999999</v>
       </c>
       <c r="H12">
-        <v>0.45887003999999998</v>
+        <v>0.115732273999999</v>
       </c>
       <c r="I12">
-        <v>6.0604057690000097</v>
+        <v>0.19492797099999901</v>
       </c>
       <c r="J12">
-        <v>0.27196870099999998</v>
+        <v>1.929590127</v>
       </c>
       <c r="K12">
-        <v>0.491854862</v>
+        <v>0.208779138</v>
       </c>
       <c r="L12">
-        <v>3.9037895489999901</v>
+        <v>0.296267271</v>
       </c>
       <c r="M12">
-        <v>1.9461340000000001E-2</v>
+        <v>2.4160647999999899E-2</v>
       </c>
       <c r="N12">
-        <v>0.54147638300000001</v>
+        <v>0.60954544300000002</v>
       </c>
       <c r="O12">
-        <v>20.695688261000001</v>
+        <v>15.416608752</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -4237,43 +3706,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.1062636999999901E-2</v>
+        <v>2.5499583999999902E-2</v>
       </c>
       <c r="D13">
-        <v>7.7881428579999898</v>
+        <v>10.0966702959999</v>
       </c>
       <c r="E13">
-        <v>0.10146572199999999</v>
+        <v>2.3306569259999899</v>
       </c>
       <c r="F13">
-        <v>1.5128203149999899</v>
+        <v>7.1235964999999998E-2</v>
       </c>
       <c r="G13">
-        <v>5.5973003999999903E-2</v>
+        <v>0.105333591</v>
       </c>
       <c r="H13">
-        <v>0.45890385499999897</v>
+        <v>0.11550263700000001</v>
       </c>
       <c r="I13">
-        <v>6.0601249340000001</v>
+        <v>0.19574702399999899</v>
       </c>
       <c r="J13">
-        <v>0.27200566399999998</v>
+        <v>1.933645957</v>
       </c>
       <c r="K13">
-        <v>0.49187511699999997</v>
+        <v>0.20902261999999999</v>
       </c>
       <c r="L13">
-        <v>3.89971205599999</v>
+        <v>0.29678373799999902</v>
       </c>
       <c r="M13">
-        <v>1.9399731E-2</v>
+        <v>2.4227780000000001E-2</v>
       </c>
       <c r="N13">
-        <v>0.53865003</v>
+        <v>0.61620193499999998</v>
       </c>
       <c r="O13">
-        <v>20.697728300000001</v>
+        <v>15.423123092999999</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -4281,43 +3750,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.1142463E-2</v>
+        <v>2.5569718999999901E-2</v>
       </c>
       <c r="D14">
-        <v>7.7880382399999997</v>
+        <v>10.1044150259999</v>
       </c>
       <c r="E14">
-        <v>0.101517158</v>
+        <v>2.3313113250000002</v>
       </c>
       <c r="F14">
-        <v>1.512929634</v>
+        <v>7.1269200999999796E-2</v>
       </c>
       <c r="G14">
-        <v>5.6057263999999898E-2</v>
+        <v>0.10592581399999999</v>
       </c>
       <c r="H14">
-        <v>0.458944827000001</v>
+        <v>0.116995985</v>
       </c>
       <c r="I14">
-        <v>6.0638440610000002</v>
+        <v>0.19550161399999999</v>
       </c>
       <c r="J14">
-        <v>0.27262192800000001</v>
+        <v>1.928080375</v>
       </c>
       <c r="K14">
-        <v>0.491883189</v>
+        <v>0.20926946299999999</v>
       </c>
       <c r="L14">
-        <v>3.895199383</v>
+        <v>0.29795526499999903</v>
       </c>
       <c r="M14">
-        <v>1.947805E-2</v>
+        <v>2.44459509999999E-2</v>
       </c>
       <c r="N14">
-        <v>0.54294027499999997</v>
+        <v>0.61003646600000005</v>
       </c>
       <c r="O14">
-        <v>20.697993238999999</v>
+        <v>15.429712941</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -4325,43 +3794,43 @@
         <v>21</v>
       </c>
       <c r="C15" s="1">
-        <v>2.1148022799999899E-2</v>
+        <v>2.5521457199999899E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>7.7888443829999998</v>
+        <v>10.0991415404999</v>
       </c>
       <c r="E15" s="1">
-        <v>0.1013372595</v>
+        <v>2.3305051410000002</v>
       </c>
       <c r="F15" s="1">
-        <v>1.5131773657000001</v>
+        <v>7.1178903799999901E-2</v>
       </c>
       <c r="G15" s="1">
-        <v>5.5961258899999998E-2</v>
+        <v>0.10564063680000001</v>
       </c>
       <c r="H15" s="1">
-        <v>0.45887892660000001</v>
+        <v>0.1165891476</v>
       </c>
       <c r="I15" s="1">
-        <v>6.0627548560999998</v>
+        <v>0.1954054365</v>
       </c>
       <c r="J15" s="1">
-        <v>0.27224948490000001</v>
+        <v>1.9289283071999901</v>
       </c>
       <c r="K15" s="1">
-        <v>0.49188873370000002</v>
+        <v>0.2089056393</v>
       </c>
       <c r="L15" s="1">
-        <v>3.8996550481000001</v>
+        <v>0.29732985619999902</v>
       </c>
       <c r="M15" s="1">
-        <v>1.9472640100000001E-2</v>
+        <v>2.4375689799999999E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.55042533940000005</v>
+        <v>0.61320205890000001</v>
       </c>
       <c r="O15" s="1">
-        <v>20.701861121499999</v>
+        <v>15.422410439199901</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -4373,13 +3842,13 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4401,225 +3870,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>4.6006060579999897</v>
-      </c>
-      <c r="D20">
-        <v>15.542913898</v>
-      </c>
-      <c r="E20">
-        <v>1.0821381290000001</v>
-      </c>
-      <c r="F20">
-        <v>44.868074825000001</v>
-      </c>
-      <c r="G20">
-        <v>22.239466582999999</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>4.6237777609999897</v>
-      </c>
-      <c r="D21">
-        <v>14.005688256999999</v>
-      </c>
-      <c r="E21">
-        <v>1.0931326799999901</v>
-      </c>
-      <c r="F21">
-        <v>45.367524641000003</v>
-      </c>
-      <c r="G21">
-        <v>20.678480005000001</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>4.5162472820000001</v>
-      </c>
-      <c r="D22">
-        <v>14.3467801379999</v>
-      </c>
-      <c r="E22">
-        <v>1.1148718719999899</v>
-      </c>
-      <c r="F22">
-        <v>44.413765368</v>
-      </c>
-      <c r="G22">
-        <v>20.931622545</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>4.8416728419999897</v>
-      </c>
-      <c r="D23">
-        <v>14.1692157299999</v>
-      </c>
-      <c r="E23">
-        <v>1.12419611599999</v>
-      </c>
-      <c r="F23">
-        <v>45.201858715999997</v>
-      </c>
-      <c r="G23">
-        <v>21.150967145999999</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24">
-        <v>4.8448703529999904</v>
-      </c>
-      <c r="D24">
-        <v>13.885040346</v>
-      </c>
-      <c r="E24">
-        <v>1.1458932610000001</v>
-      </c>
-      <c r="F24">
-        <v>44.601139498000002</v>
-      </c>
-      <c r="G24">
-        <v>20.890493974999998</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>4.7523815999999899</v>
-      </c>
-      <c r="D25">
-        <v>14.416007534999901</v>
-      </c>
-      <c r="E25">
-        <v>1.104802775</v>
-      </c>
-      <c r="F25">
-        <v>44.893572736000003</v>
-      </c>
-      <c r="G25">
-        <v>21.308788703000001</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>4.7771238329999903</v>
-      </c>
-      <c r="D26">
-        <v>14.535514169000001</v>
-      </c>
-      <c r="E26">
-        <v>1.13063033</v>
-      </c>
-      <c r="F26">
-        <v>45.022300168999998</v>
-      </c>
-      <c r="G26">
-        <v>21.462349112999998</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>7</v>
-      </c>
-      <c r="C27">
-        <v>4.6711723949999797</v>
-      </c>
-      <c r="D27">
-        <v>14.424652171999901</v>
-      </c>
-      <c r="E27">
-        <v>1.07934710399999</v>
-      </c>
-      <c r="F27">
-        <v>45.100189931999999</v>
-      </c>
-      <c r="G27">
-        <v>21.122489199</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>4.5969812780000003</v>
-      </c>
-      <c r="D28">
-        <v>14.396043703999901</v>
-      </c>
-      <c r="E28">
-        <v>1.09079157099999</v>
-      </c>
-      <c r="F28">
-        <v>44.191400801</v>
-      </c>
-      <c r="G28">
-        <v>21.039077846000001</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>9</v>
-      </c>
-      <c r="C29">
-        <v>4.7170601689999998</v>
-      </c>
-      <c r="D29">
-        <v>13.582511649999899</v>
-      </c>
-      <c r="E29">
-        <v>1.0891775480000001</v>
-      </c>
-      <c r="F29">
-        <v>45.485031241999998</v>
-      </c>
-      <c r="G29">
-        <v>20.358494032999999</v>
-      </c>
-    </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1">
-        <v>4.6941893570999902</v>
-      </c>
-      <c r="D30" s="1">
-        <v>14.3304367599</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1.1054981386</v>
-      </c>
-      <c r="F30" s="1">
-        <v>44.914485792800001</v>
-      </c>
-      <c r="G30" s="1">
-        <v>21.1182229148</v>
-      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4634,6 +3893,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF611A7-FF5C-9946-82AC-26D645B98B8C}">
   <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -4717,43 +3987,43 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.1042589E-2</v>
+        <v>2.56602529999999E-2</v>
       </c>
       <c r="D5">
-        <v>7.7889424449999902</v>
+        <v>10.092411062999901</v>
       </c>
       <c r="E5">
-        <v>0.100951946999999</v>
+        <v>2.3350925139999998</v>
       </c>
       <c r="F5">
-        <v>1.5158345339999999</v>
+        <v>6.9307840999999995E-2</v>
       </c>
       <c r="G5">
-        <v>5.5972837000000199E-2</v>
+        <v>0.58615123199999897</v>
       </c>
       <c r="H5">
-        <v>0.45902342800000101</v>
+        <v>0.118665115</v>
       </c>
       <c r="I5">
-        <v>6.0615342429999997</v>
+        <v>0.67143337400000003</v>
       </c>
       <c r="J5">
-        <v>0.27380757500000003</v>
+        <v>5.0247875339999899</v>
       </c>
       <c r="K5">
-        <v>0.49236302999999798</v>
+        <v>9.9494871550000106</v>
       </c>
       <c r="L5">
-        <v>3.9015166990000001</v>
+        <v>0.37495494899999998</v>
       </c>
       <c r="M5">
-        <v>1.9348687999999899E-2</v>
+        <v>2.3633946999999898E-2</v>
       </c>
       <c r="N5">
-        <v>0.61524506599999995</v>
+        <v>0.61694170800000003</v>
       </c>
       <c r="O5">
-        <v>20.706959798</v>
+        <v>29.289828121999999</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -4761,43 +4031,43 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.1353419999999901E-2</v>
+        <v>2.6009707999999899E-2</v>
       </c>
       <c r="D6">
-        <v>7.79279711299999</v>
+        <v>10.092801394</v>
       </c>
       <c r="E6">
-        <v>0.101451716999999</v>
+        <v>2.3346325109999899</v>
       </c>
       <c r="F6">
-        <v>1.5155008459999999</v>
+        <v>6.9917533000000101E-2</v>
       </c>
       <c r="G6">
-        <v>5.6154192000000103E-2</v>
+        <v>0.58645207299999802</v>
       </c>
       <c r="H6">
-        <v>0.45903085100000002</v>
+        <v>0.121546468</v>
       </c>
       <c r="I6">
-        <v>6.0616481880000004</v>
+        <v>0.67245170300000001</v>
       </c>
       <c r="J6">
-        <v>0.27378674200000003</v>
+        <v>5.0252363259999902</v>
       </c>
       <c r="K6">
-        <v>0.492847905999999</v>
+        <v>9.9493611210000008</v>
       </c>
       <c r="L6">
-        <v>3.8941756330000001</v>
+        <v>0.37690058399999898</v>
       </c>
       <c r="M6">
-        <v>1.9657917999999899E-2</v>
+        <v>2.4019788E-2</v>
       </c>
       <c r="N6">
-        <v>0.54726605800000006</v>
+        <v>0.59299689600000005</v>
       </c>
       <c r="O6">
-        <v>20.704733495999999</v>
+        <v>29.297806472000001</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -4805,43 +4075,43 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.0981407000000001E-2</v>
+        <v>2.5633884999999999E-2</v>
       </c>
       <c r="D7">
-        <v>7.7878332510000199</v>
+        <v>10.093617110999901</v>
       </c>
       <c r="E7">
-        <v>0.10093611299999999</v>
+        <v>2.335474472</v>
       </c>
       <c r="F7">
-        <v>1.515356916</v>
+        <v>6.9390459000000002E-2</v>
       </c>
       <c r="G7">
-        <v>5.5867665999999899E-2</v>
+        <v>0.58617621600000103</v>
       </c>
       <c r="H7">
-        <v>0.45886558199999899</v>
+        <v>0.11867947199999999</v>
       </c>
       <c r="I7">
-        <v>6.0629193100000096</v>
+        <v>0.67159537300000005</v>
       </c>
       <c r="J7">
-        <v>0.272240977</v>
+        <v>5.0303447039999796</v>
       </c>
       <c r="K7">
-        <v>0.49222443199999999</v>
+        <v>9.9532243119999695</v>
       </c>
       <c r="L7">
-        <v>3.8956862029999999</v>
+        <v>0.37461931999999898</v>
       </c>
       <c r="M7">
-        <v>1.9402821000000001E-2</v>
+        <v>2.3737149999999901E-2</v>
       </c>
       <c r="N7">
-        <v>0.55455117300000001</v>
+        <v>0.601366505</v>
       </c>
       <c r="O7">
-        <v>20.698519548</v>
+        <v>29.300475652999999</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -4849,43 +4119,43 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.0956864999999901E-2</v>
+        <v>2.5570568999999901E-2</v>
       </c>
       <c r="D8">
-        <v>7.7949866609999896</v>
+        <v>10.0915633889999</v>
       </c>
       <c r="E8">
-        <v>0.101300022</v>
+        <v>2.3350707679999898</v>
       </c>
       <c r="F8">
-        <v>1.51590531099999</v>
+        <v>6.9348543999999998E-2</v>
       </c>
       <c r="G8">
-        <v>5.5848188000000097E-2</v>
+        <v>0.58588457599999999</v>
       </c>
       <c r="H8">
-        <v>0.458857927</v>
+        <v>0.11797352899999899</v>
       </c>
       <c r="I8">
-        <v>6.0650248729999898</v>
+        <v>0.67163842600000101</v>
       </c>
       <c r="J8">
-        <v>0.271976990999999</v>
+        <v>5.0294728649999998</v>
       </c>
       <c r="K8">
-        <v>0.49213513599999997</v>
+        <v>9.9503148849999992</v>
       </c>
       <c r="L8">
-        <v>3.8964746520000002</v>
+        <v>0.374501948999999</v>
       </c>
       <c r="M8">
-        <v>1.9164344999999899E-2</v>
+        <v>2.3681457999999898E-2</v>
       </c>
       <c r="N8">
-        <v>0.548205426</v>
+        <v>0.59512648800000001</v>
       </c>
       <c r="O8">
-        <v>20.708969687</v>
+        <v>29.293122816</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -4893,43 +4163,43 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.0996747E-2</v>
+        <v>2.5600774999999999E-2</v>
       </c>
       <c r="D9">
-        <v>7.7998079390000097</v>
+        <v>10.0941521719999</v>
       </c>
       <c r="E9">
-        <v>0.10090756400000001</v>
+        <v>2.33452129699999</v>
       </c>
       <c r="F9">
-        <v>1.5161694799999901</v>
+        <v>6.9463336000000001E-2</v>
       </c>
       <c r="G9">
-        <v>5.5789725999999998E-2</v>
+        <v>0.58592276199999904</v>
       </c>
       <c r="H9">
-        <v>0.45893492999999902</v>
+        <v>0.118419817</v>
       </c>
       <c r="I9">
-        <v>6.0662951339999998</v>
+        <v>0.67170904399999898</v>
       </c>
       <c r="J9">
-        <v>0.27210715099999999</v>
+        <v>5.0216696289999998</v>
       </c>
       <c r="K9">
-        <v>0.49207820800000002</v>
+        <v>9.9507542880000006</v>
       </c>
       <c r="L9">
-        <v>3.8898433239999899</v>
+        <v>0.37420821799999998</v>
       </c>
       <c r="M9">
-        <v>1.9294316999999998E-2</v>
+        <v>2.3578144999999901E-2</v>
       </c>
       <c r="N9">
-        <v>0.55612084299999998</v>
+        <v>0.60293921699999997</v>
       </c>
       <c r="O9">
-        <v>20.708475618000001</v>
+        <v>29.288165759000002</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -4937,43 +4207,43 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.0857225999999899E-2</v>
+        <v>2.5533976999999899E-2</v>
       </c>
       <c r="D10">
-        <v>7.7925777399999898</v>
+        <v>10.093131085</v>
       </c>
       <c r="E10">
-        <v>0.100856243</v>
+        <v>2.3343073539999901</v>
       </c>
       <c r="F10">
-        <v>1.5150176310000001</v>
+        <v>6.9289595999999995E-2</v>
       </c>
       <c r="G10">
-        <v>5.5715932000000003E-2</v>
+        <v>0.58555464099999999</v>
       </c>
       <c r="H10">
-        <v>0.45881665199999999</v>
+        <v>0.11845826999999901</v>
       </c>
       <c r="I10">
-        <v>6.0656675150000003</v>
+        <v>0.67179013700000001</v>
       </c>
       <c r="J10">
-        <v>0.271613084</v>
+        <v>5.0332886299999799</v>
       </c>
       <c r="K10">
-        <v>0.492251412</v>
+        <v>9.9511270870000104</v>
       </c>
       <c r="L10">
-        <v>3.9026557720000001</v>
+        <v>0.37405508399999898</v>
       </c>
       <c r="M10">
-        <v>1.91470919999999E-2</v>
+        <v>2.363258E-2</v>
       </c>
       <c r="N10">
-        <v>0.54054987300000001</v>
+        <v>0.61195766600000001</v>
       </c>
       <c r="O10">
-        <v>20.71121874</v>
+        <v>29.298625094999998</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -4981,43 +4251,43 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.1145300999999901E-2</v>
+        <v>2.5679405999999998E-2</v>
       </c>
       <c r="D11">
-        <v>7.7946861409999801</v>
+        <v>10.094681947</v>
       </c>
       <c r="E11">
-        <v>0.10150352999999999</v>
+        <v>2.3351234269999899</v>
       </c>
       <c r="F11">
-        <v>1.5156918319999999</v>
+        <v>6.9546087999999895E-2</v>
       </c>
       <c r="G11">
-        <v>5.5788429E-2</v>
+        <v>0.58555205499999996</v>
       </c>
       <c r="H11">
-        <v>0.45897850600000001</v>
+        <v>0.119074282</v>
       </c>
       <c r="I11">
-        <v>6.0672738399999897</v>
+        <v>0.67183946899999802</v>
       </c>
       <c r="J11">
-        <v>0.27248283299999998</v>
+        <v>5.02385722799999</v>
       </c>
       <c r="K11">
-        <v>0.49234507700000002</v>
+        <v>9.9518861309999807</v>
       </c>
       <c r="L11">
-        <v>3.90366275199999</v>
+        <v>0.37504373199999902</v>
       </c>
       <c r="M11">
-        <v>1.94385929999999E-2</v>
+        <v>2.3730856000000002E-2</v>
       </c>
       <c r="N11">
-        <v>0.54143225800000006</v>
+        <v>0.58939027099999997</v>
       </c>
       <c r="O11">
-        <v>20.719628178000001</v>
+        <v>29.294494213</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -5025,43 +4295,43 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>2.1019667999999998E-2</v>
+        <v>2.5762748999999901E-2</v>
       </c>
       <c r="D12">
-        <v>7.7841760030000096</v>
+        <v>10.0950343149999</v>
       </c>
       <c r="E12">
-        <v>0.101018384</v>
+        <v>2.3347884059999999</v>
       </c>
       <c r="F12">
-        <v>1.5131399320000001</v>
+        <v>6.9538956999999901E-2</v>
       </c>
       <c r="G12">
-        <v>5.5908588000000099E-2</v>
+        <v>0.58609643300000003</v>
       </c>
       <c r="H12">
-        <v>0.45871410000000001</v>
+        <v>0.11914034999999901</v>
       </c>
       <c r="I12">
-        <v>6.0621998450000003</v>
+        <v>0.672118726000002</v>
       </c>
       <c r="J12">
-        <v>0.27208021499999901</v>
+        <v>5.0355684829999898</v>
       </c>
       <c r="K12">
-        <v>0.491994816</v>
+        <v>9.9512275350000099</v>
       </c>
       <c r="L12">
-        <v>3.9061300939999999</v>
+        <v>0.37515184299999899</v>
       </c>
       <c r="M12">
-        <v>1.9380764000000002E-2</v>
+        <v>2.3844536E-2</v>
       </c>
       <c r="N12">
-        <v>0.53954938200000002</v>
+        <v>0.61086826699999996</v>
       </c>
       <c r="O12">
-        <v>20.702092305000001</v>
+        <v>29.306426054999999</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -5069,43 +4339,43 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>2.1795710999999902E-2</v>
+        <v>2.5682871999999898E-2</v>
       </c>
       <c r="D13">
-        <v>7.7842876979999804</v>
+        <v>10.0932550689999</v>
       </c>
       <c r="E13">
-        <v>0.100048781999999</v>
+        <v>2.3355567700000002</v>
       </c>
       <c r="F13">
-        <v>1.5122951069999999</v>
+        <v>6.9579199000000203E-2</v>
       </c>
       <c r="G13">
-        <v>5.6704179000000098E-2</v>
+        <v>0.58595544200000105</v>
       </c>
       <c r="H13">
-        <v>0.45760545999999902</v>
+        <v>0.11927326299999901</v>
       </c>
       <c r="I13">
-        <v>6.060382626</v>
+        <v>0.67227896499999895</v>
       </c>
       <c r="J13">
-        <v>0.27251588799999898</v>
+        <v>5.0231090989999903</v>
       </c>
       <c r="K13">
-        <v>0.49164730800000001</v>
+        <v>9.9506232679999993</v>
       </c>
       <c r="L13">
-        <v>3.9049001079999899</v>
+        <v>0.37516839699999899</v>
       </c>
       <c r="M13">
-        <v>2.0220420999999999E-2</v>
+        <v>2.3715185999999899E-2</v>
       </c>
       <c r="N13">
-        <v>0.56252935400000004</v>
+        <v>0.58962568299999996</v>
       </c>
       <c r="O13">
-        <v>20.699717342</v>
+        <v>29.292425865999999</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -5113,43 +4383,43 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2.1231373000000001E-2</v>
+        <v>2.5864326999999899E-2</v>
       </c>
       <c r="D14">
-        <v>7.7825284329999702</v>
+        <v>10.100539513999999</v>
       </c>
       <c r="E14">
-        <v>0.101947862</v>
+        <v>2.3363436459999898</v>
       </c>
       <c r="F14">
-        <v>1.512921725</v>
+        <v>6.9665846000000003E-2</v>
       </c>
       <c r="G14">
-        <v>5.5964560999999899E-2</v>
+        <v>0.58644216900000001</v>
       </c>
       <c r="H14">
-        <v>0.45894390499999899</v>
+        <v>0.119712631</v>
       </c>
       <c r="I14">
-        <v>6.0632913069999903</v>
+        <v>0.67236185500000001</v>
       </c>
       <c r="J14">
-        <v>0.27248361399999999</v>
+        <v>5.0264629949999904</v>
       </c>
       <c r="K14">
-        <v>0.49159298099999899</v>
+        <v>9.9527652489999898</v>
       </c>
       <c r="L14">
-        <v>3.9014519409999999</v>
+        <v>0.37620061999999999</v>
       </c>
       <c r="M14">
-        <v>1.9455838E-2</v>
+        <v>2.3802161999999901E-2</v>
       </c>
       <c r="N14">
-        <v>0.54230343400000003</v>
+        <v>0.59647256599999998</v>
       </c>
       <c r="O14">
-        <v>20.698155360000001</v>
+        <v>29.308607068000001</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -5157,43 +4427,43 @@
         <v>21</v>
       </c>
       <c r="C15" s="1">
-        <v>2.1138030700000001E-2</v>
+        <v>2.5699852099999899E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>7.7902623423999904</v>
+        <v>10.0941187058999</v>
       </c>
       <c r="E15" s="1">
-        <v>0.1010922164</v>
+        <v>2.3350911164999899</v>
       </c>
       <c r="F15" s="1">
-        <v>1.5147833314000001</v>
+        <v>6.9504739900000001E-2</v>
       </c>
       <c r="G15" s="1">
-        <v>5.59714298E-2</v>
+        <v>0.58601875989999996</v>
       </c>
       <c r="H15" s="1">
-        <v>0.45877713409999998</v>
+        <v>0.11909431970000001</v>
       </c>
       <c r="I15" s="1">
-        <v>6.0636236880999999</v>
+        <v>0.6719217072</v>
       </c>
       <c r="J15" s="1">
-        <v>0.27250950699999998</v>
+        <v>5.0273797492999899</v>
       </c>
       <c r="K15" s="1">
-        <v>0.49214803059999901</v>
+        <v>9.9510771030999994</v>
       </c>
       <c r="L15" s="1">
-        <v>3.8996497178</v>
+        <v>0.37508046959999902</v>
       </c>
       <c r="M15" s="1">
-        <v>1.9451079699999999E-2</v>
+        <v>2.3737580799999901E-2</v>
       </c>
       <c r="N15" s="1">
-        <v>0.55477528669999998</v>
+        <v>0.60076852670000003</v>
       </c>
       <c r="O15" s="1">
-        <v>20.705847007199999</v>
+        <v>29.296997711900001</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
@@ -5226,225 +4496,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>4.6821826419999999</v>
-      </c>
-      <c r="D20">
-        <v>15.9062169909999</v>
-      </c>
-      <c r="E20">
-        <v>1.121482047</v>
-      </c>
-      <c r="F20">
-        <v>44.397116122</v>
-      </c>
-      <c r="G20">
-        <v>22.945172749000001</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>4.9315779149999903</v>
-      </c>
-      <c r="D21">
-        <v>16.390990083999998</v>
-      </c>
-      <c r="E21">
-        <v>1.192110045</v>
-      </c>
-      <c r="F21">
-        <v>45.113467712999999</v>
-      </c>
-      <c r="G21">
-        <v>23.885588552000002</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>4.4953373430000001</v>
-      </c>
-      <c r="D22">
-        <v>15.650422679999901</v>
-      </c>
-      <c r="E22">
-        <v>1.1235293309999901</v>
-      </c>
-      <c r="F22">
-        <v>44.746627072000003</v>
-      </c>
-      <c r="G22">
-        <v>22.479247667999999</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>4.5581672070000003</v>
-      </c>
-      <c r="D23">
-        <v>14.377298114</v>
-      </c>
-      <c r="E23">
-        <v>1.10439433899999</v>
-      </c>
-      <c r="F23">
-        <v>45.184373686000001</v>
-      </c>
-      <c r="G23">
-        <v>21.237795102</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24">
-        <v>4.5335301469999996</v>
-      </c>
-      <c r="D24">
-        <v>15.151445159</v>
-      </c>
-      <c r="E24">
-        <v>1.0928487359999901</v>
-      </c>
-      <c r="F24">
-        <v>44.322336700000001</v>
-      </c>
-      <c r="G24">
-        <v>21.952346764000001</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>4.7823800330000097</v>
-      </c>
-      <c r="D25">
-        <v>15.646650354999901</v>
-      </c>
-      <c r="E25">
-        <v>1.1116416419999999</v>
-      </c>
-      <c r="F25">
-        <v>44.701800239000001</v>
-      </c>
-      <c r="G25">
-        <v>22.869030379000002</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>4.4649637659999897</v>
-      </c>
-      <c r="D26">
-        <v>15.741240229999899</v>
-      </c>
-      <c r="E26">
-        <v>1.0914018059999899</v>
-      </c>
-      <c r="F26">
-        <v>44.399810017</v>
-      </c>
-      <c r="G26">
-        <v>22.544032024</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>7</v>
-      </c>
-      <c r="C27">
-        <v>4.7631122550000002</v>
-      </c>
-      <c r="D27">
-        <v>15.3062458429999</v>
-      </c>
-      <c r="E27">
-        <v>1.126965164</v>
-      </c>
-      <c r="F27">
-        <v>44.695782704000003</v>
-      </c>
-      <c r="G27">
-        <v>22.480037155000002</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>4.5826042339999997</v>
-      </c>
-      <c r="D28">
-        <v>15.840817636999899</v>
-      </c>
-      <c r="E28">
-        <v>1.099819111</v>
-      </c>
-      <c r="F28">
-        <v>45.131765295999998</v>
-      </c>
-      <c r="G28">
-        <v>22.729038668000001</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>9</v>
-      </c>
-      <c r="C29">
-        <v>4.5420515669999997</v>
-      </c>
-      <c r="D29">
-        <v>15.2923557439999</v>
-      </c>
-      <c r="E29">
-        <v>1.076779004</v>
-      </c>
-      <c r="F29">
-        <v>44.697798323000001</v>
-      </c>
-      <c r="G29">
-        <v>22.115088714999999</v>
-      </c>
-    </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1">
-        <v>4.6335907109000001</v>
-      </c>
-      <c r="D30" s="1">
-        <v>15.5303682837</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1.1140971225</v>
-      </c>
-      <c r="F30" s="1">
-        <v>44.739087787199999</v>
-      </c>
-      <c r="G30" s="1">
-        <v>22.523737777600001</v>
-      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754DAB99-1EEA-314D-B189-92C1CD16F1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A87567-1EA1-4546-BBAC-E465585AE33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55460" yWindow="1100" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="54880" yWindow="1100" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="58">
   <si>
     <t>Branch</t>
   </si>
@@ -155,12 +155,75 @@
   <si>
     <t>surface-physics</t>
   </si>
+  <si>
+    <t>kernel</t>
+  </si>
+  <si>
+    <t>num_regs</t>
+  </si>
+  <si>
+    <t>occupancy</t>
+  </si>
+  <si>
+    <t>local_mem</t>
+  </si>
+  <si>
+    <t>rng-reseed</t>
+  </si>
+  <si>
+    <t>Track/Ranlux++</t>
+  </si>
+  <si>
+    <t>Track/Xorwow</t>
+  </si>
+  <si>
+    <t>Trackslot/Ranlux++</t>
+  </si>
+  <si>
+    <t>Trackslot/Xorwow</t>
+  </si>
+  <si>
+    <t>annihil-2-gamma</t>
+  </si>
+  <si>
+    <t>brems-rel</t>
+  </si>
+  <si>
+    <t>brems-sb</t>
+  </si>
+  <si>
+    <t>conv-bethe-heitler</t>
+  </si>
+  <si>
+    <t>extend-from-primaries</t>
+  </si>
+  <si>
+    <t>extend-from-secondaries</t>
+  </si>
+  <si>
+    <t>geo-boundary</t>
+  </si>
+  <si>
+    <t>ioni-moller-bhabha</t>
+  </si>
+  <si>
+    <t>photoel-livermore</t>
+  </si>
+  <si>
+    <t>physics-discrete-select</t>
+  </si>
+  <si>
+    <t>scat-klein-nishina</t>
+  </si>
+  <si>
+    <t>scat-rayleigh</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -178,6 +241,20 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -208,15 +285,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,12 +639,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71848BA-D8C3-7041-A0EE-B663A4811CD2}">
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:BG35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="3" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="43" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
@@ -573,47 +666,47 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -622,71 +715,71 @@
       <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4" t="s">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4" t="s">
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4" t="s">
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4" t="s">
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4" t="s">
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4" t="s">
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4" t="s">
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="4" t="s">
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AN2" s="4"/>
-      <c r="AO2" s="4"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
@@ -818,7 +911,7 @@
         <v>2.5704619599999898E-2</v>
       </c>
       <c r="E4">
-        <f>(ABS(D4-C4)/C4)*100</f>
+        <f>((D4-C4)/C4)*100</f>
         <v>0.79429511139805808</v>
       </c>
       <c r="F4">
@@ -828,8 +921,8 @@
         <v>10.0925216713</v>
       </c>
       <c r="H4">
-        <f>(ABS(G4-F4)/F4)*100</f>
-        <v>6.9623383091443877E-2</v>
+        <f>((G4-F4)/F4)*100</f>
+        <v>-6.9623383091443877E-2</v>
       </c>
       <c r="I4">
         <v>2.330985192</v>
@@ -838,7 +931,7 @@
         <v>2.3349653803999901</v>
       </c>
       <c r="K4">
-        <f>(ABS(J4-I4)/I4)*100</f>
+        <f>((J4-I4)/I4)*100</f>
         <v>0.17075133783132793</v>
       </c>
       <c r="L4">
@@ -848,8 +941,8 @@
         <v>6.9502298399999898E-2</v>
       </c>
       <c r="N4">
-        <f>(ABS(M4-L4)/L4)*100</f>
-        <v>2.3711817350081552</v>
+        <f>((M4-L4)/L4)*100</f>
+        <v>-2.3711817350081552</v>
       </c>
       <c r="O4">
         <v>0.105847889</v>
@@ -858,7 +951,7 @@
         <v>0.58595583539999996</v>
       </c>
       <c r="Q4">
-        <f>(ABS(P4-O4)/O4)*100</f>
+        <f>((P4-O4)/O4)*100</f>
         <v>453.58292067591447</v>
       </c>
       <c r="R4">
@@ -868,7 +961,7 @@
         <v>0.1196328408</v>
       </c>
       <c r="T4">
-        <f>(ABS(S4-R4)/R4)*100</f>
+        <f>((S4-R4)/R4)*100</f>
         <v>2.3646711158041445</v>
       </c>
       <c r="U4">
@@ -878,7 +971,7 @@
         <v>0.67183863479999895</v>
       </c>
       <c r="W4">
-        <f>(ABS(V4-U4)/U4)*100</f>
+        <f>((V4-U4)/U4)*100</f>
         <v>243.61937926606197</v>
       </c>
       <c r="X4">
@@ -888,7 +981,7 @@
         <v>5.028672587</v>
       </c>
       <c r="Z4">
-        <f>(ABS(Y4-X4)/X4)*100</f>
+        <f>((Y4-X4)/X4)*100</f>
         <v>160.94126655025386</v>
       </c>
       <c r="AA4">
@@ -898,7 +991,7 @@
         <v>9.9499744934999903</v>
       </c>
       <c r="AC4">
-        <f>(ABS(AB4-AA4)/AA4)*100</f>
+        <f>((AB4-AA4)/AA4)*100</f>
         <v>4654.8583001523602</v>
       </c>
       <c r="AD4">
@@ -908,7 +1001,7 @@
         <v>0.37503557399999898</v>
       </c>
       <c r="AF4">
-        <f>(ABS(AE4-AD4)/AD4)*100</f>
+        <f>((AE4-AD4)/AD4)*100</f>
         <v>25.813209722364157</v>
       </c>
       <c r="AG4">
@@ -918,8 +1011,8 @@
         <v>2.3758901599999899E-2</v>
       </c>
       <c r="AI4">
-        <f>(ABS(AH4-AG4)/AG4)*100</f>
-        <v>2.4989388677432558</v>
+        <f>((AH4-AG4)/AG4)*100</f>
+        <v>-2.4989388677432558</v>
       </c>
       <c r="AJ4">
         <v>0.61301483700000003</v>
@@ -928,8 +1021,8 @@
         <v>0.58678082080000005</v>
       </c>
       <c r="AL4">
-        <f>(ABS(AK4-AJ4)/AJ4)*100</f>
-        <v>4.2795075447741544</v>
+        <f>((AK4-AJ4)/AJ4)*100</f>
+        <v>-4.2795075447741544</v>
       </c>
       <c r="AM4">
         <v>15.422933222999999</v>
@@ -938,7 +1031,7 @@
         <v>29.295764520799999</v>
       </c>
       <c r="AO4">
-        <f>(ABS(AN4-AM4)/AM4)*100</f>
+        <f>((AN4-AM4)/AM4)*100</f>
         <v>89.949370182784989</v>
       </c>
     </row>
@@ -953,7 +1046,7 @@
         <v>2.5699852099999899E-2</v>
       </c>
       <c r="E5">
-        <f>(ABS(D5-C5)/C5)*100</f>
+        <f>((D5-C5)/C5)*100</f>
         <v>0.69899966370259103</v>
       </c>
       <c r="F5" s="2">
@@ -963,8 +1056,8 @@
         <v>10.0941187058999</v>
       </c>
       <c r="H5">
-        <f>(ABS(G5-F5)/F5)*100</f>
-        <v>4.97352629414822E-2</v>
+        <f>((G5-F5)/F5)*100</f>
+        <v>-4.97352629414822E-2</v>
       </c>
       <c r="I5" s="2">
         <v>2.3305051410000002</v>
@@ -973,7 +1066,7 @@
         <v>2.3350911164999899</v>
       </c>
       <c r="K5">
-        <f>(ABS(J5-I5)/I5)*100</f>
+        <f>((J5-I5)/I5)*100</f>
         <v>0.19678032111192567</v>
       </c>
       <c r="L5" s="2">
@@ -983,8 +1076,8 @@
         <v>6.9504739900000001E-2</v>
       </c>
       <c r="N5">
-        <f>(ABS(M5-L5)/L5)*100</f>
-        <v>2.352050692862599</v>
+        <f>((M5-L5)/L5)*100</f>
+        <v>-2.352050692862599</v>
       </c>
       <c r="O5" s="2">
         <v>0.10564063680000001</v>
@@ -993,7 +1086,7 @@
         <v>0.58601875989999996</v>
       </c>
       <c r="Q5">
-        <f>(ABS(P5-O5)/O5)*100</f>
+        <f>((P5-O5)/O5)*100</f>
         <v>454.72853785372098</v>
       </c>
       <c r="R5" s="2">
@@ -1003,7 +1096,7 @@
         <v>0.11909431970000001</v>
       </c>
       <c r="T5">
-        <f>(ABS(S5-R5)/R5)*100</f>
+        <f>((S5-R5)/R5)*100</f>
         <v>2.1487180853186101</v>
       </c>
       <c r="U5" s="2">
@@ -1013,7 +1106,7 @@
         <v>0.6719217072</v>
       </c>
       <c r="W5">
-        <f>(ABS(V5-U5)/U5)*100</f>
+        <f>((V5-U5)/U5)*100</f>
         <v>243.86029336496992</v>
       </c>
       <c r="X5" s="2">
@@ -1023,7 +1116,7 @@
         <v>5.0273797492999899</v>
       </c>
       <c r="Z5">
-        <f>(ABS(Y5-X5)/X5)*100</f>
+        <f>((Y5-X5)/X5)*100</f>
         <v>160.6307207237617</v>
       </c>
       <c r="AA5" s="2">
@@ -1033,7 +1126,7 @@
         <v>9.9510771030999994</v>
       </c>
       <c r="AC5">
-        <f>(ABS(AB5-AA5)/AA5)*100</f>
+        <f>((AB5-AA5)/AA5)*100</f>
         <v>4663.4315360964029</v>
       </c>
       <c r="AD5" s="2">
@@ -1043,7 +1136,7 @@
         <v>0.37508046959999902</v>
       </c>
       <c r="AF5">
-        <f>(ABS(AE5-AD5)/AD5)*100</f>
+        <f>((AE5-AD5)/AD5)*100</f>
         <v>26.149615243381756</v>
       </c>
       <c r="AG5" s="2">
@@ -1053,8 +1146,8 @@
         <v>2.3737580799999901E-2</v>
       </c>
       <c r="AI5">
-        <f>(ABS(AH5-AG5)/AG5)*100</f>
-        <v>2.6178089942714093</v>
+        <f>((AH5-AG5)/AG5)*100</f>
+        <v>-2.6178089942714093</v>
       </c>
       <c r="AJ5" s="2">
         <v>0.61320205890000001</v>
@@ -1063,8 +1156,8 @@
         <v>0.60076852670000003</v>
       </c>
       <c r="AL5">
-        <f>(ABS(AK5-AJ5)/AJ5)*100</f>
-        <v>2.0276403217406069</v>
+        <f>((AK5-AJ5)/AJ5)*100</f>
+        <v>-2.0276403217406069</v>
       </c>
       <c r="AM5" s="2">
         <v>15.422410439199901</v>
@@ -1073,7 +1166,7 @@
         <v>29.296997711900001</v>
       </c>
       <c r="AO5">
-        <f>(ABS(AN5-AM5)/AM5)*100</f>
+        <f>((AN5-AM5)/AM5)*100</f>
         <v>89.963805122410562</v>
       </c>
     </row>
@@ -1082,124 +1175,162 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <f>(ABS(C4-C5)/C4)*100</f>
+        <f>((C5-C4)/C4)*100</f>
         <v>7.6069154888983442E-2</v>
       </c>
       <c r="D6">
-        <f>(ABS(D4-D5)/D4)*100</f>
-        <v>1.8547249771395283E-2</v>
-      </c>
-      <c r="E6" s="5"/>
+        <f>((D5-D4)/D4)*100</f>
+        <v>-1.8547249771395283E-2</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6">
-        <f t="shared" ref="F6:G6" si="0">(ABS(F4-F5)/F4)*100</f>
+        <f>((F4-F5)/F4)*100</f>
         <v>4.0772248719499748E-3</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>1.5823940259069226E-2</v>
-      </c>
-      <c r="H6" s="5"/>
+        <f>((G4-G5)/G4)*100</f>
+        <v>-1.5823940259069226E-2</v>
+      </c>
+      <c r="H6" s="3"/>
       <c r="I6">
-        <f t="shared" ref="I6:J6" si="1">(ABS(I4-I5)/I4)*100</f>
+        <f>((I4-I5)/I4)*100</f>
         <v>2.0594339322590378E-2</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>5.3849235220024749E-3</v>
-      </c>
-      <c r="K6" s="5"/>
+        <f>((J4-J5)/J4)*100</f>
+        <v>-5.3849235220024749E-3</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6">
-        <f t="shared" ref="L6:M6" si="2">(ABS(L4-L5)/L4)*100</f>
+        <f>((L4-L5)/L4)*100</f>
         <v>1.6079707206661627E-2</v>
       </c>
       <c r="M6">
-        <f t="shared" si="2"/>
-        <v>3.5128334692636357E-3</v>
-      </c>
-      <c r="N6" s="5"/>
+        <f>((M4-M5)/M4)*100</f>
+        <v>-3.5128334692636357E-3</v>
+      </c>
+      <c r="N6" s="3"/>
       <c r="O6">
-        <f t="shared" ref="O6:P6" si="3">(ABS(O4-O5)/O4)*100</f>
+        <f>((O4-O5)/O4)*100</f>
         <v>0.19580192100004357</v>
       </c>
       <c r="P6">
-        <f t="shared" si="3"/>
-        <v>1.0738778624339577E-2</v>
-      </c>
-      <c r="Q6" s="5"/>
+        <f>((P4-P5)/P4)*100</f>
+        <v>-1.0738778624339577E-2</v>
+      </c>
+      <c r="Q6" s="3"/>
       <c r="R6">
-        <f t="shared" ref="R6:S6" si="4">(ABS(R4-R5)/R4)*100</f>
+        <f>((R4-R5)/R4)*100</f>
         <v>0.23968611012081037</v>
       </c>
       <c r="S6">
-        <f t="shared" si="4"/>
+        <f>((S4-S5)/S4)*100</f>
         <v>0.45014487359727939</v>
       </c>
-      <c r="T6" s="5"/>
+      <c r="T6" s="3"/>
       <c r="U6">
-        <f t="shared" ref="U6:V6" si="5">(ABS(U4-U5)/U4)*100</f>
+        <f>((U4-U5)/U4)*100</f>
         <v>5.770535162441795E-2</v>
       </c>
       <c r="V6">
-        <f t="shared" si="5"/>
-        <v>1.2364933437592445E-2</v>
-      </c>
-      <c r="W6" s="5"/>
+        <f>((V4-V5)/V4)*100</f>
+        <v>-1.2364933437592445E-2</v>
+      </c>
+      <c r="W6" s="3"/>
       <c r="X6">
-        <f t="shared" ref="X6:Y6" si="6">(ABS(X4-X5)/X4)*100</f>
-        <v>9.3411702049741335E-2</v>
+        <f>((X4-X5)/X4)*100</f>
+        <v>-9.3411702049741335E-2</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="6"/>
+        <f>((Y4-Y5)/Y4)*100</f>
         <v>2.5709323437606749E-2</v>
       </c>
-      <c r="Z6" s="5"/>
+      <c r="Z6" s="3"/>
       <c r="AA6">
-        <f t="shared" ref="AA6:AB6" si="7">(ABS(AA4-AA5)/AA4)*100</f>
+        <f>((AA4-AA5)/AA4)*100</f>
         <v>0.16891866173696787</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="7"/>
-        <v>1.1081531924824282E-2</v>
-      </c>
-      <c r="AC6" s="5"/>
+        <f>((AB4-AB5)/AB4)*100</f>
+        <v>-1.1081531924824282E-2</v>
+      </c>
+      <c r="AC6" s="3"/>
       <c r="AD6">
-        <f t="shared" ref="AD6:AE6" si="8">(ABS(AD4-AD5)/AD4)*100</f>
+        <f>((AD4-AD5)/AD4)*100</f>
         <v>0.25473275553600011</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="8"/>
-        <v>1.1971024380753549E-2</v>
-      </c>
-      <c r="AF6" s="5"/>
+        <f>((AE4-AE5)/AE4)*100</f>
+        <v>-1.1971024380753549E-2</v>
+      </c>
+      <c r="AF6" s="3"/>
       <c r="AG6">
-        <f t="shared" ref="AG6:AH6" si="9">(ABS(AG4-AG5)/AG4)*100</f>
-        <v>3.2217875372537105E-2</v>
+        <f>((AG4-AG5)/AG4)*100</f>
+        <v>-3.2217875372537105E-2</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="9"/>
+        <f>((AH4-AH5)/AH4)*100</f>
         <v>8.9738155235251485E-2</v>
       </c>
-      <c r="AI6" s="5"/>
+      <c r="AI6" s="3"/>
       <c r="AJ6">
-        <f t="shared" ref="AJ6:AK6" si="10">(ABS(AJ4-AJ5)/AJ4)*100</f>
-        <v>3.0541169430125657E-2</v>
+        <f>((AJ4-AJ5)/AJ4)*100</f>
+        <v>-3.0541169430125657E-2</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="10"/>
-        <v>2.3838042083464051</v>
-      </c>
-      <c r="AL6" s="5"/>
+        <f>((AK4-AK5)/AK4)*100</f>
+        <v>-2.3838042083464051</v>
+      </c>
+      <c r="AL6" s="3"/>
       <c r="AM6">
-        <f t="shared" ref="AM6:AN6" si="11">(ABS(AM4-AM5)/AM4)*100</f>
+        <f>((AM4-AM5)/AM4)*100</f>
         <v>3.3896522311275797E-3</v>
       </c>
       <c r="AN6">
-        <f t="shared" si="11"/>
-        <v>4.2094518445728313E-3</v>
-      </c>
-      <c r="AO6" s="5"/>
+        <f>((AN4-AN5)/AN4)*100</f>
+        <v>-4.2094518445728313E-3</v>
+      </c>
+      <c r="AO6" s="3"/>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1218,76 +1349,354 @@
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
     </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>104</v>
+      </c>
+      <c r="D11">
+        <v>0.25</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>128</v>
+      </c>
+      <c r="D12">
+        <v>0.25</v>
+      </c>
+      <c r="E12">
+        <v>144</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>64</v>
+      </c>
+      <c r="H12">
+        <v>0.5</v>
+      </c>
+      <c r="I12">
+        <v>152</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>64</v>
+      </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>47</v>
+      </c>
+      <c r="H13">
+        <v>0.625</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <v>110</v>
+      </c>
+      <c r="D14">
+        <v>0.25</v>
+      </c>
+      <c r="E14">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14">
+        <v>48</v>
+      </c>
+      <c r="H14">
+        <v>0.625</v>
+      </c>
+      <c r="I14">
+        <v>64</v>
+      </c>
       <c r="T14" s="2"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C22" s="4" t="s">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="4">
+        <v>104</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4">
+        <v>128</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="4">
+        <v>144</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18">
+        <v>64</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="4">
+        <v>64</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="4">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>47</v>
+      </c>
+      <c r="H19">
+        <v>0.625</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="4">
+        <v>110</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E20" s="4">
+        <v>64</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20">
+        <v>48</v>
+      </c>
+      <c r="H20">
+        <v>0.625</v>
+      </c>
+      <c r="I20">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="C22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C23" s="4" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="C23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4" t="s">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4" t="s">
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ23" s="6"/>
+      <c r="AR23" s="6"/>
+      <c r="AS23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT23" s="6"/>
+      <c r="AU23" s="6"/>
+      <c r="AV23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW23" s="6"/>
+      <c r="AX23" s="6"/>
+      <c r="AY23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AZ23" s="6"/>
+      <c r="BA23" s="6"/>
+      <c r="BB23" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4" t="s">
+      <c r="BC23" s="6"/>
+      <c r="BD23" s="6"/>
+      <c r="BE23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="BF23" s="6"/>
+      <c r="BG23" s="6"/>
+    </row>
+    <row r="24" spans="2:59" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
       <c r="C24" t="s">
         <v>18</v>
@@ -1334,165 +1743,705 @@
       <c r="Q24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="R24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T24" t="s">
+        <v>23</v>
+      </c>
+      <c r="U24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V24" t="s">
+        <v>19</v>
+      </c>
+      <c r="W24" t="s">
+        <v>23</v>
+      </c>
+      <c r="X24" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AZ24" t="s">
+        <v>19</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB24" t="s">
+        <v>18</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE24" t="s">
+        <v>18</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>19</v>
+      </c>
+      <c r="BG24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="1">
-        <v>4.7158911735000002</v>
-      </c>
-      <c r="D25" s="1">
-        <v>4.6291748970000004</v>
+      <c r="C25" s="2">
+        <v>7.4008092825999903</v>
+      </c>
+      <c r="D25">
+        <v>7.2122729741999896</v>
       </c>
       <c r="E25">
-        <f>((C25-D25)/C25)*100</f>
-        <v>1.8388099578566284</v>
-      </c>
-      <c r="F25" s="1">
-        <v>14.966369251</v>
-      </c>
-      <c r="G25" s="1">
-        <v>15.464017373900001</v>
+        <f>((D25-C25)/C25)*100</f>
+        <v>-2.5475093493257224</v>
+      </c>
+      <c r="F25" s="2">
+        <v>22.1151813416</v>
+      </c>
+      <c r="G25">
+        <v>22.767367824899999</v>
       </c>
       <c r="H25">
-        <f>((F25-G25)/F25)*100</f>
-        <v>-3.3251092135572562</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1.1035383372000001</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1.1174958406</v>
+        <f>((G25-F25)/F25)*100</f>
+        <v>2.9490442480487244</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1.21111953E-2</v>
+      </c>
+      <c r="J25">
+        <v>2.2874528799999998E-2</v>
       </c>
       <c r="K25">
-        <f>((I25-J25)/I25)*100</f>
-        <v>-1.264795515433943</v>
-      </c>
-      <c r="L25" s="1">
-        <v>45.087971282799998</v>
-      </c>
-      <c r="M25" s="1">
-        <v>44.8257993271</v>
+        <f>((J25-I25)/I25)*100</f>
+        <v>88.870943233819361</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1.29574681999999E-2</v>
+      </c>
+      <c r="M25">
+        <v>1.8315065500000002E-2</v>
       </c>
       <c r="N25">
-        <f>((L25-M25)/L25)*100</f>
-        <v>0.5814676248252717</v>
-      </c>
-      <c r="O25" s="1">
-        <v>21.769039145499999</v>
-      </c>
-      <c r="P25" s="1">
-        <v>22.5076772191</v>
+        <f>((M25-L25)/L25)*100</f>
+        <v>41.347562790083813</v>
+      </c>
+      <c r="O25" s="2">
+        <v>2.1905743099999899E-2</v>
+      </c>
+      <c r="P25">
+        <v>0.1480761901</v>
       </c>
       <c r="Q25">
-        <f>((O25-P25)/O25)*100</f>
-        <v>-3.3930669546923422</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+        <f>((P25-O25)/O25)*100</f>
+        <v>575.96971910074433</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1.47182786999999E-2</v>
+      </c>
+      <c r="S25">
+        <v>6.6810606999999994E-2</v>
+      </c>
+      <c r="T25">
+        <f>((S25-R25)/R25)*100</f>
+        <v>353.92948701263856</v>
+      </c>
+      <c r="U25" s="2">
+        <v>2.2763139799999998E-2</v>
+      </c>
+      <c r="V25">
+        <v>2.1449032600000001E-2</v>
+      </c>
+      <c r="W25">
+        <f>((V25-U25)/U25)*100</f>
+        <v>-5.7729610745526312</v>
+      </c>
+      <c r="X25" s="2">
+        <v>9.3427465799999998E-2</v>
+      </c>
+      <c r="Y25">
+        <v>8.9015558499999994E-2</v>
+      </c>
+      <c r="Z25">
+        <f>((Y25-X25)/X25)*100</f>
+        <v>-4.7222808220492301</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>1.0199779689999999</v>
+      </c>
+      <c r="AB25">
+        <v>1.0148098673999999</v>
+      </c>
+      <c r="AC25">
+        <f>((AB25-AA25)/AA25)*100</f>
+        <v>-0.50668757140577325</v>
+      </c>
+      <c r="AD25" s="2">
+        <v>1.4899430571999901</v>
+      </c>
+      <c r="AE25">
+        <v>1.4990287536</v>
+      </c>
+      <c r="AF25">
+        <f>((AE25-AD25)/AD25)*100</f>
+        <v>0.60980158645018256</v>
+      </c>
+      <c r="AG25" s="2">
+        <v>1.8267769900000001E-2</v>
+      </c>
+      <c r="AH25">
+        <v>5.7735948999999898E-2</v>
+      </c>
+      <c r="AI25">
+        <f>((AH25-AG25)/AG25)*100</f>
+        <v>216.0536251335194</v>
+      </c>
+      <c r="AJ25" s="2">
+        <v>3.2007168499999898E-2</v>
+      </c>
+      <c r="AK25">
+        <v>0.12613044439999899</v>
+      </c>
+      <c r="AL25">
+        <f>((AK25-AJ25)/AJ25)*100</f>
+        <v>294.06936105578779</v>
+      </c>
+      <c r="AM25" s="2">
+        <v>2.32702768999999E-2</v>
+      </c>
+      <c r="AN25">
+        <v>5.4066336E-2</v>
+      </c>
+      <c r="AO25">
+        <f>((AN25-AM25)/AM25)*100</f>
+        <v>132.34075053056301</v>
+      </c>
+      <c r="AP25" s="2">
+        <v>4.90874935999999E-2</v>
+      </c>
+      <c r="AQ25">
+        <v>5.9640913999999899E-2</v>
+      </c>
+      <c r="AR25">
+        <f>((AQ25-AP25)/AP25)*100</f>
+        <v>21.499204025360996</v>
+      </c>
+      <c r="AS25" s="2">
+        <v>1.68652153E-2</v>
+      </c>
+      <c r="AT25">
+        <v>0.10740220139999899</v>
+      </c>
+      <c r="AU25">
+        <f>((AT25-AS25)/AS25)*100</f>
+        <v>536.826743623006</v>
+      </c>
+      <c r="AV25" s="2">
+        <v>1.5960736999999899E-2</v>
+      </c>
+      <c r="AW25">
+        <v>3.1303208699999897E-2</v>
+      </c>
+      <c r="AX25">
+        <f>((AW25-AV25)/AV25)*100</f>
+        <v>96.126336146006892</v>
+      </c>
+      <c r="AY25" s="2">
+        <v>1.0287948999999999E-2</v>
+      </c>
+      <c r="AZ25">
+        <v>9.6928289999999896E-3</v>
+      </c>
+      <c r="BA25">
+        <f>((AZ25-AY25)/AY25)*100</f>
+        <v>-5.7846320972237502</v>
+      </c>
+      <c r="BB25" s="2">
+        <v>44.704140538099999</v>
+      </c>
+      <c r="BC25">
+        <v>44.549388440100003</v>
+      </c>
+      <c r="BD25">
+        <f>((BC25-BB25)/BB25)*100</f>
+        <v>-0.3461694960181716</v>
+      </c>
+      <c r="BE25" s="2">
+        <v>32.4013560924</v>
+      </c>
+      <c r="BF25">
+        <v>33.336419790800001</v>
+      </c>
+      <c r="BG25">
+        <f>((BF25-BE25)/BE25)*100</f>
+        <v>2.8858782815554043</v>
+      </c>
+    </row>
+    <row r="26" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="1">
-        <v>4.6941893570999902</v>
-      </c>
-      <c r="D26" s="1">
-        <v>4.6335907109000001</v>
+      <c r="C26" s="2">
+        <v>7.3528032847000002</v>
+      </c>
+      <c r="D26" s="2">
+        <v>7.2445842304000001</v>
       </c>
       <c r="E26">
-        <f>((C26-D26)/C26)*100</f>
-        <v>1.2909288822858049</v>
-      </c>
-      <c r="F26" s="1">
-        <v>14.3304367599</v>
-      </c>
-      <c r="G26" s="1">
-        <v>15.5303682837</v>
+        <f>((D26-C26)/C26)*100</f>
+        <v>-1.471806739685074</v>
+      </c>
+      <c r="F26" s="2">
+        <v>21.197617295099999</v>
+      </c>
+      <c r="G26" s="2">
+        <v>23.122796592</v>
       </c>
       <c r="H26">
-        <f>((F26-G26)/F26)*100</f>
-        <v>-8.3733074148702595</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1.1054981386</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1.1140971225</v>
+        <f>((G26-F26)/F26)*100</f>
+        <v>9.0820551673278036</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1.08884372E-2</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2.25079043999999E-2</v>
       </c>
       <c r="K26">
-        <f>((I26-J26)/I26)*100</f>
-        <v>-0.77783793565584414</v>
-      </c>
-      <c r="L26" s="1">
-        <v>44.914485792800001</v>
-      </c>
-      <c r="M26" s="1">
-        <v>44.739087787199999</v>
+        <f>((J26-I26)/I26)*100</f>
+        <v>106.7138193165122</v>
+      </c>
+      <c r="L26" s="2">
+        <v>1.15906108999999E-2</v>
+      </c>
+      <c r="M26" s="2">
+        <v>1.7997197900000001E-2</v>
       </c>
       <c r="N26">
-        <f>((L26-M26)/L26)*100</f>
-        <v>0.39051544842158442</v>
-      </c>
-      <c r="O26" s="1">
-        <v>21.1182229148</v>
-      </c>
-      <c r="P26" s="1">
-        <v>22.523737777600001</v>
+        <f>((M26-L26)/L26)*100</f>
+        <v>55.273937286602859</v>
+      </c>
+      <c r="O26" s="2">
+        <v>2.06510244999999E-2</v>
+      </c>
+      <c r="P26" s="2">
+        <v>0.14663842560000001</v>
       </c>
       <c r="Q26">
-        <f>((O26-P26)/O26)*100</f>
-        <v>-6.6554599242107271</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+        <f>((P26-O26)/O26)*100</f>
+        <v>610.07821234244682</v>
+      </c>
+      <c r="R26" s="2">
+        <v>1.33587209999999E-2</v>
+      </c>
+      <c r="S26" s="2">
+        <v>5.0837415999999899E-2</v>
+      </c>
+      <c r="T26">
+        <f>((S26-R26)/R26)*100</f>
+        <v>280.55601280991107</v>
+      </c>
+      <c r="U26" s="2">
+        <v>2.00944897999999E-2</v>
+      </c>
+      <c r="V26" s="2">
+        <v>2.16744125E-2</v>
+      </c>
+      <c r="W26">
+        <f>((V26-U26)/U26)*100</f>
+        <v>7.8624673516224748</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0.1244133635</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0.138448987699999</v>
+      </c>
+      <c r="Z26">
+        <f>((Y26-X26)/X26)*100</f>
+        <v>11.28144421559586</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>1.0282810059999901</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>1.0113813036999999</v>
+      </c>
+      <c r="AC26">
+        <f>((AB26-AA26)/AA26)*100</f>
+        <v>-1.6434906607611037</v>
+      </c>
+      <c r="AD26" s="2">
+        <v>1.4782004491</v>
+      </c>
+      <c r="AE26" s="2">
+        <v>1.4921633096</v>
+      </c>
+      <c r="AF26">
+        <f>((AE26-AD26)/AD26)*100</f>
+        <v>0.94458505329917986</v>
+      </c>
+      <c r="AG26" s="2">
+        <v>1.67744877E-2</v>
+      </c>
+      <c r="AH26" s="2">
+        <v>5.7177692699999998E-2</v>
+      </c>
+      <c r="AI26">
+        <f>((AH26-AG26)/AG26)*100</f>
+        <v>240.86103684704477</v>
+      </c>
+      <c r="AJ26" s="2">
+        <v>3.0561777599999899E-2</v>
+      </c>
+      <c r="AK26" s="2">
+        <v>8.8825367599999899E-2</v>
+      </c>
+      <c r="AL26">
+        <f>((AK26-AJ26)/AJ26)*100</f>
+        <v>190.6420194615911</v>
+      </c>
+      <c r="AM26" s="2">
+        <v>2.1590369700000001E-2</v>
+      </c>
+      <c r="AN26" s="2">
+        <v>5.0319302199999902E-2</v>
+      </c>
+      <c r="AO26">
+        <f>((AN26-AM26)/AM26)*100</f>
+        <v>133.06364318532212</v>
+      </c>
+      <c r="AP26" s="2">
+        <v>4.4852247800000002E-2</v>
+      </c>
+      <c r="AQ26" s="2">
+        <v>5.7722189100000001E-2</v>
+      </c>
+      <c r="AR26">
+        <f>((AQ26-AP26)/AP26)*100</f>
+        <v>28.69408319821153</v>
+      </c>
+      <c r="AS26" s="2">
+        <v>1.5670265100000001E-2</v>
+      </c>
+      <c r="AT26" s="2">
+        <v>4.8876895999999899E-2</v>
+      </c>
+      <c r="AU26">
+        <f>((AT26-AS26)/AS26)*100</f>
+        <v>211.90854582287758</v>
+      </c>
+      <c r="AV26" s="2">
+        <v>1.45943386999999E-2</v>
+      </c>
+      <c r="AW26" s="2">
+        <v>2.6764942699999999E-2</v>
+      </c>
+      <c r="AX26">
+        <f>((AW26-AV26)/AV26)*100</f>
+        <v>83.39263772191461</v>
+      </c>
+      <c r="AY26" s="2">
+        <v>9.0732243999999997E-3</v>
+      </c>
+      <c r="AZ26" s="2">
+        <v>9.79943499999999E-3</v>
+      </c>
+      <c r="BA26">
+        <f>((AZ26-AY26)/AY26)*100</f>
+        <v>8.003886688837877</v>
+      </c>
+      <c r="BB26" s="2">
+        <v>44.633564197200002</v>
+      </c>
+      <c r="BC26" s="2">
+        <v>44.801128778600003</v>
+      </c>
+      <c r="BD26">
+        <f>((BC26-BB26)/BB26)*100</f>
+        <v>0.37542281109271675</v>
+      </c>
+      <c r="BE26" s="2">
+        <v>31.439556519</v>
+      </c>
+      <c r="BF26" s="2">
+        <v>33.639414801400001</v>
+      </c>
+      <c r="BG26">
+        <f>((BF26-BE26)/BE26)*100</f>
+        <v>6.9971034135629466</v>
+      </c>
+    </row>
+    <row r="27" spans="2:59" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>23</v>
       </c>
       <c r="C27">
-        <f>((C25-C26)/C25)*100</f>
-        <v>0.46018484315242458</v>
+        <f>((C26-C25)/C25)*100</f>
+        <v>-0.64865876239854925</v>
       </c>
       <c r="D27">
-        <f>((D25-D26)/D25)*100</f>
-        <v>-9.5390949753516641E-2</v>
-      </c>
+        <f>((D26-D25)/D25)*100</f>
+        <v>0.44800378903565552</v>
+      </c>
+      <c r="E27" s="3"/>
       <c r="F27">
-        <f>((F25-F26)/F25)*100</f>
-        <v>4.2490765825352694</v>
+        <f>((F26-F25)/F25)*100</f>
+        <v>-4.1490233895301918</v>
       </c>
       <c r="G27">
-        <f>((G25-G26)/G25)*100</f>
-        <v>-0.42906644629089163</v>
-      </c>
+        <f>((G26-G25)/G25)*100</f>
+        <v>1.5611324498885601</v>
+      </c>
+      <c r="H27" s="3"/>
       <c r="I27">
-        <f>((I25-I26)/I25)*100</f>
-        <v>-0.17759250711421146</v>
+        <f>((I26-I25)/I25)*100</f>
+        <v>-10.096097616392994</v>
       </c>
       <c r="J27">
-        <f>((J25-J26)/J25)*100</f>
-        <v>0.30413697989024269</v>
-      </c>
+        <f>((J26-J25)/J25)*100</f>
+        <v>-1.6027626326453486</v>
+      </c>
+      <c r="K27" s="3"/>
       <c r="L27">
-        <f>((L25-L26)/L25)*100</f>
-        <v>0.38477111536437214</v>
+        <f>((L26-L25)/L25)*100</f>
+        <v>-10.548799185939814</v>
       </c>
       <c r="M27">
-        <f>((M25-M26)/M25)*100</f>
-        <v>0.19344114595091852</v>
-      </c>
+        <f>((M26-M25)/M25)*100</f>
+        <v>-1.7355526246957755</v>
+      </c>
+      <c r="N27" s="3"/>
       <c r="O27">
-        <f>((O25-O26)/O25)*100</f>
-        <v>2.9896415103582208</v>
+        <f>((O26-O25)/O25)*100</f>
+        <v>-5.7278066042872808</v>
       </c>
       <c r="P27">
-        <f>((P25-P26)/P25)*100</f>
-        <v>-7.1355912667755608E-2</v>
-      </c>
+        <f>((P26-P25)/P25)*100</f>
+        <v>-0.9709626503957397</v>
+      </c>
+      <c r="Q27" s="3"/>
+      <c r="R27">
+        <f>((R26-R25)/R25)*100</f>
+        <v>-9.2372058425555501</v>
+      </c>
+      <c r="S27">
+        <f>((S26-S25)/S25)*100</f>
+        <v>-23.908166258690176</v>
+      </c>
+      <c r="T27" s="3"/>
+      <c r="U27">
+        <f>((U26-U25)/U25)*100</f>
+        <v>-11.723558452160887</v>
+      </c>
+      <c r="V27">
+        <f>((V26-V25)/V25)*100</f>
+        <v>1.050769534473081</v>
+      </c>
+      <c r="W27" s="3"/>
+      <c r="X27">
+        <f>((X26-X25)/X25)*100</f>
+        <v>33.165726411044325</v>
+      </c>
+      <c r="Y27">
+        <f>((Y26-Y25)/Y25)*100</f>
+        <v>55.533470814541943</v>
+      </c>
+      <c r="Z27" s="3"/>
+      <c r="AA27">
+        <f>((AA26-AA25)/AA25)*100</f>
+        <v>0.81404081777673498</v>
+      </c>
+      <c r="AB27">
+        <f>((AB26-AB25)/AB25)*100</f>
+        <v>-0.33785281461483729</v>
+      </c>
+      <c r="AC27" s="3"/>
+      <c r="AD27">
+        <f>((AD26-AD25)/AD25)*100</f>
+        <v>-0.788124622833414</v>
+      </c>
+      <c r="AE27">
+        <f>((AE26-AE25)/AE25)*100</f>
+        <v>-0.45799281591578933</v>
+      </c>
+      <c r="AF27" s="3"/>
+      <c r="AG27">
+        <f>((AG26-AG25)/AG25)*100</f>
+        <v>-8.1744088532667636</v>
+      </c>
+      <c r="AH27">
+        <f>((AH26-AH25)/AH25)*100</f>
+        <v>-0.96691283276542483</v>
+      </c>
+      <c r="AI27" s="3"/>
+      <c r="AJ27">
+        <f>((AJ26-AJ25)/AJ25)*100</f>
+        <v>-4.5158349449124309</v>
+      </c>
+      <c r="AK27">
+        <f>((AK26-AK25)/AK25)*100</f>
+        <v>-29.576583970237238</v>
+      </c>
+      <c r="AL27" s="3"/>
+      <c r="AM27">
+        <f>((AM26-AM25)/AM25)*100</f>
+        <v>-7.2191113462852989</v>
+      </c>
+      <c r="AN27">
+        <f>((AN26-AN25)/AN25)*100</f>
+        <v>-6.930437823639644</v>
+      </c>
+      <c r="AO27" s="3"/>
+      <c r="AP27">
+        <f>((AP26-AP25)/AP25)*100</f>
+        <v>-8.6279528437767024</v>
+      </c>
+      <c r="AQ27">
+        <f>((AQ26-AQ25)/AQ25)*100</f>
+        <v>-3.2171285973248178</v>
+      </c>
+      <c r="AR27" s="3"/>
+      <c r="AS27">
+        <f>((AS26-AS25)/AS25)*100</f>
+        <v>-7.085294665642361</v>
+      </c>
+      <c r="AT27">
+        <f>((AT26-AT25)/AT25)*100</f>
+        <v>-54.491718639949262</v>
+      </c>
+      <c r="AU27" s="3"/>
+      <c r="AV27">
+        <f>((AV26-AV25)/AV25)*100</f>
+        <v>-8.5609975278710948</v>
+      </c>
+      <c r="AW27">
+        <f>((AW26-AW25)/AW25)*100</f>
+        <v>-14.497766166699433</v>
+      </c>
+      <c r="AX27" s="3"/>
+      <c r="AY27">
+        <f>((AY26-AY25)/AY25)*100</f>
+        <v>-11.807257209381577</v>
+      </c>
+      <c r="AZ27">
+        <f>((AZ26-AZ25)/AZ25)*100</f>
+        <v>1.0998440187070309</v>
+      </c>
+      <c r="BA27" s="3"/>
+      <c r="BB27">
+        <f>((BB26-BB25)/BB25)*100</f>
+        <v>-0.15787428200268605</v>
+      </c>
+      <c r="BC27">
+        <f>((BC26-BC25)/BC25)*100</f>
+        <v>0.56508146871305143</v>
+      </c>
+      <c r="BD27" s="3"/>
+      <c r="BE27">
+        <f>((BE26-BE25)/BE25)*100</f>
+        <v>-2.9683929606440094</v>
+      </c>
+      <c r="BF27">
+        <f>((BF26-BF25)/BF25)*100</f>
+        <v>0.90890087328339608</v>
+      </c>
+      <c r="BG27" s="3"/>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="C22:Q22"/>
+  <mergeCells count="38">
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="C1:AO1"/>
     <mergeCell ref="U2:W2"/>
@@ -1507,14 +2456,33 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:I15"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="I23:K23"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="B9:E9"/>
     <mergeCell ref="L23:N23"/>
     <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="BE23:BG23"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="BB23:BD23"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="colorScale" priority="101">
+  <conditionalFormatting sqref="C27:D27">
+    <cfRule type="colorScale" priority="135">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1523,28 +2491,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27">
-    <cfRule type="colorScale" priority="75">
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="colorScale" priority="161">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D27">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E5">
-    <cfRule type="colorScale" priority="150">
+    <cfRule type="colorScale" priority="210">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1554,137 +2512,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E26">
-    <cfRule type="colorScale" priority="66">
+    <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
         <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27">
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25:K26">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L27">
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M27">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N25:N26">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O27">
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P27">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF92D050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q25:Q26">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FFFF3500"/>
-        <color rgb="FF92D050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1694,7 +2532,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K5">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1704,7 +2542,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N5">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1714,7 +2552,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q5">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1724,7 +2562,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T5">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1734,7 +2572,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W4:W5">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1744,7 +2582,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1754,7 +2592,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1764,7 +2602,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF4:AF5">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1774,7 +2612,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI4:AI5">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1784,7 +2622,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AL5">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1794,7 +2632,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO4:AO5">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1804,7 +2642,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:G6">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1814,7 +2652,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:J6">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1824,7 +2662,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:M6">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1834,7 +2672,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O6:P6">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1844,7 +2682,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6:S6">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1854,7 +2692,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:V6">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1864,7 +2702,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X6:Y6">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1874,7 +2712,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AB6">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1884,7 +2722,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD6:AE6">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1894,7 +2732,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG6:AH6">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1904,7 +2742,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ6:AK6">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -1914,6 +2752,366 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM6:AN6">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25:K26">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25:N26">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q25:Q26">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T25:T26">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W25:W26">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z25:Z26">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC25:AC26">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF25:AF26">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI25:AI26">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL25:AL26">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO25:AO26">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AR25:AR26">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU25:AU26">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AX25:AX26">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BA25:BA26">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BD25:BD26">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BG25:BG26">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:G27">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I27:J27">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L27:M27">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O27:P27">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R27:S27">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U27:V27">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X27:Y27">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA27:AB27">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD27:AE27">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG27:AH27">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ27:AK27">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM27:AN27">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP27:AQ27">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AS27:AT27">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AV27:AW27">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY27:AZ27">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB27:BC27">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE27:BF27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1935,15 +3133,20 @@
     <col min="2" max="2" width="10.1640625" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -1963,21 +3166,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -2508,14 +3711,14 @@
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2527,7 +3730,7 @@
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -2536,87 +3739,740 @@
         <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="M19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>7.422269988</v>
+      </c>
+      <c r="D20">
+        <v>20.973429719999999</v>
+      </c>
+      <c r="E20">
+        <v>1.0189039999999899E-2</v>
+      </c>
+      <c r="F20">
+        <v>1.1093337999999901E-2</v>
+      </c>
+      <c r="G20">
+        <v>2.0079415999999899E-2</v>
+      </c>
+      <c r="H20">
+        <v>1.2795913000000001E-2</v>
+      </c>
+      <c r="I20">
+        <v>1.84805729999999E-2</v>
+      </c>
+      <c r="J20">
+        <v>7.847635E-2</v>
+      </c>
+      <c r="K20">
+        <v>1.0278000629999999</v>
+      </c>
+      <c r="L20">
+        <v>1.48805661399999</v>
+      </c>
+      <c r="M20">
+        <v>1.5875657000000001E-2</v>
+      </c>
+      <c r="N20">
+        <v>3.03467069999999E-2</v>
+      </c>
+      <c r="O20">
+        <v>2.0522435999999901E-2</v>
+      </c>
+      <c r="P20">
+        <v>4.2784091999999899E-2</v>
+      </c>
+      <c r="Q20">
+        <v>1.491894E-2</v>
+      </c>
+      <c r="R20">
+        <v>1.3895578E-2</v>
+      </c>
+      <c r="S20">
+        <v>8.4823659999999999E-3</v>
+      </c>
+      <c r="T20">
+        <v>44.537179967999997</v>
+      </c>
+      <c r="U20">
+        <v>31.236283783000001</v>
+      </c>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>7.6188020380000099</v>
+      </c>
+      <c r="D21">
+        <v>27.896292961</v>
+      </c>
+      <c r="E21">
+        <v>1.7517990000000001E-2</v>
+      </c>
+      <c r="F21">
+        <v>1.9069963999999901E-2</v>
+      </c>
+      <c r="G21">
+        <v>2.77774659999999E-2</v>
+      </c>
+      <c r="H21">
+        <v>2.0337347999999901E-2</v>
+      </c>
+      <c r="I21">
+        <v>3.4965568999999898E-2</v>
+      </c>
+      <c r="J21">
+        <v>0.13530051900000001</v>
+      </c>
+      <c r="K21">
+        <v>1.1246259810000001</v>
+      </c>
+      <c r="L21">
+        <v>1.54620996699999</v>
+      </c>
+      <c r="M21">
+        <v>2.5000124999999901E-2</v>
+      </c>
+      <c r="N21">
+        <v>3.7133611999999899E-2</v>
+      </c>
+      <c r="O21">
+        <v>3.0151092000000001E-2</v>
+      </c>
+      <c r="P21">
+        <v>6.7247822999999998E-2</v>
+      </c>
+      <c r="Q21">
+        <v>2.2129143999999899E-2</v>
+      </c>
+      <c r="R21">
+        <v>2.17800259999999E-2</v>
+      </c>
+      <c r="S21">
+        <v>1.5491974E-2</v>
+      </c>
+      <c r="T21">
+        <v>45.907599861999998</v>
+      </c>
+      <c r="U21">
+        <v>38.706284349000001</v>
+      </c>
     </row>
     <row r="22" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>7.0703843219999998</v>
+      </c>
+      <c r="D22">
+        <v>20.762086303999901</v>
+      </c>
+      <c r="E22">
+        <v>1.0054397E-2</v>
+      </c>
+      <c r="F22">
+        <v>1.08029469999999E-2</v>
+      </c>
+      <c r="G22">
+        <v>1.9446453999999901E-2</v>
+      </c>
+      <c r="H22">
+        <v>1.2624224999999999E-2</v>
+      </c>
+      <c r="I22">
+        <v>1.8377348000000002E-2</v>
+      </c>
+      <c r="J22">
+        <v>7.7794973000000003E-2</v>
+      </c>
+      <c r="K22">
+        <v>0.96432825799999899</v>
+      </c>
+      <c r="L22">
+        <v>1.4635087739999899</v>
+      </c>
+      <c r="M22">
+        <v>1.5699682999999898E-2</v>
+      </c>
+      <c r="N22">
+        <v>2.9801441000000001E-2</v>
+      </c>
+      <c r="O22">
+        <v>2.0402060999999999E-2</v>
+      </c>
+      <c r="P22">
+        <v>4.1935385999999901E-2</v>
+      </c>
+      <c r="Q22">
+        <v>1.4826806999999999E-2</v>
+      </c>
+      <c r="R22">
+        <v>1.3889409999999901E-2</v>
+      </c>
+      <c r="S22">
+        <v>8.3245769999999997E-3</v>
+      </c>
+      <c r="T22">
+        <v>44.630055628999997</v>
+      </c>
+      <c r="U22">
+        <v>30.580454436</v>
+      </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>7.3038490829999798</v>
+      </c>
+      <c r="D23">
+        <v>22.055633064999899</v>
+      </c>
+      <c r="E23">
+        <v>1.28900659999999E-2</v>
+      </c>
+      <c r="F23">
+        <v>1.3444190999999999E-2</v>
+      </c>
+      <c r="G23">
+        <v>2.3004718999999899E-2</v>
+      </c>
+      <c r="H23">
+        <v>1.56062599999999E-2</v>
+      </c>
+      <c r="I23">
+        <v>2.4709099000000002E-2</v>
+      </c>
+      <c r="J23">
+        <v>9.8524696999999897E-2</v>
+      </c>
+      <c r="K23">
+        <v>0.99491091000000098</v>
+      </c>
+      <c r="L23">
+        <v>1.502113995</v>
+      </c>
+      <c r="M23">
+        <v>1.9284599999999898E-2</v>
+      </c>
+      <c r="N23">
+        <v>3.3256510999999898E-2</v>
+      </c>
+      <c r="O23">
+        <v>2.4200428E-2</v>
+      </c>
+      <c r="P23">
+        <v>5.1085352000000001E-2</v>
+      </c>
+      <c r="Q23">
+        <v>1.7725932999999999E-2</v>
+      </c>
+      <c r="R23">
+        <v>1.6665559999999999E-2</v>
+      </c>
+      <c r="S23">
+        <v>1.0932849E-2</v>
+      </c>
+      <c r="T23">
+        <v>44.604266998</v>
+      </c>
+      <c r="U23">
+        <v>32.252171476999997</v>
+      </c>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>7.5513238239999803</v>
+      </c>
+      <c r="D24">
+        <v>21.4786182779999</v>
+      </c>
+      <c r="E24">
+        <v>1.1750320999999999E-2</v>
+      </c>
+      <c r="F24">
+        <v>1.25569039999999E-2</v>
+      </c>
+      <c r="G24">
+        <v>2.1439166999999999E-2</v>
+      </c>
+      <c r="H24">
+        <v>1.4338396999999999E-2</v>
+      </c>
+      <c r="I24">
+        <v>2.21996909999999E-2</v>
+      </c>
+      <c r="J24">
+        <v>9.1012324000000103E-2</v>
+      </c>
+      <c r="K24">
+        <v>1.042050506</v>
+      </c>
+      <c r="L24">
+        <v>1.46941730099999</v>
+      </c>
+      <c r="M24">
+        <v>1.8134878999999899E-2</v>
+      </c>
+      <c r="N24">
+        <v>3.1238848999999898E-2</v>
+      </c>
+      <c r="O24">
+        <v>2.3297592999999901E-2</v>
+      </c>
+      <c r="P24">
+        <v>4.8082724999999903E-2</v>
+      </c>
+      <c r="Q24">
+        <v>1.6460275E-2</v>
+      </c>
+      <c r="R24">
+        <v>1.5589102999999899E-2</v>
+      </c>
+      <c r="S24">
+        <v>9.9517970000000001E-3</v>
+      </c>
+      <c r="T24">
+        <v>44.570692493999999</v>
+      </c>
+      <c r="U24">
+        <v>31.908509415000001</v>
+      </c>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
     <row r="25" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>7.6023897789999797</v>
+      </c>
+      <c r="D25">
+        <v>20.910273345</v>
+      </c>
+      <c r="E25">
+        <v>1.0335970999999999E-2</v>
+      </c>
+      <c r="F25">
+        <v>1.1155738999999901E-2</v>
+      </c>
+      <c r="G25">
+        <v>1.99115429999999E-2</v>
+      </c>
+      <c r="H25">
+        <v>1.2818519E-2</v>
+      </c>
+      <c r="I25">
+        <v>1.88498909999999E-2</v>
+      </c>
+      <c r="J25">
+        <v>7.9330277999999907E-2</v>
+      </c>
+      <c r="K25">
+        <v>1.027643839</v>
+      </c>
+      <c r="L25">
+        <v>1.4789465820000001</v>
+      </c>
+      <c r="M25">
+        <v>1.6126796999999998E-2</v>
+      </c>
+      <c r="N25">
+        <v>3.04041769999999E-2</v>
+      </c>
+      <c r="O25">
+        <v>2.0884053999999999E-2</v>
+      </c>
+      <c r="P25">
+        <v>4.2696177999999897E-2</v>
+      </c>
+      <c r="Q25">
+        <v>1.52409619999999E-2</v>
+      </c>
+      <c r="R25">
+        <v>1.41193929999999E-2</v>
+      </c>
+      <c r="S25">
+        <v>8.6262590000000007E-3</v>
+      </c>
+      <c r="T25">
+        <v>44.667078885000002</v>
+      </c>
+      <c r="U25">
+        <v>31.346722724999999</v>
+      </c>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>7.4508759830000004</v>
+      </c>
+      <c r="D26">
+        <v>22.810823974999899</v>
+      </c>
+      <c r="E26">
+        <v>1.1885843E-2</v>
+      </c>
+      <c r="F26">
+        <v>1.26635149999999E-2</v>
+      </c>
+      <c r="G26">
+        <v>2.1602151999999899E-2</v>
+      </c>
+      <c r="H26">
+        <v>1.44085019999999E-2</v>
+      </c>
+      <c r="I26">
+        <v>2.207657E-2</v>
+      </c>
+      <c r="J26">
+        <v>9.1547610000000001E-2</v>
+      </c>
+      <c r="K26">
+        <v>0.99559034500000099</v>
+      </c>
+      <c r="L26">
+        <v>1.47934390599999</v>
+      </c>
+      <c r="M26">
+        <v>1.8181401E-2</v>
+      </c>
+      <c r="N26">
+        <v>3.1755086999999897E-2</v>
+      </c>
+      <c r="O26">
+        <v>2.3216191000000001E-2</v>
+      </c>
+      <c r="P26">
+        <v>4.8322763999999997E-2</v>
+      </c>
+      <c r="Q26">
+        <v>1.6649091000000001E-2</v>
+      </c>
+      <c r="R26">
+        <v>1.5630756999999999E-2</v>
+      </c>
+      <c r="S26">
+        <v>9.9386179999999893E-3</v>
+      </c>
+      <c r="T26">
+        <v>44.593201811</v>
+      </c>
+      <c r="U26">
+        <v>33.105493414000001</v>
+      </c>
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>7.3084655869999899</v>
+      </c>
+      <c r="D27">
+        <v>22.423550133999999</v>
+      </c>
+      <c r="E27">
+        <v>1.2466428999999999E-2</v>
+      </c>
+      <c r="F27">
+        <v>1.3379607999999999E-2</v>
+      </c>
+      <c r="G27">
+        <v>2.21556989999999E-2</v>
+      </c>
+      <c r="H27">
+        <v>1.4972677999999901E-2</v>
+      </c>
+      <c r="I27">
+        <v>2.3433133999999901E-2</v>
+      </c>
+      <c r="J27">
+        <v>9.5719667999999897E-2</v>
+      </c>
+      <c r="K27">
+        <v>0.99548436199999901</v>
+      </c>
+      <c r="L27">
+        <v>1.4640565459999999</v>
+      </c>
+      <c r="M27">
+        <v>1.8684092999999902E-2</v>
+      </c>
+      <c r="N27">
+        <v>3.2627214999999897E-2</v>
+      </c>
+      <c r="O27">
+        <v>2.3869406999999902E-2</v>
+      </c>
+      <c r="P27">
+        <v>5.0014802999999997E-2</v>
+      </c>
+      <c r="Q27">
+        <v>1.7272931999999901E-2</v>
+      </c>
+      <c r="R27">
+        <v>1.6310773000000001E-2</v>
+      </c>
+      <c r="S27">
+        <v>1.0583215999999999E-2</v>
+      </c>
+      <c r="T27">
+        <v>44.941498164000002</v>
+      </c>
+      <c r="U27">
+        <v>32.575561434999997</v>
+      </c>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>7.31615744199999</v>
+      </c>
+      <c r="D28">
+        <v>22.429028375000001</v>
+      </c>
+      <c r="E28">
+        <v>1.4834576999999899E-2</v>
+      </c>
+      <c r="F28">
+        <v>1.5762637999999898E-2</v>
+      </c>
+      <c r="G28">
+        <v>2.4891438999999901E-2</v>
+      </c>
+      <c r="H28">
+        <v>1.7626726999999998E-2</v>
+      </c>
+      <c r="I28">
+        <v>2.8337721E-2</v>
+      </c>
+      <c r="J28">
+        <v>0.11666834599999901</v>
+      </c>
+      <c r="K28">
+        <v>1.001137798</v>
+      </c>
+      <c r="L28">
+        <v>1.5000514679999899</v>
+      </c>
+      <c r="M28">
+        <v>2.1039938000000001E-2</v>
+      </c>
+      <c r="N28">
+        <v>3.4517692999999898E-2</v>
+      </c>
+      <c r="O28">
+        <v>2.6916608000000002E-2</v>
+      </c>
+      <c r="P28">
+        <v>5.9800813999999897E-2</v>
+      </c>
+      <c r="Q28">
+        <v>1.9532895000000002E-2</v>
+      </c>
+      <c r="R28">
+        <v>1.8909735999999899E-2</v>
+      </c>
+      <c r="S28">
+        <v>1.31030319999999E-2</v>
+      </c>
+      <c r="T28">
+        <v>44.047112364</v>
+      </c>
+      <c r="U28">
+        <v>32.697722216000003</v>
+      </c>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>7.3635747799999898</v>
+      </c>
+      <c r="D29">
+        <v>19.412077258999901</v>
+      </c>
+      <c r="E29">
+        <v>9.1873189999999907E-3</v>
+      </c>
+      <c r="F29">
+        <v>9.6458380000000003E-3</v>
+      </c>
+      <c r="G29">
+        <v>1.8749375999999901E-2</v>
+      </c>
+      <c r="H29">
+        <v>1.1654217999999999E-2</v>
+      </c>
+      <c r="I29">
+        <v>1.6201801999999901E-2</v>
+      </c>
+      <c r="J29">
+        <v>6.9899893000000005E-2</v>
+      </c>
+      <c r="K29">
+        <v>1.0262076280000001</v>
+      </c>
+      <c r="L29">
+        <v>1.507725419</v>
+      </c>
+      <c r="M29">
+        <v>1.4650526000000001E-2</v>
+      </c>
+      <c r="N29">
+        <v>2.8990393E-2</v>
+      </c>
+      <c r="O29">
+        <v>1.92428989999999E-2</v>
+      </c>
+      <c r="P29">
+        <v>3.8904999000000003E-2</v>
+      </c>
+      <c r="Q29">
+        <v>1.3895174E-2</v>
+      </c>
+      <c r="R29">
+        <v>1.2817033999999901E-2</v>
+      </c>
+      <c r="S29">
+        <v>7.44480199999999E-3</v>
+      </c>
+      <c r="T29">
+        <v>44.542719206000001</v>
+      </c>
+      <c r="U29">
+        <v>29.604357673999999</v>
+      </c>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="C30" s="1">
+        <v>7.4008092825999903</v>
+      </c>
+      <c r="D30" s="1">
+        <v>22.1151813416</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.21111953E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1.29574681999999E-2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2.1905743099999899E-2</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1.47182786999999E-2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2.2763139799999998E-2</v>
+      </c>
+      <c r="J30" s="1">
+        <v>9.3427465799999998E-2</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1.0199779689999999</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1.4899430571999901</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1.8267769900000001E-2</v>
+      </c>
+      <c r="N30" s="1">
+        <v>3.2007168499999898E-2</v>
+      </c>
+      <c r="O30" s="1">
+        <v>2.32702768999999E-2</v>
+      </c>
+      <c r="P30" s="1">
+        <v>4.90874935999999E-2</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1.68652153E-2</v>
+      </c>
+      <c r="R30" s="1">
+        <v>1.5960736999999899E-2</v>
+      </c>
+      <c r="S30" s="1">
+        <v>1.0287948999999999E-2</v>
+      </c>
+      <c r="T30" s="1">
+        <v>44.704140538099999</v>
+      </c>
+      <c r="U30" s="1">
+        <v>32.4013560924</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2629,19 +4485,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B17374F-425A-0C4A-B316-973C7C980C22}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -2661,21 +4523,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -3205,17 +5067,17 @@
         <v>29.295764520799999</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -3226,24 +5088,738 @@
         <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="M19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>7.5513204099999802</v>
+      </c>
+      <c r="D20">
+        <v>24.247446106999998</v>
+      </c>
+      <c r="E20">
+        <v>2.7348827999999999E-2</v>
+      </c>
+      <c r="F20">
+        <v>2.3291691E-2</v>
+      </c>
+      <c r="G20">
+        <v>0.158967359</v>
+      </c>
+      <c r="H20">
+        <v>7.3688180000000103E-2</v>
+      </c>
+      <c r="I20">
+        <v>2.7546161999999999E-2</v>
+      </c>
+      <c r="J20">
+        <v>0.110198801</v>
+      </c>
+      <c r="K20">
+        <v>1.0297590569999999</v>
+      </c>
+      <c r="L20">
+        <v>1.55953680699999</v>
+      </c>
+      <c r="M20">
+        <v>6.5228102999999898E-2</v>
+      </c>
+      <c r="N20">
+        <v>0.13467681100000001</v>
+      </c>
+      <c r="O20">
+        <v>5.9815158999999903E-2</v>
+      </c>
+      <c r="P20">
+        <v>7.0869253999999895E-2</v>
+      </c>
+      <c r="Q20">
+        <v>0.111966368999999</v>
+      </c>
+      <c r="R20">
+        <v>3.60062629999999E-2</v>
+      </c>
+      <c r="S20">
+        <v>1.2321749999999999E-2</v>
+      </c>
+      <c r="T20">
+        <v>44.581382001999998</v>
+      </c>
+      <c r="U20">
+        <v>35.338243663</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>7.2698827309999903</v>
+      </c>
+      <c r="D21">
+        <v>21.404364184999999</v>
+      </c>
+      <c r="E21">
+        <v>2.1344746000000001E-2</v>
+      </c>
+      <c r="F21">
+        <v>1.7194567000000001E-2</v>
+      </c>
+      <c r="G21">
+        <v>0.14631290999999999</v>
+      </c>
+      <c r="H21">
+        <v>6.4450642000000002E-2</v>
+      </c>
+      <c r="I21">
+        <v>1.8744515E-2</v>
+      </c>
+      <c r="J21">
+        <v>7.9668263000000003E-2</v>
+      </c>
+      <c r="K21">
+        <v>1.0394987149999899</v>
+      </c>
+      <c r="L21">
+        <v>1.502645531</v>
+      </c>
+      <c r="M21">
+        <v>5.4986146999999902E-2</v>
+      </c>
+      <c r="N21">
+        <v>0.123220872999999</v>
+      </c>
+      <c r="O21">
+        <v>5.1369063999999999E-2</v>
+      </c>
+      <c r="P21">
+        <v>5.4733614999999999E-2</v>
+      </c>
+      <c r="Q21">
+        <v>0.104926855999999</v>
+      </c>
+      <c r="R21">
+        <v>2.9989466999999902E-2</v>
+      </c>
+      <c r="S21">
+        <v>8.4618609999999993E-3</v>
+      </c>
+      <c r="T21">
+        <v>44.629201148999996</v>
+      </c>
+      <c r="U21">
+        <v>32.018775931999997</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>7.3264641170000004</v>
+      </c>
+      <c r="D22">
+        <v>22.466129992999999</v>
+      </c>
+      <c r="E22">
+        <v>2.1883897999999902E-2</v>
+      </c>
+      <c r="F22">
+        <v>1.6998016000000001E-2</v>
+      </c>
+      <c r="G22">
+        <v>0.145709805999999</v>
+      </c>
+      <c r="H22">
+        <v>6.4420937999999997E-2</v>
+      </c>
+      <c r="I22">
+        <v>1.91661029999999E-2</v>
+      </c>
+      <c r="J22">
+        <v>8.1488052000000005E-2</v>
+      </c>
+      <c r="K22">
+        <v>1.0268953080000001</v>
+      </c>
+      <c r="L22">
+        <v>1.50547849199999</v>
+      </c>
+      <c r="M22">
+        <v>5.5976499999999901E-2</v>
+      </c>
+      <c r="N22">
+        <v>0.12344206299999901</v>
+      </c>
+      <c r="O22">
+        <v>5.2817087999999901E-2</v>
+      </c>
+      <c r="P22">
+        <v>5.5508145000000002E-2</v>
+      </c>
+      <c r="Q22">
+        <v>0.10604079999999901</v>
+      </c>
+      <c r="R22">
+        <v>3.0152759000000001E-2</v>
+      </c>
+      <c r="S22">
+        <v>8.7461080000000007E-3</v>
+      </c>
+      <c r="T22">
+        <v>44.415855835999999</v>
+      </c>
+      <c r="U22">
+        <v>33.134981281999998</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>6.9689155059999903</v>
+      </c>
+      <c r="D23">
+        <v>22.495646430000001</v>
+      </c>
+      <c r="E23">
+        <v>2.1391297999999899E-2</v>
+      </c>
+      <c r="F23">
+        <v>1.7374040999999899E-2</v>
+      </c>
+      <c r="G23">
+        <v>0.14401679100000001</v>
+      </c>
+      <c r="H23">
+        <v>6.4167501999999904E-2</v>
+      </c>
+      <c r="I23">
+        <v>1.93272309999999E-2</v>
+      </c>
+      <c r="J23">
+        <v>8.1496805999999894E-2</v>
+      </c>
+      <c r="K23">
+        <v>0.99248199599999898</v>
+      </c>
+      <c r="L23">
+        <v>1.4710147149999899</v>
+      </c>
+      <c r="M23">
+        <v>5.4580605999999997E-2</v>
+      </c>
+      <c r="N23">
+        <v>0.122943679999999</v>
+      </c>
+      <c r="O23">
+        <v>5.1444298999999902E-2</v>
+      </c>
+      <c r="P23">
+        <v>5.5920819999999899E-2</v>
+      </c>
+      <c r="Q23">
+        <v>0.10951282699999999</v>
+      </c>
+      <c r="R23">
+        <v>2.9763003999999899E-2</v>
+      </c>
+      <c r="S23">
+        <v>8.6898849999999892E-3</v>
+      </c>
+      <c r="T23">
+        <v>44.570476214999999</v>
+      </c>
+      <c r="U23">
+        <v>32.736548630000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>7.2512274760000102</v>
+      </c>
+      <c r="D24">
+        <v>24.166148569999901</v>
+      </c>
+      <c r="E24">
+        <v>2.3038829999999899E-2</v>
+      </c>
+      <c r="F24">
+        <v>1.8695356E-2</v>
+      </c>
+      <c r="G24">
+        <v>0.14824976500000001</v>
+      </c>
+      <c r="H24">
+        <v>7.0914667999999806E-2</v>
+      </c>
+      <c r="I24">
+        <v>2.2338318999999902E-2</v>
+      </c>
+      <c r="J24">
+        <v>9.1780653999999906E-2</v>
+      </c>
+      <c r="K24">
+        <v>1.0279256779999899</v>
+      </c>
+      <c r="L24">
+        <v>1.4851478469999999</v>
+      </c>
+      <c r="M24">
+        <v>6.1005547E-2</v>
+      </c>
+      <c r="N24">
+        <v>0.126195998999999</v>
+      </c>
+      <c r="O24">
+        <v>5.6547677999999997E-2</v>
+      </c>
+      <c r="P24">
+        <v>6.2264739999999902E-2</v>
+      </c>
+      <c r="Q24">
+        <v>0.10774690299999901</v>
+      </c>
+      <c r="R24">
+        <v>3.1223648999999999E-2</v>
+      </c>
+      <c r="S24">
+        <v>1.0053657999999899E-2</v>
+      </c>
+      <c r="T24">
+        <v>44.435750783000003</v>
+      </c>
+      <c r="U24">
+        <v>34.791765472999998</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>7.6200290430000104</v>
+      </c>
+      <c r="D25">
+        <v>22.806770280999999</v>
+      </c>
+      <c r="E25">
+        <v>2.4653596999999999E-2</v>
+      </c>
+      <c r="F25">
+        <v>2.0331005999999999E-2</v>
+      </c>
+      <c r="G25">
+        <v>0.15134049299999999</v>
+      </c>
+      <c r="H25">
+        <v>6.8483931999999997E-2</v>
+      </c>
+      <c r="I25">
+        <v>2.5593478999999999E-2</v>
+      </c>
+      <c r="J25">
+        <v>0.10309397300000001</v>
+      </c>
+      <c r="K25">
+        <v>1.0561028050000001</v>
+      </c>
+      <c r="L25">
+        <v>1.5346946829999999</v>
+      </c>
+      <c r="M25">
+        <v>6.1456138999999903E-2</v>
+      </c>
+      <c r="N25">
+        <v>0.130431254999999</v>
+      </c>
+      <c r="O25">
+        <v>5.73902359999999E-2</v>
+      </c>
+      <c r="P25">
+        <v>6.6581584000000096E-2</v>
+      </c>
+      <c r="Q25">
+        <v>0.10899137</v>
+      </c>
+      <c r="R25">
+        <v>3.3565759000000001E-2</v>
+      </c>
+      <c r="S25">
+        <v>1.1520897999999899E-2</v>
+      </c>
+      <c r="T25">
+        <v>44.333628619000002</v>
+      </c>
+      <c r="U25">
+        <v>33.916633288</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>6.906543375</v>
+      </c>
+      <c r="D26">
+        <v>21.649262527999898</v>
+      </c>
+      <c r="E26">
+        <v>2.2310980000000001E-2</v>
+      </c>
+      <c r="F26">
+        <v>1.7362046999999901E-2</v>
+      </c>
+      <c r="G26">
+        <v>0.14566406100000001</v>
+      </c>
+      <c r="H26">
+        <v>6.5316368E-2</v>
+      </c>
+      <c r="I26">
+        <v>2.0239139E-2</v>
+      </c>
+      <c r="J26">
+        <v>8.4663461999999995E-2</v>
+      </c>
+      <c r="K26">
+        <v>0.95842297399999998</v>
+      </c>
+      <c r="L26">
+        <v>1.4724399029999899</v>
+      </c>
+      <c r="M26">
+        <v>6.0050554999999999E-2</v>
+      </c>
+      <c r="N26">
+        <v>0.125079679999999</v>
+      </c>
+      <c r="O26">
+        <v>5.1933507999999899E-2</v>
+      </c>
+      <c r="P26">
+        <v>5.8317038999999897E-2</v>
+      </c>
+      <c r="Q26">
+        <v>0.105434426</v>
+      </c>
+      <c r="R26">
+        <v>3.0656197E-2</v>
+      </c>
+      <c r="S26">
+        <v>9.1085229999999899E-3</v>
+      </c>
+      <c r="T26">
+        <v>44.570538892000002</v>
+      </c>
+      <c r="U26">
+        <v>31.811781061000001</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>6.9750089059999896</v>
+      </c>
+      <c r="D27">
+        <v>22.571584022</v>
+      </c>
+      <c r="E27">
+        <v>2.1942482999999999E-2</v>
+      </c>
+      <c r="F27">
+        <v>1.63554299999999E-2</v>
+      </c>
+      <c r="G27">
+        <v>0.145589158</v>
+      </c>
+      <c r="H27">
+        <v>6.4587031000000003E-2</v>
+      </c>
+      <c r="I27">
+        <v>1.98113E-2</v>
+      </c>
+      <c r="J27">
+        <v>8.4279973999999994E-2</v>
+      </c>
+      <c r="K27">
+        <v>0.95833263700000004</v>
+      </c>
+      <c r="L27">
+        <v>1.4730278189999899</v>
+      </c>
+      <c r="M27">
+        <v>5.5542592999999897E-2</v>
+      </c>
+      <c r="N27">
+        <v>0.12401807399999901</v>
+      </c>
+      <c r="O27">
+        <v>5.2996541000000098E-2</v>
+      </c>
+      <c r="P27">
+        <v>5.6223126999999998E-2</v>
+      </c>
+      <c r="Q27">
+        <v>0.105089269999999</v>
+      </c>
+      <c r="R27">
+        <v>3.0083537E-2</v>
+      </c>
+      <c r="S27">
+        <v>9.0125689999999894E-3</v>
+      </c>
+      <c r="T27">
+        <v>44.430006251999998</v>
+      </c>
+      <c r="U27">
+        <v>32.791702336</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>7.0259362999999899</v>
+      </c>
+      <c r="D28">
+        <v>21.658646385999901</v>
+      </c>
+      <c r="E28">
+        <v>2.0627121000000002E-2</v>
+      </c>
+      <c r="F28">
+        <v>1.6267680999999999E-2</v>
+      </c>
+      <c r="G28">
+        <v>0.143698732999999</v>
+      </c>
+      <c r="H28">
+        <v>6.3873458999999994E-2</v>
+      </c>
+      <c r="I28">
+        <v>1.6579975E-2</v>
+      </c>
+      <c r="J28">
+        <v>7.2332363999999899E-2</v>
+      </c>
+      <c r="K28">
+        <v>1.0161890119999899</v>
+      </c>
+      <c r="L28">
+        <v>1.486110949</v>
+      </c>
+      <c r="M28">
+        <v>5.0317859999999999E-2</v>
+      </c>
+      <c r="N28">
+        <v>0.12218572</v>
+      </c>
+      <c r="O28">
+        <v>4.7604535000000003E-2</v>
+      </c>
+      <c r="P28">
+        <v>5.1483073999999997E-2</v>
+      </c>
+      <c r="Q28">
+        <v>0.105260303999999</v>
+      </c>
+      <c r="R28">
+        <v>2.8828474999999899E-2</v>
+      </c>
+      <c r="S28">
+        <v>7.7234779999999902E-3</v>
+      </c>
+      <c r="T28">
+        <v>44.663933141000001</v>
+      </c>
+      <c r="U28">
+        <v>31.958183706</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>7.2274018779999798</v>
+      </c>
+      <c r="D29">
+        <v>24.207679746999901</v>
+      </c>
+      <c r="E29">
+        <v>2.4203506999999999E-2</v>
+      </c>
+      <c r="F29">
+        <v>1.9280820000000001E-2</v>
+      </c>
+      <c r="G29">
+        <v>0.151212824999999</v>
+      </c>
+      <c r="H29">
+        <v>6.8203349999999996E-2</v>
+      </c>
+      <c r="I29">
+        <v>2.5144103000000001E-2</v>
+      </c>
+      <c r="J29">
+        <v>0.10115323599999899</v>
+      </c>
+      <c r="K29">
+        <v>1.042490492</v>
+      </c>
+      <c r="L29">
+        <v>1.50019079</v>
+      </c>
+      <c r="M29">
+        <v>5.8215439999999903E-2</v>
+      </c>
+      <c r="N29">
+        <v>0.12911028899999899</v>
+      </c>
+      <c r="O29">
+        <v>5.8745251999999998E-2</v>
+      </c>
+      <c r="P29">
+        <v>6.4507741999999896E-2</v>
+      </c>
+      <c r="Q29">
+        <v>0.109052889</v>
+      </c>
+      <c r="R29">
+        <v>3.2762976999999999E-2</v>
+      </c>
+      <c r="S29">
+        <v>1.1289560000000001E-2</v>
+      </c>
+      <c r="T29">
+        <v>44.863111512000003</v>
+      </c>
+      <c r="U29">
+        <v>34.865582537000002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="C30" s="1">
+        <v>7.2122729741999896</v>
+      </c>
+      <c r="D30" s="1">
+        <v>22.767367824899999</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2.2874528799999998E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1.8315065500000002E-2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.1480761901</v>
+      </c>
+      <c r="H30" s="1">
+        <v>6.6810606999999994E-2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2.1449032600000001E-2</v>
+      </c>
+      <c r="J30" s="1">
+        <v>8.9015558499999994E-2</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1.0148098673999999</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1.4990287536</v>
+      </c>
+      <c r="M30" s="1">
+        <v>5.7735948999999898E-2</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0.12613044439999899</v>
+      </c>
+      <c r="O30" s="1">
+        <v>5.4066336E-2</v>
+      </c>
+      <c r="P30" s="1">
+        <v>5.9640913999999899E-2</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0.10740220139999899</v>
+      </c>
+      <c r="R30" s="1">
+        <v>3.1303208699999897E-2</v>
+      </c>
+      <c r="S30" s="1">
+        <v>9.6928289999999896E-3</v>
+      </c>
+      <c r="T30" s="1">
+        <v>44.549388440100003</v>
+      </c>
+      <c r="U30" s="1">
+        <v>33.336419790800001</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3256,7 +5832,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE3BDD0-3A87-544A-A16E-D142A4C1F8FB}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -3289,21 +5865,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -3833,15 +6409,15 @@
         <v>15.422410439199901</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -3850,7 +6426,7 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -3861,24 +6437,738 @@
         <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="M19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>7.1846088389999903</v>
+      </c>
+      <c r="D20">
+        <v>22.968327054</v>
+      </c>
+      <c r="E20">
+        <v>1.3658208E-2</v>
+      </c>
+      <c r="F20">
+        <v>1.47979069999999E-2</v>
+      </c>
+      <c r="G20">
+        <v>2.3332511999999899E-2</v>
+      </c>
+      <c r="H20">
+        <v>1.63317079999999E-2</v>
+      </c>
+      <c r="I20">
+        <v>2.6502664999999901E-2</v>
+      </c>
+      <c r="J20">
+        <v>0.14607609799999999</v>
+      </c>
+      <c r="K20">
+        <v>0.96770050399999896</v>
+      </c>
+      <c r="L20">
+        <v>1.44445634699999</v>
+      </c>
+      <c r="M20">
+        <v>2.0000416E-2</v>
+      </c>
+      <c r="N20">
+        <v>3.3727324000000003E-2</v>
+      </c>
+      <c r="O20">
+        <v>2.49904759999999E-2</v>
+      </c>
+      <c r="P20">
+        <v>5.3637763999999997E-2</v>
+      </c>
+      <c r="Q20">
+        <v>1.8676583999999899E-2</v>
+      </c>
+      <c r="R20">
+        <v>1.75354449999999E-2</v>
+      </c>
+      <c r="S20">
+        <v>1.16978839999999E-2</v>
+      </c>
+      <c r="T20">
+        <v>44.700189727999998</v>
+      </c>
+      <c r="U20">
+        <v>33.022369670000003</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>7.2504183859999998</v>
+      </c>
+      <c r="D21">
+        <v>20.674760056999901</v>
+      </c>
+      <c r="E21">
+        <v>1.0745784E-2</v>
+      </c>
+      <c r="F21">
+        <v>1.1279472999999899E-2</v>
+      </c>
+      <c r="G21">
+        <v>2.0105579999999901E-2</v>
+      </c>
+      <c r="H21">
+        <v>1.33515329999999E-2</v>
+      </c>
+      <c r="I21">
+        <v>2.0045930999999899E-2</v>
+      </c>
+      <c r="J21">
+        <v>0.12396632</v>
+      </c>
+      <c r="K21">
+        <v>0.98069630899999904</v>
+      </c>
+      <c r="L21">
+        <v>1.4559042849999999</v>
+      </c>
+      <c r="M21">
+        <v>1.7120713999999999E-2</v>
+      </c>
+      <c r="N21">
+        <v>2.94945379999999E-2</v>
+      </c>
+      <c r="O21">
+        <v>2.1910464000000001E-2</v>
+      </c>
+      <c r="P21">
+        <v>4.4338133999999897E-2</v>
+      </c>
+      <c r="Q21">
+        <v>1.5144212000000001E-2</v>
+      </c>
+      <c r="R21">
+        <v>1.44695409999999E-2</v>
+      </c>
+      <c r="S21">
+        <v>9.0278860000000006E-3</v>
+      </c>
+      <c r="T21">
+        <v>44.372622671999999</v>
+      </c>
+      <c r="U21">
+        <v>30.741129004000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>7.0756666310000096</v>
+      </c>
+      <c r="D22">
+        <v>21.210381155</v>
+      </c>
+      <c r="E22">
+        <v>1.05551379999999E-2</v>
+      </c>
+      <c r="F22">
+        <v>1.1077547999999901E-2</v>
+      </c>
+      <c r="G22">
+        <v>2.0460232999999901E-2</v>
+      </c>
+      <c r="H22">
+        <v>1.3007589999999901E-2</v>
+      </c>
+      <c r="I22">
+        <v>1.92502489999999E-2</v>
+      </c>
+      <c r="J22">
+        <v>0.121968620999999</v>
+      </c>
+      <c r="K22">
+        <v>0.98416287499999999</v>
+      </c>
+      <c r="L22">
+        <v>1.4825264309999999</v>
+      </c>
+      <c r="M22">
+        <v>1.66769549999999E-2</v>
+      </c>
+      <c r="N22">
+        <v>3.04185469999999E-2</v>
+      </c>
+      <c r="O22">
+        <v>2.1391639E-2</v>
+      </c>
+      <c r="P22">
+        <v>4.3333069000000002E-2</v>
+      </c>
+      <c r="Q22">
+        <v>1.53670659999999E-2</v>
+      </c>
+      <c r="R22">
+        <v>1.42551209999999E-2</v>
+      </c>
+      <c r="S22">
+        <v>8.6408779999999994E-3</v>
+      </c>
+      <c r="T22">
+        <v>44.485469029000001</v>
+      </c>
+      <c r="U22">
+        <v>31.126606148</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>7.5884141100000102</v>
+      </c>
+      <c r="D23">
+        <v>20.952814533000002</v>
+      </c>
+      <c r="E23">
+        <v>1.0623741000000001E-2</v>
+      </c>
+      <c r="F23">
+        <v>1.10656619999999E-2</v>
+      </c>
+      <c r="G23">
+        <v>2.0923034E-2</v>
+      </c>
+      <c r="H23">
+        <v>1.3123301E-2</v>
+      </c>
+      <c r="I23">
+        <v>1.94829869999999E-2</v>
+      </c>
+      <c r="J23">
+        <v>0.122268514999999</v>
+      </c>
+      <c r="K23">
+        <v>1.0785246179999901</v>
+      </c>
+      <c r="L23">
+        <v>1.5016997999999899</v>
+      </c>
+      <c r="M23">
+        <v>1.6595830999999901E-2</v>
+      </c>
+      <c r="N23">
+        <v>3.0412688999999899E-2</v>
+      </c>
+      <c r="O23">
+        <v>2.1344474999999901E-2</v>
+      </c>
+      <c r="P23">
+        <v>4.4542283999999897E-2</v>
+      </c>
+      <c r="Q23">
+        <v>1.5459848E-2</v>
+      </c>
+      <c r="R23">
+        <v>1.4492405999999999E-2</v>
+      </c>
+      <c r="S23">
+        <v>8.8919429999999907E-3</v>
+      </c>
+      <c r="T23">
+        <v>44.919536483999998</v>
+      </c>
+      <c r="U23">
+        <v>31.498343984000002</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>7.5763775259999999</v>
+      </c>
+      <c r="D24">
+        <v>20.573066979999901</v>
+      </c>
+      <c r="E24">
+        <v>9.6985800000000105E-3</v>
+      </c>
+      <c r="F24">
+        <v>1.05203139999999E-2</v>
+      </c>
+      <c r="G24">
+        <v>1.99988859999999E-2</v>
+      </c>
+      <c r="H24">
+        <v>1.20842839999999E-2</v>
+      </c>
+      <c r="I24">
+        <v>1.7382418E-2</v>
+      </c>
+      <c r="J24">
+        <v>0.114189544999999</v>
+      </c>
+      <c r="K24">
+        <v>1.10670999599999</v>
+      </c>
+      <c r="L24">
+        <v>1.5405908770000001</v>
+      </c>
+      <c r="M24">
+        <v>1.5144846999999901E-2</v>
+      </c>
+      <c r="N24">
+        <v>2.99720879999999E-2</v>
+      </c>
+      <c r="O24">
+        <v>1.9899824E-2</v>
+      </c>
+      <c r="P24">
+        <v>4.0788927999999898E-2</v>
+      </c>
+      <c r="Q24">
+        <v>1.4748944E-2</v>
+      </c>
+      <c r="R24">
+        <v>1.3283154E-2</v>
+      </c>
+      <c r="S24">
+        <v>8.0259379999999998E-3</v>
+      </c>
+      <c r="T24">
+        <v>44.427370293000003</v>
+      </c>
+      <c r="U24">
+        <v>31.147951966000001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>7.4380483760000002</v>
+      </c>
+      <c r="D25">
+        <v>21.341291623</v>
+      </c>
+      <c r="E25">
+        <v>1.2543802999999999E-2</v>
+      </c>
+      <c r="F25">
+        <v>1.31401359999999E-2</v>
+      </c>
+      <c r="G25">
+        <v>2.1730309E-2</v>
+      </c>
+      <c r="H25">
+        <v>1.4853921000000001E-2</v>
+      </c>
+      <c r="I25">
+        <v>2.3431385999999998E-2</v>
+      </c>
+      <c r="J25">
+        <v>0.13604090399999899</v>
+      </c>
+      <c r="K25">
+        <v>1.04457373599999</v>
+      </c>
+      <c r="L25">
+        <v>1.4698679619999999</v>
+      </c>
+      <c r="M25">
+        <v>1.8776869000000002E-2</v>
+      </c>
+      <c r="N25">
+        <v>3.1998261999999902E-2</v>
+      </c>
+      <c r="O25">
+        <v>2.3821845000000001E-2</v>
+      </c>
+      <c r="P25">
+        <v>5.0729153999999999E-2</v>
+      </c>
+      <c r="Q25">
+        <v>1.7433281999999901E-2</v>
+      </c>
+      <c r="R25">
+        <v>1.6182730999999999E-2</v>
+      </c>
+      <c r="S25">
+        <v>1.0603957000000001E-2</v>
+      </c>
+      <c r="T25">
+        <v>44.657496166000001</v>
+      </c>
+      <c r="U25">
+        <v>31.717726393</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>7.4971758980000001</v>
+      </c>
+      <c r="D26">
+        <v>21.523719694999901</v>
+      </c>
+      <c r="E26">
+        <v>1.0296655999999901E-2</v>
+      </c>
+      <c r="F26">
+        <v>1.1440011999999999E-2</v>
+      </c>
+      <c r="G26">
+        <v>2.0334681999999899E-2</v>
+      </c>
+      <c r="H26">
+        <v>1.2890972000000001E-2</v>
+      </c>
+      <c r="I26">
+        <v>1.8652522000000001E-2</v>
+      </c>
+      <c r="J26">
+        <v>0.123924125999999</v>
+      </c>
+      <c r="K26">
+        <v>1.09690533</v>
+      </c>
+      <c r="L26">
+        <v>1.5163021510000001</v>
+      </c>
+      <c r="M26">
+        <v>1.5945990999999899E-2</v>
+      </c>
+      <c r="N26">
+        <v>3.02766719999999E-2</v>
+      </c>
+      <c r="O26">
+        <v>2.0790896999999999E-2</v>
+      </c>
+      <c r="P26">
+        <v>4.2388606999999898E-2</v>
+      </c>
+      <c r="Q26">
+        <v>1.5100852E-2</v>
+      </c>
+      <c r="R26">
+        <v>1.39293019999999E-2</v>
+      </c>
+      <c r="S26">
+        <v>8.4932279999999898E-3</v>
+      </c>
+      <c r="T26">
+        <v>44.544102008999999</v>
+      </c>
+      <c r="U26">
+        <v>32.005566565000002</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>7.3237509479999998</v>
+      </c>
+      <c r="D27">
+        <v>21.274888356999998</v>
+      </c>
+      <c r="E27">
+        <v>1.0157500999999999E-2</v>
+      </c>
+      <c r="F27">
+        <v>1.0895833000000001E-2</v>
+      </c>
+      <c r="G27">
+        <v>1.9959342000000001E-2</v>
+      </c>
+      <c r="H27">
+        <v>1.255413E-2</v>
+      </c>
+      <c r="I27">
+        <v>1.8468452E-2</v>
+      </c>
+      <c r="J27">
+        <v>0.118518705</v>
+      </c>
+      <c r="K27">
+        <v>0.99681556800000004</v>
+      </c>
+      <c r="L27">
+        <v>1.4437548929999999</v>
+      </c>
+      <c r="M27">
+        <v>1.6051514999999999E-2</v>
+      </c>
+      <c r="N27">
+        <v>2.9992243999999901E-2</v>
+      </c>
+      <c r="O27">
+        <v>2.07419529999999E-2</v>
+      </c>
+      <c r="P27">
+        <v>4.2851995999999899E-2</v>
+      </c>
+      <c r="Q27">
+        <v>1.47877329999999E-2</v>
+      </c>
+      <c r="R27">
+        <v>1.384761E-2</v>
+      </c>
+      <c r="S27">
+        <v>8.2885560000000007E-3</v>
+      </c>
+      <c r="T27">
+        <v>44.765935663999997</v>
+      </c>
+      <c r="U27">
+        <v>31.402882573999999</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>7.2010290220000002</v>
+      </c>
+      <c r="D28">
+        <v>21.266226643</v>
+      </c>
+      <c r="E28">
+        <v>1.0226548E-2</v>
+      </c>
+      <c r="F28">
+        <v>1.0839262000000001E-2</v>
+      </c>
+      <c r="G28">
+        <v>1.9803628999999899E-2</v>
+      </c>
+      <c r="H28">
+        <v>1.2654478E-2</v>
+      </c>
+      <c r="I28">
+        <v>1.8664719E-2</v>
+      </c>
+      <c r="J28">
+        <v>0.11831808099999901</v>
+      </c>
+      <c r="K28">
+        <v>0.99991025500000097</v>
+      </c>
+      <c r="L28">
+        <v>1.4694996010000001</v>
+      </c>
+      <c r="M28">
+        <v>1.55755989999999E-2</v>
+      </c>
+      <c r="N28">
+        <v>2.9864908999999901E-2</v>
+      </c>
+      <c r="O28">
+        <v>2.0289204000000002E-2</v>
+      </c>
+      <c r="P28">
+        <v>4.2582162999999999E-2</v>
+      </c>
+      <c r="Q28">
+        <v>1.5082231E-2</v>
+      </c>
+      <c r="R28">
+        <v>1.3791372999999999E-2</v>
+      </c>
+      <c r="S28">
+        <v>8.4904479999999994E-3</v>
+      </c>
+      <c r="T28">
+        <v>44.986198622000003</v>
+      </c>
+      <c r="U28">
+        <v>31.299673079000002</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>7.3925431109999904</v>
+      </c>
+      <c r="D29">
+        <v>20.190696853999899</v>
+      </c>
+      <c r="E29">
+        <v>1.0378413E-2</v>
+      </c>
+      <c r="F29">
+        <v>1.0849961999999999E-2</v>
+      </c>
+      <c r="G29">
+        <v>1.9862037999999999E-2</v>
+      </c>
+      <c r="H29">
+        <v>1.2735293E-2</v>
+      </c>
+      <c r="I29">
+        <v>1.9063568999999898E-2</v>
+      </c>
+      <c r="J29">
+        <v>0.11886272000000001</v>
+      </c>
+      <c r="K29">
+        <v>1.02681086899999</v>
+      </c>
+      <c r="L29">
+        <v>1.457402144</v>
+      </c>
+      <c r="M29">
+        <v>1.5856139999999901E-2</v>
+      </c>
+      <c r="N29">
+        <v>2.9460502999999898E-2</v>
+      </c>
+      <c r="O29">
+        <v>2.0722919999999902E-2</v>
+      </c>
+      <c r="P29">
+        <v>4.3330378999999898E-2</v>
+      </c>
+      <c r="Q29">
+        <v>1.4901899E-2</v>
+      </c>
+      <c r="R29">
+        <v>1.41567039999999E-2</v>
+      </c>
+      <c r="S29">
+        <v>8.5715259999999908E-3</v>
+      </c>
+      <c r="T29">
+        <v>44.476721304999998</v>
+      </c>
+      <c r="U29">
+        <v>30.433315807</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="C30" s="1">
+        <v>7.3528032847000002</v>
+      </c>
+      <c r="D30" s="1">
+        <v>21.197617295099999</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.08884372E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1.15906108999999E-2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2.06510244999999E-2</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1.33587209999999E-2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2.00944897999999E-2</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.1244133635</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1.0282810059999901</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1.4782004491</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1.67744877E-2</v>
+      </c>
+      <c r="N30" s="1">
+        <v>3.0561777599999899E-2</v>
+      </c>
+      <c r="O30" s="1">
+        <v>2.1590369700000001E-2</v>
+      </c>
+      <c r="P30" s="1">
+        <v>4.4852247800000002E-2</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1.5670265100000001E-2</v>
+      </c>
+      <c r="R30" s="1">
+        <v>1.45943386999999E-2</v>
+      </c>
+      <c r="S30" s="1">
+        <v>9.0732243999999997E-3</v>
+      </c>
+      <c r="T30" s="1">
+        <v>44.633564197200002</v>
+      </c>
+      <c r="U30" s="1">
+        <v>31.439556519</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3891,18 +7181,25 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF611A7-FF5C-9946-82AC-26D645B98B8C}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -3922,21 +7219,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -4466,17 +7763,17 @@
         <v>29.296997711900001</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4487,24 +7784,738 @@
         <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="M19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>7.3429957330000004</v>
+      </c>
+      <c r="D20">
+        <v>23.5528792889999</v>
+      </c>
+      <c r="E20">
+        <v>2.2620458999999898E-2</v>
+      </c>
+      <c r="F20">
+        <v>1.7666388000000002E-2</v>
+      </c>
+      <c r="G20">
+        <v>0.14779814899999999</v>
+      </c>
+      <c r="H20">
+        <v>5.0323279999999901E-2</v>
+      </c>
+      <c r="I20">
+        <v>2.2018187000000002E-2</v>
+      </c>
+      <c r="J20">
+        <v>0.14023852099999901</v>
+      </c>
+      <c r="K20">
+        <v>0.99313356799999997</v>
+      </c>
+      <c r="L20">
+        <v>1.4879229940000001</v>
+      </c>
+      <c r="M20">
+        <v>5.7572734999999903E-2</v>
+      </c>
+      <c r="N20">
+        <v>8.9242616999999594E-2</v>
+      </c>
+      <c r="O20">
+        <v>5.1359735999999899E-2</v>
+      </c>
+      <c r="P20">
+        <v>5.8862575E-2</v>
+      </c>
+      <c r="Q20">
+        <v>4.8653609999999903E-2</v>
+      </c>
+      <c r="R20">
+        <v>2.6870714E-2</v>
+      </c>
+      <c r="S20">
+        <v>9.8894080000000006E-3</v>
+      </c>
+      <c r="T20">
+        <v>44.637736338000003</v>
+      </c>
+      <c r="U20">
+        <v>34.151176130000003</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>7.6465857979999896</v>
+      </c>
+      <c r="D21">
+        <v>24.111935548999998</v>
+      </c>
+      <c r="E21">
+        <v>2.4796648000000001E-2</v>
+      </c>
+      <c r="F21">
+        <v>2.0543705999999998E-2</v>
+      </c>
+      <c r="G21">
+        <v>0.151560048</v>
+      </c>
+      <c r="H21">
+        <v>5.3783333999999898E-2</v>
+      </c>
+      <c r="I21">
+        <v>2.6243694000000001E-2</v>
+      </c>
+      <c r="J21">
+        <v>0.15705011299999999</v>
+      </c>
+      <c r="K21">
+        <v>1.08782644</v>
+      </c>
+      <c r="L21">
+        <v>1.5883181989999899</v>
+      </c>
+      <c r="M21">
+        <v>6.2205495999999902E-2</v>
+      </c>
+      <c r="N21">
+        <v>9.3053926000000203E-2</v>
+      </c>
+      <c r="O21">
+        <v>5.4576554999999902E-2</v>
+      </c>
+      <c r="P21">
+        <v>6.6792717000000099E-2</v>
+      </c>
+      <c r="Q21">
+        <v>5.7100578999999999E-2</v>
+      </c>
+      <c r="R21">
+        <v>2.9248020999999898E-2</v>
+      </c>
+      <c r="S21">
+        <v>1.17948339999999E-2</v>
+      </c>
+      <c r="T21">
+        <v>44.585326533</v>
+      </c>
+      <c r="U21">
+        <v>35.280097681999997</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>6.9999426260000002</v>
+      </c>
+      <c r="D22">
+        <v>23.207032851999902</v>
+      </c>
+      <c r="E22">
+        <v>2.09554949999999E-2</v>
+      </c>
+      <c r="F22">
+        <v>1.5969487000000001E-2</v>
+      </c>
+      <c r="G22">
+        <v>0.14263055999999999</v>
+      </c>
+      <c r="H22">
+        <v>4.9040318999999902E-2</v>
+      </c>
+      <c r="I22">
+        <v>1.8640305999999999E-2</v>
+      </c>
+      <c r="J22">
+        <v>0.12785405899999899</v>
+      </c>
+      <c r="K22">
+        <v>0.99638753099999899</v>
+      </c>
+      <c r="L22">
+        <v>1.5101618539999899</v>
+      </c>
+      <c r="M22">
+        <v>6.0660000999999998E-2</v>
+      </c>
+      <c r="N22">
+        <v>8.6552726999999996E-2</v>
+      </c>
+      <c r="O22">
+        <v>4.8532211999999901E-2</v>
+      </c>
+      <c r="P22">
+        <v>5.2929047E-2</v>
+      </c>
+      <c r="Q22">
+        <v>4.6941822999999903E-2</v>
+      </c>
+      <c r="R22">
+        <v>2.4901836E-2</v>
+      </c>
+      <c r="S22">
+        <v>8.46168099999999E-3</v>
+      </c>
+      <c r="T22">
+        <v>47.429885763000001</v>
+      </c>
+      <c r="U22">
+        <v>33.445042813000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>7.1114162529999998</v>
+      </c>
+      <c r="D23">
+        <v>21.393974953000001</v>
+      </c>
+      <c r="E23">
+        <v>2.1377959999999901E-2</v>
+      </c>
+      <c r="F23">
+        <v>1.62649419999999E-2</v>
+      </c>
+      <c r="G23">
+        <v>0.145113676999999</v>
+      </c>
+      <c r="H23">
+        <v>4.9385938999999802E-2</v>
+      </c>
+      <c r="I23">
+        <v>1.9798126999999999E-2</v>
+      </c>
+      <c r="J23">
+        <v>0.12967936099999999</v>
+      </c>
+      <c r="K23">
+        <v>0.979273595</v>
+      </c>
+      <c r="L23">
+        <v>1.478360125</v>
+      </c>
+      <c r="M23">
+        <v>5.41061519999999E-2</v>
+      </c>
+      <c r="N23">
+        <v>8.7020491999999797E-2</v>
+      </c>
+      <c r="O23">
+        <v>4.8209202999999902E-2</v>
+      </c>
+      <c r="P23">
+        <v>5.4615232999999798E-2</v>
+      </c>
+      <c r="Q23">
+        <v>4.6568422999999901E-2</v>
+      </c>
+      <c r="R23">
+        <v>2.5496920999999999E-2</v>
+      </c>
+      <c r="S23">
+        <v>8.9988350000000002E-3</v>
+      </c>
+      <c r="T23">
+        <v>44.370894585999999</v>
+      </c>
+      <c r="U23">
+        <v>31.697978109000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>7.0712179669999999</v>
+      </c>
+      <c r="D24">
+        <v>23.185986245999899</v>
+      </c>
+      <c r="E24">
+        <v>2.0277168999999901E-2</v>
+      </c>
+      <c r="F24">
+        <v>1.5665299000000001E-2</v>
+      </c>
+      <c r="G24">
+        <v>0.14336747999999999</v>
+      </c>
+      <c r="H24">
+        <v>4.8257206999999899E-2</v>
+      </c>
+      <c r="I24">
+        <v>1.7000789999999901E-2</v>
+      </c>
+      <c r="J24">
+        <v>0.122402846999999</v>
+      </c>
+      <c r="K24">
+        <v>0.98738956899999997</v>
+      </c>
+      <c r="L24">
+        <v>1.4665971010000001</v>
+      </c>
+      <c r="M24">
+        <v>5.2556973999999999E-2</v>
+      </c>
+      <c r="N24">
+        <v>8.55300229999999E-2</v>
+      </c>
+      <c r="O24">
+        <v>4.7149626E-2</v>
+      </c>
+      <c r="P24">
+        <v>4.9819033999999998E-2</v>
+      </c>
+      <c r="Q24">
+        <v>4.5880861999999897E-2</v>
+      </c>
+      <c r="R24">
+        <v>2.4413463999999899E-2</v>
+      </c>
+      <c r="S24">
+        <v>8.0040069999999901E-3</v>
+      </c>
+      <c r="T24">
+        <v>44.525312751000001</v>
+      </c>
+      <c r="U24">
+        <v>33.417211205000001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>7.4741345190000104</v>
+      </c>
+      <c r="D25">
+        <v>23.2393809359999</v>
+      </c>
+      <c r="E25">
+        <v>2.5034706999999899E-2</v>
+      </c>
+      <c r="F25">
+        <v>2.1265757999999899E-2</v>
+      </c>
+      <c r="G25">
+        <v>0.14998962499999899</v>
+      </c>
+      <c r="H25">
+        <v>5.3509197999999897E-2</v>
+      </c>
+      <c r="I25">
+        <v>2.6597907E-2</v>
+      </c>
+      <c r="J25">
+        <v>0.15665696199999901</v>
+      </c>
+      <c r="K25">
+        <v>1.0575633470000001</v>
+      </c>
+      <c r="L25">
+        <v>1.4969219119999999</v>
+      </c>
+      <c r="M25">
+        <v>6.0103785000000097E-2</v>
+      </c>
+      <c r="N25">
+        <v>9.2436424000000003E-2</v>
+      </c>
+      <c r="O25">
+        <v>5.4050882999999897E-2</v>
+      </c>
+      <c r="P25">
+        <v>6.5438214999999897E-2</v>
+      </c>
+      <c r="Q25">
+        <v>5.0290345999999903E-2</v>
+      </c>
+      <c r="R25">
+        <v>2.9568048999999999E-2</v>
+      </c>
+      <c r="S25">
+        <v>1.1890443999999899E-2</v>
+      </c>
+      <c r="T25">
+        <v>44.388077471999999</v>
+      </c>
+      <c r="U25">
+        <v>34.10185517</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>6.9968288940000001</v>
+      </c>
+      <c r="D26">
+        <v>23.439458288000001</v>
+      </c>
+      <c r="E26">
+        <v>2.4164664999999901E-2</v>
+      </c>
+      <c r="F26">
+        <v>1.9576948E-2</v>
+      </c>
+      <c r="G26">
+        <v>0.15033519100000001</v>
+      </c>
+      <c r="H26">
+        <v>5.3049750999999798E-2</v>
+      </c>
+      <c r="I26">
+        <v>2.3999398000000002E-2</v>
+      </c>
+      <c r="J26">
+        <v>0.14630080600000001</v>
+      </c>
+      <c r="K26">
+        <v>0.97363515700000103</v>
+      </c>
+      <c r="L26">
+        <v>1.4542293229999901</v>
+      </c>
+      <c r="M26">
+        <v>5.8520236999999899E-2</v>
+      </c>
+      <c r="N26">
+        <v>9.0921041999999896E-2</v>
+      </c>
+      <c r="O26">
+        <v>5.1384410999999901E-2</v>
+      </c>
+      <c r="P26">
+        <v>6.1125301999999999E-2</v>
+      </c>
+      <c r="Q26">
+        <v>4.9877523999999902E-2</v>
+      </c>
+      <c r="R26">
+        <v>2.8591103E-2</v>
+      </c>
+      <c r="S26">
+        <v>1.0781765999999899E-2</v>
+      </c>
+      <c r="T26">
+        <v>44.305936688000003</v>
+      </c>
+      <c r="U26">
+        <v>33.666576411000001</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>7.4625611049999998</v>
+      </c>
+      <c r="D27">
+        <v>22.82496085</v>
+      </c>
+      <c r="E27">
+        <v>2.230615E-2</v>
+      </c>
+      <c r="F27">
+        <v>1.8076180000000001E-2</v>
+      </c>
+      <c r="G27">
+        <v>0.14676730099999999</v>
+      </c>
+      <c r="H27">
+        <v>5.0970807E-2</v>
+      </c>
+      <c r="I27">
+        <v>2.1388586000000001E-2</v>
+      </c>
+      <c r="J27">
+        <v>0.136882066</v>
+      </c>
+      <c r="K27">
+        <v>1.0994674949999901</v>
+      </c>
+      <c r="L27">
+        <v>1.5105352320000001</v>
+      </c>
+      <c r="M27">
+        <v>5.6234381999999999E-2</v>
+      </c>
+      <c r="N27">
+        <v>8.8913810999999995E-2</v>
+      </c>
+      <c r="O27">
+        <v>4.9755001000000097E-2</v>
+      </c>
+      <c r="P27">
+        <v>5.7125241E-2</v>
+      </c>
+      <c r="Q27">
+        <v>4.9070291000000002E-2</v>
+      </c>
+      <c r="R27">
+        <v>2.6501138E-2</v>
+      </c>
+      <c r="S27">
+        <v>9.6319949999999904E-3</v>
+      </c>
+      <c r="T27">
+        <v>44.357667693000003</v>
+      </c>
+      <c r="U27">
+        <v>33.661574203000001</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>7.1563601400000003</v>
+      </c>
+      <c r="D28">
+        <v>23.487976738</v>
+      </c>
+      <c r="E28">
+        <v>2.2029765E-2</v>
+      </c>
+      <c r="F28">
+        <v>1.7306138999999901E-2</v>
+      </c>
+      <c r="G28">
+        <v>0.14432615999999901</v>
+      </c>
+      <c r="H28">
+        <v>5.05491309999999E-2</v>
+      </c>
+      <c r="I28">
+        <v>2.0907203999999999E-2</v>
+      </c>
+      <c r="J28">
+        <v>0.134842781999999</v>
+      </c>
+      <c r="K28">
+        <v>0.96798176000000002</v>
+      </c>
+      <c r="L28">
+        <v>1.4766407349999899</v>
+      </c>
+      <c r="M28">
+        <v>5.5088902000000002E-2</v>
+      </c>
+      <c r="N28">
+        <v>8.7782424999999997E-2</v>
+      </c>
+      <c r="O28">
+        <v>4.9518433000000001E-2</v>
+      </c>
+      <c r="P28">
+        <v>5.5879732999999897E-2</v>
+      </c>
+      <c r="Q28">
+        <v>4.7897324999999998E-2</v>
+      </c>
+      <c r="R28">
+        <v>2.6084820000000002E-2</v>
+      </c>
+      <c r="S28">
+        <v>9.3965949999999902E-3</v>
+      </c>
+      <c r="T28">
+        <v>44.507929421999997</v>
+      </c>
+      <c r="U28">
+        <v>33.840298513999997</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>7.1837992689999997</v>
+      </c>
+      <c r="D29">
+        <v>22.784380218999999</v>
+      </c>
+      <c r="E29">
+        <v>2.15160259999999E-2</v>
+      </c>
+      <c r="F29">
+        <v>1.7637131999999899E-2</v>
+      </c>
+      <c r="G29">
+        <v>0.14449606499999901</v>
+      </c>
+      <c r="H29">
+        <v>4.9505193999999898E-2</v>
+      </c>
+      <c r="I29">
+        <v>2.0149925999999999E-2</v>
+      </c>
+      <c r="J29">
+        <v>0.13258235999999901</v>
+      </c>
+      <c r="K29">
+        <v>0.97115457500000002</v>
+      </c>
+      <c r="L29">
+        <v>1.4519456209999899</v>
+      </c>
+      <c r="M29">
+        <v>5.4728262999999999E-2</v>
+      </c>
+      <c r="N29">
+        <v>8.6800188999999695E-2</v>
+      </c>
+      <c r="O29">
+        <v>4.8656961999999998E-2</v>
+      </c>
+      <c r="P29">
+        <v>5.4634794E-2</v>
+      </c>
+      <c r="Q29">
+        <v>4.6488176999999999E-2</v>
+      </c>
+      <c r="R29">
+        <v>2.59733609999999E-2</v>
+      </c>
+      <c r="S29">
+        <v>9.1447849999999904E-3</v>
+      </c>
+      <c r="T29">
+        <v>44.902520539999998</v>
+      </c>
+      <c r="U29">
+        <v>33.132337776999996</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="C30" s="1">
+        <v>7.2445842304000001</v>
+      </c>
+      <c r="D30" s="1">
+        <v>23.122796592</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2.25079043999999E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1.7997197900000001E-2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.14663842560000001</v>
+      </c>
+      <c r="H30" s="1">
+        <v>5.0837415999999899E-2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2.16744125E-2</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.138448987699999</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1.0113813036999999</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1.4921633096</v>
+      </c>
+      <c r="M30" s="1">
+        <v>5.7177692699999998E-2</v>
+      </c>
+      <c r="N30" s="1">
+        <v>8.8825367599999899E-2</v>
+      </c>
+      <c r="O30" s="1">
+        <v>5.0319302199999902E-2</v>
+      </c>
+      <c r="P30" s="1">
+        <v>5.7722189100000001E-2</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>4.8876895999999899E-2</v>
+      </c>
+      <c r="R30" s="1">
+        <v>2.6764942699999999E-2</v>
+      </c>
+      <c r="S30" s="1">
+        <v>9.79943499999999E-3</v>
+      </c>
+      <c r="T30" s="1">
+        <v>44.801128778600003</v>
+      </c>
+      <c r="U30" s="1">
+        <v>33.639414801400001</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A87567-1EA1-4546-BBAC-E465585AE33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AED7FF-68B8-274E-AA2B-435BFEA4FCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="54880" yWindow="1100" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="58">
   <si>
     <t>Branch</t>
   </si>
@@ -285,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -293,9 +293,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1292,47 +1289,59 @@
       </c>
       <c r="AO6" s="3"/>
     </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
+      <c r="F10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="4">
+        <v>104</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
       <c r="T10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
@@ -1351,172 +1360,183 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="D11">
+        <v>0.5</v>
+      </c>
+      <c r="E11">
+        <v>152</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4">
+        <v>128</v>
+      </c>
+      <c r="H11" s="4">
         <v>0.25</v>
       </c>
-      <c r="E11">
-        <v>0</v>
+      <c r="I11" s="4">
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="D12">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="E12">
-        <v>144</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="4">
         <v>64</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="4">
         <v>0.5</v>
       </c>
-      <c r="I12">
-        <v>152</v>
+      <c r="I12" s="4">
+        <v>8</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
+        <v>48</v>
+      </c>
+      <c r="D13">
+        <v>0.625</v>
+      </c>
+      <c r="E13">
         <v>64</v>
       </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>47</v>
-      </c>
-      <c r="H13">
-        <v>0.625</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+      <c r="F13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="4">
+        <v>110</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="4">
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14">
-        <v>110</v>
-      </c>
-      <c r="D14">
-        <v>0.25</v>
-      </c>
-      <c r="E14">
-        <v>64</v>
-      </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14">
-        <v>48</v>
-      </c>
-      <c r="H14">
-        <v>0.625</v>
-      </c>
-      <c r="I14">
-        <v>64</v>
-      </c>
+      <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
       <c r="T14" s="2"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <v>104</v>
+      </c>
+      <c r="H16">
+        <v>0.25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="4">
-        <v>104</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <v>0.5</v>
+      </c>
+      <c r="E17">
+        <v>152</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>128</v>
+      </c>
+      <c r="H17">
         <v>0.25</v>
       </c>
-      <c r="E17" s="4">
+      <c r="I17">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>47</v>
+      </c>
+      <c r="D18">
+        <v>0.625</v>
+      </c>
+      <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="B18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="4">
-        <v>128</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E18" s="4">
-        <v>144</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>64</v>
@@ -1525,58 +1545,32 @@
         <v>0.5</v>
       </c>
       <c r="I18">
-        <v>152</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="B19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>0.625</v>
+      </c>
+      <c r="E19">
         <v>64</v>
       </c>
-      <c r="D19" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="4">
-        <v>8</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G19">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="H19">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="B20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="4">
-        <v>110</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E20" s="4">
-        <v>64</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20">
-        <v>48</v>
-      </c>
-      <c r="H20">
-        <v>0.625</v>
-      </c>
-      <c r="I20">
         <v>64</v>
       </c>
     </row>
@@ -2436,12 +2430,64 @@
       </c>
       <c r="BG27" s="3"/>
     </row>
+    <row r="30" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31">
+        <v>80</v>
+      </c>
+      <c r="D31">
+        <v>0.375</v>
+      </c>
+      <c r="E31">
+        <v>32</v>
+      </c>
+    </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="BE23:BG23"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="BB23:BD23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="C1:AO1"/>
     <mergeCell ref="U2:W2"/>
@@ -2456,33 +2502,9 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:Q22"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="AA23:AC23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="BE23:BG23"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AV23:AX23"/>
-    <mergeCell ref="AY23:BA23"/>
-    <mergeCell ref="BB23:BD23"/>
   </mergeCells>
-  <conditionalFormatting sqref="C27:D27">
-    <cfRule type="colorScale" priority="135">
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="colorScale" priority="161">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2491,8 +2513,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="colorScale" priority="161">
+  <conditionalFormatting sqref="C27:D27">
+    <cfRule type="colorScale" priority="135">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2521,8 +2543,58 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F6:G6">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:G27">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H4:H5">
     <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:J6">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I27:J27">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2541,8 +2613,68 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K25:K26">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:M6">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L27:M27">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N4:N5">
     <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25:N26">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O6:P6">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O27:P27">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2561,8 +2693,68 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q25:Q26">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6:S6">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R27:S27">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="T4:T5">
     <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T25:T26">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6:V6">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U27:V27">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2581,8 +2773,68 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W25:W26">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X6:Y6">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X27:Y27">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z5">
     <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z25:Z26">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AB6">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA27:AB27">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2601,8 +2853,68 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC25:AC26">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6:AE6">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD27:AE27">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AF4:AF5">
     <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF25:AF26">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG6:AH6">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG27:AH27">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2621,8 +2933,68 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AI25:AI26">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6:AK6">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ27:AK27">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AL5">
     <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL25:AL26">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM6:AN6">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM27:AN27">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2641,8 +3013,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:G6">
-    <cfRule type="colorScale" priority="48">
+  <conditionalFormatting sqref="AO25:AO26">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2651,228 +3023,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J6">
-    <cfRule type="colorScale" priority="47">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L6:M6">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O6:P6">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6:S6">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6:V6">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X6:Y6">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AB6">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6:AE6">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG6:AH6">
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AK6">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM6:AN6">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25:K26">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N25:N26">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q25:Q26">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T25:T26">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W25:W26">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z25:Z26">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC25:AC26">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF25:AF26">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI25:AI26">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL25:AL26">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO25:AO26">
-    <cfRule type="colorScale" priority="25">
+  <conditionalFormatting sqref="AP27:AQ27">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2891,8 +3043,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AS27:AT27">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AU25:AU26">
     <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AV27:AW27">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2911,8 +3083,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AY27:AZ27">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BA25:BA26">
     <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB27:BC27">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2931,8 +3123,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG25:BG26">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="BE27:BF27">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2941,178 +3133,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27:G27">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27:J27">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L27:M27">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O27:P27">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R27:S27">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U27:V27">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X27:Y27">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA27:AB27">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD27:AE27">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG27:AH27">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ27:AK27">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM27:AN27">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP27:AQ27">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AS27:AT27">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AV27:AW27">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AY27:AZ27">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB27:BC27">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE27:BF27">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="BG25:BG26">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AED7FF-68B8-274E-AA2B-435BFEA4FCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E1BABC-A604-5C4E-A95A-C61A11CAFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="54880" yWindow="1100" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="58">
   <si>
     <t>Branch</t>
   </si>
@@ -223,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -241,20 +241,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -285,13 +271,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -663,47 +647,47 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="6"/>
-      <c r="AO1" s="6"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -712,71 +696,71 @@
       <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6" t="s">
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6" t="s">
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6" t="s">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6" t="s">
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6" t="s">
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6" t="s">
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6" t="s">
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6" t="s">
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AK2" s="6"/>
-      <c r="AL2" s="6"/>
-      <c r="AM2" s="6" t="s">
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AN2" s="6"/>
-      <c r="AO2" s="6"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
@@ -1289,58 +1273,84 @@
       </c>
       <c r="AO6" s="3"/>
     </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>40</v>
+      <c r="F9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9">
+        <v>104</v>
+      </c>
+      <c r="H9">
+        <v>0.25</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="F10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="4">
-        <v>104</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>64</v>
+      </c>
+      <c r="D10">
+        <v>0.5</v>
+      </c>
+      <c r="E10">
+        <v>152</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>128</v>
+      </c>
+      <c r="H10">
         <v>0.25</v>
       </c>
-      <c r="I10" s="4">
-        <v>0</v>
+      <c r="I10">
+        <v>144</v>
       </c>
       <c r="T10" s="1"/>
       <c r="AB10" s="1"/>
@@ -1360,36 +1370,36 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
+        <v>47</v>
+      </c>
+      <c r="D11">
+        <v>0.625</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
         <v>64</v>
       </c>
-      <c r="D11">
+      <c r="H11">
         <v>0.5</v>
       </c>
-      <c r="E11">
-        <v>152</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="4">
-        <v>128</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="I11" s="4">
-        <v>144</v>
+      <c r="I11">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C12">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12">
         <v>0.625</v>
@@ -1397,16 +1407,16 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="F12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12">
         <v>64</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12">
         <v>0.5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12">
         <v>8</v>
       </c>
       <c r="J12" s="1"/>
@@ -1425,32 +1435,32 @@
       <c r="E13">
         <v>64</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13">
         <v>110</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13">
         <v>0.25</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="T14" s="2"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -1550,145 +1560,171 @@
     </row>
     <row r="19" spans="2:59" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19">
         <v>0.625</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19">
         <v>64</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G19">
+      <c r="C20">
+        <v>48</v>
+      </c>
+      <c r="D20">
+        <v>0.625</v>
+      </c>
+      <c r="E20">
+        <v>64</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20">
         <v>110</v>
       </c>
-      <c r="H19">
+      <c r="H20">
         <v>0.25</v>
       </c>
-      <c r="I19">
+      <c r="I20">
         <v>64</v>
       </c>
     </row>
     <row r="22" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6" t="s">
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6" t="s">
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6" t="s">
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6" t="s">
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6" t="s">
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6" t="s">
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6" t="s">
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AB23" s="6"/>
-      <c r="AC23" s="6"/>
-      <c r="AD23" s="6" t="s">
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AE23" s="6"/>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6" t="s">
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="4"/>
+      <c r="AG23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AH23" s="6"/>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="6" t="s">
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AK23" s="6"/>
-      <c r="AL23" s="6"/>
-      <c r="AM23" s="6" t="s">
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AN23" s="6"/>
-      <c r="AO23" s="6"/>
-      <c r="AP23" s="6" t="s">
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AQ23" s="6"/>
-      <c r="AR23" s="6"/>
-      <c r="AS23" s="6" t="s">
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="4"/>
+      <c r="AS23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AT23" s="6"/>
-      <c r="AU23" s="6"/>
-      <c r="AV23" s="6" t="s">
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AW23" s="6"/>
-      <c r="AX23" s="6"/>
-      <c r="AY23" s="6" t="s">
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="4"/>
+      <c r="AY23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AZ23" s="6"/>
-      <c r="BA23" s="6"/>
-      <c r="BB23" s="6" t="s">
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="BC23" s="6"/>
-      <c r="BD23" s="6"/>
-      <c r="BE23" s="6" t="s">
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="BF23" s="6"/>
-      <c r="BG23" s="6"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
     </row>
     <row r="24" spans="2:59" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
@@ -2464,29 +2500,9 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="BE23:BG23"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AV23:AX23"/>
-    <mergeCell ref="AY23:BA23"/>
-    <mergeCell ref="BB23:BD23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="AA23:AC23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:I7"/>
     <mergeCell ref="F14:I14"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="C1:AO1"/>
@@ -2502,6 +2518,26 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="BE23:BG23"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="BB23:BD23"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:D6">
     <cfRule type="colorScale" priority="161">
@@ -3188,21 +3224,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -3733,14 +3769,14 @@
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -4545,21 +4581,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -5090,14 +5126,14 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -5887,21 +5923,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -6432,14 +6468,14 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -7241,21 +7277,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -7786,14 +7822,14 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E1BABC-A604-5C4E-A95A-C61A11CAFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96C642-41FE-8C42-895A-EFA6443F2F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="54880" yWindow="1100" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="58">
   <si>
     <t>Branch</t>
   </si>
@@ -2466,22 +2466,62 @@
       </c>
       <c r="BG27" s="3"/>
     </row>
+    <row r="28" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="30" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" t="s">
-        <v>40</v>
+      <c r="F30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30">
+        <v>104</v>
+      </c>
+      <c r="H30">
+        <v>0.25</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:59" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C31">
@@ -2493,18 +2533,125 @@
       <c r="E31">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="F31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>80</v>
+      </c>
+      <c r="H31">
+        <v>0.375</v>
+      </c>
+      <c r="I31">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="2:59" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34">
+        <v>104</v>
+      </c>
+      <c r="H34">
+        <v>0.25</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35">
+        <v>80</v>
+      </c>
+      <c r="D35">
+        <v>0.375</v>
+      </c>
+      <c r="E35">
+        <v>32</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>80</v>
+      </c>
+      <c r="H35">
+        <v>0.375</v>
+      </c>
+      <c r="I35">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="AM2:AO2"/>
+  <mergeCells count="42">
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="BE23:BG23"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="BB23:BD23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
     <mergeCell ref="C1:AO1"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:Z2"/>
@@ -2518,26 +2665,11 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="AA23:AC23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="BE23:BG23"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AV23:AX23"/>
-    <mergeCell ref="AY23:BA23"/>
-    <mergeCell ref="BB23:BD23"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="AM2:AO2"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:D6">
     <cfRule type="colorScale" priority="161">

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEEF76D-2C15-074D-8A3F-D53FE1BF52CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAC97F2-2DA5-FF49-8AB7-FC0C51C98A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53000" yWindow="680" windowWidth="47520" windowHeight="26040" activeTab="2" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="50740" yWindow="1020" windowWidth="47520" windowHeight="26040" activeTab="4" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="62">
   <si>
     <t>Branch</t>
   </si>
@@ -224,6 +224,12 @@
   <si>
     <t>% improvement</t>
   </si>
+  <si>
+    <t>Always advance</t>
+  </si>
+  <si>
+    <t>Analytic rayleigh</t>
+  </si>
 </sst>
 </file>
 
@@ -277,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -285,6 +291,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2517,11 +2524,27 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="BE23:BG23"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="C22:Q22"/>
     <mergeCell ref="L23:N23"/>
     <mergeCell ref="O23:Q23"/>
@@ -2538,27 +2561,11 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="BE23:BG23"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AV23:AX23"/>
-    <mergeCell ref="AY23:BA23"/>
-    <mergeCell ref="BB23:BD23"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="AA23:AC23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="AM2:AO2"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:D6">
     <cfRule type="colorScale" priority="161">
@@ -7032,7 +7039,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF611A7-FF5C-9946-82AC-26D645B98B8C}">
-  <dimension ref="A1:U46"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -8271,6 +8278,632 @@
         <v>9.5429186571999995</v>
       </c>
     </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>6</v>
+      </c>
+      <c r="I50" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" t="s">
+        <v>33</v>
+      </c>
+      <c r="L50" t="s">
+        <v>34</v>
+      </c>
+      <c r="M50" t="s">
+        <v>14</v>
+      </c>
+      <c r="N50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>0.19884370999999901</v>
+      </c>
+      <c r="D51">
+        <v>2.6854955039999902</v>
+      </c>
+      <c r="E51">
+        <v>1.4223785709999901</v>
+      </c>
+      <c r="F51">
+        <v>0.22175318899999899</v>
+      </c>
+      <c r="G51">
+        <v>1.58286534099999</v>
+      </c>
+      <c r="H51">
+        <v>0.39481889399999898</v>
+      </c>
+      <c r="I51">
+        <v>1.633501026</v>
+      </c>
+      <c r="J51">
+        <v>1.0946146019999901</v>
+      </c>
+      <c r="K51">
+        <v>15.2927611369999</v>
+      </c>
+      <c r="L51">
+        <v>0.29369754299999901</v>
+      </c>
+      <c r="M51">
+        <v>0.19080815800000001</v>
+      </c>
+      <c r="N51">
+        <v>0.32957895700000001</v>
+      </c>
+      <c r="O51">
+        <v>25.018738300999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>0.19552512899999999</v>
+      </c>
+      <c r="D52">
+        <v>2.7188690519999898</v>
+      </c>
+      <c r="E52">
+        <v>1.4199247209999999</v>
+      </c>
+      <c r="F52">
+        <v>0.21758560899999899</v>
+      </c>
+      <c r="G52">
+        <v>1.60711424</v>
+      </c>
+      <c r="H52">
+        <v>0.39061643699999998</v>
+      </c>
+      <c r="I52">
+        <v>1.68378018699999</v>
+      </c>
+      <c r="J52">
+        <v>1.1209142409999999</v>
+      </c>
+      <c r="K52">
+        <v>15.531351381</v>
+      </c>
+      <c r="L52">
+        <v>0.29287765499999902</v>
+      </c>
+      <c r="M52">
+        <v>0.19584457799999999</v>
+      </c>
+      <c r="N52">
+        <v>0.32470463599999999</v>
+      </c>
+      <c r="O52">
+        <v>25.381233592000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>0.245785749</v>
+      </c>
+      <c r="D53">
+        <v>2.8739708739999998</v>
+      </c>
+      <c r="E53">
+        <v>1.53520410999999</v>
+      </c>
+      <c r="F53">
+        <v>0.267486629999999</v>
+      </c>
+      <c r="G53">
+        <v>1.7192921379999999</v>
+      </c>
+      <c r="H53">
+        <v>0.50894172599999898</v>
+      </c>
+      <c r="I53">
+        <v>1.7789894340000001</v>
+      </c>
+      <c r="J53">
+        <v>1.250638178</v>
+      </c>
+      <c r="K53">
+        <v>16.337012117999901</v>
+      </c>
+      <c r="L53">
+        <v>0.348213152999999</v>
+      </c>
+      <c r="M53">
+        <v>0.246125547999999</v>
+      </c>
+      <c r="N53">
+        <v>0.32607998399999999</v>
+      </c>
+      <c r="O53">
+        <v>27.118603063999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>0.44541758300000001</v>
+      </c>
+      <c r="D54">
+        <v>3.4899507149999902</v>
+      </c>
+      <c r="E54">
+        <v>1.936346141</v>
+      </c>
+      <c r="F54">
+        <v>0.46516570699999998</v>
+      </c>
+      <c r="G54">
+        <v>2.1223275049999999</v>
+      </c>
+      <c r="H54">
+        <v>0.91314220699999904</v>
+      </c>
+      <c r="I54">
+        <v>2.1900645879999998</v>
+      </c>
+      <c r="J54">
+        <v>1.6433379619999899</v>
+      </c>
+      <c r="K54">
+        <v>19.251694924999999</v>
+      </c>
+      <c r="L54">
+        <v>0.54314839699999995</v>
+      </c>
+      <c r="M54">
+        <v>0.44180143999999999</v>
+      </c>
+      <c r="N54">
+        <v>0.359054237</v>
+      </c>
+      <c r="O54">
+        <v>33.450040117999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55">
+        <v>0.79665547699999995</v>
+      </c>
+      <c r="D55">
+        <v>3.5530795209999999</v>
+      </c>
+      <c r="E55">
+        <v>2.1290387420000001</v>
+      </c>
+      <c r="F55">
+        <v>0.81662700699999902</v>
+      </c>
+      <c r="G55">
+        <v>2.2999014199999999</v>
+      </c>
+      <c r="H55">
+        <v>1.596025426</v>
+      </c>
+      <c r="I55">
+        <v>2.3582386610000001</v>
+      </c>
+      <c r="J55">
+        <v>1.8310272139999899</v>
+      </c>
+      <c r="K55">
+        <v>17.921814298999902</v>
+      </c>
+      <c r="L55">
+        <v>0.88777081099999899</v>
+      </c>
+      <c r="M55">
+        <v>0.78515675999999901</v>
+      </c>
+      <c r="N55">
+        <v>0.72366604700000003</v>
+      </c>
+      <c r="O55">
+        <v>34.983426395999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <v>0.38219216299999997</v>
+      </c>
+      <c r="D56">
+        <v>3.2884343899999999</v>
+      </c>
+      <c r="E56">
+        <v>1.7992350370000001</v>
+      </c>
+      <c r="F56">
+        <v>0.39907138399999897</v>
+      </c>
+      <c r="G56">
+        <v>2.02512109399999</v>
+      </c>
+      <c r="H56">
+        <v>0.78087062699999898</v>
+      </c>
+      <c r="I56">
+        <v>2.073346913</v>
+      </c>
+      <c r="J56">
+        <v>1.5546284640000001</v>
+      </c>
+      <c r="K56">
+        <v>18.474188861999899</v>
+      </c>
+      <c r="L56">
+        <v>0.47911483199999999</v>
+      </c>
+      <c r="M56">
+        <v>0.376892756</v>
+      </c>
+      <c r="N56">
+        <v>0.53230668000000003</v>
+      </c>
+      <c r="O56">
+        <v>31.640321468</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>9.5015229999999892E-3</v>
+      </c>
+      <c r="D57">
+        <v>2.1657371009999999</v>
+      </c>
+      <c r="E57">
+        <v>1.0648173439999999</v>
+      </c>
+      <c r="F57">
+        <v>2.9270861999999901E-2</v>
+      </c>
+      <c r="G57">
+        <v>1.2529029540000001</v>
+      </c>
+      <c r="H57">
+        <v>4.31910989999999E-2</v>
+      </c>
+      <c r="I57">
+        <v>1.32012464299999</v>
+      </c>
+      <c r="J57">
+        <v>0.79625313899999905</v>
+      </c>
+      <c r="K57">
+        <v>12.912349682999899</v>
+      </c>
+      <c r="L57">
+        <v>0.103363648</v>
+      </c>
+      <c r="M57">
+        <v>8.5210159999999906E-3</v>
+      </c>
+      <c r="N57">
+        <v>0.60051398600000006</v>
+      </c>
+      <c r="O57">
+        <v>19.712409943000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>9.9846319999999794E-3</v>
+      </c>
+      <c r="D58">
+        <v>2.1658805390000002</v>
+      </c>
+      <c r="E58">
+        <v>1.06686614399999</v>
+      </c>
+      <c r="F58">
+        <v>2.9749281999999901E-2</v>
+      </c>
+      <c r="G58">
+        <v>1.2541892369999901</v>
+      </c>
+      <c r="H58">
+        <v>4.6644512999999901E-2</v>
+      </c>
+      <c r="I58">
+        <v>1.3200061679999899</v>
+      </c>
+      <c r="J58">
+        <v>0.797954837999999</v>
+      </c>
+      <c r="K58">
+        <v>12.9035803999999</v>
+      </c>
+      <c r="L58">
+        <v>0.104938452</v>
+      </c>
+      <c r="M58">
+        <v>8.6517969999999906E-3</v>
+      </c>
+      <c r="N58">
+        <v>0.59436843399999995</v>
+      </c>
+      <c r="O58">
+        <v>19.714900135000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>2.1652396000000001E-2</v>
+      </c>
+      <c r="D59">
+        <v>2.1945287819999999</v>
+      </c>
+      <c r="E59">
+        <v>1.084733347</v>
+      </c>
+      <c r="F59">
+        <v>4.0794991999999898E-2</v>
+      </c>
+      <c r="G59">
+        <v>1.2729837639999999</v>
+      </c>
+      <c r="H59">
+        <v>6.5652614999999998E-2</v>
+      </c>
+      <c r="I59">
+        <v>1.340612395</v>
+      </c>
+      <c r="J59">
+        <v>0.81278455199999999</v>
+      </c>
+      <c r="K59">
+        <v>13.03780147</v>
+      </c>
+      <c r="L59">
+        <v>0.116459829999999</v>
+      </c>
+      <c r="M59">
+        <v>1.9818659999999998E-2</v>
+      </c>
+      <c r="N59">
+        <v>0.60064432599999995</v>
+      </c>
+      <c r="O59">
+        <v>20.014397721000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>9</v>
+      </c>
+      <c r="C60">
+        <v>4.3221753999999897E-2</v>
+      </c>
+      <c r="D60">
+        <v>2.2651926419999899</v>
+      </c>
+      <c r="E60">
+        <v>1.127282347</v>
+      </c>
+      <c r="F60">
+        <v>6.2886738999999997E-2</v>
+      </c>
+      <c r="G60">
+        <v>1.31724933899999</v>
+      </c>
+      <c r="H60">
+        <v>0.106868212</v>
+      </c>
+      <c r="I60">
+        <v>1.3815467909999899</v>
+      </c>
+      <c r="J60">
+        <v>0.84972274699999994</v>
+      </c>
+      <c r="K60">
+        <v>13.350605562</v>
+      </c>
+      <c r="L60">
+        <v>0.13819600500000001</v>
+      </c>
+      <c r="M60">
+        <v>4.1816882999999902E-2</v>
+      </c>
+      <c r="N60">
+        <v>0.59630817000000003</v>
+      </c>
+      <c r="O60">
+        <v>20.691055486</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" t="s">
+        <v>6</v>
+      </c>
+      <c r="I63" t="s">
+        <v>12</v>
+      </c>
+      <c r="J63" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" t="s">
+        <v>33</v>
+      </c>
+      <c r="L63" t="s">
+        <v>34</v>
+      </c>
+      <c r="M63" t="s">
+        <v>14</v>
+      </c>
+      <c r="N63" t="s">
+        <v>15</v>
+      </c>
+      <c r="O63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+    </row>
+    <row r="65" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="E66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+    </row>
+    <row r="67" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+    </row>
+    <row r="68" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+    </row>
+    <row r="69" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="G69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+    </row>
+    <row r="70" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+    </row>
+    <row r="71" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+    </row>
+    <row r="72" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+    </row>
+    <row r="73" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C3:O3"/>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqe/Codes/celeritas/analysis/celer_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58F6660-D615-6641-83E6-1E6224E9A28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D6FA9E-DB6B-6E47-85A4-1E6F303F9CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54280" yWindow="620" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
+    <workbookView xWindow="51700" yWindow="1160" windowWidth="47520" windowHeight="26040" xr2:uid="{18F4029D-343F-3648-AF31-0004853598C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Results" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="110">
   <si>
     <t>Branch</t>
   </si>
@@ -367,9 +367,6 @@
   </si>
   <si>
     <t>Analytic rayleight intrinsics</t>
-  </si>
-  <si>
-    <t>\</t>
   </si>
   <si>
     <t>GPU Results</t>
@@ -438,10 +435,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,47 +807,47 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -859,75 +856,75 @@
       <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5" t="s">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5" t="s">
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5" t="s">
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5" t="s">
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5" t="s">
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5" t="s">
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5" t="s">
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5" t="s">
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -1440,18 +1437,18 @@
       <c r="AO6" s="3"/>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
@@ -1777,75 +1774,75 @@
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5" t="s">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5" t="s">
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5" t="s">
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5" t="s">
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5" t="s">
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5" t="s">
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5" t="s">
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5" t="s">
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AE23" s="5"/>
-      <c r="AF23" s="5"/>
-      <c r="AG23" s="5" t="s">
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AH23" s="5"/>
-      <c r="AI23" s="5"/>
-      <c r="AJ23" s="5" t="s">
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AK23" s="5"/>
-      <c r="AL23" s="5"/>
-      <c r="AM23" s="5" t="s">
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="AN23" s="5"/>
-      <c r="AO23" s="5"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1974,6 +1971,84 @@
       <c r="B26" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C26">
+        <v>0.89503198299999898</v>
+      </c>
+      <c r="D26">
+        <v>0.90620918399999995</v>
+      </c>
+      <c r="F26">
+        <v>312.54964165099898</v>
+      </c>
+      <c r="G26">
+        <v>315.76352629100001</v>
+      </c>
+      <c r="I26">
+        <v>128.179545939999</v>
+      </c>
+      <c r="J26">
+        <v>128.62074752699999</v>
+      </c>
+      <c r="L26">
+        <v>4.5853856190000002</v>
+      </c>
+      <c r="M26">
+        <v>4.7102769559999897</v>
+      </c>
+      <c r="O26">
+        <v>12.801752455000001</v>
+      </c>
+      <c r="P26">
+        <v>24.191855702000002</v>
+      </c>
+      <c r="R26">
+        <v>1.06181758999999</v>
+      </c>
+      <c r="S26">
+        <v>1.0720492049999899</v>
+      </c>
+      <c r="U26">
+        <v>31.383126765</v>
+      </c>
+      <c r="V26">
+        <v>41.567862636999998</v>
+      </c>
+      <c r="X26">
+        <v>50.975662948</v>
+      </c>
+      <c r="Y26">
+        <v>61.964946992999899</v>
+      </c>
+      <c r="AA26">
+        <v>69.596211320999799</v>
+      </c>
+      <c r="AB26">
+        <v>127.706090266999</v>
+      </c>
+      <c r="AD26">
+        <v>15.1870613549999</v>
+      </c>
+      <c r="AE26">
+        <v>15.309698388999999</v>
+      </c>
+      <c r="AG26">
+        <v>0.65303869599999997</v>
+      </c>
+      <c r="AH26">
+        <v>0.67380779999999996</v>
+      </c>
+      <c r="AJ26">
+        <v>0.88998490500000005</v>
+      </c>
+      <c r="AK26">
+        <v>5.004635725</v>
+      </c>
+      <c r="AM26">
+        <v>627.87864325099997</v>
+      </c>
+      <c r="AN26">
+        <v>722.49734004000004</v>
+      </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
@@ -1981,9 +2056,7 @@
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="s">
-        <v>108</v>
-      </c>
+      <c r="B28" s="1"/>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B32" s="4"/>
@@ -1995,38 +2068,21 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1"/>
       <c r="F35" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="AA23:AC23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="C1:AO1"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:Z2"/>
@@ -2040,10 +2096,30 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AD23:AF23"/>
   </mergeCells>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E4:E5">
     <cfRule type="colorScale" priority="235">
       <colorScale>
@@ -2054,8 +2130,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="colorScale" priority="25">
+  <conditionalFormatting sqref="F6:G6">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2074,8 +2150,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I6:J6">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K4:K5">
     <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:M6">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2094,8 +2190,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O6:P6">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q5">
     <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6:S6">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2114,8 +2230,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:G6">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="U6:V6">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2124,48 +2240,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J6">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L6:M6">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O6:P6">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6:S6">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6:V6">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="W4:W5">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2184,8 +2260,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Z4:Z5">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AB6">
     <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC4:AC5">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2204,8 +2300,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AF4:AF5">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AG6:AH6">
     <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI4:AI5">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2224,56 +2340,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W4:W5">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:Z5">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF4:AF5">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI4:AI5">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AL4:AL5">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -2284,8 +2350,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO4:AO5">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="AM6:AN6">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2294,8 +2360,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM6:AN6">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="AO4:AO5">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2350,21 +2416,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -2917,21 +2983,21 @@
       <c r="U19" s="1"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
@@ -3518,21 +3584,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -4085,21 +4151,21 @@
       <c r="U19" s="1"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
@@ -4640,55 +4706,55 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <f>(ABS(C32-C15)/C15)*100</f>
+        <f t="shared" ref="C33:O33" si="0">(ABS(C32-C15)/C15)*100</f>
         <v>2.5373254315725826</v>
       </c>
       <c r="D33">
-        <f>(ABS(D32-D15)/D15)*100</f>
+        <f t="shared" si="0"/>
         <v>4.8575078252121769E-2</v>
       </c>
       <c r="E33">
-        <f>(ABS(E32-E15)/E15)*100</f>
+        <f t="shared" si="0"/>
         <v>6.4746590664436679E-2</v>
       </c>
       <c r="F33">
-        <f>(ABS(F32-F15)/F15)*100</f>
+        <f t="shared" si="0"/>
         <v>0.59588037021878149</v>
       </c>
       <c r="G33">
-        <f>(ABS(G32-G15)/G15)*100</f>
+        <f t="shared" si="0"/>
         <v>7.3043186234344111</v>
       </c>
       <c r="H33">
-        <f>(ABS(H32-H15)/H15)*100</f>
+        <f t="shared" si="0"/>
         <v>1.6414384340402826</v>
       </c>
       <c r="I33">
-        <f>(ABS(I32-I15)/I15)*100</f>
+        <f t="shared" si="0"/>
         <v>9.8352363874801494</v>
       </c>
       <c r="J33">
-        <f>(ABS(J32-J15)/J15)*100</f>
+        <f t="shared" si="0"/>
         <v>10.309023483807945</v>
       </c>
       <c r="K33">
-        <f>(ABS(K32-K15)/K15)*100</f>
+        <f t="shared" si="0"/>
         <v>4.5690246325511135</v>
       </c>
       <c r="L33">
-        <f>(ABS(L32-L15)/L15)*100</f>
+        <f t="shared" si="0"/>
         <v>0.22275625420726244</v>
       </c>
       <c r="M33">
-        <f>(ABS(M32-M15)/M15)*100</f>
+        <f t="shared" si="0"/>
         <v>1.9808939390407569</v>
       </c>
       <c r="N33">
-        <f>(ABS(N32-N15)/N15)*100</f>
+        <f t="shared" si="0"/>
         <v>0.83492147066446787</v>
       </c>
       <c r="O33">
-        <f>(ABS(O32-O15)/O15)*100</f>
+        <f t="shared" si="0"/>
         <v>3.3987192176065153</v>
       </c>
     </row>
@@ -4736,21 +4802,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -5303,21 +5369,21 @@
       <c r="U19" s="1"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
@@ -5902,21 +5968,21 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -6469,21 +6535,21 @@
       <c r="U19" s="1"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
@@ -7567,28 +7633,28 @@
       <c r="C50">
         <v>5.3710379999999903E-3</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="H50" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J50" s="6" t="s">
+      <c r="J50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="5" t="s">
         <v>48</v>
       </c>
       <c r="L50">
@@ -7611,28 +7677,28 @@
       <c r="C51">
         <v>5.1900009999999996E-3</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>49</v>
       </c>
       <c r="E51">
         <v>0.62383930399999998</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" s="5" t="s">
         <v>51</v>
       </c>
       <c r="H51">
         <v>2.5043871999999901E-2</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="5" t="s">
         <v>54</v>
       </c>
       <c r="L51">
@@ -7655,28 +7721,28 @@
       <c r="C52">
         <v>5.4049849999999898E-3</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="5" t="s">
         <v>58</v>
       </c>
       <c r="H52">
         <v>2.5908E-2</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J52" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="K52" s="6" t="s">
+      <c r="K52" s="5" t="s">
         <v>61</v>
       </c>
       <c r="L52">
@@ -7699,10 +7765,10 @@
       <c r="C53">
         <v>5.3902519999999999E-3</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>63</v>
       </c>
       <c r="F53">
@@ -7714,13 +7780,13 @@
       <c r="H53">
         <v>2.5085654999999998E-2</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I53" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="K53" s="6" t="s">
+      <c r="K53" s="5" t="s">
         <v>66</v>
       </c>
       <c r="L53">
@@ -7743,28 +7809,28 @@
       <c r="C54">
         <v>5.201102E-3</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="5" t="s">
         <v>68</v>
       </c>
       <c r="F54">
         <v>1.8176338999999899E-2</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I54" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="K54" s="6" t="s">
+      <c r="K54" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L54">
@@ -7787,28 +7853,28 @@
       <c r="C55">
         <v>5.179693E-3</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H55">
         <v>2.5341619999999999E-2</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K55" s="6" t="s">
+      <c r="K55" s="5" t="s">
         <v>80</v>
       </c>
       <c r="L55">
@@ -7831,25 +7897,25 @@
       <c r="C56">
         <v>5.1358560000000003E-3</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="5" t="s">
         <v>82</v>
       </c>
       <c r="F56">
         <v>1.8089773999999999E-2</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="H56" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J56" s="6" t="s">
+      <c r="J56" s="5" t="s">
         <v>86</v>
       </c>
       <c r="K56">
@@ -7875,13 +7941,13 @@
       <c r="C57">
         <v>5.1441630000000002E-3</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="5" t="s">
         <v>89</v>
       </c>
       <c r="G57">
@@ -7890,13 +7956,13 @@
       <c r="H57">
         <v>2.5511971000000001E-2</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K57" s="6" t="s">
+      <c r="K57" s="5" t="s">
         <v>92</v>
       </c>
       <c r="L57">
@@ -7919,28 +7985,28 @@
       <c r="C58">
         <v>5.2187300000000004E-3</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H58" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="5" t="s">
         <v>98</v>
       </c>
       <c r="J58">
         <v>0.23785994499999999</v>
       </c>
-      <c r="K58" s="6" t="s">
+      <c r="K58" s="5" t="s">
         <v>99</v>
       </c>
       <c r="L58">
@@ -7963,28 +8029,28 @@
       <c r="C59">
         <v>5.2164029999999997E-3</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="I59" s="5" t="s">
         <v>105</v>
       </c>
       <c r="J59">
         <v>0.23842300799999999</v>
       </c>
-      <c r="K59" s="6" t="s">
+      <c r="K59" s="5" t="s">
         <v>106</v>
       </c>
       <c r="L59">
